--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
@@ -542,11 +542,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[TODO: afinar query al perfil]</t>
+          <t>research field: genetics/statistics OR neuroscience OR psychiatry; country: all EU/EEA; keywords "statistical genetics", "GWAS", "polygenic risk score", "psychiatric genetics", "sleep genetics"</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -653,7 +653,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[TODO: afinar query al perfil]</t>
+          <t>subject: Biological Sciences / Psychology; keywords "statistical genetics", "psychiatric genetics", "GWAS", "PRS", "behavioural genetics", "sleep"</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -701,7 +701,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[TODO: afinar query al perfil]</t>
+          <t>keywords "statistical genetics", "GWAS", "polygenic risk score", "psychiatric genetics", "behavioural genetics", "sleep genetics"; all countries</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -749,7 +749,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[TODO: afinar query al perfil]</t>
+          <t>keywords "statistical genetics", "psychiatric genetics", "GWAS", "PRS", "computational genetics"</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -797,7 +797,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[TODO: afinar query al perfil]</t>
+          <t>field: Genetics / Neuroscience / Psychology; keywords "statistical genetics", "psychiatric genetics", "GWAS", "PRS"</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -845,7 +845,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[TODO: afinar query al perfil]</t>
+          <t>keywords "statistical genetics", "psychiatric genetics", "GWAS", "PRS", "sleep genetics", "behavioural genetics"</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -893,7 +893,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[TODO: afinar query al perfil]</t>
+          <t>keywords "statistical genetics", "genetic epidemiology", "sleep genetics" — the Netherlands is a hub for both (Erasmus MC, VU Netherlands Twin Register)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -941,7 +941,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[TODO: afinar query al perfil]</t>
+          <t>keywords "statistical genetics", "psychiatric genetics", "GWAS", "PRS", "behavioural genetics"</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -989,7 +989,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[TODO: titulos de rol segun perfil]</t>
+          <t>titles: "statistical geneticist", "computational genetics", "genetic epidemiologist", "medical science liaison", "medical writer", "science communication officer"; countries: EU/EEA, Australia, USA, UK and other English-speaking, remote included</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[TODO: afinar query al perfil]</t>
+          <t>keywords "statistical genetics", "computational biology", "genomics", "clinical genetics"; companies of interest: 23andMe, Invitae, Color Health, Genomics England, Regeneron Genetics Center, Illumina, deCODE genetics</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>annual call page + open calendar</t>
+          <t>annual call page + open calendar; verify mobility rule against her Spain/Australia/Japan last-3-years residence</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1133,7 +1133,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>rolling; check eligibility window</t>
+          <t>rolling; check eligibility window against Feb 2028 (ETA) defense date</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1181,7 +1181,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>annual call page</t>
+          <t>annual call page; cross-disciplinary angle (genetics + neuroscience) is a good fit</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1229,7 +1229,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[TODO: mantener solo si España/Portugal entra en juego]</t>
+          <t>Junior Leader Incoming/Retaining calls; Spain is home base, keep in play</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1277,7 +1277,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[TODO: mantener solo si España entra en juego]</t>
+          <t>Sara Borrell y Rio Hortega (postdoc temprano); Miguel Servet (mas senior, vigilar plazo); España sigue en juego</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1325,7 +1325,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[TODO: mantener solo si España entra en juego]</t>
+          <t>Juan de la Cierva Formación/Incorporación y Ramón y Cajal; España sigue en juego</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1373,7 +1373,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[TODO: mantener solo si Alemania entra en juego]</t>
+          <t>Alemania esta en juego (UE/EEE sin exclusiones); rolling postdoc fellowships</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1421,7 +1421,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[TODO: mantener solo si UK entra en juego]</t>
+          <t>Reino Unido esta en juego (angloparlante YES); relevante por los hubs de genetica psiquiatrica (King's, Cardiff, Edinburgh)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1469,7 +1469,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>jobs + training + kavli network</t>
+          <t>jobs + training + kavli network; keywords behavioural/cognitive neuroscience</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1517,7 +1517,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[TODO: afinar query al perfil]</t>
+          <t>schools and grants relevant to behavioural/cognitive neuroscience and to her Japan-stay skill set (electrophysiology/optogenetics)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1565,7 +1565,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>[TODO: afinar query al perfil]</t>
+          <t>keywords "statistical genetics", "GWAS", "PRS", "sleep", "electrophysiology"</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1709,7 +1709,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[TODO: afinar query al perfil]</t>
+          <t>keywords "statistical genetics", "genomics", "computational neuroscience"</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1757,7 +1757,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[TODO: paneles LS segun perfil]</t>
+          <t>panel LS2 (Genetics, Genomics, Bioinformatics) and LS5 (Neuroscience/Neurology/Psychiatry)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1805,12 +1805,204 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>semilla 2026-08-23; revisar cuando el perfil este definido</t>
+          <t>afinada tras definir el perfil, 2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SRC-0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>World Congress of Psychiatric Genetics (WCPG)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://worldcongressofpsychiatricgenetics.org</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Central annual venue for GWAS/PRS psychiatric genetics: dates, abstract deadline, travel awards</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>abstract deadline + travel award programme</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>añadida tras definir el perfil, 2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SRC-0027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Psychiatric Genomics Consortium (PGC)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://pgc.unc.edu</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Working-group membership and activity map for GWAS/PRS psychiatric genetics; occasional analyst/training openings</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>working group pages by disorder; new working-group calls</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>añadida tras definir el perfil, 2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SRC-0028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Boletín Oficial del Estado (BOE) — especialidad de Genética</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.boe.es</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Real decreto y desarrollo de la via transitoria de la especialidad de Genetica Medica y de Laboratorio</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>buscar "Genética Médica y de Laboratorio", "vía transitoria", "real decreto especialidad"</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>añadida tras definir el perfil, 2026-08-23; carril B, primera clase</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SRC-0029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bolsas/oposiciones de Genética por Comunidad Autónoma</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[TODO: una URL por CCAA — servicio de salud de cada comunidad]</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Convocatorias de facultativo especialista en Genética/Análisis Clínicos por CCAA (bolsa de empleo, oposición o concurso: mecanismo distinto por comunidad)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>revisar cada portal de salud autonómico por separado; empezar por Andalucía (SAS, dado el destino de la residencia en Málaga) y ampliar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>añadida tras definir el perfil, 2026-08-23; carril B, primera clase — URLs por CCAA pendientes de completar en la primera pasada</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J26"/>
+  <autoFilter ref="A1:J30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -23,17 +23,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
@@ -650,7 +650,11 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -698,7 +702,11 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -746,7 +754,11 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -794,7 +806,11 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -842,7 +858,11 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -890,7 +910,11 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -938,7 +962,11 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -1946,7 +1974,11 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>añadida tras definir el perfil, 2026-08-23; carril B, primera clase</t>
@@ -1994,15 +2026,1371 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>añadida tras definir el perfil, 2026-08-23; carril B, primera clase — URLs por CCAA pendientes de completar en la primera pasada</t>
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SRC-0030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ISPG Job Postings (International Society of Psychiatric Genetics)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://ispg.net/resources/job-postings/</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Tablon de la sociedad para puestos de genetica psiquiatrica en todo el mundo: postdocs, staff scientists, clinical research associates. Poco volumen y mucha senal para sus lineas 1 y 2.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Leer la pagina entera: solo lista un punado de anuncios cada vez. Contrastar cada uno con los agregadores que ya cubren las otras ramas.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Se obtiene sin bloqueos, con el texto completo del anuncio, salario y plazos. La sociedad (WCPG) ya es SRC-0026, pero su tablon de empleo no estaba. Es el mejor canal de novedad hallado en esta pasada: produjo la unica plaza verificada de la semana (MPI Nijmegen).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SRC-0031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sleep Research Society - Trainee Job Board</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://sleepresearchsociety.org/jobs/</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Puestos postdoctorales y de inicio de carrera en sueno y ritmos circadianos, mayoritariamente en EE. UU. Muestra la fecha de publicacion, asi que la novedad es facil de juzgar.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revisar fechas de publicacion; conservar solo lo de menos de ~14 dias y filtrar por genetica, genomica, epidemiologia o analisis de cohortes.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>biweekly</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Se obtiene sin bloqueos y es gratuito para quien busca empleo. Muy centrado en EE. UU., asi que casi todo exige visado. El sueno es su tercera linea, de ahi quincenal y no semanal. El 2026-08-23 habia 7 anuncios vivos, ninguno de genetica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SRC-0032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Behavior Genetics Association - job listings</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://bga.org/</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Postdocs de genetica del comportamiento y estadistica (disenos de gemelos, GWAS, cohortes longitudinales), su linea 1; incluye el laboratorio CTG de la VU de Amsterdam.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Navegar la categoria de empleo/anuncios; si el modulo de listados sale vacio, buscar site:bga.org jobs.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>BLOQUEO 2026-08-23: la pagina del modulo de listados no devuelve contenido al fetch automatico y bga.org/category/jobs/ da HTTP 403. No gastar presupuesto en redescubrirlo: abrir en navegador o seguir la cuenta de LinkedIn de la BGA. Filtro tematico mas fino que el de EURAXESS para sus lineas 1 y 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SRC-0033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>European Sleep Research Society (ESRS) - Job Board</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://esrs.eu/job-board/</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Vacantes europeas de medicina e investigacion del sueno; el equivalente europeo del tablon de la SRS y por tanto sin problema de visado para ella.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>No determinado: la pagina no se pudo leer en esta pasada.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>biweekly</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>BLOQUEO 2026-08-23: HTTP 403 al fetch automatico, intentado una sola vez segun la regla de jerarquia de fuentes. No reintentar cada semana. Alternativa: suscribirse al boletin de la ESRS para que los anuncios lleguen por correo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SRC-0034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>European Society of Human Genetics (ESHG) - Job Offers</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.eshg.org/home</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Vacantes europeas de genetica academica y clinica o de laboratorio: interesa a la vez a su carril investigador y a su carril de Laboratorio Clinico / Genetica Medica, combinacion que casi ningun tablon cubre.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Navegar desde la pagina de inicio hasta Job Offers; los enlaces profundos son inestables.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>biweekly</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>URL INESTABLE 2026-08-23: eshg.org/36.0.html devuelve 404 y el host alternativo indexado 7.eshg.org no resuelve (fallo DNS). El tablon existe pero hay que reencontrar el punto de entrada a mano desde la home. Potencialmente valioso para su carril de genetica clinica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SRC-0035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>jobRxiv</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://jobrxiv.org/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Tablon de empleo de ciencias de la vida donde los propios PI publican las vacantes de su laboratorio; suele traer contacto nominal con el anuncio.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Buscar 'statistical genetics', 'GWAS', 'polygenic'.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>biweekly</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Poco volumen, publicado por PI, lo que encaja mejor con la estrategia de contacto especulativo que los tablones grandes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SRC-0036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HigherEdJobs</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.higheredjobs.com/search/advanced_action.cfm?Keyword=polygenic</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Vacantes postdoctorales y de personal investigador en universidades de EE. UU., incluidas facultades de medicina que no siempre replican en Nature Careers.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Palabras clave 'polygenic', 'statistical genetics', 'psychiatric genetics'; tipo postdoc; orden por mas reciente.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>biweekly</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>BLOQUEO PARCIAL 2026-08-23: el intento devolvio cuerpo vacio (no un 403); el formulario de busqueda parece requerir POST. Puede necesitar navegador. Valor bajo hasta 2027 por los plazos de visado en EE. UU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SRC-0037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>QIMR Berghofer - vacantes (portal TurboRecruit)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://qimrberghofer.turborecruit.com.au/</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Todas las vacantes de QIMR Berghofer, incluidas las del programa Mental Health &amp; Neuroscience (Research Officer, postdoc, bioestadistica). Es su via de contacto real: hizo alli una estancia de ~3 meses.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>No hace falta palabra clave: la lista de todo el instituto es corta (2 vacantes el 2026-08-23). Leerla entera y filtrar a ojo por 'Research Officer', 'Postdoctoral', 'Biostatistician', 'Mental Health'.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>CAMBIO DE DOMINIO importante: qimrberghofer.edu.au redirige (301) a qimrb.edu.au. Ir directamente a la URL de TurboRecruit y saltarse ambos. La vista de lista NO muestra fechas de cierre ni division: hay que abrir cada job_details.cfm?id= para eso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SRC-0038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cardiff University - busqueda de vacantes (portal eploy)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://cardiffuniweb.eploy.net/vacancies/vacancy-search-results.aspx?culture=en-GB</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Todas las vacantes de Cardiff, incluida la School of Medicine / Division of Psychological Medicine and Clinical Neurosciences, que alberga el MRC Centre for Neuropsychiatric Genetics and Genomics.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Filtrar por Job Group = Research y revisar la columna Division buscando 'Psychological Medicine &amp; Clinical Neurosciences'. Son 3 paginas y la division se ve en linea, asi que no hace falta busqueda por palabra clave.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>NOTA DE BLOQUEO que ahorra presupuesto: cardiff.ac.uk/jobs/search devuelve HTTP 403 al fetch automatico, no reintentarlo; jobs.cardiff.ac.uk redirige (302) aqui. Usar directamente esta URL de eploy. En esta pasada solo se leyo la pagina 1 de 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SRC-0039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>King's College London - busqueda de vacantes (IoPPN / SGDP Centre)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/search</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Las ~106 vacantes de KCL con filtro por facultad 'Psychiatry, Psychology &amp; Neuroscience': la via a los puestos de Research Associate/Fellow del SGDP Centre y a los puestos de clinico-investigador del IoPPN, que encajan con su titulo de medicina.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Filtro: job category = Research, facultad = Institute of Psychiatry, Psychology &amp; Neuroscience; ordenar por fecha de apertura. El listado muestra titulo, facultad, campus y fecha de cierre, pero NO el salario.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>jobs.kcl.ac.uk redirige (301) a kcl.ac.uk/jobs y /jobs/search-jobs?keywords= es un 404: solo funciona /jobs/search. Los anuncios individuales viven en /jobs/{id}-{slug}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Broad Institute - portal de empleo (Avature)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://broadinstitute.avature.net/careers</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Todas las vacantes del Broad, incluidas las de computational scientist y postdoc del Stanley Center for Psychiatric Research (laboratorio McCarroll y otros).</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Busqueda por palabra clave en el segmento de ruta, p. ej. /careers/SearchJobs/genetics; probar tambien 'Stanley', 'psychiatric', 'statistical genetics', 'postdoctoral'. Filtros: Job Family (Research), Job Type.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>fortnightly</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>La vista de resultados solo da titulo y fecha de publicacion: ni cierre, ni salario, ni URL por anuncio; hay que abrir cada uno. Los puestos del Stanley Center NO se etiquetan 'Stanley Center' sino por laboratorio (p. ej. 'McCarroll Lab'), asi que buscar solo 'Stanley' los pierde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SRC-0041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>deCODE genetics - portal de empleo (50skills)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://jobs.50skills.com/decode/is/</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Vacantes de genetica estadistica, biologia computacional, bioinformatica y ciencia de datos de deCODE en Reikiavik.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Recorrer la lista completa: deCODE tiene ~200 personas y la lista es corta. No se han identificado parametros de consulta utiles en la URL.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>BLOQUEO: la pagina de 50skills se renderiza con JavaScript y al fetch automatico solo devolvio la cabecera '50skills Careers', cero anuncios extraibles. Hay que abrirla en navegador; el punto de entrada humano es decode.com/careers/. deCODE es empresa (filial de Amgen), asi que son puestos de I+D industrial, no postdocs academicos, pero siguen siendo su carril 1 (investigacion en cualquier entorno).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SRC-0042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam - vacantes</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://workingat.vu.nl/vacancies</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Vacantes de la VU, incluida la Faculty of Behavioural and Movement Sciences / Biological Psychology, sede del Netherlands Twin Register (genetica del comportamiento y de rasgos complejos).</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Filtrar por 'Area of expertise = Researcher / Postdoc' y facultad Behavioural and Movement Sciences. No se veia caja de texto libre.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>fortnightly</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Comprobado el 2026-08-23: los unicos postdocs abiertos eran de Economia/Empresa y Sociologia, nada de genetica del comportamiento ni del Netherlands Twin Register. Los listados muestran fecha de cierre pero no salario (aplica la escala UFO neerlandesa). Sin problema de visado para ella.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SRC-0043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Erasmus MC - vacantes (werkenbijerasmusmc)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.werkenbijerasmusmc.nl/vacatures</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Vacantes del Erasmus MC; en principio la via a los puestos de epidemiologia genetica de Molecular and Systems Epidemiology (Rotterdam Study).</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>El parametro ?q= funciona, p. ej. ?q=postdoc. Pero ver Notas: el portal esta dominado por puestos clinicos y de enfermeria.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>fortnightly</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>CALLEJON PARCIAL, conviene dejarlo escrito: las vacantes de investigacion del Erasmus MC no parecen salir por este portal en neerlandes (141 vacantes, ?q=postdoc no devolvio nada academico). La proxima vez probar (a) erasmusmc.nl/en/research/groups/molecular-and-systems-epidemiology para contacto directo con el grupo y (b) AcademicTransfer (SRC-0007) filtrado a Erasmus MC. Terminos en neerlandes: 'onderzoeker', 'epidemiologie'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SRC-0044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>University of Edinburgh - jobs</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.ed.ac.uk/jobs</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>En principio los puestos de genetica psiquiatrica de Edimburgo (Centre for Genomic and Experimental Medicine, Division of Psychiatry, Generation Scotland).</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Sin determinar en esta pasada: no se alcanzo ninguna busqueda publica de vacantes desde la pagina de entrada.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>fortnightly</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>BLOQUEO / SIN RESOLVER 2026-08-23: jobs.ed.ac.uk redirige (301) a ed.ac.uk/jobs, y esa pagina solo expone el portal Oracle Cloud INTERNO de movilidad (elxw.fa.em3.oraclecloud.com, solo personal actual). No se encontro la URL publica de busqueda. La proxima vez: buscar la URL externa de Oracle CX (patron .../hcmUI/CandidateExperience/en/sites/CX_1/requisitions) o tirar de jobs.ac.uk (SRC-0002) filtrado a Edimburgo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SRC-0045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Aarhus University - vacant positions</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://international.au.dk/about/profile/vacant-positions</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Postdocs del NCRR, iPSYCH y el Center for Quantitative Genetics and Genomics: el grupo mas denso de contratacion en genetica psiquiatrica y estadistica hallado en la UE en esta pasada.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Buscar 'genetics', 'epidemiology'.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>BLOQUEO: international.au.dk devuelve HTTP 403 al fetch automatico (probadas las dos paginas de empleo). Los mismos puestos suelen replicarse en EURAXESS, que es la via practicable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SRC-0046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>EURAXESS - busqueda por facetas (no por palabra clave)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/search?f%5B0%5D=job_research_profile%3A448&amp;f%5B1%5D=offer_type%3Ajob_offer</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Listados de EURAXESS acotados por perfil de investigador (R1=447, R2=448, R3=449, R4=450), tipo de oferta (job_offer / funding / hosting) y campo de investigacion (job_research_field:&lt;id&gt;).</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>f[0]=job_research_profile:448 ; f[0]=offer_type:job_offer ; sort[name]=created&amp;sort[direction]=DESC</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Nombres de faceta extraidos del HTML de EURAXESS en esta pasada. IMPORTANTE: la busqueda de texto libre NO funciona por fetch automatico - keywords=, search_api_fulltext= y search_text= fueron ignorados y devolvieron siempre la misma lista generica de 7.980 ofertas. Las facetas son el unico mecanismo de acotacion util para un agente. Complementa a SRC-0001 (misma URL base, consulta distinta).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SRC-0047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CNAG - portal de empleo</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.cnag.eu/jobs</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Vacantes del centro genomico de Barcelona y, sobre todo, sus llamadas anuales de acogida de doctorandos y postdocs con financiacion propia (Juan de la Cierva, EMBO, la Caixa INPhINIT).</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Abrir el indice /jobs; las llamadas de acogida aparecen entre noviembre y febrero de cada ciclo.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Se obtiene sin bloqueos. Poco volumen: dos puestos abiertos el 2026-08-23, ninguno relevante. El valor esta en el mecanismo de acogida, que encaja con su reloj (feb 2028) mucho mejor que una vacante asalariada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SRC-0048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CRG - portal de seleccion</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://recruitment.crg.eu/</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Puestos de postdoc y staff scientist en el instituto genomico de referencia de Espana, muchos en proyectos financiados por el ERC.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Listado de posiciones; filtrar por grupos computacionales y de genetica.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>BLOQUEO: devuelve HTTP 403 al fetch automatico. Registrar las pistas como UNVERIFIED y que la duena abra los enlaces a mano; no gastar presupuesto en reintentos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SRC-0049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Regeneron Careers - Genetics &amp; Genomics</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://careers.regeneron.com/en/genetics-and-genomics-jobs/</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Vacantes continuas del Regeneron Genetics Center en genetica estadistica y genomica computacional, con banda salarial publicada.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>'statistical genetics', 'computational genomics'; filtrar por nivel 0-2 anos post-doctorado; atencion a la modalidad de 4 dias presenciales en Tarrytown.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Empresa objetivo, no candidatura inmediata: exige doctorado defendido (feb 2028) y patrocinio de visado en EE. UU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SRC-0050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SAS - Bolsa de Empleo (Bolsa Unica, Andalucia)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.sspa.juntadeandalucia.es/servicioandaluzdesalud/profesionales/ofertas-de-empleo/bolsa-de-empleo</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Bolsa permanentemente abierta y actualizable (bolsa de seleccion + bolsa de provision/PIT) para nombramientos estatutarios temporales, incluido Facultativo Especialista de Area; baremo, cortes de meritos y alegaciones.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Categoria FEA - Analisis Clinicos / Bioquimica Clinica / Laboratorio Clinico; provincia Malaga y resto de Andalucia; revisar ademas /normativa-de-bolsa-de-empleo por cambios de baremo.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Cierra el hueco de SRC-0029 para Andalucia. Mecanismo = bolsa con baremo, sin examen. Inscripcion posible desde el 22-05-2027. Subsecciones utiles: /bolsa-de-seleccion y /bolsa-de-provision-pit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SRC-0051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SERMAS / Comunidad de Madrid - empleo publico sanitario (sede electronica)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://sede.comunidad.madrid/oferta-empleo/facultativo-especialista-analisis-clinic</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Ficha viva del proceso selectivo de Facultativo Especialista en Analisis Clinicos (concurso-oposicion): convocatoria en BOCM, listas de meritos, eleccion de plaza y resoluciones.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Buscar 'Facultativo Especialista' + 'Analisis Clinicos' / 'Laboratorio Clinico' / 'Genetica' en el buscador de ofertas de la sede; vigilar el BOCM para la proxima OEP.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Cierra SRC-0029 para Madrid. Mecanismo = concurso-oposicion (examen mas meritos), con ciclo largo: convocatoria dic-2021 y toma de posesion jul-2026. La categoria se sigue llamando 'Analisis Clinicos', no 'Laboratorio Clinico'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SRC-0052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ICS - Borsa de treball (Institut Catala de la Salut)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://ics.gencat.cat/ca/lics/treballeu-a-lics/treball-temporal/borsa-de-treball/</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Bolsa permanente de seleccion temporal del ICS; el curriculo inscrito se reutiliza para las oposiciones del propio ICS; convocatorias de trabajo temporal.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Perfils professionals -&gt; facultatiu especialista; inscripcion en www1.ics.gencat.cat/sgrh/acces.aspx; convocatorias en /treball-temporal/convocatories-de-treball-temporal/.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Cierra SRC-0029 para Cataluna. Mecanismo = borsa permanente mas oposiciones que beben del mismo CV. Ojo: los hospitales concertados (p. ej. Sant Joan de Reus) convocan sus propias bolsas fuera del ICS, via CIDO (cido.diba.cat).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SRC-0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Conselleria de Sanitat GVA - listas de empleo temporal</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.san.gva.es/es/web/recursos-humans/listas-empleo-temporal</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Bolsas sanitarias valencianas: inscripcion abierta 24/7, ediciones con baremo, listas de reserva, activacion y desactivacion, disponibilidad para vacantes y corta duracion.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Inscripcion en /lista-de-empleo-temporal-abierta-permanente; edicion vigente en /edicion-vigente; categoria FE Analisis Clinicos.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Cierra SRC-0029 para la Comunitat Valenciana. Mecanismo = listas permanentes por ediciones con baremo. Requisito especifico: acreditacion de valenciano B2 en algunos supuestos. URLs tomadas de resultados del propio dominio, no abiertas una a una (LIKELY).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SRC-0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Servicio Murciano de Salud - bolsas de trabajo (MurciaSalud)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.murciasalud.es/empleo.php?idsec=39</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Bolsas de trabajo del SMS para personal estatutario temporal (facultativos especialistas), ordenes de llamamiento, bolsas suspendidas y aportacion de meritos.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Inscripcion y gestion en sms.carm.es/sms/bolsa; llamamientos en /sms/bolsa/view/info/elegirBolsaUltimosLlamamientos.xhtml; OPE en el BORM.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Cierra SRC-0029 para Murcia (la universidad de su doctorado). Mecanismo = bolsa con baremo mas OPE por oposicion libre publicada en BORM. Telefono de seleccion 968 288 449.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SRC-0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ministerio de Sanidad - audiencia e informacion publica de proyectos normativos</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.sanidad.gob.es/normativa/audiencia/home.htm</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Proyectos de real decreto en tramite de audiencia publica, incluidos los de formacion sanitaria especializada: es donde apareceran los RD de Genetica Medica y de Genetica de Laboratorio antes de llegar al BOE.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Buscar 'Genetica' en proyectos abiertos y cerrados; complementar con sanidad.gob.es/normativa/ (consultas publicas previas).</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Fuente de aviso temprano, un escalon antes que SRC-0028 (BOE): da semanas de margen y publica el texto con las disposiciones transitorias. Comprobado el 2026-08-23: ningun proyecto de Genetica en audiencia abierta.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2013,16 +3401,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
@@ -2074,8 +3462,55 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LinkedIn (notificacion automatica, updates-noreply@linkedin.com)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Resumen automatico de red de LinkedIn</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Resumen automatico de conversaciones de red. El unico elemento de oportunidad es una beca de formacion practica de la Universidad Complutense de Madrid en la Unidad de Igualdad, restringida a estudiantes de Estadistica Aplicada: es una ayuda de grado/master para estudiantes, no accesible a una medica que termina el doctorado. Ningun otro elemento de carrera, financiacion, evento o formacion.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/feed/update/urn:li:activity:7485253533538263040</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2086,17 +3521,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2141,8 +3576,1076 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>P-0001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Postdocs in psychiatric epidemiology and/or statistical genetics</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 5, Status CLOSED, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://international.au.dk/about/profile/vacant-positions/job/postdocs-in-psychiatric-epidemiology-and-or-statistical-genetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>P-0002</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Scientist in Statistical Genomics / Genetic Epidemiology</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status ROLLING, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://recruitingapp-5569.de.umantis.com/Vacancies/496/Description/2?lang=eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>P-0003</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow in Psychiatric Genomics</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status OPEN, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/postdoctoral-fellow-in-psychiatric-genomics-icahn-school-of-medicine-at-mount-sinai-ismms-mshs-754125</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P-0004</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Postdoctoral Researcher in Psychiatric and Genetic Epidemiology (ERC StressGene)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status CLOSED, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/557315</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P-0005</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Postdoc Statistical Genetics (Complex Trait Genetics lab)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.academictransfer.com/en/jobs/352365/postdoc-statistical-genetics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>P-0006</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Scientist in host genetics and data integration for liver cancer risk prediction</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSR614/postdoctoral-research-scientist-in-host-genetics-and-data-integration-for-liver-cancer-risk-predication-and-early-detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>P-0007</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Postdoc in method development in human statistical genetics (classification of complex traits)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status CLOSED, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/12856703/postdoc-position-in-method-development-in-human-statistical-genetics-with-a-focus-on-classificat-/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>P-0008</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Computational Scientist I - McCarroll Lab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://broadinstitute.avature.net/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>P-0009</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PhD / Postdoc Fellowship Call 2026 - Functional Genomics Team (llamada de acogida)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.cnag.eu/jobs/phd-postdoc-fellowship-call-2026-functional-genomics-team</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>P-0010</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Postdoctoral Scientist, Computational Epigenomics and Genetics</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status OPEN, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://recruitment.crg.eu/content/jobs/position/postdoctoral-scientist-computational-epigenomics-and-genetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>P-0011</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Postdoctoral positions in human population genetics, complex disease and cancer</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status OPEN, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/postdoctoral-positions-in-human-population-genetics-complex-disease-and-cancer-in-new-york-city-usa-albert-einstein-college-of-medicine-einstein-757285</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>P-0012</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Junior Research Data Scientist</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 2, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSR260/junior-research-data-scientist</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>P-0013</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Associate in Epidemiology and Health Data Science</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 2, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSM851/postdoctoral-research-associate-in-epidemiology-and-health-data-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>P-0014</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Research Assistant (Moondance Dementia Laboratory)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 2, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://cardiffuniweb.eploy.net/vacancies/vacancy-search-results.aspx?culture=en-GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>P-0015</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Clinical Research Associate (IoPPN)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 2, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/154086-clinical-research-associate</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>P-0016</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Clinical Research Fellow (IoPPN)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 2, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/155765-clinical-research-fellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>P-0017</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Research Officer - Experimental Biology and Surveillance Innovation</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 1, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://qimrberghofer.turborecruit.com.au/job/job_details.cfm?id=581998</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>J-0001</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Associate Manager, Statistical Genetics - Regeneron Genetics Center</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://careers.regeneron.com/en/jobs/r48469/associate-manager-statistical-genetics-regeneron-genetics-center/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>J-0002</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Bolsa Unica de Empleo del SAS - inscripcion como Facultativo Especialista de Area (Laboratorio Clinico)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status ROLLING, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.sspa.juntadeandalucia.es/servicioandaluzdesalud/profesionales/ofertas-de-empleo/bolsa-de-empleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>J-0003</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Via transitoria al titulo de especialista en Genetica Medica y en Genetica de Laboratorio - seguimiento normativo</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status PENDING, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.sanidad.gob.es/normativa/audiencia/home.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>J-0004</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Facultativo Especialista en Analisis Clinicos - concurso-oposicion SERMAS (ref. E907, 47 plazas)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://sede.comunidad.madrid/oferta-empleo/facultativo-especialista-analisis-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>J-0005</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Facultativo/a Especialista en Analisis Clinicos - concurso de meritos Ley 20/2021 (estabilizacion)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 2, Status CLOSED, Confidence LIKELY.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://sede.gva.es/es/detall-ocupacio-publica?id_emp=87684</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>J-0006</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>OPE Libre - Facultativo Especialista en Analisis Clinicos (6 plazas)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 2, Status CLOSED, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.murciasalud.es/empleo.php?idsec=39</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ampliacion de la superficie de vigilancia</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>26 fuentes nuevas (portales de institucion, tablones de sociedad, cinco portales de empleo publico autonomico y el tramite de audiencia previa del Ministerio de Sanidad), con las notas de bloqueo de cada una.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>subscriptions</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Alertas propuestas</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2 altas TODO (tope por pasada): alertas del BOE para el RD de Genetica y busquedas guardadas de EURAXESS. El resto de candidatas quedan en runs/ a la espera de las proximas pasadas.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>inbox_triage</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Pasada de buzon de la semana</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CHECKED</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Conector de Gmail operativo. Pase A (label:Research newer_than:8d) sin hilos: la etiqueta existe pero ningun filtro la aplica todavia. Pase B: 1 mensaje relevante, enrutado IGNORE. Nada quedo PENDING.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2548,39 +5051,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="52" customWidth="1" min="20" max="20"/>
     <col width="17" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="15" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="52" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="52" customWidth="1" min="29" max="29"/>
+    <col width="52" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2735,8 +5238,2282 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Postdocs in psychiatric epidemiology and/or statistical genetics</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Aarhus University</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>National Centre for Register-based Research (NCRR) / iPSYCH, Dept of Public Health</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Aarhus</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Postdoc, fixed-term full-time</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>PhD in statistical genetics, biostatistics, epidemiology or bioinformatics; GWAS tooling (PLINK, BOLT-LMM, GCTA); Danish register data; R/Python</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Closest institutional match found in the EU to her top two research lines at once: register-based psychiatric epidemiology plus statistical genetics of psychiatric disorders. iPSYCH is the Danish psychiatric-genetics cohort that feeds the PGC, whose GWAS/PRS output she already works alongside. The stated toolkit (PLINK, GWAS pipelines, R) is exactly her independent level and nothing here requires the neuroimaging or electrophysiology she has only at supervised level. Her MD plus Laboratory Medicine residency is a real differentiator in a centre that reasons about registry diagnoses, phenotype definition and clinical validity. Denmark is EU/EEA: no visa, no permit, relocation only; Danish postdoc pay is collectively bargained and above any floor (she has set none). INELIGIBLE / NOT APPLICABLE NOW: this advert asked for a 2026-06-01 start and is long closed, and any Aarhus postdoc opening now will be filled well before her Feb 2028 (ETA) defence; she cannot take a PhD-required postdoc before then, nor anything at all before 2027-05-22 when the residency ends. Kept at Fit 5 because Fit measures profile match, not timing, and this row exists to mark a recurring hiring channel: AU/NCRR/iPSYCH has advertised statistical-genetics postdocs repeatedly on EURAXESS. Application work is nil now and moderate later (CV, research statement, referees). Hook for 2027: the QIMR Berghofer connection (QIMR and iPSYCH/PGC circles overlap heavily) and the Nature Mental Health manuscript if accepted by then.</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Flagship international psychiatric-genetics centre, English-language, advertised EU-wide on EURAXESS; global applicant pool</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>No aplicar: ventana equivocada. En Q2 2027 revisar las vacantes de AU y EURAXESS para la siguiente ronda NCRR/iPSYCH y escribir al group leader indicando defensa prevista en feb 2028 y disponibilidad H1 2028; preguntar tambien si acogen candidaturas Marie Curie / danesas, que es el mecanismo que si encaja con su reloj.</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>https://international.au.dk/about/profile/vacant-positions/job/postdocs-in-psychiatric-epidemiology-and-or-statistical-genetics</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Rama 1 (EURAXESS/portales UE). international.au.dk devuelve HTTP 403 al fetch automatico, asi que no se pudieron leer fechas en el origen; listados EURAXESS historicos del mismo centro confirman el canal recurrente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Scientist in Statistical Genomics / Genetic Epidemiology</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Max Planck Institute for Psycholinguistics</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Population Genetics of Human Communication group</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Beate St Pourcain</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nijmegen</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Full-time postdoc (39 h/week)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>73999-91055 bruto (incl. 8% holiday bonus), segun experiencia</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-12-01 (negociable)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>PhD en genomica estadistica, epidemiologia genetica, bioestadistica o campo cuantitativo afin; metodos omicos para arquitectura genetica de fenotipos humanos; R, Python, Perl, shell. Deseable: SEM, meta-analisis, neuroimagen. SIN PLAZO FIJO: revision continua a partir del 2026-10-08 hasta cubrir.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>On content this is as close to her profile as an advert gets: genomic analysis of the genetic correlates of social behaviour from infancy onwards, aimed at trajectories of mental-health outcomes. That is the intersection of all three of her lines - statistical genetics of complex traits, GWAS/PRS of mental-health phenotypes, and genetics of infant/toddler phenotypes - and the desirable extras (SEM, meta-analysis, neuroimaging familiarity) match her QIMR Berghofer training and the Nature Mental Health manuscript rather than demanding neuroimaging she cannot run solo. PLINK/R/some-Python is the required stack. EU citizenship means no permit issue in the Netherlands and the salary is far above any floor (none set). INELIGIBLE FOR THIS INSTANCE: the post requires an already-defended PhD (hers is an ETA of Feb 2028) and a 2026-12-01 start, while she is committed to the Malaga residency until 2027-05-22 - unreachable even with negotiation, and rolling review from Oct 2026 means it will be filled first. Held at 4 rather than 5 for that reason plus a thin publication record (two first-author manuscripts under review) against a Max Planck pool. Application would be CV, research statement and referees: XS now, S later. Hook: St Pourcain works on exactly her infant-phenotype/psychiatric-genetics overlap.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Razonado, no medido: financiacion Max Planck, PI conocida en el campo, salario en el tramo alto europeo, instituto internacional anglofono y revision continua que premia al que llega antes</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>No aplicar: arranque dic-2026 y PhD ya defendido, ambos fuera de su ventana. Anadir a St Pourcain y al grupo Population Genetics of Human Communication a la lista de contactos y escribirle en Q1-Q2 2027 preguntando por aperturas para finales de 2027 / 2028; vigilar la pagina de vacantes cada ciclo.</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>https://recruitingapp-5569.de.umantis.com/Vacancies/496/Description/2?lang=eng</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Rama 5 (novedad). Localizado en el tablon de empleo de la ISPG y VERIFICADO en el portal propio de la Max Planck Society, que muestra publicacion el 2026-08-12. No lo indexa ninguno de los agregadores que cubren las otras ramas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow in Psychiatric Genomics</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Icahn School of Medicine at Mount Sinai</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mullins Lab - Dept of Psychiatry / Genetics and Genomic Sciences; International Suicide Genetics Consortium (ISGC)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Niamh Mullins</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Postdoctoral fellowship</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Analisis estadistico de datos geneticos/genomicos a gran escala e historia clinica electronica; ~75% consorcio ISGC, ~25% prediccion de riesgo genetico; redaccion de manuscritos. Doctorado presumiblemente exigido (sin confirmar: la pagina no se pudo abrir).</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Content-wise this is her research line 2 almost verbatim: GWAS of psychiatric disorders inside a PGC-adjacent consortium (ISGC) with an explicit genetic risk prediction workstream, i.e. PRS. The 25% EHR/risk-prediction component is where the MD stops being a curiosity and becomes the argument - phenotype definition from electronic health records is exactly where a Laboratory Medicine specialist outperforms a pure statistical geneticist, and it is the sharpest framing she has for any US application. The advert reportedly offers visa sponsorship, relocation assistance and subsidised housing, which removes the main structural obstacle for a non-US citizen; she would still need J-1 or H-1B, adding 4-6 months of lead time after any offer. Held at 4, not 5: the posting could not be opened (Nature Careers returns HTTP 400 to automated fetching) so duration, salary, deadline and the exact PhD wording are unconfirmed; the timing is wrong for this instance, since a fellowship advertised now will not still be open in Feb 2028; and her record of two manuscripts under review is light against US applicants who typically arrive with several first-author genomics papers. Application would be CV, research statement and 3 references.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Laboratorio de genomica psiquiatrica de alto perfil en una facultad de medicina estadounidense, anunciado internacionalmente y con patrocinio de visado</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>La duena debe abrir la URL de Nature Careers en un navegador (bloquea el fetch automatico) para leer plazo y requisito de doctorado. Accion estrategica, no ahora: Niamh Mullins es un contacto nominal que merece un acercamiento real a mediados de 2027; la via ISGC/PGC conecta ademas con el WCPG (SRC-0026), el sitio mas barato para conocerla en persona antes de solicitar. Vigilar si el laboratorio reanuncia anualmente.</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/postdoctoral-fellow-in-psychiatric-genomics-icahn-school-of-medicine-at-mount-sinai-ismms-mshs-754125</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Rama 2 (tablones academicos), via Nature Careers (SRC-0003). El fetch directo devolvio HTTP 400 y labs.icahn.mssm.edu 403: los datos proceden solo de resumenes de resultados de busqueda, de ahi UNVERIFIED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Postdoctoral Researcher in Psychiatric and Genetic Epidemiology (ERC StressGene)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>University of Iceland</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Centre of Public Health Sciences, Faculty of Medicine - proyecto ERC StressGene</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Unnur Valdimarsdottir</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reykjavik</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Doctorado; epidemiologia genetica y psiquiatrica; variantes de secuencia asociadas a trastornos psiquiatricos relacionados con el estres; datos de cohorte/biobanco</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ERC-funded team working on genetic variants underlying stress-related psychiatric disorders in deeply phenotyped Icelandic cohorts - squarely her line 2 and methodologically adjacent to line 1. Iceland is EEA, so no permit is needed, and the group works in English (her C2), which matters because she has no Icelandic. The MD is a genuine asset in a public-health-sciences centre that phenotypes psychiatric outcomes from health registries, and her Laboratory Medicine training reads well against biobank and genotype data handling. Short of a 5 because the group's centre of gravity is the epidemiology of trauma and stress rather than statistical-genetics method development, so she would enter as the genetics analyst on an epidemiology team - a reframing job - and her record (two first-author manuscripts under review, nothing accepted) is thin for an ERC-funded slot. INELIGIBLE / CLOSED: the EURAXESS advert (job 557315) no longer resolves, and expired EURAXESS ads redirect silently to the search page; an ERC project recruiting in 2026 will not still be recruiting for a Feb 2028 start. The value of this row is the group, not the vacancy.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Puesto financiado por el ERC en un centro de cohortes de renombre internacional, anunciado en EURAXESS</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Registrar el grupo, no el anuncio. Hacia mediados de 2027 comprobar si StressGene o su ERC sucesor sigue reclutando y escribir al grupo de Unnur Valdimarsdottir con una nota de encaje de una pagina; mientras tanto mantener el centro en la lista de posibles acogidas MSCA-PF, que es la via que si encaja con una defensa en feb 2028.</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/557315</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Rama 1 (EURAXESS). Hallado con busqueda restringida al dominio euraxess.ec.europa.eu; la URL del puesto ahora redirige a la busqueda generica, es decir, el anuncio ha expirado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Postdoc Statistical Genetics (Complex Trait Genetics lab)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Dept of Complex Trait Genetics, Center for Neurogenomics and Cognitive Research (CNCR)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Danielle Posthuma</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Fijo-discontinuo, min. 0.8 FTE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1 ano (prorrogable segun financiacion)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>40500-64000 base (escala 10, 3378-5331 EUR bruto/mes; excluye 8% vacaciones y 8,3% paga de fin de ano)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>-431</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Doctorado en estadistica, matematicas, biologia computacional o genetica estadistica; programacion y desarrollo de software; genetica de big data en la interseccion genetica-biologia-neurociencia</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>The CTG lab is the flagship European group for statistical genetics of complex traits and brain/psychiatric phenotypes - her research lines 1 and 2 in one place - hiring through a board she can monitor, in the EU where she needs no sponsorship at all. Its day-to-day is what she already does independently, GWAS/PRS pipelines in PLINK/R, and its neuro-cognitive angle lets her use the MRI and computational-neuroscience training as context rather than as a skill she must run solo, which is the honest limit of that training. Dutch scale 10 plus holiday and year-end allowances is comfortably above any floor (none set) and the working language is English. Two honest deductions from a 5: CTG postings lean towards method and software development, while she is a pipeline user with AI-assisted Python rather than a developer, so she would compete against applicants with a stats or maths PhD; and CTG postdocs are normally recruited with a strong first-author record she will not have until the two manuscripts land. CLOSED: deadline 2025-06-18, more than a year before this run. The value is the recurring pattern, and the contract being only one year is thin for an international move. Hook: her PRS/psychiatric-genetics work plus the QIMR Berghofer collaboration, which overlaps CTG's consortium world; the natural vehicle is an MSCA Postdoctoral Fellowship with CTG as host, which needs the host conversation about 12 months ahead.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Laboratorio de genetica de rasgos complejos mas conocido de Europa continental; sus plazas atraen candidaturas internacionales y circulan por la BGA y EURAXESS</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Crear un filtro permanente en AcademicTransfer (empleador Vrije Universiteit Amsterdam + palabra clave genetics) y revisarlo mensualmente; CTG ha anunciado postdoc de genetica estadistica al menos una vez en el ciclo 2025, asi que cabe esperar reapertura. Aparte, es la mejor candidata a correo especulativo a Danielle Posthuma en otono de 2027 (~6 meses antes de la defensa ETA feb 2028), proponiendo una MSCA-PF con CTG como acogida.</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>https://www.academictransfer.com/en/jobs/352365/postdoc-statistical-genetics/</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Ramas 1 y 2 (misma plaza, fusionada). AcademicTransfer (SRC-0007) abierta el 2026-08-23 y declara cerrada la solicitud (deadline 18 jun 25). La URL propia de VU (workingat.vu.nl/vacancies/postdoc-statistical-genetics-amsterdam-1174461) devuelve 404. Registrada a proposito como patron de vacante recurrente, no como apertura accionable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Scientist in host genetics and data integration for liver cancer risk prediction</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>University of Oxford</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Nuffield Department of Medicine, Experimental Medicine - consorcio DeLIVER</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Azim Ansari (genetica); Eleanor Barnes (IP DeLIVER); Hamish Innes (estadistica)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Oxford</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Postdoc a jornada completa, duracion determinada</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2 anos</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>45300-55000 aprox (GBP 39424-47779)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>19</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Doctorado obtenido o proximo a completarse en genetica estadistica, epidemiologia genetica, biologia computacional, bioinformatica o estadistica; R y/o Python; GWAS, QC de genotipado, estructura poblacional, imputacion, mapeo de QTL, aleatorizacion mendeliana, prediccion poligenica, integracion multiomica</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Technique match is close to exact for her research line 1: the advert asks for GWAS pipelines, imputation, population structure and polygenic risk prediction in R/Python, the PLINK+R stack she runs independently, and it explicitly accepts a PhD close to completion - rare wording that would suit her mid-2027 to Feb-2028 window if it recurred. The MD is a genuine differentiator because DeLIVER is a clinical cohort study of liver cancer surveillance, so someone who can read the clinical phenotyping is worth more than a pure bioinformatician. Two things hold it at 3: the disease domain is hepatology/oncology rather than psychiatric or sleep genetics, so she would move her methods to a new phenotype with no liver publications to point at; and the timing is fatal for this instance, closing 2026-09-11 for a start long before she is free. Post-Brexit she would need a UK Skilled Worker visa, which Oxford routinely sponsors, though the advert carries no right-to-work statement so this is unconfirmed. Application is a full Oxford supporting statement against about ten selection criteria plus two referees: M effort. Salary is well above her (absent) floor.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Postdoc de genetica estadistica en Oxford NDM con elegibilidad cuantitativa amplia (8 disciplinas admitidas) y anuncio internacional abierto en jobs.ac.uk</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>No aplicar: no puede incorporarse antes de mediados de 2027. En su lugar, crear una alerta guardada en jobs.ac.uk con University of Oxford + statistical genetics / genetic epidemiology y revisar NDM Experimental Medicine en Q4 2027. Si quiere un gancho ya, escribir a Azim Ansari en otono de 2027 (no antes) con el articulo de Nature Mental Health una vez aceptado, preguntando si estos puestos se repiten.</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSR614/postdoctoral-research-scientist-in-host-genetics-and-data-integration-for-liver-cancer-risk-predication-and-early-detection</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Rama 2, jobs.ac.uk (SRC-0002), anuncio abierto y fechas leidas directamente el 2026-08-23. Es el unico postdoc real de genetica estadistica que devolvieron tres consultas distintas de jobs.ac.uk esta semana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Postdoc in method development in human statistical genetics (classification of complex traits)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Aarhus University</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Center for Quantitative Genetics and Genomics (QGG)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Doug Speed (doug@qgg.au.dk)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Aarhus</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2 anos</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>-114</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Doctorado; desarrollo de metodos estadisticos para datos GWAS de rasgos complejos humanos, con foco en clasificacion; base cuantitativa y de programacion solida</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Topic is her research line 1 stated plainly - statistical genetics of human complex traits - and Doug Speed's group (LDAK, SumHer) builds tools she already uses downstream, which makes for a credible cold-contact hook. Denmark is EU: no visa, English-working group, and a two-year contract rather than the one-year Dutch norm. The honest brake is the phrase method development: this post is about writing and benchmarking new estimators, not applying GWAS/PRS pipelines, and her independent level is pipeline execution in PLINK/R with AI-assisted Python. She would be below the bar unless she spends the next 18 months deliberately building methods evidence - a small public repo, a simulation study, a methods section she owns end to end in the Nature Mental Health paper - which is a legitimate thing to plan for and is why this is kept at 3 rather than dropped. No salary published; Danish postdoc pay is above any floor (none set). CONFLICTING SOURCES, unreconciled: branch 1 read a deadline of 2026-05-01 (hence CLOSED here), while branch 2's Nature Careers listing showed no deadline and appeared live; both agree on a 2026-10-01 start, which is consistent with a spring deadline. Nature Careers blocks automated fetching (HTTP 400), so neither could open the source page. Either way the dates are far ahead of her Feb 2028 (ETA) defence.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Postdoc de metodos anunciado internacionalmente en un centro lider de genetica cuantitativa; los puestos de desarrollo metodologico atraen perfiles muy cuantitativos</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Ninguna sobre el anuncio, y confirmar el estado real (abierto o cerrado) abriendo la ficha de Nature Careers en un navegador, porque las dos ramas discrepan. Tratarlo como objetivo de competencias: durante el proximo ano producir un resultado con sabor metodologico al que poder apuntar; despues vigilar las vacantes de QGG desde la primavera de 2027 y considerar el grupo de Doug Speed como acogida MSCA-PF para 2028.</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/12856703/postdoc-position-in-method-development-in-human-statistical-genetics-with-a-focus-on-classificat-/</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Ramas 1 y 2 (misma plaza, fusionada; ver el conflicto de fechas en Fit_Rationale). Nature Careers bloquea el fetch automatico (HTTP 400) y la pagina de vacantes de AU TECH no mostraba el puesto, por eso UNVERIFIED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Computational Scientist I - McCarroll Lab</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Broad Institute of MIT and Harvard</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>McCarroll Lab (Stanley Center for Psychiatric Research / Genomic Neurobiology)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Steven McCarroll</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Staff scientist (Computational Scientist I)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Genomica computacional y estadistica; datos geneticos humanos a gran escala. Requisitos exactos no legibles desde la vista de listado del portal; sin fecha de cierre publicada.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>The only role found this run inside the Stanley Center orbit, and the most valuable single data point of the institution-direct branch: McCarroll is Director of Genomic Neurobiology at the Stanley Center and the lab is the psychiatric-genetics engine at the Broad. Her fit: statistical genetics of complex traits is her top line and PLINK/R GWAS-PRS pipelines are what she runs independently, which is the right half of this job. The gap is that the group works heavily in single-cell brain genomics and a Computational Scientist hire there is normally expected to be independently productive in Python and single-cell pipelines on day one, while her Python is AI-assisted and her neuroimaging and electrophysiology are supervised level. The MD+PhD combination is a genuine differentiator at the Stanley Center specifically, because they value clinicians who can reason about psychiatric phenotypes. TIMING, plainly: posted 2026-06-23 and will be filled long before she is free. Visa: USA, she is an EU citizen and would need H-1B or J-1 sponsorship; the Broad does sponsor, but it lengthens any offer. An application would need the Nature Mental Health manuscript out of review and ideally accepted, plus a demonstrable Python portfolio. Treat as intelligence: it establishes that the Stanley Center hires computational staff scientists, not only postdocs, on rolling adverts without deadlines.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Los puestos computacionales del Broad atraen candidaturas internacionales y McCarroll es un PI de alto perfil en genomica psiquiatrica</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>No aplicar ahora (publicado en jun 2026; ella no esta disponible hasta mediados de 2027 como pronto). Desde mediados de 2027, revisar el portal del Broad mensualmente; en paralelo, redactar un correo especulativo a Steven McCarroll para finales de 2027 encabezado por la combinacion MD+PhD y el articulo QIMR/Nature Mental Health. La proxima pasada: capturar la URL directa del anuncio y su fecha de cierre abriendo la ficha del portal.</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>https://broadinstitute.avature.net/careers</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Rama 3 (institucion directa). Leido en el portal Avature propio del Broad (Tier 1) el 2026-08-23, con 6 vacantes visibles. La vista de listado solo muestra titulo y fecha de publicacion: no expone URL por anuncio, ni cierre, ni salario, de ahi los campos vacios en vez de inventados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P-0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PhD / Postdoc Fellowship Call 2026 - Functional Genomics Team (llamada de acogida)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CNAG (Centro Nacional de Analisis Genomico)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Functional Genomics Team</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Contactos publicados: anna.esteve@cnag.eu, mireya.fernandez@cnag.eu</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Acogida de candidaturas con financiacion propia (PhD o postdoc)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>-185</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Doctorado completado para la via postdoc; candidatura canalizada via Juan de la Cierva, EMBO o la Caixa INPhINIT Incoming/Retaining; perfil de genomica/bioinformatica</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Not a salaried vacancy but a host call: CNAG names the fellowship schemes it will support and invites candidates to apply with it as host. That structure is exactly what her clock needs - she cannot take a PhD-required postdoc before Feb 2028 (ETA), but she can be writing a Juan de la Cierva or la Caixa INPhINIT Retaining application in late 2027 for a 2028 start, and CNAG says in advance that it will host. Barcelona means no relocation out of Spain and no permit, and it keeps the Spanish Laboratory Medicine / Genetica Medica lane physically reachable, which matters because she wants that track genuinely alive rather than as a fallback. The content fit is partial and honest: CNAG's Functional Genomics team is sequencing- and functional-genomics-led rather than complex-trait statistical genetics, so she would move one field sideways - which her profile explicitly allows - and her PLINK/R/GWAS skills transfer to the analysis side, not the functional side. Effort is front-loaded onto the fellowship application itself, weeks of work plus a host agreement, not onto this call. The 2026 edition closed 2026-02-19. Note the mechanism overlaps the fellowships routine: what belongs in this tab is CNAG-as-host, not the schemes themselves.</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Llamada de acogida, no plaza unica: el cuello de botella real son las convocatorias competitivas subyacentes (Juan de la Cierva, la Caixa INPhINIT), no la seleccion del CNAG</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Agendar la edicion 2027: el CNAG lanza esta llamada anualmente con cierre global hacia febrero y plazos de las becas anteriores (Juan de la Cierva ~dic, EMBO ~ene, INPhINIT ~ene/feb). En otono de 2027, escribir a anna.esteve@cnag.eu preguntando si Functional Genomics o un equipo de analisis acogeria una solicitud Juan de la Cierva / INPhINIT Retaining con inicio a mediados de 2028.</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>https://www.cnag.eu/jobs/phd-postdoc-fellowship-call-2026-functional-genomics-team</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Rama 1. Pagina de la convocatoria leida directamente; plazos y correos de contacto tomados de ella.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P-0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Postdoctoral Scientist, Computational Epigenomics and Genetics</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Centre for Genomic Regulation (CRG)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Computational epigenomics and genetics</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Doctorado; genomica/epigenomica computacional; analisis estadistico de grandes conjuntos genomicos (detalle no leido: portal bloqueado con HTTP 403)</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Worth keeping for where it is and what it borders, not because it is a bullseye. The CRG is Spain's flagship genomics institute, ERC-dense and English-working, in Barcelona - one of very few places where a serious computational-genetics career and the Spanish clinical / Genetica Medica lane can coexist without leaving the country or losing the Laboratory Medicine option. Content is adjacent rather than central: computational epigenomics is not her statistical-genetics-of-complex-traits core, but her profile explicitly allows adjacent fields, and epigenetics already sits inside her sleep-genetics reading - her Journal of Sleep Research review covers the genetics and epigenetics of early-childhood sleep - so the reframing story writes itself. Transferable strengths are the GWAS/PRS pipeline work and large-dataset statistical handling; what she lacks is wet-lab epigenomics and heavy method development, so she should target the analysis seat, not the tool-building seat. UNREAD: recruitment.crg.eu returns HTTP 403 to automated fetching, so deadline, duration, salary and requirements are all unread and the OPEN status rests only on the portal listing it as live. Timing caveat as everywhere: a post open in Aug 2026 will not survive to Feb 2028, so its real use is to mark the CRG as a host to approach for an MSCA-PF or Juan de la Cierva agreement.</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Anuncio no legible (403); el CRG es en general competitivo y de difusion internacional</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>La duena debe abrir el enlace del CRG en un navegador para leer plazo y perfil (el portal bloquea el acceso automatico). Al margen de este anuncio, anadir el CRG a la lista corta de acogidas espanolas a las que dirigirse en 2027 para un inicio financiado en 2028.</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>https://recruitment.crg.eu/content/jobs/position/postdoctoral-scientist-computational-epigenomics-and-genetics</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Rama 1. Surgido al rastrear centros genomicos de Barcelona; el portal del CRG devolvio HTTP 403 en el unico intento de fetch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P-0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Postdoctoral positions in human population genetics, complex disease and cancer</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Albert Einstein College of Medicine</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Experiencia en GWAS y puntuaciones de riesgo poligenico en poblaciones de ascendencia diversa (segun resumen del listado; pagina no abierta)</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>GWAS plus polygenic risk scores in diverse-ancestry populations is squarely the toolkit she runs independently, and cross-ancestry PRS transferability is a growth area where her psychiatric-genetics angle would transfer rather than restart. But almost everything else is unknown: no PI named, no group, no deadline, no salary, and no confirmation of what fraction is cancer versus complex disease - and neither her line 2 nor line 3 appears, so she would be pivoting phenotype. As a US post it needs J-1 or H-1B sponsorship, which Einstein routinely does but which the listing did not confirm. Given her currently light publication record, an unnamed-PI US advert is a weak use of application effort compared with a targeted approach to a lab whose papers she can name. Logged at 3 for the technique overlap, with the caveat that a human must verify it before anyone spends effort on it.</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Informacion insuficiente: el anuncio no se pudo abrir</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>La duena debe abrir la URL de Nature Careers manualmente e identificar al PI; si trabaja en fenotipos psiquiatricos o conductuales, ascender a elemento de seguimiento, y si no, descartar. En cualquier caso no es accionable antes de mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/postdoctoral-positions-in-human-population-genetics-complex-disease-and-cancer-in-new-york-city-usa-albert-einstein-college-of-medicine-einstein-757285</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Rama 2, Nature Careers (SRC-0003); fetch bloqueado (HTTP 400), contenido solo desde el resumen de busqueda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P-0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Junior Research Data Scientist</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NIHR BioResource Centre Maudsley, Social, Genetic &amp; Developmental Psychiatry (SGDP) Centre</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Duracion determinada</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-10-01 a 2029-09-30, prorrogable segun financiacion</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>45000-50500 aprox (GBP 39076-43909 incl. London Weighting)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>11</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Titulacion cuantitativa o experiencia equivalente (no exige doctorado); R o Python, SQL, limpieza de datos, REDCap/Qualtrics; deseable Git, Snakemake/Nextflow/Singularity, datos genomicos y longitudinales</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Right centre - SGDP is the UK home of psychiatric and behavioural genetics - but wrong role and wrong clock: a data-engineering post that does not require a PhD, starting 2026-10-01 while she is still in residency, and a step sideways from research.</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>El listón de entrada sin doctorado amplia el grupo de candidatos, pero la mezcla de competencias (SQL, pipelines reproducibles, plataformas de datos de investigacion) lo estrecha</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Sin solicitud. Se conserva como prueba de que KCL SGDP / NIHR BioResource Maudsley contrata personal cuantitativo con regularidad: crear una alerta en jobs.ac.uk con King's College London + Social, Genetic para anuncios de grado postdoc a partir de finales de 2027.</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSR260/junior-research-data-scientist</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Rama 2, jobs.ac.uk (SRC-0002), anuncio abierto y fechas leidas directamente el 2026-08-23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P-0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Associate in Epidemiology and Health Data Science</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Queen Mary University of London</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Centre for Primary Care, Wolfson Institute of Population Health</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Duracion determinada</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>44200-59500 aprox (GBP 38419-51755)</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>14</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Doctorado obtenido o proximo en epidemiologia, ciencia de datos en salud, estadistica o bioinformatica; datos longitudinales de salud a gran escala en R; deseable historia clinica del NHS enlazada, entornos seguros de investigacion, fragilidad/diabetes, datos genomicos y puntuaciones poligenicas</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Genomics and PRS appear only as desirable extras on what is fundamentally an NHS electronic-health-record epidemiology post in primary care, so it uses her MD more than her statistical genetics, and it closes 2026-09-06, long before she is available.</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Elegibilidad cuantitativa amplia y grado postdoc estandar de Londres</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Sin accion. Se conserva solo para dejar constancia de que el Wolfson Institute of Population Health combina a veces epidemiologia de historia clinica con puntuaciones poligenicas, un nicho MD + genetica estadistica plausible que conviene revisar en 2027.</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSM851/postdoctoral-research-associate-in-epidemiology-and-health-data-science</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Rama 2, jobs.ac.uk (SRC-0002), anuncio abierto y fechas leidas directamente el 2026-08-23; lo devolvio la consulta polygenic, no statistical genetics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P-0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Research Assistant (Moondance Dementia Laboratory)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cardiff University</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Division of Psychological Medicine and Clinical Neurosciences (misma division que el MRC Centre for Neuropsychiatric Genetics and Genomics)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Research Assistant</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>39000-42100 aprox (GBP 33951-36636)</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>25</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Trabajo de evaluacion patologica en un laboratorio de demencia: banco y neuropatologia, no genetica estadistica</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Right division and right university but the wrong work - dementia neuropathology at the bench, not GWAS/PRS - and it closes 2026-09-17, nine months before she is available.</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Puesto de grado Research Assistant en el Reino Unido; volumen de candidaturas estandar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Sin accion. Lo util es la URL de vacantes de Cardiff que si funciona: revisarla desde mediados de 2027 buscando plazas de Research Associate en genetica estadistica del MRC CNGG.</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>https://cardiffuniweb.eploy.net/vacancies/vacancy-search-results.aspx?culture=en-GB</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Rama 3. Portal eploy propio de Cardiff (Tier 1), vacante ref 442. cardiff.ac.uk/jobs devuelve HTTP 403 al fetch automatico; jobs.cardiff.ac.uk redirige (302) a esta URL de eploy, que si funciona. Solo se leyo la pagina 1 de 3 y no aparecio ningun puesto del MRC CNGG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P-0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Clinical Research Associate (IoPPN)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Institute of Psychiatry, Psychology &amp; Neuroscience (IoPPN), Denmark Hill</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Clinical Research Associate</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Puesto clinico en el IoPPN; los puestos clinicos de KCL exigen normalmente registro GMC en el Reino Unido</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Her MD makes her nominally eligible for an IoPPN clinical research post, but it closes in four days, it is clinical rather than statistical-genetics work, and UK clinical registration plus her residency running to 2027-05-22 rule it out.</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Sin accion. Se registra para dejar constancia de que el IoPPN si anuncia puestos de investigacion de via clinica, un carril que merece vigilancia por su titulo de medicina a partir de mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/154086-clinical-research-associate</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Rama 3. Visto en la busqueda de vacantes propia de KCL (Tier 1); la vista de listado dio titulo, facultad, ubicacion y cierre, pero no salario. URL reconstruida desde la ruta relativa del listado, no abierta individualmente: enlace provisional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P-0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Clinical Research Fellow (IoPPN)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Institute of Psychiatry, Psychology &amp; Neuroscience (IoPPN), Denmark Hill</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Clinical Research Fellow</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>9</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Beca clinica en el IoPPN; normalmente exige registro clinico en el Reino Unido</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Same as the IoPPN Clinical Research Associate above - an MD-track research post at exactly the right institute, but closing 2026-09-01 and requiring UK clinical registration she does not hold.</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Sin accion mas alla de anotar el patron: el IoPPN mantiene un flujo constante de puestos de clinico-investigador. Revisar desde mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/155765-clinical-research-fellow</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Rama 3. Visto en la busqueda de vacantes propia de KCL (Tier 1), 106 vacantes en total. URL reconstruida desde la ruta relativa del listado: enlace provisional. Ningun puesto del SGDP Centre era visible en la primera pagina de resultados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P-0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Research Officer - Experimental Biology and Surveillance Innovation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>QIMR Berghofer Medical Research Institute</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Experimental Biology and Surveillance Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Research Officer</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Cientifico experimental de laboratorio humedo (ref BV000084)</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Wet-lab experimental biology with nothing to do with her statistical-genetics profile - logged only to record that QIMR's portal held no relevant vacancy on 2026-08-23.</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Sin accion. La jugada real en QIMR es la via de contacto personal, no el portal.</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>https://qimrberghofer.turborecruit.com.au/job/job_details.cfm?id=581998</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Rama 3. Portal TurboRecruit propio de QIMR (Tier 1). Solo habia DOS vacantes en todo el instituto el 2026-08-23 (esta y una administrativa), ninguna en Mental Health &amp; Neuroscience.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD1"/>
+  <autoFilter ref="A1:AD18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2747,37 +7524,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="52" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="52" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="52" customWidth="1" min="27" max="27"/>
+    <col width="52" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2922,8 +7699,766 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>J-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Associate Manager, Statistical Genetics - Regeneron Genetics Center</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Regeneron Pharmaceuticals (Regeneron Genetics Center)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pharma/biotech R&amp;D</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Tarrytown, New York</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Hibrido (4 dias presenciales, indicado en el anuncio)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Indefinido de industria, via staff scientist / manager</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>101000-165000 aprox (el anuncio publica 109900-179300 USD)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Doctorado en genetica humana, bioestadistica o afin; 0-2 anos post-doctorado; GWAS/ExWAS, analisis de variante rara, aleatorizacion mendeliana, LD score regression, modelizacion de PRS, meta-analisis; PLINK, REGENIE, R, Python, C/C++; datos genotipo+fenotipo de ~3M de personas</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Closest match to research line 1 (statistical genetics of complex traits) found this run: the required toolkit - PLINK, R, GWAS, PRS, meta-analysis - is exactly the level she commands independently, and the 0-2 years post-PhD band is written for someone at her stage. Two real conditions. (a) TIMING: the advert requires a defended PhD (hers is an ETA of Feb 2028), so this requisition will be long closed; the row is a target-company record, not an apply-now item, and RGC posts statistical-genetics and computational-genomics requisitions continuously, so the action is to track the careers page and apply from late 2027. (b) VISA: USA, so H-1B or O-1 sponsorship is needed; Regeneron does sponsor but it is a filter, and four days onsite in Tarrytown rules out the remote working she prefers. An application needs a CV led with the MD+PhD combination - rare in an RGC analyst pool and directly useful for phenotype curation from EHR data - plus the Nature Mental Health first-author paper once accepted and evidence of pipeline work at scale. REGENIE is the concrete gap: she has PLINK, the advert names REGENIE explicitly, and a few months of self-directed work on UK Biobank-style data would close it. Salary is far above any Spanish public option and she has set no floor. Hook: RGC's psychiatric and behavioural phenotype work against her GWAS/PRS line; the natural meeting place is WCPG (SRC-0026) rather than a cold Workday application.</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Grupo de genetica estadistica de referencia en la industria; grupo global de candidatos recien doctorados y postdocs para una banda de 0-2 anos, con el patrocinio de visado como filtro adicional</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>No aplicar ahora (doctorado sin defender). Anadir el filtro de genetica y genomica de careers.regeneron.com a la vigilancia; cerrar durante 2027 la laguna de REGENIE y pipelines de cohortes grandes; reabrir esta fila en otono de 2027.</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>https://careers.regeneron.com/en/jobs/r48469/associate-manager-statistical-genetics-regeneron-genetics-center/</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Rama 4. Pagina de empleo propia de Regeneron abierta directamente (Tier 1). La banda salarial la publica Regeneron en USD; la cifra en EUR es una aproximacion, no un importe oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>J-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bolsa Unica de Empleo del SAS - inscripcion como Facultativo Especialista de Area (Laboratorio Clinico)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Servicio Andaluz de Salud (SAS), Junta de Andalucia</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sanidad publica espanola (CCAA Andalucia)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Andalucia (eleccion de provincia; Malaga relevante)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Nombramientos estatutarios temporales desde una bolsa permanente baremada</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Titulo de especialista en la categoria correspondiente (el suyo: Laboratorio Clinico, segun RD 101/2025, al terminar la residencia el 22-05-2027); inscripcion en la Bolsa Unica, permanentemente abierta y actualizable; baremo de meritos con cortes periodicos; dos subbolsas, seleccion y provision (PIT)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>The single most actionable item in career lane 2, and actionable precisely because it is not an advert. Her residency ends in Malaga on 2027-05-22, and the SAS is the service that already knows her: registering in the Bolsa Unica the week the titulo is issued starts the clock on a baremo that rewards exactly what she is accumulating - residency months in an SAS centre, publications, congress activity, and doctorate points once she defends in 2028. The MD half of the profile is what qualifies her here; the PhD adds baremo points rather than eligibility. Effort is small: an electronic registration plus documented merits, no exam, and no deadline to miss, since the pool is permanently open and merits are re-scored at cut-offs. No visa issue. Salary is the statutory FEA scale, well below industry but stable, and she has set no floor. RISK TO FLAG, verified this run: the category she will hold from May 2027 is Laboratorio Clinico, a title created by RD 101/2025 which suppressed Analisis Clinicos and Bioquimica Clinica, while CCAA bolsa catalogues still name the old categories - she must confirm with the SAS which category code her titulo maps to rather than assume, and register under the Analisis Clinicos/Bioquimica Clinica equivalence if the new code is not yet live. Contact: SAS 955 012 012, or the personnel unit of the Hospital Regional Universitario de Malaga, which handles this routinely for its own residents.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Las categorias FEA de laboratorio son deficitarias de forma cronica en Andalucia; se compite por posicion en el baremo, no por examen, y los residentes del propio servicio parten con ventaja</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Nada que presentar antes de mayo de 2027. Hasta entonces: mantener archivada la documentacion de meritos (contratos, cursos, posteres, publicaciones) y, a principios de 2027, preguntar a la unidad de personal de Malaga a que categoria de bolsa se mapea el nuevo titulo de Laboratorio Clinico. Inscribirse en la Bolsa Unica inmediatamente despues del 22-05-2027.</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>https://www.sspa.juntadeandalucia.es/servicioandaluzdesalud/profesionales/ofertas-de-empleo/bolsa-de-empleo</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Rama 4. Pagina de bolsa del SAS abierta (Tier 1): expone las subbolsas de seleccion y provision (PIT) y el proceso de baremo y alegaciones. La pagina no enumera por si misma el listado de categorias FEA, de ahi la advertencia y no una afirmacion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>J-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Via transitoria al titulo de especialista en Genetica Medica y en Genetica de Laboratorio - seguimiento normativo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ministerio de Sanidad / BOE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sanidad publica espanola (via de acceso al titulo)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Via de acceso excepcional al titulo de especialista, no un puesto</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Aun sin publicar: el real decreto que debe contener la disposicion transitoria no esta en el BOE a 2026-08-23. Las fuentes profesionales anticipan acceso directo para especialistas y no especialistas que acrediten prestacion de servicios durante un numero de anos todavia sin concretar; ni baremo ni plazo publicados.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Not a vacancy but the gate to the whole of career lane 2, and the brief names it explicitly as something this routine tracks. STATUS AT 2026-08-23, established by opening the Ministry's own pages: there is no open window and none announced with dates, because the real decreto is not yet in the BOE. Documented chronology: the SNS Human Resources Commission approved creating both specialties on 2024-12-05; the Ministry formally announced the approval on 2025-06-13 (Genetica Medica reserved to medical graduates, Genetica de Laboratorio open to Medicine, Pharmacy, Biology, Chemistry and Veterinary, both four years, handled as two separate reales decretos); the prior public consultation on the Genetica de Laboratorio draft was published on 2025-07-01; in March 2026 the Ministry described the RD as ready and pending public hearing. CHECKED DIRECTLY THIS RUN: the official audiencia e informacion publica listing shows NO Genetica project open, so the hearing stage did not open between March and August 2026 and the RD cannot be in the BOE. Why this matters to her specifically: she is an MD, so Genetica Medica would be open to her, and a transitional route would let her hold the genetics title without repeating MIR - the difference between her clinical lane being laboratory medicine only and being clinical genetics. The window, when it opens, will be short (months from entry into force), which is why it is worth a standing BOE alert rather than a weekly check. UNRESOLVED CONFLICT, recorded rather than silently decided: the AEGH page contains text suggesting a real decreto reached the Council of Ministers and the BOE, but gives no date or disposition number, and most likely refers to the RD on Formacion Sanitaria Especializada rather than the Genetica ones.</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>No hay convocatoria: sin texto publicado no hay ni baremo ni concurrencia que estimar</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Dar de alta una alerta del BOE con 'Genetica Medica' y 'Genetica de Laboratorio' (ver SUB-0001) y vigilar semanalmente el listado de audiencia publica de Sanidad, que da semanas de margen sobre el BOE y publica ya el texto de la disposicion transitoria. La proxima pasada: intentar la busqueda de legislacion del BOE por titulo con 'Genetica' para cerrar el conflicto de la pagina de la AEGH.</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>https://www.sanidad.gob.es/normativa/audiencia/home.htm</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Rama 4. Listado oficial de audiencia e informacion publica de Sanidad abierto el 2026-08-23: ningun proyecto de Genetica, solo el de electrodependencia. Nota de prensa del Ministerio de 2025-06-13 (id=6697) y consulta publica previa de 2025-07-01 como respaldo documental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>J-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Facultativo Especialista en Analisis Clinicos - concurso-oposicion SERMAS (ref. E907, 47 plazas)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Servicio Madrileno de Salud (SERMAS), Comunidad de Madrid</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sanidad publica espanola (CCAA Madrid)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Plaza estatutaria fija</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2021-12-14</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Titulo de especialista en Analisis Clinicos en el momento de solicitar; concurso-oposicion (examen mas meritos); 44 plazas turno libre + 3 de discapacidad</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Logged not as an opportunity but as the calibration point for lane 2 in Madrid, where she took her degree (UCM) and has a network. The process is over - convoked in BOCM on 2021-12-14, definitive merit list 2026-01-23, plaza choice 14-28 May 2026, successful candidates 2026-06-18, documentation to 2026-07-02 - and that tells us two useful things. First, the cycle length: four and a half years from convocatoria to appointment, so an OEP she entered in 2028 would resolve around 2032, which makes the bolsa the only near-term route to actually working in Madrid. Second, the category in Madrid is still named Analisis Clinicos, not the new Laboratorio Clinico of RD 101/2025 - the same catalogue-lag risk flagged in the SAS row, confirmed in a second CCAA. She is not eligible for this edition and it is closed; what to watch is the next SERMAS OEP in the category, and she will hold the titulo from 2027-05-22, comfortably before any plausible 2028-or-later convocatoria deadline. Effort when it comes is real: a concurso-oposicion means an exam on clinical laboratory content, so months of preparation, unlike the bolsa.</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Grupo nacional de especialistas compitiendo por 47 plazas fijas en Madrid mediante examen; las plazas estatutarias fijas en una region atractiva son la via mas disputada</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Vigilar sede.comunidad.madrid y el BOCM para la proxima convocatoria de OEP en la categoria; mientras tanto tratar Madrid como opcion solo de bolsa antes de 2028.</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>https://sede.comunidad.madrid/oferta-empleo/facultativo-especialista-analisis-clinic</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Rama 4. Ficha del proceso en la sede electronica de la Comunidad de Madrid abierta (Tier 1); fechas y numero de plazas leidos en ella. Convocatoria original BOCM 14-12-2021; resolucion de superacion BOCM 13-05-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>J-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Facultativo/a Especialista en Analisis Clinicos - concurso de meritos Ley 20/2021 (estabilizacion)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Conselleria de Sanitat, Generalitat Valenciana</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sanidad publica espanola (CCAA Comunitat Valenciana)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Valencia (destinos en toda la Comunitat)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Plaza estatutaria fija por concurso de meritos extraordinario</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Titulo de especialista; concurso solo de meritos (sin examen) restringido al proceso de estabilizacion de la Ley 20/2021; oferta de vacantes y eleccion de destino resueltas el 23-07-2026, acto presencial de destinos el 30-07-2026</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Closed and structurally unrepeatable: the Ley 20/2021 estabilizacion was a one-off merits-only route that has now consumed the Valencian vacancies in her category, so her realistic Valencian entry is the permanently open lista de empleo temporal recorded in sources.</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Sin accion; usar en su lugar la lista de empleo temporal de la GVA.</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>https://sede.gva.es/es/detall-ocupacio-publica?id_emp=87684</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Rama 4. No abierta directamente (presupuesto); las fechas las corroboran dos informaciones secundarias independientes sobre la resolucion del 23-07-2026 y el acto de destinos del 30-07-2026. Tratar como LIKELY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>J-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OPE Libre - Facultativo Especialista en Analisis Clinicos (6 plazas)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Servicio Murciano de Salud (SMS)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sanidad publica espanola (CCAA Region de Murcia)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Murcia</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Plaza estatutaria fija (oposicion libre)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Titulo de especialista en Analisis Clinicos; oposicion libre; 6 plazas en la OPE de 2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Recorded only as evidence that Murcia - where her PhD is registered - runs OPEs in her category at a workable volume, so its bolsa and the next OPE are worth watching even though this edition predates her titulo.</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Confirmar numero de plazas y estado contra el BORM cuando aparezca la proxima OPE del SMS; inscribirse en la bolsa del SMS despues de mayo de 2027.</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>https://www.murciasalud.es/empleo.php?idsec=39</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Rama 4. El numero de plazas procede de un resumen sindical/secundario de la OPE 2025 del SMS, no del BORM, de ahi UNVERIFIED. La URL del portal si esta verificada.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB1"/>
+  <autoFilter ref="A1:AB7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3719,19 +9254,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3786,8 +9321,112 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SUB-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Alertas del BOE (servicio de alertas / Mi BOE)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.boe.es</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Aviso el mismo dia de publicacion de cualquier disposicion que contenga 'Genetica Medica' o 'Genetica de Laboratorio', incluida la disposicion transitoria de acceso excepcional al titulo.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Es el carril 2 entero. La via transitoria tendra un plazo de solicitud corto contado desde la entrada en vigor del RD, que a 2026-08-23 ni siquiera ha entrado en audiencia publica; enterarse tarde equivale a perder la unica ventana de acceso al titulo de genetica sin repetir el MIR.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>La URL exacta del alta NO esta confirmada: en esta pasada no se abrio la pagina del servicio de alertas, solo se verifico el dominio. Localizar 'Mi BOE' / servicio de alertas desde la portada. Anadida por la rutina positions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SUB-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EURAXESS - alertas de busqueda guardada (requiere cuenta)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/search</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Correo con las ofertas nuevas que encajen en busquedas guardadas ('statistical genetics', 'polygenic', 'GWAS', 'psychiatric genetics', 'sleep') con perfil de investigador R2.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Desbloquea una rama entera: la busqueda de texto libre de EURAXESS es inservible para un agente automatico (tres parametros distintos devolvieron siempre la misma lista generica de 7.980 ofertas), asi que sin estas alertas la rama 1 seguira produciendo casi nada cada semana.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Requiere que la duena cree la cuenta y las busquedas guardadas una sola vez; despues las alertas pueden reenviarse al buzon del rastreador y las lee la rama 5. Anadida por la rutina positions.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:J3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -22,18 +22,18 @@
     <sheet name="readme" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,21 +451,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,8 +530,68 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F-0019</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FENS/IBRO-PERC Exchange Fellowships</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fellowships</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SHORT_STAY</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>hasta 4000</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antes del 15-10-2026: confirmar u obtener la membresia de SENC o la individual de FENS, escribir a 2 o 3 PI candidatos para la carta de aceptacion, y decidir si la estancia es una rotacion externa de la residencia (necesita visto bueno del tutor, conviene empezar esa conversacion ya) o una estancia posterior al 22-05-2027 solicitada en la ronda del 15 de abril de 2027.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.fens.org/careers/grants-and-stipends/grant/fens-ibro-perc-exchange-fellowships</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -542,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1158,7 +1218,11 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -1206,7 +1270,11 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -1254,7 +1322,11 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -1302,7 +1374,11 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -1350,7 +1426,11 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -1398,7 +1478,11 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -1446,7 +1530,11 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -1494,7 +1582,11 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -1542,7 +1634,11 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -1878,7 +1974,11 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>añadida tras definir el perfil, 2026-08-23</t>
@@ -3389,8 +3489,1100 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SRC-0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ISCIII - texto completo de la resolucion de convocatoria AES (PDF)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>El texto legal integro de la Accion Estrategica en Salud: ventanas exactas por actuacion (art. 7.6), requisitos por contrato (Rio Hortega art. 34, Sara Borrell art. 40, Miguel Servet art. 46, Juan Rodes art. 51), importes y cupos por centro.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Descargar el PDF cada diciembre, cuando se firma la nueva AES; extraer el texto localmente y leer los arts. 7.6, 34, 40 y 46.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>TIER 1 y con diferencia la fuente espanola de mas valor de esta pasada: es el documento que sostiene todo lo que sabemos de Rio Hortega. Las paginas HTML de isciii.es devuelven HTTP 503 al fetch automatico, pero esta URL de documento descarga bien. Es un PDF firmado, asi que WebFetch no puede leerlo: hay que descargar y extraer localmente (no hay pdftotext ni pdfminer en este entorno; funciono un extractor con zlib y expresiones regulares sobre los flujos FlateDecode).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SRC-0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>HFSP - Postdoctoral Fellowships y bases anuales</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.hfsp.org/funding/hfsp-funding/postdoctoral-fellowships</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>El calendario LOI / propuesta completa de las becas posdoctorales de HFSP y las bases anuales, incluida la clausula que permite presentarse sin doctorado concedido.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Revisar en febrero-marzo de cada ano para la apertura del portal de LOI; descargar las Application Guidelines del ano correspondiente.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>SRC-0013 apunta solo a la raiz de hfsp.org; esta es la pagina que lleva las fechas y la redaccion de elegibilidad. CONFLICTO REGISTRADO: la lectura automatica del PDF de bases del ano 2027 devolvio 'A PhD ... is required at the time of application', que contradice esta pagina web y una segunda fuente independiente. Leer las bases a mano antes de comprometerse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SRC-0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>EMBO - elegibilidad de las Postdoctoral Fellowships</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.embo.org/funding/fellowships-grants-and-career-support/postdoctoral-fellowships/eligibility/</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Cortes de cada ronda, la regla de doctorado al empezar y no al presentar, la exigencia de un articulo de primera autora aceptado, y la regla de una sola candidata por laboratorio de acogida y ronda.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Revisar hacia marzo y hacia septiembre para los cortes; el proximo corte duro es el 22-01-2027, 14:00 CET.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>biannual</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>SRC-0012 es el hub generico de financiacion de EMBO; esta es la pagina con el articulado. Desde las solicitudes posteriores al 22-01-2027 ya no se permite volver a presentarse: un solo intento, asi que la eleccion de ronda es deliberada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SRC-0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>EMBO - Scientific Exchange Grants (elegibilidad)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.embo.org/funding/fellowships-grants-and-career-support/scientific-exchange-grants/eligibility/</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Financiacion rodante de estancias cortas (hasta 3 meses) abierta a doctorandas, con la lista de paises elegibles.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>No hace falta filtro: es rodante. Consultar cada vez que se identifique un laboratorio de acogida.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>biannual</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Distinta de las becas posdoctorales de EMBO. Australia NO es destino elegible, asi que no sirve para volver a QIMR. Quedan por abrir dos PDF con los importes reales: SEG_guidelines_for_applicants.pdf y SEG_subsistence_rates_and_travel_allowance.pdf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SRC-0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FENS - Careers: Grants and Stipends</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.fens.org/careers/grants-and-stipends</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Las FENS/IBRO-PERC Exchange Fellowships y otras ayudas de viaje y estancia de FENS abiertas a doctorandas.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Recorrer la lista de ayudas; la Exchange Fellowship tiene rondas fijas el 15 de abril y el 15 de octubre.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>biannual</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>SRC-0019 apunta solo a la raiz de fens.org; esta es la subpagina accionable. Exige ser socia de una sociedad miembro de FENS (la SENC en Espana) para poder solicitar: la membresia es tarea previa, no detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SRC-0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Boehringer Ingelheim Fonds - Travel Grants</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.bifonds.de/fellowships-grants/travel-grants.html</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Ayudas rodantes y mundiales de estancia corta o curso para estudiantes de medicina y de doctorado: la unica via hallada que puede financiar una estancia en Australia (QIMR).</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Rodante; presentar entre 6 semanas y 6 meses antes de la salida.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>as-needed</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>No estaba en sources.tsv en ninguna forma. Vigilar la restriccion de ambito: financia investigacion biomedica BASICA y excluye explicitamente los estudios sobre el curso de las enfermedades. La URL /how-to-apply.html devolvio 404.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SRC-0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>JSPS - International Fellowships for Research in Japan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.jsps.go.jp/english/e-fellow/</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Las becas posdoctorales Standard y Short-term para investigadoras extranjeras en Japon, con calendario por ejercicio fiscal y bases completas.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Seguir el indice 'Application' y despues la pagina del programa Standard (e-ippan/appliguidelines.html) y la de Short-term PE (e-oubei-s/appliguidelines.html).</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>El esquema mas amable con su reloj de todos los hallados: admite a quien 'expects to receive a Ph.D. by the start date'. Ojo: la solicitud la presenta el anfitrion japones, no la candidata. jsps.go.jp/english/e-fellow/postdoctoral.html devuelve 404; las rutas buenas son e-fellow/ y e-fellow/e-ippan/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SRC-0063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BBRF - Grants and Prizes</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://bbrfoundation.org/grants-prizes</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Las fechas del ciclo de la Young Investigator Grant y el PDF de bases anual (el unico sitio donde aparece el texto literal de elegibilidad), mas las Independent y Distinguished Investigator.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Abrir la pagina de la Young Investigator cada enero y descargar las Application Guidelines de ese ano; el texto de elegibilidad se reedita cada ano y ha cambiado (tres solicitudes frente a dos).</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>No estaba en sources.tsv. El PDF de bases derrota al fetch automatico: es un PDF de form-XObject y hay que extraerlo localmente o abrirlo en navegador. Sin restriccion de nacionalidad ni de pais de acogida, algo inusual en una fundacion estadounidense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SRC-0064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sleep Research Society Foundation - programas de ayudas</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://sleepresearchsociety.org/foundation/</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>El SRSF Career Development Award y las demas ayudas de la fundacion, con convocatorias publicadas cada mayo.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Comprobar cuando salen las convocatorias (mediados de mayo) y otra vez un mes antes del plazo de agosto.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>SRC-0031 cubre el tablon de empleo para trainees de la SRS, no el lado de FINANCIACION de la Fundacion: son paginas y propositos distintos. Exige membresia activa de la SRS al solicitar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SRC-0065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sleep Research Society - Conference Awards</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://sleepresearchsociety.org/awards/conference-awards/</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Trainee Merit, Diversity Travel (hasta 2000 USD), First-Time Attendee y premios de taller para el congreso SLEEP.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Revisar entre enero y marzo cada ano.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Las doctorandas tienen condicion de trainee. El Diversity Travel Award parece no exigir membresia, a diferencia del Trainee Merit: es el primer movimiento mas barato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SRC-0066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Sueno - Becas y Premios</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://ses.org.es/profesionales/becas-y-premios/</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Todas las becas de investigacion, ayudas de movilidad e intercambio y premios de la SES, en castellano y para trabajo hecho en Espana.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Leer las tres paginas de convocatoria enlazadas; las etiquetas 'Convocatoria abierta' del indice no son fiables, hay que mirar siempre el plazo dentro.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>No estaba en sources.tsv. Con puerta de membresia, asi que tiene un plazo de maduracion medido en anos: por eso merece seguimiento ahora y no despues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SRC-0067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ISPG - Early Career Investigator Program (ECIP)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://ispg.net/ecip-program/</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Ayuda de viaje al WCPG mas emparejamiento con un mentor senior para investigadoras de inicio de carrera en genetica psiquiatrica.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>El plazo se anuncia en la pagina del WCPG del ano, no en la del ECIP: revisar siempre las dos, entre febrero y mayo.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>SRC-0026 cubre el WCPG y SRC-0030 el tablon de empleo de la ISPG, pero no la linea de ayudas. Es lo unico de todo el calendario para lo que es plenamente elegible hoy: 'post-doctoral researcher, or less than five years out of a doctoral program'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SRC-0068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ESHG - sitio del congreso anual (subdominios por ano)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://2027.eshg.org/abstracts/</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Plazos de resumenes y ayudas de congreso / premios de inicio de carrera del European Human Genetics Conference.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Patron: https://&lt;ano&gt;.eshg.org/abstracts/ y /abstracts/fellowship-information/.</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ESHG 2027: Roterdam, 12-15 de junio de 2027, resumenes hasta el 04-02-2027 - tres semanas despues de que acabe su residencia, el encaje de calendario mas limpio de la pasada. SRC-0034 apunta solo a la home de la sociedad, que ademas tiene el enlace de empleo roto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SRC-0069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Instituto de Neurociencias Federico Oloriz (UGR) - Premio de Investigacion</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://ineurociencias.ugr.es/instituto/noticias/premio-instituto-neurociencias-2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Premio anual nacional de neurociencia (1250 euros) abierto a matriculadas en doctorado, basado en un articulo publicado.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Se anuncia en el hilo de noticias del instituto hacia primeros de mayo; ventana de 30 dias.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Caso modelo de toda una clase de premios pequenos de sociedades e institutos espanoles que merece rastrear de forma sistematica en proximas pasadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SRC-0070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>The Company of Biologists - Travelling Fellowships</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.biologists.com/travelling-fellowships/</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Hasta 3000 GBP para visitas colaborativas a laboratorios, con estudiantes de posgrado elegibles y sin restriccion de nacionalidad.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tres rondas al ano; buscar las fechas de 2027 despues de la ronda del 23-10-2026.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>El filtro de ambito de las revistas (Development / JCS / JEB) lo hace mal encaje para la genetica estadistica humana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SRC-0071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>jobRxiv y ECRcentral - directorios de ayudas de viaje</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://ecrcentral.org/travel-grants/</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Directorio mantenido por la comunidad de ayudas de viaje a congresos y financiacion de estancias cortas para investigadoras de inicio de carrera, con resumenes de elegibilidad.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Filtrar por disciplina y elegibilidad; tratar cada entrada como pista a verificar en la pagina del financiador.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Agregador Tier 2 por definicion: bueno para descubrir, nunca para fechas. Util sobre todo para rodear bloqueos como los de ESRS y BGA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SRC-0072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>EU Funding and Tenders Portal - paginas de topic MSCA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-search</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>La fecha de apertura, el plazo y el estado juridicamente vinculantes de cada edicion de las MSCA Postdoctoral Fellowships, y los topics futuros del proximo Programa Marco.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Busqueda de topic 'MSCA Postdoctoral Fellowships'; filtrar estado Forthcoming y Open para detectar pronto la edicion de 2027 y la del programa sucesor.</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Dominio distinto del de marie-sklodowska-curie-actions.ec.europa.eu, que ya esta en sources.tsv (SRC-0011). Hace falta porque el sitio de la MSCA publica las fechas de 2027 marcadas 'TBC' y ningun importe. El portal es una aplicacion JavaScript: un fetch simple devolvio una cascara vacia, asi que es de navegador salvo que se encuentre un espejo estatico. Su primera MSCA alcanzable es una convocatoria de 2028 bajo un programa que aun no existe, y aqui es donde se confirmara primero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SRC-0073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AEI - Calendario previsto de convocatorias</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.aei.gob.es/en/announcements/calendario-previsto-convocatorias-agencia-estatal-investigacion</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Ventanas previstas de publicacion y presentacion de todas las convocatorias de la AEI, incluidas Juan de la Cierva y Ramon y Cajal, publicadas antes que el BOE.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Revisar cada octubre las ventanas de JDC y RYC del ano siguiente.</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>BLOQUEADO: devolvio HTTP 503 dos veces el 2026-08-23 (esta pagina y las de anuncio de RYC y JDC 2026). La duena debe abrirlo en navegador. Distinta de SRC-0016, que es la raiz de aei.gob.es.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SRC-0074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>DFG - Walter Benjamin Programme (bases, formulario 50.10 en)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.dfg.de/resource/blob/168116/50-10-en.pdf</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>El texto vinculante de elegibilidad e importes de la beca posdoctoral alemana rodante, incluida la definicion de fase posdoctoral temprana.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Leer una vez; revisar anualmente por si hay revisiones.</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>No abierto en esta pasada; identificado como el documento Tier 1 detras de la pagina del programa. Sin techo numerico publicado de anos posdoctorales, que es lo que la hace valiosa para una fecha de defensa incierta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SRC-0075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>UKRI Funding Finder - becas del MRC</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/early-independence-career-development-fellowship/</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>El marco reestructurado de becas del MRC (Early Independence: Career Development Fellowship y las vias de Clinical Research Training Fellowship) con plazos y elegibilidad.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Filtrar el UKRI Funding Finder por council = MRC y tipo = fellowship.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>El MRC Career Development Award ha cambiado de nombre dentro del Fellowship Investment Framework: buscar por los nombres antiguos devuelve resultados obsoletos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SRC-0076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NHMRC - Investigator Grants y bases anuales</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.nhmrc.gov.au/funding/find-funding/investigator-grants</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>El unico esquema australiano que absorbio las antiguas becas de inicio de carrera y de desarrollo del NHMRC: fechas anuales, reglas de la categoria EL y normas de tiempo en el extranjero.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Revisar cada abril para las fechas de la ronda de junio; descargar las bases del ano.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Las oficinas de investigacion australianas (UQ, Macquarie) replican los PDF de bases y se obtienen mas facilmente que nhmrc.gov.au.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J56"/>
+  <autoFilter ref="A1:J77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3521,12 +4713,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -4644,8 +5836,2176 @@
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>F-0001</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Contratos Rio Hortega (ISCIII, Accion Estrategica en Salud)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 5, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>F-0002</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Contratos Sara Borrell (ISCIII, Accion Estrategica en Salud)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 5, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>F-0003</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Contratos Miguel Servet (ISCIII, Accion Estrategica en Salud)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 2, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>F-0004</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ayudas para contratos Juan de la Cierva (JDC) 2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status CLOSED, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.aei.gob.es/convocatorias/buscador-convocatorias</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>F-0005</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ayudas para contratos Ramon y Cajal (RYC) 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status CLOSED, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.aei.gob.es/convocatorias/buscador-convocatorias/ayudas-contratos-ramon-cajal-ryc-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>F-0006</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Postdoctoral Junior Leader - modalidad Retaining</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status CLOSED, Confidence LIKELY.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://lacaixafoundation.org/en/postdoctoral-junior-leader-fellowships-retaining-call</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>F-0007</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>HFSP Postdoctoral Fellowships (Long-Term Fellowship, LTF)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.hfsp.org/funding/hfsp-funding/postdoctoral-fellowships</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>F-0008</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>EMBO Postdoctoral Fellowships</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.embo.org/funding/fellowships-grants-and-career-support/postdoctoral-fellowships/eligibility/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>F-0009</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MSCA Postdoctoral Fellowships (European Fellowship; variante Global)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/actions/postdoctoral-fellowships</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>F-0010</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Humboldt Research Fellowship for Postdoctoral Researchers</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status ROLLING, Confidence LIKELY.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.humboldt-foundation.de/en/apply/sponsorship-programmes/humboldt-research-fellowship</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>F-0011</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>DFG Walter Benjamin Programme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status ROLLING, Confidence LIKELY.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.dfg.de/en/research-funding/funding-opportunities/programmes/individual/walter-benjamin</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>F-0012</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Wellcome Early-Career Awards</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status CLOSED, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://wellcome.org/research-funding/schemes/early-career-awards</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>F-0013</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>MRC Early Independence: Career Development Fellowship</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status CLOSED, Confidence LIKELY.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/early-independence-career-development-fellowship/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>F-0014</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NIH Pathway to Independence Award (K99/R00), con participacion del NIMH</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status ROLLING, Confidence LIKELY.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://grants.nih.gov/grants/guide/pa-files/PA-24-194.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>F-0015</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NIH Ruth L. Kirschstein NRSA Postdoctoral Fellowship (F32)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 1, Status CLOSED, Confidence LIKELY.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://researchtraining.nih.gov/programs/fellowships/F32</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>F-0016</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>NHMRC Investigator Grants - Emerging Leadership (EL1)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status CLOSED, Confidence LIKELY.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.nhmrc.gov.au/funding/find-funding/investigator-grants</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>F-0017</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>BBRF Young Investigator Grant (antes NARSAD Young Investigator)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://bbrfoundation.org/grants-prizes/bbrf-young-investigator-grants</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>F-0018</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ERC Starting Grant</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 2, Status CLOSED, Confidence LIKELY.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://erc.europa.eu/apply-grant/starting-grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>F-0019</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>FENS/IBRO-PERC Exchange Fellowships</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.fens.org/careers/grants-and-stipends/grant/fens-ibro-perc-exchange-fellowships</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>F-0020</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>EMBO Scientific Exchange Grants</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status ROLLING, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.embo.org/funding/fellowships-grants-and-career-support/scientific-exchange-grants/eligibility/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>F-0021</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Boehringer Ingelheim Fonds (BIF) Travel Grants</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status ROLLING, Confidence LIKELY.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.bifonds.de/fellowships-grants/travel-grants.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>F-0022</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>JSPS Postdoctoral Fellowships for Research in Japan (Standard Program)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.jsps.go.jp/english/e-fellow/e-ippan/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>F-0023</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ESHG 2027 - conference fellowships / early career awards</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status OPEN, Confidence LIKELY.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://2027.eshg.org/abstracts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>F-0024</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Premios L'Oreal-UNESCO For Women in Science Espana (XXI edicion, prevista)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.loreal.com/es-es/espana/news/commitment/loreal-unesco-abre-convocatoria-de-premios-for-women-in-science/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>F-0025</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SRSF Career Development Award</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://sleepresearchsociety.org/foundation/srsf-career-development-award/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>F-0026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ESRS grants: Travel Grants, Two-Week Training Grants y Meetings &amp; Courses Fellowships</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status OPEN, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://esrs.eu/grants-awards/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>F-0027</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>BGA Student Travel Awards (congreso anual de la Behavior Genetics Association)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status OPEN, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>http://bga.org/student-travel-awards/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>F-0028</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>BGA Outstanding Associate Member Oral / Poster Presentation Awards</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 3, Status OPEN, Confidence LIKELY.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://bga.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>F-0029</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>The Company of Biologists Travelling Fellowships</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 2, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.biologists.com/travelling-fellowships/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>F-0030</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Premio de Investigacion del Instituto de Neurociencias Federico Oloriz (UGR)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 4, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://ineurociencias.ugr.es/instituto/noticias/premio-instituto-neurociencias-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>F-0031</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Guarantors of Brain Travel Grants</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 1, Status ROLLING, Confidence LIKELY.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://guarantorsofbrain.org/grants/travel-grants/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>F-0032</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>BBRF Independent Investigator Grant</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 1, Status OPEN, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://bbrfoundation.org/grants-prizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>F-0033</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BBRF Distinguished Investigator Grant</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 1, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://bbrfoundation.org/grants-prizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>F-0034</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Stanley Center Sklar Program (Sklar Research Award / Sklar BSRP Fellowship)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 1, Status CLOSED, Confidence VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.broadinstitute.org/stanley-center-sklar-program</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>F-0035</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>L'Oreal-UNESCO For Women in Science International Awards / International Rising Talents</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 1, Status CLOSED, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.forwomeninscience.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>F-0036</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>CSIC Premios a Tesis Doctorales Relevantes (IV edicion)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alta en la pasada de siembra. Fit 1, Status OPEN, Confidence UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.csic.es/es/actualidad-del-csic/el-csic-lanza-la-convocatoria-2026-de-los-premios-tesis-doctorales-relevantes-y-la-supervision-del-personal-investigador</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>W-0001</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>HFSP Postdoctoral Fellowships - convocatoria del ano 2027</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: Portal de LOI ~marzo de 2027, plazo de LOI ~mayo de 2027, propuesta completa ~septiembre d (confianza HIGH).</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.hfsp.org/funding/hfsp-funding/postdoctoral-fellowships</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>W-0002</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Contratos Rio Hortega - edicion AES 2026</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: 2027-02-10 (ventana ~10 feb - 5 mar 2027; publicacion en BOE prevista en diciembre de 2026 (confianza LIKELY).</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>W-0003</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Contratos Sara Borrell - edicion AES 2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: 2027-02-10 (ventana ~10 feb - 5 mar 2027); su primera edicion realista es la AES 2029 (confianza LIKELY).</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>W-0004</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Contratos Miguel Servet - edicion AES 2026</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: 2027-02-11 (ventana ~11 feb - 4 mar 2027) (confianza LIKELY).</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>W-0005</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Wellcome Early-Career Awards - ronda de julio de 2026</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: Esquema rodante con varias rondas al ano: proximos plazos ~10-11-2026 y ~06-04-2027, y otr (confianza HIGH).</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://wellcome.org/research-funding/schemes/early-career-awards</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>W-0006</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>NHMRC Investigator Grants - ronda 2027</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: Ronda 2028 prevista con apertura ~2-6-2027 y cierre ~28-7-2027 (17:00 AEST); ronda 2029 ~j (confianza HIGH).</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.nhmrc.gov.au/funding/find-funding/investigator-grants</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>W-0007</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>BBRF Young Investigator Grant - ciclo 2026</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: Principios de febrero de 2027, con cierre a principios de marzo de 2027 (confianza HIGH).</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://bbrfoundation.org/grants-prizes/bbrf-young-investigator-grants</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>W-0008</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Postdoctoral Junior Leader - modalidad Incoming, convocatoria 2027</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: Hacia abril-mayo de 2027 para la Incoming de 2028 (cierre historicamente a finales de juli (confianza LIKELY).</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://lacaixafoundation.org/en/postdoctoral-junior-leader-fellowships-incoming-call</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>W-0009</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ISPG Early Career Investigator Program (ECIP) - ayuda de viaje al WCPG</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: Portal de resumenes del WCPG 2027 hacia febrero-marzo de 2027; plazo de resumenes y de ECI (confianza MEDIUM).</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://ispg.net/ecip-program/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>W-0010</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SRS Trainee Awards del congreso SLEEP (Trainee Merit, Diversity Travel, First-Time Attendee)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: Enero-marzo de 2027 para SLEEP 2027; la propia pagina de la SRS indica que el ciclo del Tr (confianza LIKELY).</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://sleepresearchsociety.org/awards/conference-awards/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>W-0011</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Premio de Investigacion del Instituto de Neurociencias Federico Oloriz (UGR) - edicion 2026</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: Mayo de 2027, convocatoria anual con ventana de solo 30 dias naturales (confianza LIKELY).</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://ineurociencias.ugr.es/instituto/noticias/premio-instituto-neurociencias-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>W-0012</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Becas de Investigacion de la SES (Sociedad Espanola de Sueno)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: ~noviembre-diciembre de 2026, con plazo ~25 de enero de 2027 (confianza MEDIUM).</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://ses.org.es/blog-post/becas-2022-2-5-3-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>W-0013</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ESRS Meetings and Courses Fellowship</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: ~finales de 2026, con plazo ~31 de enero de 2027 (confianza LOW-MEDIUM).</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://esrs.eu/grants-awards/meetings-and-courses-fellowship/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>W-0014</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>One Mind Rising Star Awards 2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Convocatoria cerrada en seguimiento. Reapertura prevista: ~marzo de 2027 (anual) (confianza MEDIUM).</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://onemind.org/what-we-do/one-mind-rising-star-academy/one-mind-rising-star-awards/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Ampliacion de la superficie de vigilancia</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>21 fuentes nuevas de financiacion (el PDF de la AES del ISCIII, las paginas de articulado de HFSP y EMBO, JSPS, BBRF, SRS Foundation, SES, ISPG ECIP y el portal de topics de la UE), con sus notas de bloqueo.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>subscriptions</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Alertas propuestas</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2 altas TODO (tope por pasada): membresia de la SENC, que habilita el plazo del 15-10-2026, y avisos del ISCIII, que habilitan Rio Hortega. El resto de candidatas queda en runs/.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H27"/>
+  <autoFilter ref="A1:H79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5834,7 +9194,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-431</v>
+        <v>-432</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -5980,7 +9340,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -6122,7 +9482,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -6387,7 +9747,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-185</v>
+        <v>-186</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -6779,7 +10139,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -6917,7 +10277,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -7051,7 +10411,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -7181,7 +10541,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -7311,7 +10671,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -8469,37 +11829,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="52" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="52" customWidth="1" min="27" max="27"/>
+    <col width="52" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8644,8 +12004,4620 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>F-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Contratos Rio Hortega (ISCIII, Accion Estrategica en Salud)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Instituto de Salud Carlos III (ISCIII) - AES</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Espana; el contrato se ejecuta en un centro asistencial de titularidad publica del SNS. Sin restriccion de nacionalidad; los titulos de especialidad extranjeros deben estar ya homologados (no vale la solicitud de homologacion en tramite).</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA y la solicita el centro, no ella. Necesita un jefe de grupo vinculado a un centro asistencial publico del SNS. Cupos por centro (AES 2026, art. 33.3): centros de un IIS, 14 solicitudes y 8 concesiones; otros centros asistenciales, 8 y 4. Un jefe de grupo con un Rio Hortega AES-2025 activo no puede solicitar. Hay que ganar antes una preseleccion interna: empezar la conversacion en otono de 2026.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>30000 el primer ano + 35000 el segundo (bruto, AES 2026), para quienes hicieron una FSE de mas de tres anos, que es su caso (Laboratorio Clinico, 4 anos). La cuota patronal la asume el centro.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2 anos</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>NO APLICA: no exige doctorado. El reloj es el de la residencia (haber terminado la FSE en 2021 o despues, incluidos quienes la terminen durante el ano de la convocatoria).</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Art. 34 AES 2026, literal: '1o. Estar en posesion del titulo oficial de Especialidad Medica (MIR), Farmaceutica (FIR), o del certificado oficial de especialidad en Biologia (BIR), Quimica (QIR), Bioquimica, Psicologia (PIR), Enfermeria (EIR) o Radiofisica Hospitalaria (RIR).' Y '2o. Haber finalizado el programa de FSE ... durante el ano 2021, o en fecha posterior, incluyendo a los que lo hagan en 2026, siempre que sea con anterioridad a la fecha que se establezca para la finalizacion del plazo de alegaciones a la resolucion provisional de concesion.' NO se menciona el titulo de doctor en ningun punto de los arts. 31-36. No haber disfrutado ya un Rio Hortega.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>EL HALLAZGO PRINCIPAL DE ESTA PASADA: Rio Hortega no exige doctorado en ningun momento, asi que su defensa prevista para febrero de 2028 es irrelevante para la elegibilidad, y el unico reloj que cuenta -el de la residencia- corre a su favor. Comprobado punto por punto: (a) titulo de especialista: termina Laboratorio Clinico en el Hospital Regional Universitario de Malaga el 22-05-2027, asi que para la AES 2027 (plazo previsto ~5 de marzo de 2027) entraria en el grupo de 'los que lo hagan en 2027', y el 22-05-2027 cae holgadamente antes del plazo de alegaciones de la resolucion provisional, que historicamente es en otono del ano de la convocatoria; puede por tanto solicitar SIENDO AUN RESIDENTE, unos tres meses antes de acabar. (b) Ventana FSE: terminar en 2027 la mantiene elegible desde la AES 2027 hasta aproximadamente la AES 2031, asi que fallar un ano no es fatal. (c) No hay regla de movilidad, ni recuento de publicaciones, ni doctorado. (d) Su expediente de publicaciones, hoy flojo, pesa aqui menos que en cualquier esquema basado en el doctorado, porque se evalua el proyecto y el perfil de clinica investigadora junto a los meritos. LINEA CON LA QUE ENCABEZAR: genetica estadistica de rasgos complejos reformulada para un servicio de laboratorio - un plan de formacion sobre puntuaciones de riesgo poligenico e interpretacion genomica clinica dentro de un servicio de genetica o laboratorio hospitalario se lee como investigacion traslacional para los evaluadores del ISCIII y ademas alimenta su segundo carril, la nueva especialidad de Genetica Medica y de Laboratorio. GWAS/PRS en psiquiatria es el segundo encuadre; la genetica del sueno infantil es el que peor encaja en un laboratorio hospitalario. VALOR ESTRATEGICO MAS ALLA DEL DINERO: completar un Rio Hortega es una puerta explicita en las propias bases de la AES - Juan Rodes (art. 51.2o) y Miguel Servet (art. 46.1, que levanta el techo de fecha de tesis para quienes completaron Rio Hortega o Sara Borrell). Es el unico punto de entrada que mantiene abiertos a la vez el carril investigador y el carril sanitario publico, porque el contrato obliga a simultanear actividad asistencial en su especialidad. CUELLO DE BOTELLA: la acogida. Solicita el hospital y hay cupo por centro. TRABAJO: memoria en plantilla normalizada, CVA-ISCIII y documentacion del grupo, 3-7 dias de escritura propia una vez acordada la acogida.</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>No es una tasa nacional: el filtro real es el cupo por centro leido en el art. 33.3 de la AES 2026 (centros de IIS, 14 solicitudes y 8 concesiones). Ganar la plaza interna del hospital es la mayor parte de la batalla.</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Antes de diciembre de 2026: identificar y abordar a un jefe de grupo (IBIMA / Hospital Regional Universitario de Malaga primero, por estar ya alli; una segunda opcion en otro IIS). Cuando aparezca la resolucion AES 2027 en el BOE (previsible en diciembre de 2026), releer el art. 34.2o para confirmar que dice '2022 o posterior, incluyendo a los que lo hagan en 2027' y que la fecha de alegaciones cae despues del 22-05-2027.</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Rama 2. Tier 1: texto integro de la resolucion de la AES 2026 descargado de isciii.es y extraido localmente (las paginas HTML de isciii.es devuelven HTTP 503 al fetch automatico, pero el endpoint del documento si descarga). Plazos en el art. 7.6; condiciones en los arts. 31-34.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Contratos Sara Borrell (ISCIII, Accion Estrategica en Salud)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Instituto de Salud Carlos III (ISCIII) - AES</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Espana; el centro de desarrollo debe tener actividad asistencial salvo el pequeno cupo de Salud Publica.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA y la solicita el centro. El grupo receptor debe ser DISTINTO y estar en un CENTRO DISTINTO de aquel donde hizo la tesis (y, si es un IIS, en otro IIS), salvo que acredite una estancia posdoctoral continuada en el extranjero de al menos un ano. El jefe de grupo debe ser doctor. Cupos: IIS 10 solicitudes / 5 concesiones; otros centros asistenciales 5 / 2.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>30000 en cada una de las dos primeras anualidades + 35000 en la tercera, bruto, 12 pagas, financiado al 100% por el ISCIII (AES 2026)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Hasta 3 anos</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>AES 2026: doctorado (fecha de lectura y aprobacion de la tesis) obtenido despues del 1 de enero de 2022, ampliable por maternidad/paternidad, baja de mas de 3 meses y cuidado de dependientes.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Art. 40.1.a) literal: 'Haber obtenido el doctorado, entendiendose como tal la fecha de lectura y aprobacion de la tesis doctoral, en fecha posterior al 1 de enero de 2022.' El titulo de doctor o certificacion universitaria con la fecha debe presentarse CON la solicitud (art. 41.1.b), asi que en la practica la tesis debe estar leida antes del plazo: Sara Borrell NO admite 'doctorado antes de empezar'. No haber disfrutado ya un Sara Borrell.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>El paso natural despues de Rio Hortega y el mejor contrato posdoctoral puro de Espana para una medica que quiere un centro investigador con cara asistencial. Punto por punto: (a) el doctorado debe estar leido antes del plazo: con una ETA de febrero de 2028, la AES 2028 (plazo ~5 de marzo de 2028) va al filo y depende de que la defensa ocurra de verdad en febrero y de que la certificacion se emita a tiempo; lo realista es apuntar a la AES 2029, donde una defensa de febrero de 2028 queda comodamente dentro de la ventana. (b) Despues sigue elegible hasta aproximadamente la AES 2032, o sea cuatro intentos reales y no uno. (c) La residencia no estorba: acaba el 22-05-2027, mucho antes de cualquier solicitud. (d) La regla de cambio de grupo le resulta facil: su tesis es de la Universidad de Murcia, asi que cualquier grupo de Malaga, Madrid, Barcelona, Valencia o Granada la cumple sin necesidad de la exencion del ano en el extranjero (sus estancias de Australia y Japon son de ~3 meses cada una y NO servirian para esa exencion). LINEA CON LA QUE ENCABEZAR: GWAS/PRS de trastornos psiquiatricos y de salud mental, porque Sara Borrell se evalua en un instituto de investigacion sanitaria y la genomica psiquiatrica con angulo de traslacion clinica (estratificacion de riesgo, biomarcadores via un servicio de laboratorio) juega a la vez con su titulo de medicina y con sus pipelines de PLINK/R. NO encabezar con neuroimagen ni electrofisiologia: a nivel supervisado seria sobrevenderse en una convocatoria competitiva. TRABAJO: memoria normalizada, CVA-ISCIII y documentacion del grupo, comparable a Rio Hortega pero con mucho mas peso de las publicaciones, que es hoy su punto debil - conseguir que acepten los dos manuscritos antes de solicitar es la preparacion de mayor valor.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Cupos por centro leidos en el art. 39.3 de la AES 2026 (IIS: 10 solicitudes / 5 concesiones) y baremo con fuerte peso curricular para su etapa.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Aparcar hasta 2027. El punto de decision es si la defensa de febrero de 2028 cae antes del plazo de la AES 2028 (~5 de marzo de 2028): pedir al director de tesis a mediados de 2027 que fije la fecha, porque defender en febrero o en abril de 2028 la mueve un ano entero en este esquema. Mientras tanto, empujar los dos manuscritos hasta la aceptacion.</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Rama 2. Tier 1: resolucion AES 2026, arts. 37-41 y art. 7.6, leidos en el texto completo extraido del PDF oficial del ISCIII.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Contratos Miguel Servet (ISCIII, Accion Estrategica en Salud)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Instituto de Salud Carlos III (ISCIII) - AES</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Espana; institutos y centros de investigacion sanitaria con actividad asistencial</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: solicita el centro y debe comprometerse a crear una plaza estable (art. 85.1 Ley 14/2007).</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5 anos</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>AES 2026: tesis leida entre el 1 de enero de 2014 y el 31 de diciembre de 2021, con una EXCEPCION relevante para ella: 'Cuando se trate de personas candidatas que hayan completado el programa de formacion en investigacion Rio Hortega o Sara Borrell, o que se encuentren en el segundo o tercer ano de estos contratos respectivamente, la fecha de lectura de la tesis podra ser posterior a 2021.'</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Inelegible para ella durante aproximadamente una decada por la via ordinaria (la tesis debe ser anterior a 2022), pero completar un Rio Hortega o un Sara Borrell levanta por completo ese techo de fecha.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Se registra como destino de la escalera del clinico investigador espanol, no como convocatoria que pueda solicitar: con una tesis de febrero de 2028 queda muy fuera de la ventana ordinaria y su unica via realista de entrada es la excepcion de Rio Hortega / Sara Borrell, que es precisamente el motivo estrategico para tomar un Rio Hortega en 2027.</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Esquema de consolidacion con compromiso de plaza estable y pocas concesiones nacionales.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Ninguna ahora. Revisar en 2030-2031 si completa un Rio Hortega o un Sara Borrell.</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Rama 2. Tier 1: resolucion AES 2026, art. 46 y art. 7.6. Importes no extraidos en esta pasada: no citarlos sin releer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ayudas para contratos Juan de la Cierva (JDC) 2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Agencia Estatal de Investigacion (AEI) - MICIU</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Espana; centros de I+D espanoles, sin restriccion de nacionalidad</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: un centro de I+D espanol solicita con candidata nominada y linea/tutor de investigacion. La ventana de solicitud dura menos de cuatro semanas, asi que la conversacion con el centro corresponde al verano previo.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2 anos</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Segun fuentes secundarias: doctorado en posesion en el momento de la solicitud, obtenido como maximo 3 anos antes de la fecha de cierre. SIN VERIFICAR.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>DOCTORADO YA CONCEDIDO EN LA FECHA LIMITE, explicitamente no 'en tramite de defensa'. Ventana de recencia de tres anos contada hacia atras desde el cierre. Es por tanto inelegible en las ediciones de 2026 y 2027.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>El contrato posdoctoral temprano por defecto en Espana y un encaje real con su investigacion, pero el reloj descarta las ediciones proximas: con defensa en febrero de 2028 no puede tocar ni la convocatoria de 2026 ni la de 2027, y su primer intento es la JDC 2028 (convocatoria ~noviembre de 2028), donde una defensa de febrero de 2028 cae comodamente dentro de una ventana de recencia de tres anos. Despues sigue elegible hasta aproximadamente la edicion de 2030. Punto por punto: (a) doctorado en la fecha limite: falla hasta 2028, pasa desde 2028; (b) la residencia es irrelevante, acaba el 22-05-2027; (c) no hay regla de movilidad tipo MSCA, asi que las fechas sin fijar de sus estancias de Australia y Japon no importan aqui; (d) ciudadania de la UE y base espanola eliminan cualquier obstaculo administrativo. LINEA CON LA QUE ENCABEZAR: genetica estadistica de rasgos complejos, porque la JDC la evaluan paneles de la AEI donde dominan la solidez metodologica y la trayectoria del grupo de acogida, asi que un proyecto intensivo en PLINK/R con un grupo espanol fuerte de genetica estadistica o genomica (CNAG, CRG, ISGlobal, grupos de genetica psiquiatrica de CIBERSAM) es el encuadre mas potente; GWAS/PRS psiquiatrico es la capa de aplicacion natural. RIESGO A VIGILAR: la AEI ha reestructurado el esquema mas de una vez, asi que esta fila hay que reverificarla cada otono, no reutilizarla.</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>500 contratos nacionales en todas las areas para 2026 segun fuentes secundarias; las tasas de exito historicas en el panel biomedico estan muy por debajo del 25% (sin verificar).</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>La duena debe abrir https://www.aei.gob.es/convocatorias/buscador-convocatorias en un navegador (el sitio bloquea el fetch automatico con HTTP 503) y confirmar las fechas de la JDC 2026 y la redaccion exacta sobre la fecha del doctorado, que es la que gobernara su intento de 2028.</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>https://www.aei.gob.es/convocatorias/buscador-convocatorias</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Rama 2. Solo Tier 2: paginas de oficinas de investigacion y agregadores espanoles (FIBAO, OTRI UMH, tesify) que coinciden en el calendario AEI 2026 (12 nov - 3 dic 2026). Las paginas propias de la AEI, incluido el 'Calendario previsto de convocatorias', devolvieron 503.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ayudas para contratos Ramon y Cajal (RYC) 2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Agencia Estatal de Investigacion (AEI) - MICIU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Espana; centros de I+D y universidades espanolas, sin restriccion de nacionalidad</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: un centro espanol avala la solicitud y, en el modelo de 2026, recibe un incentivo por crear una plaza estable.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>38270 al ano en la primera fase segun fuentes secundarias; presupuesto total de la convocatoria 132346140 para 494 contratos</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Hasta 5 anos, mas incentivo a la creacion de plaza estable</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No leida en esta pasada. Historicamente una banda de varios anos (aproximadamente 2-10 antes del cierre, con prorrogas). NO fiarse de ese dato hasta leer las bases de 2026.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Exige doctorado. La edicion de 2026 introduce, segun fuentes secundarias, una entrevista con las comisiones tecnicas de la AEI y financia ademas un proyecto liderado por la solicitante. Regla exacta de fecha de doctorado sin verificar.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>La puerta de entrada a la carrera estable en Espana y el final del carril academico que dice querer, pero es un esquema para quien ya tiene trayectoria independiente, no para una recien doctorada. Punto por punto: (a) exige doctorado leido antes del cierre, asi que 2026 y 2027 quedan fuera; (b) incluso desde 2028 estaria en el ultimo escalon del grupo de candidatos, compitiendo con gente con 4-8 anos de produccion posdoctoral, y su expediente actual (dos manuscritos en revision, ningun articulo destacado) no sobreviviria al baremo curricular; (c) la entrada realista es hacia 2031-2033, despues de un Rio Hortega/Sara Borrell o de un posdoc internacional. LINEA CON LA QUE ENCABEZAR cuando llegue el momento: un programa propio de genetica estadistica, ya que la reforma de 2026 financia el proyecto de la IP y eso favorece una linea metodologicamente distintiva frente a una prestada. Se registra ahora porque el calendario (noviembre-diciembre cada ano) es estable y conviene que conozca el esquema al planificar los anos posdoctorales, no porque sea accionable.</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>494 contratos nacionales en todas las areas; la edicion de 2026 anade fase de entrevista.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Ninguna ahora. Reverificar la ventana de fecha de doctorado en otono de 2028, cuando decida entre un posdoc espanol y salir fuera.</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>https://www.aei.gob.es/convocatorias/buscador-convocatorias/ayudas-contratos-ramon-cajal-ryc-2026</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Rama 2. URL tomada de un listado de resultados (pagina propia de la AEI para RYC 2026); no se pudo abrir (HTTP 503). Cifras de paginas secundarias de oficinas de investigacion y de noticias del MICIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Postdoctoral Junior Leader - modalidad Retaining</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fundacion la Caixa</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cualquier nacionalidad; la investigacion se realiza en una universidad o centro de investigacion de Espana o Portugal. La modalidad Retaining admite cualquier centro acreditado, a diferencia de Incoming, restringida a centros Severo Ochoa / Maria de Maeztu, institutos de investigacion sanitaria Carlos III y unidades portuguesas de excelencia.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: un centro de acogida en Espana o Portugal debe aceptar el proyecto. Una candidatura seria son 2-4 semanas de escritura mas preparacion de entrevista.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Hasta 320100 en total por ayuda (segun fuentes secundarias)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Hasta 3 anos</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Doctorado obtenido entre dos y siete anos antes del cierre de la convocatoria, contando la fecha de lectura de la tesis; prorrogas en supuestos tasados.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>DOCTORADO YA CONCEDIDO en la fecha de cierre y con al menos dos anos de antiguedad: el esquema excluye por diseno a las recien doctoradas. Retaining exige ademas estancias de investigacion fuera de Espana que sumen AL MENOS SEIS MESES durante el doctorado o el posdoctorado, completadas antes del cierre. 20 Retaining + 20 Incoming al ano.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>La via mejor dotada para volver a Espana liderando linea propia, y la modalidad que le corresponde es Retaining, no Incoming, porque esta basada en Espana y pretende quedarse o volver. Punto por punto: (a) doctorado de 2 a 7 anos al cierre: con defensa en febrero de 2028, su primera edicion elegible es la que cierre despues de febrero de 2030, es decir la convocatoria Retaining de 2031, y su ventana sigue abierta hasta aproximadamente 2035; nada anterior merece un minuto. (b) LA REGLA DE LOS SEIS MESES EN EL EXTRANJERO ES EL PUNTO CRITICO Y NO ESTA RESUELTO: sus estancias en QIMR Berghofer y en Japon son de unos tres meses cada una, o sea justo en la linea de los seis meses, y como las fechas exactas no estan fijadas esto queda en LIKELY y no en VERIFIED. Si se queda por debajo de seis meses, una tercera estancia de tres meses antes de 2030 lo arregla para siempre y es barata de organizar a traves del contacto que ya tiene en QIMR. (c) Ciudadania de la UE y centro espanol: ningun problema de permisos. LINEA CON LA QUE ENCABEZAR: genetica estadistica de rasgos complejos con aplicacion en genomica psiquiatrica, acogida en un centro genomico (CNAG, CRG, ISGlobal) o en un instituto de investigacion sanitaria; los paneles de la Caixa premian un proyecto independiente bien acotado y la exposicion internacional, asi que la colaboracion australiana y el manuscrito de Nature Mental Health son los activos a poner delante. LA ACCION DE ESTE ANO ES CERO: esta fila existe para que el recuento de los seis meses se arregle ahora, que todavia es barato.</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>20 ayudas Retaining al ano para todas las disciplinas STEM de Espana y Portugal.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Dos cosas, ambas baratas: (1) fijar las fechas exactas de inicio y fin de las estancias de QIMR Berghofer y Japon y comprobar si suman seis meses - este unico dato condiciona la Caixa Retaining y varios esquemas mas con baremo de movilidad; (2) la duena debe abrir las bases oficiales en un navegador (lacaixafoundation.org bloquea el fetch automatico con 403) para confirmar la fecha de cierre de la Retaining 2027.</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>https://lacaixafoundation.org/en/postdoctoral-junior-leader-fellowships-retaining-call</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Rama 2. Tier 2: paginas de anuncio de centros de acogida (CLPU, Institut de Recerca Sant Joan de Deu) que reproducen las condiciones de la Retaining 2027. Marcada CLOSED porque, aunque la edicion en curso siga abierta para el mundo (cierre estimado 23-09-2026), esta cerrada PARA ELLA hasta 2031: la convencion del repositorio es que una convocatoria de la que no es elegible se registra como cerrada y se explica aqui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HFSP Postdoctoral Fellowships (Long-Term Fellowship, LTF)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Human Frontier Science Program (HFSP)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cualquier nacionalidad y cualquier pais de acogida EXCEPTO el propio pais de nacionalidad y el pais donde obtuvo el doctorado o donde trabajo mas de 12 meses. Para ella: Espana excluida, todo lo demas abierto (UE/EEE, EE. UU., Australia, Japon, Canada).</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA y anterior a la carta de intencion: la LOI nombra el laboratorio de acogida y necesita el acuerdo del anfitrion y un proyecto escrito conjuntamente. En la practica, de 3 a 6 meses de contacto previo; empezar a buscar acogida unos 12 meses antes de la LOI.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>No publicado en las paginas leidas: 'Living Allowance + Research and Travel Allowance' variables por pais de acogida, mas complementos por hijos, parentales y de mudanza. Una fuente secundaria cita ~60000 USD/ano: SIN VERIFICAR, no citarlo.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3 anos (36 meses), no renovable</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>'Applicants are not eligible if the doctoral degree has been conferred more than 3 years (36 months) prior to the submission deadline of the Full Proposal', con exenciones por enfermedad, permisos parentales, cuidados y servicio militar. No hay minimo: se admite un doctorado aun no concedido.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>EL PUNTO DECISIVO: el doctorado NO tiene que estar concedido en la fecha limite. Literal de hfsp.org: 'The applicant must have completed their PhD or a comparable doctoral degree with equivalent research experience (for instance, an MD, medical PhD, or DEng) before starting the fellowship, and before 31 December 2027 at the latest' (fecha que se desplaza un ano por cada ano de convocatoria), y no se exige doctorado completado en el momento de la carta de intencion. Ademas: el proyecto debe suponer un cambio real de direccion investigadora hacia una pregunta interdisciplinar de frontera. LTF es la via para quien tiene doctorado en ciencias de la vida; CDF es para doctorados en fisica/matematicas/informatica con poca experiencia biologica, que no es su caso.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>El buque insignia cuyo reloj SI encaja con el suyo, y por eso es la pieza central del plan de 2027. Solicitar a la convocatoria del ano 2028 significa una LOI hacia mayo de 2027 -el mismo mes en que acaba la residencia, el 22-05-2027-, propuesta completa hacia septiembre de 2027, decision hacia marzo de 2028 (un mes despues de su defensa prevista) y activacion entre abril de 2028 y enero de 2029, con el doctorado exigido solo antes de empezar y antes del 31 de diciembre de 2028. Todos sus relojes pasan: no hace falta doctorado al presentar, no hay minimo posdoctoral, y el tope de 3 anos se cumple trivialmente porque el titulo ni siquiera estara concedido en la fecha limite. LINEA CON LA QUE ENCABEZAR: genetica estadistica de rasgos complejos reformulada como problema de frontera en un laboratorio que NO sea principalmente de genetica estadistica; HFSP premia entrar en territorio nuevo y penaliza la continuidad con la tesis, asi que el discurso es 'medica + genetica estadistica que se mueve hacia X' (genomica funcional o de celula unica, neurobiologia del sueno, neurociencia computacional), no 'mas GWAS'. Su combinacion MD+PhD y las estancias de QIMR y Japon son justo la evidencia interdisciplinar que HFSP busca. SU DEBILIDAD REAL es el expediente de publicaciones: dos manuscritos de primera autora en revision, y conseguir que ambos se acepten antes de septiembre de 2027 cambia materialmente la solicitud. Elegibilidad punto por punto: nacionalidad espanola -&gt; acogida fuera de Espana; doctorado espanol -&gt; Espana tambien excluida por esa via; las dos estancias de ~3 meses estan holgadamente por debajo del tope acumulado de 12 meses, asi que Australia y Japon siguen siendo paises de acogida validos, pero conviene fijar las fechas exactas antes de contar con ello. TRABAJO: alto (L), identificacion de acogida y proyecto co-escrito, 2-4 semanas de escritura concentrada sobre meses de cortejo; el filtro real es la LOI.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Esquema global con doble filtro LOI/propuesta completa y tasas de exito historicamente de un digito; tasa exacta no publicada en las paginas leidas.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>De aqui a la primavera de 2027: preseleccionar de 3 a 5 laboratorios de acogida en el extranjero que representen un cambio real de campo y abrir contacto como muy tarde en enero de 2027. Revisar hfsp.org en marzo de 2027 para las fechas de la LOI del ano 2028.</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>https://www.hfsp.org/funding/hfsp-funding/postdoctoral-fellowships</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Ramas 1 y 5 (fusionadas). Tier 1: pagina de hfsp.org y PDF oficial 'HFSP Fellowships 2027 - Application Guidelines'. CONFLICTO REGISTRADO: la lectura automatica de ese PDF devolvio 'A PhD or equivalent doctorate is required at the time of application', que contradice la pagina web y una segunda fuente independiente. La fila sigue la pagina web, pero la duena deberia leer ella misma las bases del ano 2028 antes de comprometerse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EMBO Postdoctoral Fellowships</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EMBO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Laboratorio de acogida en un Estado miembro de la EMBC, cualquier nacionalidad. Destinos fuera de la EMBC (EE. UU., Canada, Australia) solo si se cumplen las tres: nacionalidad de un Estado EMBC + doctorado obtenido en un Estado EMBC + traslado desde un Estado EMBC. Ella es espanola con doctorado espanol, asi que esa via tambien le queda abierta.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: el laboratorio de acogida y un proyecto conjunto forman parte de la solicitud, y solo se admite UNA candidatura por laboratorio de acogida y ronda, asi que hay que asegurar el anfitrion y confirmar que no presenta a otra persona esa ronda. De 3 a 6 meses de preparacion.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2027-01-22</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>151</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>No publicado en las paginas leidas: salario o estipendio, ayuda de mudanza y apoyo para becarias con hijos, con tarifas por pais en un documento de Contract Rates que no se abrio.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Hasta 2 anos</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>'Applicants must hold a doctorate or equivalent at the start of the fellowship'; si ya se tiene el doctorado al solicitar, debe haberse obtenido en los dos anos anteriores a la fecha de solicitud. Excepciones por interrupcion de carrera con aprobacion previa de la Fellowships Office.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>EL PUNTO DECISIVO: el doctorado se exige solo AL EMPEZAR la beca, no en la fecha limite; el FAQ de EMBO dice que se puede solicitar durante el doctorado y 'you must provide us with your PhD degree before the starting date of your fellowship'. SEGUNDA restriccion decisiva: la beca debe iniciarse 'within 9 months of the offer', y eso es lo que fija de verdad su ventana. TERCERA: al menos un articulo de PRIMERA AUTORA aceptado o publicado en revista internacional revisada por pares en el momento de solicitar (vale un preprint de primera autora con revisiones independientes verificables) - hoy NO lo cumple. Movilidad: nada en el laboratorio/instituto/departamento de la tesis, ni volver con el director de tesis este donde este, ni continuar el trabajo doctoral; cambio de pais obligatorio, asi que Espana queda excluida. Desde la ronda de otono de 2027 (solicitudes posteriores al 22-01-2027) ya no se permite volver a solicitar: un solo intento.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>El instrumento mejor emparejado para un traslado europeo despues de una defensa en febrero de 2028, y sorprendentemente indulgente con el reloj del doctorado: puede solicitar antes de defender. La regla de los 9 meses para incorporarse fija la sincronizacion con precision: una solicitud en el corte de ~julio de 2027 se resolveria hacia noviembre de 2027 y tendria que empezar hacia agosto de 2028, lo que abraza comodamente una defensa de febrero de 2028; una solicitud en el corte del 22-01-2027 se resolveria en primavera de 2027 y caducaria a principios de 2028, demasiado justo para una ETA que puede deslizarse. El objetivo es por tanto el corte de mediados de 2027, con el de enero de 2028 como alternativa. EL BLOQUEO REAL NO ES EL RELOJ SINO LAS PUBLICACIONES: EMBO exige un articulo de primera autora ACEPTADO al presentar, y los dos suyos (revision en Journal of Sleep Research; articulo empirico en Nature Mental Health) siguen en revision. Si ninguno se acepta antes de mediados de 2027 es inelegible, sin matices, asi que perseguir esas decisiones es la accion de mayor valor aqui. LINEA CON LA QUE ENCABEZAR: el trabajo de genetica psiquiatrica derivado de QIMR y la genetica estadistica de rasgos complejos, eligiendo acogida en un entorno molecular, celular o genomico donde ella aporte el lado cuantitativo; el centro de gravedad de EMBO son las ciencias de la vida moleculares, asi que un proyecto puramente epidemiologico de GWAS se lee fuera de mision y necesita un gancho mecanicistico. TRABAJO: L, sobre todo cortejo de acogida mas descripcion conjunta del proyecto. La regla de un solo intento obliga a no quemarlo en un emparejamiento debil.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Esquema europeo prestigioso de larga trayectoria con la exigencia de publicacion de primera autora como prefiltro; tasa de exito no publicada en las paginas leidas.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Vigilar la aceptacion de los dos manuscritos de primera autora: son el elemento que condiciona todo. En paralelo, desde principios de 2027 abordar laboratorios de acogida en Estados EMBC (una candidata por laboratorio y ronda, asi que hay que confirmar que nadie mas de ese laboratorio se presenta). Revisar embo.org hacia marzo de 2027 para el corte exacto de mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>https://www.embo.org/funding/fellowships-grants-and-career-support/postdoctoral-fellowships/eligibility/</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Rama 1. Tier 1: paginas de elegibilidad, FAQ y presentacion de las becas posdoctorales de embo.org, leidas el 2026-08-23. La fecha proyectada del corte de mediados de 2027 es LIKELY, no confirmada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MSCA Postdoctoral Fellowships (European Fellowship; variante Global)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Comision Europea - Horizonte Europa, Marie Sklodowska-Curie Actions</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Acogida en un Estado miembro de la UE o pais asociado a Horizonte Europa; las Global Fellowships anaden una fase de salida a un tercer pais (por ejemplo Australia o Japon) con retorno obligatorio a Europa. Cualquier nacionalidad.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: una MSCA-PF se escribe conjuntamente con un supervisor y una entidad beneficiaria que deben comprometerse antes de presentar. Las buenas acogidas se llenan entre 6 y 9 meses antes del plazo de septiembre y muchas universidades hacen preseleccion interna con plazos en primavera.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>No publicado en las paginas de la CE leidas (asignaciones de manutencion, movilidad, familia, investigacion y gestion como costes unitarios corregidos por pais). No citar cifras sin consultar el Portal de Financiacion y Licitaciones.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>European Fellowships 1-2 anos; Global Fellowships 2-3 anos incluida la fase de retorno</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>'Maximum of eight years experience in research, from the date of the award of their PhD degree'; no cuentan el tiempo fuera de la investigacion, las interrupciones de carrera ni los anos de investigacion en terceros paises para nacionales de la UE que se reincorporan a Europa.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>EL PUNTO DECISIVO, Y VA EN SU CONTRA: el doctorado debe estar en su poder EN LA FECHA LIMITE de la convocatoria, no al empezar. La pagina de la MSCA dice que las candidatas 'should have a PhD degree at the time of the deadline for applications. Applicants who have successfully defended their doctoral thesis but who have not yet formally been awarded the doctoral degree will also be considered eligible to apply'. Con una defensa prevista para febrero de 2028 falla el plazo del 09-09-2026 y el del 08-09-2027, y ni siquiera puede acogerse a la concesion de 'defendida pero no expedida', porque no habra defendido en septiembre de 2027. Movilidad: no haber residido ni ejercido su actividad principal en el pais de la beneficiaria mas de 12 meses en los 36 anteriores al plazo.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>El instrumento le encaja casi perfectamente -ciudadana de la UE, perfil MD+PhD, una linea computacional portatil que cualquier acogida europea puede absorber y una beca de 1-2 anos que podria empezar en 2029- pero la regla del doctorado en la fecha limite hace inalcanzables las dos convocatorias que quedan de Horizonte Europa, y ESE ES EL HALLAZGO MAS IMPORTANTE DE ESTA RAMA. Su primera opcion es una convocatoria de 2028 bajo el programa que suceda a Horizonte Europa (que termina en 2027), asi que el esquema es para planificar, no para solicitar: el riesgo a senalar no es su elegibilidad en 2028 (una defensa en febrero de 2028 supera con margen un plazo de septiembre de 2028, e incluso un retraso de varios meses seguiria pasando) sino si el programa sucesor mantiene el instrumento con el mismo ritmo anual. Sobre movilidad, comprobado punto por punto: ha vivido en Malaga de forma continuada desde el 22-05-2023 salvo dos estancias de ~3 meses, asi que en cualquier ventana de 36 meses que termine en un plazo de 2028 su residencia espanola supera de largo los 12 meses; LA REGLA DE MOVILIDAD DESCARTA DE FACTO UNA ACOGIDA ESPANOLA y deja bien cualquier otro pais de la UE o asociado. Como las dos estancias fueron de solo ~3 meses, tampoco descalifican a Australia ni a Japon como acogida de salida de una Global Fellowship, pero como las fechas exactas no estan fijadas toda esta valoracion de movilidad es LIKELY, no VERIFIED. LINEA CON LA QUE ENCABEZAR: genetica estadistica de rasgos complejos y la linea de GWAS/PRS psiquiatrico, eligiendo una acogida cuyo entorno ERC o de consorcio pueda absorber a una clinica genetista. TRABAJO: pesado (L), propuesta completa de Horizonte Europa mas compromiso de acogida, pero es trabajo de 2028. Registrada como CLOSED porque la convocatoria de 2026 sigue abierta al mundo hasta el 09-09-2026 pero esta cerrada PARA ELLA.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>399,05 millones de euros para ~1600 ayudas en la convocatoria de 2026 frente a un grupo de solicitantes historicamente mucho mayor (en torno a una de cada siete en ediciones recientes, sin verificar).</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Ninguna accion posible antes de 2028. En 2027, vigilar el programa de trabajo del programa sucesor y si la MSCA-PF sobrevive con la misma forma; mientras tanto, fijar los meses exactos de las estancias de QIMR y Japon para poder elevar el calculo de movilidad a VERIFIED. No construir una relacion de acogida sobre la suposicion de que una solicitud en 2027 es posible.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/actions/postdoctoral-fellowships</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Rama 1. Tier 1: pagina de la accion MSCA (redaccion de elegibilidad), noticia de la convocatoria 2026 (fechas, presupuesto, ~1600 ayudas) y pagina de la convocatoria 2027, con las fechas marcadas TBC por la propia MSCA. Que 2027 sea la ultima convocatoria de este marco financiero procede de una fuente secundaria y NO esta confirmado en la pagina de la MSCA: tratar como LIKELY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Humboldt Research Fellowship for Postdoctoral Researchers</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Alexander von Humboldt Foundation (Alemania)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Investigadoras de cualquier nacionalidad procedentes del extranjero; la investigacion se realiza en Alemania.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: un anfitrion aleman debe confirmar la acogida y co-desarrollar el plan de investigacion antes de presentar. Humboldt espera un compromiso sustantivo, no una carta de formulario.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3000 al mes mas complementos (segun fuentes secundarias)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>De 6 a 24 meses</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Doctorado completado hace menos de cuatro anos en la fecha de solicitud (segun fuentes secundarias).</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>DOCTORADO EXIGIDO AL SOLICITAR: el reloj de cuatro anos corre del doctorado a la fecha de solicitud, asi que no se puede presentar una tesis sin defender. Ademas, regla de residencia: quien viene del extranjero debe haber vivido fuera de Alemania al menos 12 meses en total durante los 18 anteriores a la presentacion. Sin plazo fijo; el comite de seleccion se reune en marzo, julio y noviembre.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Un plazo rodante es especialmente valioso para alguien cuya fecha de defensa es una estimacion: no tiene que acertar una ventana, solicita cuando la tesis este de verdad terminada. Punto por punto: (a) doctorado al solicitar: elegible desde su defensa (ETA febrero de 2028) hasta aproximadamente febrero de 2032, una pista de cuatro anos que absorbe cualquier retraso, que es exactamente la propiedad que necesita; (b) la regla de 12 de los ultimos 18 meses fuera de Alemania se cumple trivialmente -ha estado en Espana todo el tiempo, con estancias cortas en Australia y Japon-, asi que, a diferencia de las reglas tipo MSCA, esta se puede puntuar sin conocer sus fechas exactas; (c) ciudadania de la UE, sin problema de visado. LINEA CON LA QUE ENCABEZAR: GWAS/PRS de trastornos psiquiatricos, porque la capacidad alemana en genetica psiquiatrica (Instituto Central de Salud Mental de Mannheim, MPI de Psiquiatria de Munich, Bonn) es un hogar natural para su segunda linea y una fuente realista de un anfitrion que co-escriba el plan; la genetica estadistica de rasgos complejos es el encuadre metodologico. EL PROBLEMA: Humboldt puntua con fuerza el expediente de publicaciones y la posicion cientifica independiente, hoy su dimension mas debil, asi que los dos manuscritos deben estar aceptados antes de solicitar. La duracion de 6-24 meses la convierte en un puente mas que en un puesto de carrera, lo que encaja bien con un primer movimiento al extranjero despues de la residencia y la tesis. TRABAJO: M, 1-2 semanas una vez acordada la acogida.</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Esquema de prestigio con tres rondas de seleccion al ano en todas las disciplinas; tasa de exito no leida en esta pasada.</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Verificar en humboldt-foundation.de en una pasada posterior si el reloj de cuatro anos se cuenta desde la fecha de solicitud o desde el inicio de la beca, y si las candidatas espanolas MD+PhD necesitan el acuerdo de acogida ya al presentar. No urgente antes de mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>https://www.humboldt-foundation.de/en/apply/sponsorship-programmes/humboldt-research-fellowship</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Rama 2. Agregacion Tier 2 (base de datos de becas del DAAD, Max Planck Society, DAAD Norteamerica) coherente entre fuentes, pero la pagina propia de la fundacion aun debe leerse una vez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DFG Walter Benjamin Programme</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Deutsche Forschungsgemeinschaft (DFG)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Abierto con independencia de la nacionalidad segun las reglas de la DFG; la beca puede disfrutarse en una institucion de Alemania o del extranjero.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: hay que identificar institucion y persona de acogida, y no haber trabajado en esa institucion mas de un ano en el momento de solicitar.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Habitualmente hasta 2 anos (no verificado en esta pasada)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No publica un numero fijo de anos: exige doctorado completado y estar en la fase posdoctoral temprana de cualificacion.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Doctorado EXIGIDO al solicitar; fase posdoctoral temprana; no haber trabajado en la institucion de acogida elegida mas de un ano. Como la DFG no publica techo numerico de anos posdoctorales, una defensa en febrero de 2028 no acarrea riesgo de reloj, algo poco habitual y util.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>La otra opcion alemana rodante, y la mas flexible de las dos: sin plazo y sin techo publicado de anos posdoctorales, su fecha de defensa incierta no le cuesta nada, y la beca puede incluso disfrutarse fuera de Alemania. Punto por punto: (a) exige doctorado, asi que la bloquea hasta febrero de 2028 y luego se abre sin caducidad dura; (b) la regla del ano en la institucion de acogida le es irrelevante, no tiene vinculacion alemana; (c) ciudadania de la UE, sin permisos; (d) el fin de la residencia en mayo de 2027 le deja nueve meses limpios de preparacion. LINEA CON LA QUE ENCABEZAR: genetica estadistica de rasgos complejos formulada como proyecto propio e independiente - Walter Benjamin financia el plan de investigacion de la solicitante y no el proyecto de un anfitrion, lo que encaja con quien elige deliberadamente una linea en vez de sumarse a otra, y le permite escribir ella misma la aplicacion a genomica psiquiatrica. La evaluacion de la DFG es una revision cientifica completa de la propuesta, asi que se escribe mas pesado que Humboldt (2-4 semanas) y lo que la sostiene es la calidad de la propuesta y no solo el CV, lo que en su caso ayuda dado un expediente de publicaciones fino. Util sobre todo como alternativa si se le pasa el reloj de cuatro anos de Humboldt o una ronda del comite.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Revision individual por pares, sin cupo; tasa de exito no leida en esta pasada.</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Leer https://www.dfg.de/resource/blob/168116/50-10-en.pdf en una pasada posterior para la redaccion exacta de elegibilidad, las tarifas y si las solicitantes no residentes en Alemania necesitan anfitrion aleman ya al presentar.</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>https://www.dfg.de/en/research-funding/funding-opportunities/programmes/individual/walter-benjamin</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Rama 2. URLs Tier 1 identificadas (pagina del programa, FAQ, PDF de bases) pero el contenido se leyo por resumenes secundarios en esta pasada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Wellcome Early-Career Awards</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Wellcome Trust (Reino Unido)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>La institucion de acogida debe estar en el Reino Unido, la Republica de Irlanda o un pais de renta baja o media elegible (excluidas India y China continental). La nacionalidad no es en si una barrera, pero un puesto en el Reino Unido implica patrocinio de visado para una no britanica.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: una institucion de acogida elegible debe avalar la solicitud y garantizar el entorno de investigacion; Wellcome espera que se comprometa con su transicion a la independencia. Meses de conversacion previa.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Salario de la beneficiaria mas hasta 400000 GBP de gastos de investigacion (segun fuentes secundarias); no convertido a euros</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Hasta 5 anos</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Se informa de hasta tres anos de experiencia posdoctoral al solicitar, con margen por interrupciones, jornada parcial y cambios de disciplina. CONFLICTO A SENALAR: algunas fuentes describen una via de 'doctorado (viva superado) O al menos cuatro anos de experiencia investigadora', y otras una ventana de 5-10 anos posdoctorales; esta ultima corresponde casi con seguridad a los Career Development Awards, un esquema distinto y posterior. Verificar en wellcome.org.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>La via estandar parece exigir el doctorado (viva superado) al solicitar, es decir concedido en la fecha limite y no al empezar; pero ESTE ES JUSTO EL PUNTO QUE NO SE PUDO VERIFICAR, porque wellcome.org devuelve HTTP 403 al fetch automatico. Rondas multiples al ano: la de julio de 2026 cerro el 21-07-2026 (una fuente dice el 22, conflicto sin resolver) y las siguientes se situan hacia el 10-11-2026 y el 06-04-2027.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>La opcion britanica mas fuerte para ella, y aquella cuya geografia coincide con donde vive de verdad su campo: KCL/SGDP, el MRC Centre for Neuropsychiatric Genetics and Genomics de Cardiff y Edimburgo son los tres nucleos europeos de genetica psiquiatrica y los tres son acogidas elegibles por Wellcome. Punto por punto: (a) si el techo de tres anos posdoctorales es correcto, su ventana va de la defensa de febrero de 2028 a aproximadamente febrero de 2031 - estrecha, y es la unica ventana donde la incertidumbre de su fecha de defensa muerde de verdad, porque un retraso a finales de 2028 desplaza todas las rondas; (b) la residencia acaba el 22-05-2027, sin choque; (c) como ciudadana de la UE necesita patrocinio de visado britanico, que las universidades elegibles tramitan de forma rutinaria (Global Talent o Skilled Worker): es una senal, no un bloqueo; (d) el problema profundo no es la elegibilidad sino la competitividad, porque estos premios esperan a alguien que ya parezca una futura lider independiente, y con dos manuscritos en revision todavia no lo parece. LINEA CON LA QUE ENCABEZAR: GWAS/PRS de trastornos psiquiatricos y de salud mental, sin ambiguedad - es la linea que se corresponde con los nucleos britanicos, donde sus competencias de PLINK/R son directamente desplegables, y la prioridad de salud mental de Wellcome la hace financiable; su titulo de medicina es un diferenciador real en un campo dominado por no clinicos. PLAN REALISTA: un posdoc ordinario en uno de esos nucleos desde 2028 y despues una candidatura desde dentro.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Esquema insignia de inicio de carrera de Wellcome, abierto internacionalmente a candidaturas acogidas en Reino Unido, Irlanda o paises de renta baja/media; tasas historicas en el mejor de los casos de dos digitos bajos (sin verificar).</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>La duena debe abrir https://wellcome.org/research-funding/schemes/early-career-awards en un navegador y resolver dos cosas: si el doctorado se exige en la fecha limite o solo al empezar, y el techo exacto de experiencia posdoctoral. Es el dato que decide si su entrada es la ronda de noviembre de 2027 o las de mediados de 2028.</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>https://wellcome.org/research-funding/schemes/early-career-awards</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Ramas 2 y 5 (fusionadas). Solo Tier 2, y las fuentes se contradicen entre si sobre la ventana de elegibilidad: se registra el conflicto en vez de resolverlo. wellcome.org es un bloqueo 403 confirmado para el fetch automatico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MRC Early Independence: Career Development Fellowship</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Medical Research Council (MRC) / UKRI</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Hay que estar en una organizacion de investigacion britanica elegible; las no britanicas necesitan patrocinio de visado de la acogida.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: aval y sede en una organizacion de investigacion britanica elegible, con un plan de investigacion independiente que no se solape significativamente con el del supervisor o jefe de grupo actual.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>No leida en esta pasada (historicamente unos 5 anos)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>El MRC no fija numero de anos posdoctorales ni limite de edad: la elegibilidad se juzga por la evidencia de progresion y de estar lista para la independencia, con doctorado (o cualificacion/experiencia equivalente) exigido.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Doctorado o equivalente exigido; plan independiente y acogida britanica. La ausencia de techo numerico posdoctoral significa que su defensa de febrero de 2028 no crea un corte duro, pero el liston que lo sustituye -independencia demostrada- no lo alcanzara hasta varios anos despues del doctorado. La ronda de 2026 cerraba el 15-09-2026.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Merece registro porque el marco reestructurado de becas del MRC no tiene techo de anos posdoctorales, algo raro que elimina el riesgo de reloj que su fecha de defensa incierta crea en otros sitios, pero lo cambia por un liston que no puede superar ni en 2026 ni en 2028. Punto por punto: (a) exige doctorado, fuera hasta febrero de 2028; (b) exige acogida britanica, asi que solo se vuelve real si antes hace un posdoc en KCL, Cardiff o Edimburgo, que es el mismo camino que implica Wellcome; (c) necesita patrocinio de visado como ciudadana de la UE, algo rutinario en las universidades britanicas; (d) el plazo del 15-09-2026 le es irrelevante y se registra solo para establecer la cadencia anual. LINEA CON LA QUE ENCABEZAR cuando aplique: genomica psiquiatrica con angulo de traslacion clinica, porque el MRC valora el perfil de clinica cientifica y su titulo de medicina mas la especialidad de Laboratorio Clinico son un diferenciador real en un grupo britanico de candidatas. Nota adicional para su perfil clinico: el MRC tiene vias separadas de Clinical Research Training Fellowship pensadas para clinicos que entran en investigacion, pero son de intencion predoctoral o doctoral y ella ya ha pasado ese punto.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Principal beca de independencia temprana del MRC, una ronda al ano, competencia nacional.</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Releer https://www.ukri.org/opportunity/early-independence-career-development-fellowship/ en 2028 para la ronda vigente entonces; hasta que este basada en el Reino Unido esto es contexto, no objetivo.</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/early-independence-career-development-fellowship/</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Rama 2. URL Tier 1 identificada en ukri.org; contenido leido por resumenes de resultados de busqueda en esta pasada. Registrada CLOSED porque la ronda de 2026 esta cerrada para ella por elegibilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F-0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NIH Pathway to Independence Award (K99/R00), con participacion del NIMH</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>National Institutes of Health (EE. UU.); NIMH entre los institutos participantes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sin requisito de ciudadania para las candidatas K99; la fase K99 se disfruta en una institucion estadounidense, asi que hace falta visado de trabajo.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: debe ocupar ya un puesto posdoctoral tutelado en una institucion de EE. UU. con mentor nominado; la fase R00 se traslada despues a un puesto de facultad independiente.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Hasta 5 anos (K99 tutelada hasta 2 anos + R00 independiente hasta 3)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Normalmente no mas de 4 anos de experiencia posdoctoral en la solicitud inicial (hubo una prorroga temporal del NIH para ventanas que terminaban entre octubre de 2024 y enero de 2026). No reverificado para el anuncio vigente.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Exige doctorado. A diferencia del F32, NO hay requisito de ciudadania para las candidatas K99: este es el hallazgo que mantiene a EE. UU. sobre la mesa. La puerta real es otra: debe ser ya posdoc en una institucion estadounidense al solicitar, y el techo de ~4 anos posdoctorales obliga a solicitar pronto dentro de ese posdoc.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>La unica via estadounidense realista para ella, y conviene conocerla ya porque cambia como secuenciaria un traslado a EE. UU. mas que ser algo a lo que se solicita en frio. Punto por punto: (a) exige doctorado, desde febrero de 2028; (b) sin barrera de ciudadania, que es lo que mantiene viva la opcion estadounidense; (c) primero debe conseguir un posdoc en EE. UU. con patrocinio de visado (J-1 o H-1B), que es el trabajo de verdad, y despues solicitar dentro de los dos primeros anos, porque el techo de ~4 anos posdoctorales se cuenta desde el inicio de la experiencia posdoctoral, o sea que sus anos posdoctorales espanoles o europeos contarian en contra: el traslado a EE. UU. debe ser temprano, no tardio; (d) el fin de la residencia en mayo de 2027 y la defensa en febrero de 2028 hacen viable un inicio estadounidense en 2028-2029. LINEA CON LA QUE ENCABEZAR: genetica estadistica y genomica psiquiatrica en un centro con masa critica (Broad, Mount Sinai, UNC y la orbita del PGC); su manuscrito de Nature Mental Health del proyecto de QIMR es la credencial a poner delante y su titulo de medicina se lee bien frente a las prioridades traslacionales del NIMH. TRABAJO: pesado (L), plan completo de desarrollo de carrera mas plan de investigacion, 3-4 semanas, pero se escribe desde dentro del laboratorio de acogida y con apoyo. SENAL: las condiciones de la financiacion federal estadounidense han sido volatiles, asi que hay que verificar que el mecanismo sigue existiendo antes de planificar sobre el.</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Mecanismo de transicion de carrera de todo el NIH; las tasas varian mucho por instituto y no se leyeron en esta pasada.</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Si un posdoc estadounidense se vuelve opcion viva en 2028, leer el anuncio matriz vigente en grants.nih.gov y confirmar (a) que la clausula de ciudadania sigue igual y (b) como trata el reloj de experiencia posdoctoral el tiempo posdoctoral fuera de EE. UU.</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>https://grants.nih.gov/grants/guide/pa-files/PA-24-194.html</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Rama 2. Guias secundarias Tier 2 que remiten al anuncio matriz PA-24-194 y a la participacion del NIMH; el numero de anuncio procede de esas fuentes y debe reverificarse, porque el NIH los reedita ciclicamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F-0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NIH Ruth L. Kirschstein NRSA Postdoctoral Fellowship (F32)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>National Institutes of Health (EE. UU.), incl. NIMH</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>EE. UU., y restringida por ciudadania</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: institucion patrocinadora estadounidense y mentor nominado.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Hasta 3 anos</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Posdoctorado temprano; no leida, porque la regla de ciudadania es dirimente.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>En el momento de la concesion hay que ser ciudadana estadounidense, nacional no ciudadana o residente permanente legal. Ella es ciudadana espanola sin residencia permanente en EE. UU.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inelegible: el F32 exige ciudadania o residencia permanente estadounidense en el momento de la concesion, algo que ningun patrocinio de visado sustituye; se registra para que no vuelva a redescubrirse.</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>No evaluada: no puede solicitar.</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Ninguna. No volver a sacarla salvo que cambie su situacion de residencia.</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>https://researchtraining.nih.gov/programs/fellowships/F32</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Rama 2. Resumenes Tier 2 del anuncio matriz del NIH F32; la clausula de ciudadania es antigua y estable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>F-0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NHMRC Investigator Grants - Emerging Leadership (EL1)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>National Health and Medical Research Council (Australia)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Australia: la ayuda se disfruta en una Administering Institution australiana; una no residente necesitaria patrocinio de visado de esa institucion.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: una Administering Institution australiana elegible (por ejemplo QIMR Berghofer) debe presentar la solicitud por ella. Las beneficiarias EL1/EL2 pueden pasar hasta el 50% de la duracion en el extranjero, pero el ultimo ano debe cumplirse en Australia. Los datos minimos vencen casi un mes antes de la solicitud completa.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>5 anos</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>La categoria Emerging Leadership se limita a 10 anos o menos desde el doctorado (o equivalente), con subniveles EL1 y EL2 y ajustes relativos a la oportunidad.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Exige doctorado y el reloj corre desde el: una defensa en febrero de 2028 abre una ventana hasta aproximadamente 2038, inusualmente generosa. Las restricciones que atan son institucionales, no temporales: debe presentar una Administering Institution australiana y el ultimo ano debe cumplirse en Australia.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Australia sigue en la lista sobre todo porque tiene alli una via humana viva -la estancia en QIMR Berghofer le da un contacto que puede asesorar sobre una candidatura y potencialmente acogerla- y no porque el esquema convenga a una recien doctorada. Punto por punto: (a) 10 anos o menos desde el doctorado es la ventana mas ancha de toda esta rama, asi que desde febrero de 2028 es elegible durante una decada y la incertidumbre de la ETA no le cuesta nada; (b) necesita que una institucion australiana presente por ella, y como las Investigator Grants financian a una persona y su programa, una candidatura recien salida del doctorado se puntuaria frente a EL1 consolidadas con mucha mas produccion: lo realista es 2030 o mas tarde, despues de un posdoc; (c) como no residente necesita patrocinio de visado, y la regla del ultimo ano en Australia significa que debe querer estar alli de verdad; (d) importante: el NHMRC ya no tiene becas posdoctorales independientes -las antiguas de inicio de carrera se fundieron en las Investigator Grants EL1-, asi que esta fila es todo el carril NHMRC australiano, no una opcion entre varias. LINEA CON LA QUE ENCABEZAR: GWAS/PRS de trastornos psiquiatricos, acogida en la orbita de epidemiologia genetica de QIMR Berghofer donde nacio su manuscrito de Nature Mental Health; ese manuscrito mas una relacion de supervision existente es la unica credencial australiana que tiene, y es real.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Esquema insignia de apoyo a personas de Australia, competencia nacional en toda la investigacion sanitaria; EL1 es la categoria mas concurrida.</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Barato y de alto valor: usar el contacto de QIMR Berghofer para preguntar que necesitaria de verdad una candidatura EL1 de una MD-PhD basada en Europa, y si QIMR consideraria administrarla. Revisar las fechas de la ronda en abril de 2027 en nhmrc.gov.au.</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>https://www.nhmrc.gov.au/funding/find-funding/investigator-grants</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Ramas 2 y 5 (fusionadas). Tier 2: PDFs de bases del NHMRC alojados por oficinas de investigacion australianas (UQ, Macquarie) y la pagina del esquema resumida por busqueda; el PDF de bases de 2027 no se abrio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>F-0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BBRF Young Investigator Grant (antes NARSAD Young Investigator)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Brain and Behavior Research Foundation (BBRF)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Mundial, literal de las bases de 2026: 'Funds will be granted to universities, institutions or medical research centers operating in the United States, Canada, or any foreign country. All international applicants are welcome to apply. Researchers need not be U.S. citizens.' Una institucion espanola o europea vale, y no hay visado de por medio.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA y en forma especifica: debe estar ya empleada en un puesto de formacion investigadora o de facultad Y contar con 'an on-site mentor or senior collaborator who is an established investigator in areas relevant to psychiatric disorders'. El mentor debe estar en el mismo centro, asi que el puesto posdoctoral tiene que existir antes: es una ayuda para llevar A un puesto, no para crearlo.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>35000 USD al ano hasta dos anos, es decir 70000 USD en total (literal de las bases de 2026; no convertido a euros)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Hasta 2 anos</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No hay limite numerico publicado de anos desde el doctorado: la ventana se define por rango - 'The YI Grant is intended to support advanced post-doctoral fellows, instructors and assistant professors (or equivalent)'. Quedan excluidas por abajo las predoctorales y las posdoctorales de primer ano, y por arriba las profesoras asociadas o quien haya sido IP de un R01 del NIH o equivalente.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>EL PUNTO DECISIVO: el titulo de doctorado debe estar ya en su poder al solicitar - 'Applicants must have a doctoral level degree (e.g., M.D. with minimum PGY-IV training, Ph.D., Psy.D., Pharm.D., etc.) and already be employed in research training or a faculty research position.' Es crucial que EL TITULO DE MEDICINA CUENTA como doctorado cualificante siempre que tenga al menos formacion PGY-IV, cosa que alcanza durante su residencia (iniciada el 22-05-2023), asi que aqui la puerta no es estrictamente el doctorado sino EL PUESTO INVESTIGADOR. Exige ademas mentor en el propio centro y que la investigacion sea relevante para trastornos cerebrales y del comportamiento graves.</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Cientificamente es el encaje mas proximo de toda esta rama con su linea 2: GWAS/PRS de trastornos psiquiatricos y de salud mental es exactamente el ambito de la BBRF, y el manuscrito de Nature Mental Health del proyecto de QIMR es la pieza con la que encabezar. Es ademas el raro buque insignia sin restriccion de nacionalidad ni de geografia y con una solicitud modesta y escribible (S-M: plan corto, carta del mentor, portada; nada parecido a una MSCA o una HFSP), y 70000 dolares discrecionales son palanca real para un proyecto computacional que apenas necesita mas que computo y su tiempo. EL BLOQUEO ES LA ETAPA DE CARRERA, NO EL CALENDARIO: exige doctorado en mano y empleo actual en un puesto de formacion investigadora o de facultad, y excluye explicitamente a las posdoctorales de primer ano. Punto por punto: no puede solicitar en la ronda de marzo de 2027 porque seguira siendo residente hasta el 22-05-2027 y no estara empleada en un puesto investigador; el caso limite interesante es la ronda de marzo de 2028, cuando ya tendra el titulo de medicina con formacion muy por encima de PGY-IV y, SI ha pasado a un puesto de formacion investigadora desde mediados de 2027, la via del MD significa que no necesitaria que la defensa de febrero de 2028 hubiera ocurrido - aunque 'advanced post-doctoral fellow' es forzado para quien lleva meses en su primer puesto, y los revisores lo leen de forma literal. El objetivo realista es la ronda de 2029, ya como posdoc de segundo ano con un mentor consolidado de genetica psiquiatrica en el mismo centro.</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>La BBRF concedio 165 Young Investigator Grants en una ronda reciente frente a un grupo internacional amplio; la fundacion advierte de capacidad limitada de revision y no da retroalimentacion. Tasa exacta sin verificar.</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Nada que presentar antes de 2028. Tratarla como la primera ayuda a escribir en cuanto tenga un posdoc con mentor de psiquiatria en el mismo centro, y releer las bases cada enero (el texto de elegibilidad se reedita anualmente). Merece la pena preguntar a la BBRF por correo si una MD con PGY-IV o mas en un primer ano de puesto investigador cuenta como 'advanced post-doctoral fellow'.</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>https://bbrfoundation.org/grants-prizes/bbrf-young-investigator-grants</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Rama 1. Tier 1: pagina de ayudas de la BBRF mas el PDF oficial '2026 BBRF YOUNG INVESTIGATOR GRANT Application Guidelines'; el fetch automatico no pudo leer el PDF (es un form-XObject), asi que se descomprimio y se leyo localmente y las citas son literales del documento del financiador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>F-0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ERC Starting Grant</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>European Research Council (Horizonte Europa / sucesor)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Institucion de acogida en un Estado miembro de la UE o pais asociado; cualquier nacionalidad.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: una institucion debe comprometerse formalmente a acogerla como IP independiente, lo que en la practica presupone trayectoria posdoctoral y a menudo una oferta de plaza. Inalcanzable desde una residencia o un primer ano posdoctoral.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Hasta 1500000 en 5 anos, mas hasta 1000000 adicional justificado (o hasta 2000000 para IP que se trasladan desde terceros paises no asociados); 100% de costes directos mas 25% indirectos</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>5 anos</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>La pagina del ERC indica ahora '0-10 years of experience since completion of PhD', contados desde 'the certified date of the successful PhD defence', con prorrogas por permisos parentales, enfermedad, servicio nacional, FORMACION CLINICA, catastrofes, asilo y violencia de genero.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Exige doctorado y una trayectoria que la acredite como IP independiente. Con una defensa en febrero de 2028 y sin periodo minimo posdoctoral bajo la regla actual de 0-10 anos seria formalmente elegible desde la convocatoria ERC-2029 y hasta aproximadamente 2038, y sus anos de formacion clinica espanola son ademas causa admitida de prorroga.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>No es una opcion en anos -financia a IP independientes con institucion de acogida y expediente de publicaciones de primera linea, y no tiene ninguna de las dos cosas- pero el reloj merece quedar registrado: seria formalmente elegible desde la convocatoria de 2029 y su formacion clinica cuenta como motivo de prorroga encima de eso.</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Las Starting Grants se mueven en torno a una de cada siete u ocho segun panel (sin verificar en esta pasada).</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Nada antes de 2029. Reverificar la ventana de elegibilidad (2-7 frente a 0-10 anos) cuando este a dos anos de solicitar: la respuesta cambia a que convocatorias puede entrar.</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>https://erc.europa.eu/apply-grant/starting-grant</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Rama 1. Pagina Tier 1 leida directamente, pero la afirmacion de 0-10 anos contradice la ventana historica publicada de 2-7 anos para Starting Grant: se registra como conflicto y no se resuelve. Confirmar en el Information for Applicants de la convocatoria antes de fiarse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>F-0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FENS/IBRO-PERC Exchange Fellowships</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SHORT_STAY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Federation of European Neuroscience Societies (FENS) + IBRO Pan-Europe Regional Committee</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Laboratorio de origen y de acogida ambos en Europa; el intercambio DEBE cruzar una frontera nacional. Candidatas con base en Espana elegibles.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SI: carta de aceptacion del laboratorio de acogida al presentar, mas carta de recomendacion del laboratorio de origen. Calcular de 3 a 6 semanas para conseguir ambas antes del 15 de octubre.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>52</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>hasta 4000</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>De 4 semanas a 4 meses (mas solo con cofinanciacion documentada)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>NO APLICA: admite predoctorales. Estudiantes de master o doctorado en neurociencia, o posdoctorales dentro de los 5 anos desde el inicio del posdoc.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Estudiante de master o doctorado en neurociencia, o posdoc temprana (menos de 5 anos). Debe ser miembro de una sociedad miembro de FENS (en Espana: SENC), miembro individual de FENS, o de una organizacion de IBRO en la region Pan-Europe. Carta de acogida y recomendacion de origen. Pago 60% antes / 40% tras el informe.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ABIERTA PARA ELLA AHORA MISMO como estudiante de doctorado: es la unica ayuda de toda esta pasada con un plazo vivo que puede cumplir. Encabezar con la linea 3 (genetica del sueno infantil) o con la linea 2 (GWAS/PRS de trastornos psiquiatricos) reformulada como neurociencia, y plantear la visita como adquisicion de metodo, que es justo lo que el programa premia y lo que su CV sostiene con honestidad: sus competencias de neuroimagen, neurociencia computacional y electrofisiologia son de nivel supervisado, asi que 'ir a aprender la tecnica X en un laboratorio europeo' es una solicitud veraz y bien fundamentada, no un estiramiento. Acogidas naturales: CTG en la VU de Amsterdam, SGDP en KCL, iPSYCH en Aarhus, NORMENT en Oslo - todos grupos de genetica estadistica de su campo y todos fuera de Espana, con lo que se cumple la regla de cambio de pais. Punto por punto: (a) no exige doctorado, asi que la ETA de febrero de 2028 es irrelevante; (b) no hay ventana de anos posdoctorales; (c) ciudadana de la UE, estancia intraeuropea, sin visado; (d) LA RESTRICCION REAL es el minimo de 4 semanas frente a la residencia de Malaga, que corre hasta el 22-05-2027: o negocia una rotacion externa o permiso (los programas de residencia espanoles admiten rotaciones externas, tipicamente de 1 a 3 meses, con visto bueno del tutor y del hospital) o coloca la estancia despues del 22-05-2027, lo que sigue siendo alcanzable en la ronda del 15 de abril de 2027. TRABAJO: S - CV, plan de proyecto y acogida de 1-2 paginas, dos cartas. La membresia en SENC o la individual de FENS debe estar hecha ANTES de solicitar: tratarlo como tarea previa, no como detalle.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>MEDIUM-LOW</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Esquema de movilidad intraeuropea de poca cuantia con dos rondas al ano y una lista publicada de beneficiarias de tamano modesto; no se publica tasa de exito, asi que esto es una inferencia por volumen de concesiones y no una cifra declarada.</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Antes del 15-10-2026: confirmar u obtener la membresia de SENC o la individual de FENS, escribir a 2 o 3 PI candidatos para la carta de aceptacion, y decidir si la estancia es una rotacion externa de la residencia (necesita visto bueno del tutor, conviene empezar esa conversacion ya) o una estancia posterior al 22-05-2027 solicitada en la ronda del 15 de abril de 2027.</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>https://www.fens.org/careers/grants-and-stipends/grant/fens-ibro-perc-exchange-fellowships</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Rama 4. Tier 1: pagina propia de la ayuda en fens.org leida el 2026-08-23; plazo corroborado por una noticia de FENS y por el anuncio de la Swiss Society for Neuroscience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>F-0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EMBO Scientific Exchange Grants</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SHORT_STAY</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EMBO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>El laboratorio de origen debe estar en un Estado miembro de la EMBC (Espana vale) o en un socio global EMBC/EMBO (Chile, India, Singapur, Taiwan) o en un laboratorio financiado por JST en Japon; el de acogida igual. NO vale entre dos laboratorios del mismo pais. Australia NO es destino elegible, asi que esto no puede financiar una vuelta a QIMR.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SI en la practica: el intercambio es entre dos laboratorios nominados y el de acogida debe aceptar recibirla; calcular de 2 a 4 semanas. La pagina de elegibilidad de EMBO no detalla un documento formal de invitacion, asi que el papeleo exacto queda sin confirmar.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Variable: viaje mas dieta diaria segun las tablas publicadas por EMBO (cifras concretas no leidas en esta pasada)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Hasta 3 meses</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>NO APLICA: cualquier etapa de carrera con al menos un ano de experiencia investigadora de posgrado, asi que las doctorandas entran.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Investigadora en activo en cualquier etapa con un ano o mas de experiencia investigadora de posgrado. No financia cursos, talleres ni simposios. No disponible cuando los dos laboratorios ya tienen proyectos conjuntos, copublicaciones o un intercambio previo. Debe volver al laboratorio de origen inmediatamente despues y permanecer alli al menos 6 meses consecutivos.</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>ABIERTA PARA ELLA AHORA: 'any career stage with at least one year of graduate-level research experience' cubre explicitamente a una doctoranda, y al ser rodante no hay plazo que perder. Es el instrumento mas flexible de todo el rastreador para su situacion actual. Encabezar con la linea 1 (genetica estadistica de rasgos complejos) y plantear la visita como adquisicion de un metodo que hoy no ejecuta de forma independiente -seguimiento de genomica funcional de hallazgos de GWAS, o pipelines de genetica de imagen-, lo que es honesto dado su nivel supervisado en neuroimagen y electrofisiologia. Punto por punto: (a) no exige doctorado, la ETA de febrero de 2028 es irrelevante; (b) sin ventana posdoctoral; (c) ciudadana de la UE, y los destinos elegibles son la UE/EMBC mas Chile, India, Singapur, Taiwan y Japon con financiacion JST - su laboratorio japones anterior podria ser acogida si esta financiado por JST, mientras que su relacion con QIMR no sirve aqui porque Australia queda fuera; (d) la residencia hasta el 22-05-2027 es la restriccion que ata: el maximo de 3 meses es inusable, pero no hay minimo declarado, asi que lo realista es una estancia de 2 a 4 semanas planificada como rotacion externa. La obligacion de volver y quedarse 6 meses se cumple trivialmente porque esta anclada en Malaga. TRABAJO: S - propuesta corta, CV y datos de la acogida; la exclusion por copublicacion previa obliga a elegir un laboratorio con el que NO haya publicado.</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Esquema rodante de poca cuantia sin tasa de exito publicada; historicamente los instrumentos cortos de EMBO son de los mas alcanzables, pero es una inferencia y no una cifra del financiador.</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Abrir los dos PDF de EMBO que no se leyeron (SEG_guidelines_for_applicants.pdf y SEG_subsistence_rates_and_travel_allowance.pdf) para fijar los importes por dia, la estancia minima y el papeleo de acogida; en paralelo, preseleccionar una acogida en un pais EMBC distinto de Espana y sin copublicacion previa.</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>https://www.embo.org/funding/fellowships-grants-and-career-support/scientific-exchange-grants/eligibility/</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Rama 4. Tier 1: paginas propias del esquema y de elegibilidad de EMBO leidas el 2026-08-23. Importes deliberadamente sin cuantificar en vez de inventados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>F-0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Boehringer Ingelheim Fonds (BIF) Travel Grants</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SHORT_STAY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Boehringer Ingelheim Fonds</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ciudadanas europeas que trabajan en Europa Y en ultramar (mas no europeas que trabajan en Europa). Es el UNICO instrumento hallado en esta pasada que podria financiar una vuelta a QIMR Berghofer, Australia.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SI: financia una estancia en un laboratorio de acogida nominado (o un curso practico), asi que el anfitrion debe haber aceptado antes de solicitar; el conjunto exacto de documentos no se pudo verificar (la URL de 'how to apply' devolvio 404).</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Cantidad a tanto alzado para viaje, alojamiento y matricula de cursos (techo exacto sin verificar); no cubre gastos de manutencion, transporte local, visado ni seguro.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Hasta 3 meses</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>NO APLICA: estudiantes de medicina, doctorandas durante la tesis y posdoctorales.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Debe estar desarrollando un proyecto EXPERIMENTAL de investigacion biomedica BASICA. Excluidos explicitamente: investigacion aplicada (diagnostico, desarrollo biotecnologico o farmaceutico) y estudios sobre el curso de las enfermedades o el tratamiento de sintomas. No sirve para completar financiacion insuficiente ni para duplicar una estancia ya financiada. Debe llegar como muy tarde 6 semanas antes, y no antes de 6 meses antes, de la fecha de salida prevista.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Abierta para ella ahora como doctoranda, rodante, y unica capaz de financiar una vuelta a QIMR Berghofer, donde ya tiene relacion y un articulo de Nature Mental Health en revision surgido de ese proyecto: esa combinacion es la razon de que este aqui pese a un riesgo real de encaje tematico. EL RIESGO: BIF financia 'proyectos experimentales de investigacion biomedica basica' y excluye explicitamente los estudios sobre el curso de las enfermedades. Un estudio de GWAS/PRS de un trastorno psiquiatrico puede leerse como investigacion del curso de la enfermedad ante un revisor; su linea de genetica del sueno infantil, planteada como elucidacion de un fenomeno biologico basico del desarrollo humano, es el encuadre mas seguro, y una estancia planteada como aprendizaje de una tecnica experimental (seguimiento funcional de laboratorio, o la electrofisiologia que solo ha hecho supervisada) lo es todavia mas que una visita puramente computacional. Punto por punto: (a) no exige doctorado, la ETA de febrero de 2028 es irrelevante; (b) ciudadana de la UE que trabaja en Europa, claramente elegible, y el destino en ultramar esta permitido; (c) Australia necesita visado, que BIF NO cubre y que debe presupuestar aparte; (d) la residencia hasta el 22-05-2027 vuelve a limitar la estancia realista a 2-4 semanas en lugar de los 3 meses permitidos, y la ventana de 6 semanas a 6 meses le permite ajustarla con precision a una rotacion aprobada. TRABAJO: S-M, las solicitudes de BIF son mas sustanciales que un formulario de sociedad (descripcion del proyecto, confirmacion de la acogida, referencia del supervisor).</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>La elegibilidad mundial y el prestigio del financiador suben la competencia; no hay tasa de exito publicada especificamente para la linea de travel grants.</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Leer en un navegador las paginas 'who can apply' y FAQ de bifonds.de para confirmar el techo a tanto alzado y los documentos exigidos, y despues sondear a su contacto de QIMR sobre una estancia de 2-4 semanas centrada en metodo, trabajando hacia atras desde la regla de las 6 semanas minimas.</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>https://www.bifonds.de/fellowships-grants/travel-grants.html</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Rama 4. Pagina Tier 1 de resumen leida (ambito de elegibilidad, tope de 3 meses, alcance mundial). La regla de 6 semanas/6 meses, la de ciudadania y la lista de exclusiones proceden de fuentes secundarias coincidentes (base de becas del DAAD, UChicagoGRAD, MESA), de ahi LIKELY y no VERIFIED. La URL /how-to-apply.html devolvio 404.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>F-0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>JSPS Postdoctoral Fellowships for Research in Japan (Standard Program)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Japan Society for the Promotion of Science (JSPS)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Nacionales de cualquier pais con relaciones diplomaticas con Japon (Espana incluida); excluidas las personas japonesas o con residencia permanente. La investigacion se realiza en Japon.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA y sin puerta de entrada por parte de la candidata: hace falta un investigador anfitrion japones asegurado de antemano, y en la via de Open Call la solicitud la presenta a JSPS EL ANFITRION JAPONES a traves del rector o director de su universidad o instituto, no ella.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>362000 JPY/mes de manutencion + 200000 JPY de instalacion + billete de ida y vuelta (~2000-2300 EUR/mes a tipos recientes; la conversion NO esta verificada)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>De 12 a 24 meses</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Doctorado obtenido dentro de los 6 anos, contados desde el 2 de abril de seis anos antes del ejercicio fiscal y evaluados a 1 de abril del ejercicio de la beca; ampliable a prorrata por permisos parentales. La pagina admite ademas a quien 'expects to receive a Ph.D. by the start date'.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>DOCTORADO NO EXIGIDO EN LA FECHA LIMITE. Literal leido en la pagina 'About the Program (Standard)' de JSPS: las candidatas pueden haber 'obtained a doctoral degree within six years' O bien tener previsto 'receive a Ph.D. by the start date'; no se exige certificado del titulo al solicitar, pero si antes de que empiece la beca. Ademas: ser nacional de un pais con relaciones diplomaticas con Japon; el anfitrion debe ser investigador a tiempo completo en una institucion japonesa elegible; las condiciones deben cumplirse a 1 de abril del ejercicio y mantenerse. El plazo del Open Call Standard NO figuraba en las paginas leidas (esta en appliguidelines.html, no abierta).</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>ENCABEZAR CON: las lineas 1 y 2 (genetica estadistica y GWAS/PRS psiquiatrico) como ciencia, y el vinculo japones ya existente como la relacion que hace plausible una acogida. POR QUE ELLA: ya hizo una estancia de ~3 meses en un laboratorio japones de neurociencia, asi que tiene un contacto vivo dentro de la unica estructura que puede presentar la solicitud, que es la institucion anfitriona japonesa. La combinacion MD+PhD se lee bien en los departamentos japoneses de acogida, y una posdoctoral de genetica estadistica no le cuesta equipamiento al laboratorio. RELOJES, PUNTO POR PUNTO: (a) doctorado - es el raro esquema cuya propia redaccion admite a quien 'expects to receive a Ph.D. by the start date', asi que una defensa en febrero de 2028 NO impide una solicitud presentada en 2027 para una beca que empiece despues de la defensa; el certificado se debe antes de empezar, que es exactamente el punto de riesgo si la defensa se retrasa. (b) Residencia - atada a Malaga hasta el 22-05-2027, asi que solo sirven inicios desde mediados de 2027, y un inicio posterior a febrero de 2028 es la construccion segura. (c) La ventana de 6 anos le es irrelevante. (d) Nacionalidad - Espana vale, y el visado lo gestiona JSPS como parte de la beca, con lo que el problema habitual de patrocinio fuera de la UE lo resuelve el propio esquema. (e) Sin regla de movilidad tipo MSCA. SALVEDAD HONESTA: su contacto japones es un laboratorio de electrofisiologia y optogenetica, competencias de nivel supervisado que no puede ejecutar sola; o reformula el proyecto como genetica estadistica en un grupo japones de genetica o genomica psiquiatrica (RIKEN CBS, Tokio, Osaka), lo que implica buscar acogida NUEVA, o plantea un proyecto con sabor genetico en el laboratorio que ya conoce. Esa reformulacion es el trabajo real. TRABAJO: M - plan de investigacion acordado con el anfitrion, CV y lista de publicaciones; la carga administrativa recae en la institucion japonesa, no en ella.</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>JSPS no publica ratios en las paginas leidas; el programa Standard es el buque insignia de entrada posdoctoral para todas las disciplinas y todos los paises. Calificado HIGH por alcance, no por una cifra publicada.</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Abrir https://www.jsps.go.jp/english/e-fellow/e-ippan/appliguidelines.html para fijar el plazo del Open Call Standard del ejercicio 2027 y su ventana de inicio; en paralelo, decidir si aborda a su antiguo anfitrion japones o a un grupo japones de genetica estadistica, ya que es el anfitrion quien presenta.</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>https://www.jsps.go.jp/english/e-fellow/e-ippan/index.html</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Rama 3. Tier 1: paginas 'About the Program (Standard)' e indice de solicitud de JSPS, leidas el 2026-08-23. Confirmacion de la via: 'applications must be submitted to JSPS by a host researcher in Japan via the head of their university or institution'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>F-0023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ESHG 2027 - conference fellowships / early career awards</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TRAVEL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>European Society of Human Genetics</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Internacional; sin restriccion de nacionalidad conocida</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NINGUNA: es una ayuda de asistencia a congreso.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2027-02-04</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>164</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Sin verificar; historicamente exencion de matricula mas una aportacion de viaje</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Congreso, 12-15 de junio de 2027, Roterdam (hibrido)</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Investigadoras de inicio de carrera con no mas de 4 anos de experiencia laboral de posgrado; incluye a doctorandas.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Hace falta un resumen enviado; la ayuda se solicita marcando la casilla correspondiente dentro del formulario de envio de resumenes, asi que esa fecha manda. Notificacion del resultado del resumen a principios de abril de 2027.</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>El mejor objetivo de viaje a congreso dentro de su disciplina real y uno que puede preparar como doctoranda. La ESHG es el congreso europeo de genetica humana: la genetica estadistica de rasgos complejos y el GWAS/PRS de trastornos psiquiatricos (sus lineas 1 y 2) son contenido central del programa, y el trabajo derivado de QIMR es material listo. Punto por punto: (a) la elegibilidad es de 4 anos o menos de experiencia de posgrado, que una doctoranda cumple, y su defensa prevista para febrero de 2028 no es barrera; (b) el congreso cae del 12 al 15 de junio de 2027, es decir TRES SEMANAS DESPUES de que acabe la residencia el 22-05-2027, sin necesidad de negociar permiso, lo que lo convierte en el encaje de calendario mas limpio de toda esta rama; (c) Roterdam, UE, sin visado; (d) el plazo de resumenes del 04-02-2027 cae mientras sigue siendo residente, asi que el trabajo es escribir un resumen, no viajar. TRABAJO: XS-S, un resumen y una casilla. Nada que asegurar con una acogida. SALVEDAD: las condiciones concretas de las ayudas de 2027 aun no estan publicadas; el mecanismo y la regla de los 4 anos se infieren de las ediciones de 2025 y 2026.</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>La ESHG concede un numero considerable de ayudas cada ano frente a un grupo amplio de resumenes; sin tasa publicada.</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Revisar 2027.eshg.org en noviembre de 2026 para la pagina de ayudas; redactar el resumen en enero de 2027 y enviarlo antes del 04-02-2027 con la casilla de ayuda marcada.</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>https://2027.eshg.org/abstracts/</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Rama 4. Fechas, sede y plazo de resumenes VERIFICADOS en el sitio de la ESHG 2027. La elegibilidad y el mecanismo de las ayudas se arrastran de las paginas de 2025/2026 via resultados de busqueda: aun sin confirmar para 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>F-0024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Premios L'Oreal-UNESCO For Women in Science Espana (XXI edicion, prevista)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>L'Oreal Espana / UNESCO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Los proyectos deben ejecutarse 'en centros de investigacion de nuestro pais'. La convocatoria leida no exige nacionalidad.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA y de forma inusualmente estricta: 'la investigadora debe contar con un contrato en vigor con el centro de investigacion solicitante tanto en el momento de presentar la candidatura como durante la ejecucion del proyecto'. La entidad solicitante es el centro de investigacion.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>15000 por premio (cinco premios)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Proyecto ejecutado en los dos anos naturales siguientes</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Ninguna declarada. El reloj que ata es de edad: menores de 40 anos. El texto publicado de la convocatoria no dice que se exija doctorado.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>DOCTORADO NO DECLARADO COMO REQUISITO en el texto leido: las condiciones que filtran son ser menor de 40, un proyecto en Ciencias de la Vida y Medioambiente (que incluye explicitamente 'genetica, fisiologia, neurociencia') y un CONTRATO EN VIGOR con el centro de investigacion solicitante, tanto al presentar como durante la ejecucion. Las bases legales completas no se abrieron, asi que la ausencia de requisito de doctorado es una lectura del anuncio, no del articulado.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>ENCABEZAR CON: la linea 1 (genetica estadistica de rasgos complejos) presentada como genetica y neurociencia - la lista de areas elegibles nombra 'genetica' y 'neurociencia' de forma literal, y un proyecto de PRS sobre rasgos psiquiatricos con encuadre de impacto social (salud mental en jovenes) es exactamente la forma que premia este jurado. POR QUE ELLA: mujer menor de 40 en Espana, en un area explicitamente elegible, con un perfil MD+PhD que resulta distintivo ante un jurado no especialista; y es uno de los poquisimos esquemas que no parece exigir el doctorado en mano, algo que importa enormemente con una ETA de febrero de 2028. Punto por punto: (a) doctorado no exigido segun el texto, asi que en principio podria presentarse en la edicion de noviembre de 2026 o en la de noviembre de 2027, es decir ANOS antes de que se abra ninguna otra fila de esta rama; (b) menor de 40, holgadamente; (c) la residencia en Espana hasta el 22-05-2027 juega a favor y no en contra, porque el proyecto debe ejecutarse en un centro espanol; (d) sin barrera de nacionalidad ni regla de movilidad. LA CONDICION QUE HAY QUE RESOLVER, Y ES TODA LA FILA: necesita un contrato en vigor con el centro solicitante. Su contrato de residencia es con el Hospital Regional Universitario de Malaga y su doctorado esta en la Universidad de Murcia, y si alguno de los dos cuenta como 'el centro de investigacion solicitante' con contrato valido es la unica pregunta que decide la elegibilidad: hay que resolverla con las bases legales y con la oficina de investigacion del centro, no adivinarla. Si el instituto del hospital (IBIMA) o la Universidad de Murcia actuan como solicitante, esta pasa a ser una fila fuerte; si no, es inelegible hasta que tenga contrato posdoctoral. TRABAJO: S-M, propuesta corta, CV y narrativa de impacto social, mas el visto bueno institucional.</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Cinco premios para toda Espana en el conjunto de Ciencias de la Vida y Medioambiente; L'Oreal Espana no publica numero de solicitudes.</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Antes de finales de octubre de 2026: descargar las bases legales de la XX edicion y responder a una pregunta - un contrato MIR de residencia o una matricula de doctorado, satisfacen 'contrato en vigor con el centro de investigacion solicitante'? Preguntar a IBIMA (Malaga) y a la oficina de investigacion de la Universidad de Murcia si alguno actuaria como centro solicitante.</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>https://www.loreal.com/es-es/espana/news/commitment/loreal-unesco-abre-convocatoria-de-premios-for-women-in-science/</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Rama 3. Tier 1: anuncios de L'Oreal Espana de las ediciones XIX (abierta 24-10-2024, cerrada 04-12-2024) y XX (abierta 23-10-2025, cerrada 17-11-2025), leidos el 2026-08-23. Bases legales no abiertas. La XXI edicion se espera hacia finales de octubre de 2026: LIKELY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>F-0025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SRSF Career Development Award</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sleep Research Society Foundation (SRSF)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Mundial: 'qualified applications will be reviewed for US and non-US residents'. Las ayudas se conceden a la institucion, no a la persona.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: ayuda tutelada, con uno o dos mentores nominados (no necesariamente especialistas en sueno), y la ayuda se paga a la institucion de acogida, asi que debe tener ya un puesto en algun sitio antes de solicitar.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>hasta 50000 USD (~43000-46000 EUR; conversion NO verificada)</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1 ano (periodo de financiacion de enero a diciembre); sin segundo ano</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Dentro de los 10 anos desde la obtencion del titulo de doctorado. Ojo: la lista de titulos incluye el de medicina, asi que sobre su MD (2019) esa ventana corre hasta 2029, y sobre el doctorado (ETA febrero de 2028) hasta 2038.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>TITULO DE DOCTORADO (O EQUIVALENTE) EXIGIDO Y YA CONCEDIDO AL SOLICITAR: 'Applicants must be early career investigators within 10 years of receiving their doctoral degree' y deben tener 'a doctoral level degree, such as MD, PhD, DO and/or comparable degree'. Ademas: estar en nivel posdoctoral, instructor o profesora ayudante; no tener plaza permanente; no haber tenido financiacion por encima de 75000 USD/ano como IP; y 'Applicants must be an active Sleep Research Society (SRS) member at the time of applying'. La edicion de 2026 cerraba el 23-08-2026.</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>ENCABEZAR CON: la linea 3 (genetica del sueno infantil) - es el unico esquema de esta rama donde su linea peor clasificada es el billete de entrada, y su revision de primera autora en revision en el Journal of Sleep Research es justo la credencial que este publico reconoce. El angulo interesante es que la SRSF cuenta el titulo de medicina como doctorado cualificante, lo que significa que el reloj de 10 anos YA ha empezado para ella (2019) y expira en 2029: no puede esperar al reloj del doctorado. Punto por punto: (a) titulo de doctorado - satisfecho desde 2019 via el MD, asi que, a diferencia de casi todas las filas, la ETA del doctorado no la bloquea; (b) LA ETAPA DE CARRERA ES LO QUE LA BLOQUEA HOY: debe estar 'at the post-doctoral, instructor, or assistant professor level', y hasta mediados de 2027 es residente y doctoranda, que no es un nombramiento posdoctoral; la primera edicion plausible es la de 2027 si para agosto de ese ano ya esta en un posdoc, y comodamente la de 2028; (c) la residencia hasta el 22-05-2027 es compatible, porque un periodo de financiacion de enero a diciembre significa que la edicion de 2027 financiaria el ano natural 2028; (d) sin barrera de nacionalidad ni exigencia de acogida estadounidense, algo inusual en una fundacion de EE. UU. y lo que mantiene viva esta fila. CONDICION A RESOLVER: la membresia de la SRS debe estar activa AL SOLICITAR, y como el dinero va a una institucion necesita a la vez acogida posdoctoral y mentor nominado.</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Hasta cuatro ayudas en todo el mundo por edicion para el conjunto de la investigacion en sueno y ritmos circadianos; sin numero de solicitudes publicado.</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Nada que presentar en esta edicion. Paso concreto ahora: hacerse socia de la Sleep Research Society (la membresia es condicion previa dura y tarda en estar 'activa'), y agendar mediados de mayo de 2027 para la siguiente convocatoria.</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>https://sleepresearchsociety.org/foundation/srsf-career-development-award/</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Rama 3. Tier 1: pagina del premio de la SRSF leida el 2026-08-23. El plazo coincidia con la fecha de esta pasada, asi que se trata como cerrada a efectos de planificacion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>F-0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ESRS grants: Travel Grants, Two-Week Training Grants y Meetings &amp; Courses Fellowships</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SHORT_STAY</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>European Sleep Research Society (ESRS)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Europa (ambito de la ESRS); detalles sin verificar</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Para la ayuda de formacion de dos semanas haria falta que un laboratorio de sueno de acogida aceptase de antemano; condiciones sin verificar.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Dos semanas (ayuda de formacion); asistencia a congresos o cursos en las otras lineas</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Sin verificar</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>La membresia de la ESRS es muy probablemente obligatoria; la elegibilidad de doctorandas no esta confirmada. Nada verificado: esrs.eu devolvio HTTP 403 en las dos rutas probadas.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Se incluye pese a no estar verificada porque la forma del instrumento parece hecha a medida de sus restricciones: una ayuda de formacion de DOS SEMANAS es la unica duracion de estancia que cabe comodamente dentro de una residencia espanola sin rotacion externa formal, y la investigacion del sueno es su linea 3, con una revision ya en consideracion en el Journal of Sleep Research, que es la revista de la ESRS y por tanto una conexion real y comprobable con la que encabezar. Punto por punto: nada de esto exige doctorado terminado, asi que la ETA de febrero de 2028 y el fin de la residencia el 22-05-2027 son en principio compatibles; pero elegibilidad, importes y plazos estan todos sin confirmar. TRABAJO: casi con seguridad S. Tratarla como pista a abrir en un navegador, no como fila verificada, y no dejar que desplace a las filas de FENS/IBRO-PERC y EMBO, que si estan confirmadas.</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>No evaluable: la pagina del financiador es inalcanzable.</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>La duena debe abrir https://esrs.eu/grants-awards/ manualmente en un navegador (el fetch automatico esta bloqueado, 403 en dos rutas distintas) y anotar elegibilidad, importe y plazos; comprobar tambien si la membresia de la ESRS es condicion previa y que deja abierto Sleep Europe 2026 (septiembre de 2026) para 2027-28.</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>https://esrs.eu/grants-awards/</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Ramas 3 y 4 (fusionadas). La existencia de las tres lineas procede de fragmentos de busqueda de las paginas de ayudas de la ESRS; tanto https://esrs.eu/grants-awards/ como https://www.esrs.eu/education-career/grants-awards.html devolvieron 403 al fetch automatico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>F-0027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BGA Student Travel Awards (congreso anual de la Behavior Genetics Association)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TRAVEL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Behavior Genetics Association</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Internacional (la BGA es una sociedad global); sin verificar</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NINGUNA: ayuda de viaje a congreso.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Asistencia al congreso anual</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>NO APLICA: es una ayuda para estudiantes.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Condicion de estudiante; las ayudas se conceden por necesidad percibida y merito academico. El requisito de membresia no esta verificado. Historicamente ligada al ciclo de resumenes del congreso anual, que suele celebrarse en junio.</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>La BGA es la sociedad cuyo ambito coincide con mas exactitud con su tesis -genetica del comportamiento de rasgos complejos, metodologia de gemelos, GWAS y PRS- y la ayuda es explicitamente PARA ESTUDIANTES, asi que le esta abierta ahora, que es justo el sentido de esta rama. Que se concedan en parte por 'necesidad percibida' favorece a una residente autofinanciada sin ninguna ayuda de investigacion detras. Punto por punto: no exige doctorado, asi que la ETA de febrero de 2028 es irrelevante; la restriccion es de calendario y coste, porque los congresos de la BGA suelen ser en junio y a menudo en Norteamerica, lo que despues del 22-05-2027 es viable en tiempo pero anade visado o ESTA y un billete de larga distancia que una pequena ayuda para estudiantes quiza solo cubra en parte. TRABAJO: XS-S, resumen mas una solicitud corta. BLOQUEADO EN ESTA PASADA: bga.org devolvio 403, asi que la sede y las fechas del congreso de 2027 y el importe estan sin verificar.</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>LOW-MEDIUM</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Sociedad pequena, grupo modesto de estudiantes en un unico congreso anual; sin cifras publicadas.</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>La duena debe abrir http://bga.org/student-travel-awards/ y https://bga.org/current-meeting/ en un navegador (403 al fetch automatico) para capturar fechas y sede de 2027, el importe y el plazo.</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>http://bga.org/student-travel-awards/</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Rama 4. La existencia y el criterio de seleccion ('perceived need and scholarly merit') proceden de fragmentos de busqueda de bga.org; la pagina en si es inalcanzable al fetch automatico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>F-0028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BGA Outstanding Associate Member Oral / Poster Presentation Awards</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PRIZE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Behavior Genetics Association (BGA)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Mundial: ligada a la asistencia al congreso anual, no a residencia ni nacionalidad.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NINGUNA: solo membresia asociada de la BGA y un resumen aceptado presentado en persona en el congreso. El coste es matricula mas viaje (la financiacion del viaje es la fila anterior).</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Premio puntual</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Ninguna publicada: la puerta es la membresia asociada, la categoria de estudiante o en formacion de la BGA, que mantiene mientras termina el doctorado y perderia al pasar a miembro de pleno derecho.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Se concede a la mejor comunicacion oral y al mejor poster presentados por una miembro asociada; se juzga en el congreso y no parece haber solicitud separada. Aqui no se plantea la cuestion del doctorado: es precisamente un esquema donde NO tenerlo todavia es la condicion que cualifica.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Pequeno en dinero y prestigio al lado del resto de esta rama, pero es de lo poco para lo que es elegible AHORA MISMO y el esfuerzo por encima de asistir a un congreso al que deberia ir de todas formas es casi nulo: la BGA es la sociedad natural de su tesis y su congreso de 2023 se celebro en Murcia, su propia universidad, asi que la red ya es contigua. El encuadre de solo-asociadas juega a su favor exactamente mientras el doctorado siga sin terminar, es decir hasta la defensa de febrero de 2028, lo que le deja el congreso de 2027 como el tiro limpio. ENCABEZAR CON: el trabajo empirico de genetica psiquiatrica (el envio a Nature Mental Health) mas que con la revision de sueno - una comunicacion oral sobre un analisis de PRS encaja mejor ante un publico de genetica del comportamiento que una revision bibliografica. Su valor real no es el premio sino lo que compra: un resultado con nombre en la sociedad donde estan sentados varios anfitriones posdoctorales plausibles, que es la misma caza de acogida que exigen HFSP y EMBO en 2027.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Se juzga entre las miembros asociadas que presentan en un unico congreso anual: un grupo pequeno y bien definido, a diferencia de los esquemas internacionales de esta rama.</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Confirmar su situacion de membresia asociada y vigilar bga.org para el plazo de resumenes del congreso de 2027; escribir a la secretaria de la BGA para preguntar si los premios de miembros asociadas requieren alguna nominacion aparte. Coordinar con la fila de ayudas de viaje de la BGA.</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>https://bga.org/</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Rama 1. Tier 1: pagina de premios de la BGA, que confirma los premios, su cambio de nombre en 2024 y el criterio de miembro asociada, pero no publica plazo, importe ni procedimiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>F-0029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>The Company of Biologists Travelling Fellowships</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SHORT_STAY</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>The Company of Biologists</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sin restriccion de nacionalidad; cualquier laboratorio de acogida del mundo, Australia incluida</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SI: carta de apoyo del laboratorio de acogida al solicitar.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>60</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>hasta 3000 GBP (equivalente en euros variable; no convertido para no inventar cifra)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>El viaje debe realizarse en los seis meses siguientes a la concesion</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>NO APLICA: estudiantes de posgrado y posdoctorales.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Estudiantes de posgrado e investigadoras posdoctorales; una revista por ronda; el trabajo debe caer dentro del ambito de Development, Journal of Cell Science o Journal of Experimental Biology. La ronda del 07-08-2026 ya paso y las de 2027 no estan publicadas.</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Genuinamente abierta para ella como doctoranda y uno de los pocos esquemas que podria pagar una vuelta a QIMR Berghofer sin limites de nacionalidad, pero el filtro de ambito de las revistas es el problema: la genetica estadistica humana, el GWAS/PRS y la epidemiologia del sueno infantil quedan fuera de Development, Journal of Cell Science y Journal of Experimental Biology, asi que una solicitud honesta tendria que construirse sobre una visita de biologia celular u organismica que hoy no esta proponiendo.</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Tres rondas al ano repartidas entre tres revistas; sin tasa de exito publicada.</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Volver a ella solo si una estancia futura tiene un componente real de biologia celular, del desarrollo o experimental; si no, dejarla registrada y no redescubrirla.</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>https://www.biologists.com/travelling-fellowships/</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Rama 4. Tier 1: pagina propia de The Company of Biologists leida el 2026-08-23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>F-0030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Premio de Investigacion del Instituto de Neurociencias Federico Oloriz (UGR)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PRIZE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Instituto de Neurociencias Federico Oloriz, Universidad de Granada</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Espana; ambito nacional, no restringido a la UGR</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NINGUNA: es un premio a un articulo publicado.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Predoctorales o doctoradas con titulo posterior al 31-12-2022</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Abierto a investigadoras de inicio de carrera de toda Espana, incluidas explicitamente las meramente 'matriculadas en doctorado'. Premia un articulo publicado en neurociencia basica o aplicada de los tres anos anteriores (2023-2025 para la edicion de 2026). La ganadora imparte una conferencia divulgativa. La ventana de solicitud es de solo 30 dias naturales.</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Un premio real y de baja competencia al que puede optar COMO DOCTORANDA ACTUAL: la convocatoria admite explicitamente a quien solo esta matriculada en un programa de doctorado, y 1250 euros mas una conferencia invitada son una linea de CV citable y genuina para alguien con un expediente de publicaciones todavia fino. El calendario juega a su favor: sus dos manuscritos de primera autora (la revision en Journal of Sleep Research y el articulo empirico de Nature Mental Health del proyecto de QIMR) estan en revision ahora, asi que si alguno aparece en 2026 quedaria dentro de la ventana elegible de las ediciones de 2027 y 2028. Punto por punto: no exige doctorado terminado; es nacional y ella esta en Espana; no hay acogida que asegurar; el esfuerzo es minimo. LA RESTRICCION: la ventana es de solo 30 dias una vez abierta, hacia mayo, asi que hay que tener el recordatorio puesto. Es ademas el caso modelo de toda una clase de premios pequenos de sociedades e institutos espanoles que merece la pena rastrear sistematicamente en proximas pasadas.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Un unico premio de ambito nacional pero de escasa visibilidad, dirigido a investigadoras de inicio de carrera en neurociencia; el grupo real de solicitantes suele ser pequeno.</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Poner recordatorio a principios de mayo de 2027 y revisar la web del instituto: la ventana dura solo 30 dias. Comprobar antes cual de los dos manuscritos ha salido publicado y en que ano, porque eso determina en que edicion encaja.</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>https://ineurociencias.ugr.es/instituto/noticias/premio-instituto-neurociencias-2026</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Rama 4. VERIFICADO contra el anuncio propio del instituto el 2026-08-23: ambito nacional, predoc o doctorado posterior al 31-12-2022, premio unico de 1250 euros, articulo publicado en 2023-2025 para la edicion de 2026. La edicion de 2026 cerro el 06-06-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>F-0031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Guarantors of Brain Travel Grants</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TRAVEL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Brain: The Charity (Guarantors of Brain)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Solo instituciones del Reino Unido</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NINGUNA: ayuda de viaje a congreso.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>500 GBP (congresos en el Reino Unido) / 800 GBP (Europa) / 1200 GBP (internacional)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Un congreso</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Formacion doctoral, o MD de investigacion de 3 anos con base en el Reino Unido, o formacion posdoctoral</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Restringida a quienes estan en formacion doctoral en instituciones del REINO UNIDO; exige cofinanciacion institucional parcial; maximo 3 ayudas de por vida y una cada 12 meses. Hay que solicitar al menos 9 semanas antes del congreso.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Excluida de plano: la ayuda se restringe a doctorandas y personal en formacion con base en instituciones britanicas, y ella esta matriculada en la Universidad de Murcia y empleada en Malaga, asi que es inelegible al margen del merito.</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>No aplicable: inelegible.</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Ninguna; se registra para que no vuelva a redescubrirse. Solo seria relevante si se traslada a una institucion britanica.</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>https://guarantorsofbrain.org/grants/travel-grants/</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Rama 4. Condiciones tomadas de varias fuentes secundarias coincidentes (ECRcentral, Edinburgh Neuroscience, ScientifyResearch); la pagina del financiador no se abrio directamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>F-0032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BBRF Independent Investigator Grant</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Brain and Behavior Research Foundation (NARSAD)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sin restriccion de pais en la pagina leida, pero el liston de etapa de carrera es lo que ata.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: debe ser investigadora principal con financiacion competitiva nacional en una institucion academica.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>hasta 100000 USD en dos anos, o hasta 50000 USD en uno</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1 o 2 anos</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No se expresa en anos desde el doctorado sino por rango: nivel de profesora asociada o equivalente.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>INELEGIBLE PARA ELLA: exige nivel de profesora asociada o equivalente y ser IP en activo de financiacion competitiva nacional (las profesoras ayudantes solo cualifican si tienen un R01 del NIH). La investigacion debe abordar esquizofrenia, trastornos afectivos mayores u otra enfermedad mental grave. La BBRF indica que esta 'in the process of determining the acceptance period'.</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Inelegible por un margen amplio: exige una IP independiente consolidada con financiacion competitiva nacional, algo que queda a una decada de una defensa en febrero de 2028.</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>La BBRF no publica numero de solicitudes.</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Ninguna en anos. La Young Investigator Grant sigue siendo el unico mecanismo de la BBRF para el que llegara a ser elegible.</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>https://bbrfoundation.org/grants-prizes</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Rama 3. Tier 1: pagina de ayudas y premios de la BBRF leida el 2026-08-23. El foco tematico (esquizofrenia y trastornos afectivos mayores) si coincide con su linea 2; lo que no encaja es la etapa de carrera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>F-0033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BBRF Distinguished Investigator Grant</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Brain and Behavior Research Foundation (NARSAD)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sin restriccion de pais en la pagina leida.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: catedratica o equivalente en una institucion academica.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>100000 USD para un ano</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1 ano</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No aplica: catedratica o equivalente</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>INELEGIBLE PARA ELLA: restringida a catedraticas o equivalente. El ciclo de 2025 fue del 20-08-2025 al 25-09-2025; las fechas de 2026 no figuran en la pagina leida.</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Inelegible: es un esquema de nivel de catedra; se registra solo para cerrar el mapa de mecanismos de la BBRF y que ninguna pasada futura vuelva a abrir la pregunta.</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>La BBRF no publica numero de solicitudes.</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Ninguna.</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>https://bbrfoundation.org/grants-prizes</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Rama 3. Tier 1: pagina de ayudas y premios de la BBRF leida el 2026-08-23. Los demas mecanismos de la BBRF (Klerman y Freedman, Lieber, Colvin, Ruane, Goldman-Rakic, Maltz, Pardes, Productive Lives) son premios de trayectoria por nominacion y ninguno es via de financiacion de inicio de carrera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>F-0034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Stanley Center Sklar Program (Sklar Research Award / Sklar BSRP Fellowship)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Stanley Center for Psychiatric Research, Broad Institute of MIT and Harvard</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Solo EE. UU.: 'You need to be a US citizen or permanent resident to apply.'</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA y cerrada: el Sklar Research Award se limita a residentes de psiquiatria del PSTP de MGH/McLean o de la via de investigacion de BWH/HMS; la beca BSRP es para estudiantes de grado.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>INELEGIBLE PARA ELLA solo por ciudadania: exige ser ciudadana estadounidense o residente permanente. Ademas, los dos componentes vivos se dirigen a estudiantes de grado y a residentes de psiquiatria de programas nominados de Boston.</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Inelegible por ciudadania y por via de carrera; el valor real del Stanley Center para ella es como EMPLEADOR (las vacantes del Broad, ya recogidas en SRC-0040), no como financiador.</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Sin cifras publicadas.</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Descartar como via de financiacion. Mantener el portal de empleo del Broad (SRC-0040) como canal vivo; un correo a sklarprogram@broadinstitute.org zanjaria el estado de la beca si alguna vez merece el esfuerzo.</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>https://www.broadinstitute.org/stanley-center-sklar-program</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Rama 3. Tier 1: pagina del Sklar Program del Broad leida el 2026-08-23. CONFLICTO REGISTRADO: la pagina mantiene una seccion 'Sklar Fellows' mientras fuentes secundarias afirman que la beca posdoctoral termino en 2024; se reporta, no se resuelve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>F-0035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>L'Oreal-UNESCO For Women in Science International Awards / International Rising Talents</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PRIZE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Fondation L'Oreal / UNESCO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Global, por regiones del mundo</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>OBLIGATORIA: afiliacion academica o investigadora; las laureadas internacionales son cientificas senior consolidadas.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>NO APLICABLE A ELLA: los International Awards son solo por nominacion y para mujeres cientificas eminentes (cinco laureadas al ano en todo el mundo); las International Rising Talents se seleccionan ENTRE las ganadoras de los programas nacionales o regionales, no por solicitud directa.</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Se registra solo para que no vuelva a redescubrirse: el nivel internacional es por nominacion para laureadas senior y el nivel Rising Talents se nutre de las ganadoras nacionales, asi que su unica puerta de entrada es la edicion espanola registrada aparte.</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Cinco laureadas internacionales al ano en todo el mundo.</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Ninguna. Revisar solo si gana la edicion espanola.</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>https://www.forwomeninscience.com/</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Rama 3. La pagina del programa de la UNESCO (unesco.org/en/prizes/women-science) devolvio HTTP 503 el 2026-08-23; la estructura se describe solo desde fuentes secundarias: tratar como pista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>F-0036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CSIC Premios a Tesis Doctorales Relevantes (IV edicion)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PRIZE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Consejo Superior de Investigaciones Cientificas (CSIC)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Espana</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NINGUNA: premio a la tesis.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1000 por premio (6 premios: 2 Vida, 2 Materia, 2 Sociedad)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Tesis defendidas recientemente</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Casi con seguridad restringido a tesis dirigidas dentro de institutos del CSIC; sin verificar.</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Su tesis es de la Universidad de Murcia y sin direccion del CSIC, asi que la convocatoria le esta muy probablemente cerrada, y en cualquier caso no habra defendido antes de febrero de 2028.</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>No aplicable.</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Ninguna salvo que aparezca una codireccion del CSIC; reexaminar tras la defensa de febrero de 2028 solo si la restriccion del CSIC resulta ser mas laxa.</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>https://www.csic.es/es/actualidad-del-csic/el-csic-lanza-la-convocatoria-2026-de-los-premios-tesis-doctorales-relevantes-y-la-supervision-del-personal-investigador</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Rama 4. Solo fragmento de busqueda; la restriccion de afiliacion al CSIC es una suposicion marcada como no verificada.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB1"/>
+  <autoFilter ref="A1:AB37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9163,21 +17135,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9242,8 +17214,876 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>W-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HFSP Postdoctoral Fellowships - convocatoria del ano 2027</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Human Frontier Science Program</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Portal de LOI ~marzo de 2027, plazo de LOI ~mayo de 2027, propuesta completa ~septiembre de 2027, para la convocatoria del ano 2028 (activacion de abril de 2028 a enero de 2029)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Es el buque insignia alcanzable. La LOI del ano 2028, hacia mayo de 2027, cae en el mismo mes en que acaba su residencia, no exige doctorado en mano al presentar, y su ventana de activacion (abril de 2028 a enero de 2029) encaja justo encima de su defensa prevista para febrero de 2028. Perder la LOI de mayo de 2027 le cuesta un ano entero.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://www.hfsp.org/funding/hfsp-funding/postdoctoral-fellowships</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Ver F-0007. El laboratorio de acogida debe estar comprometido antes de la LOI y el proyecto debe suponer un cambio real de campo; Espana excluida por nacionalidad y por pais del doctorado. Poner revision en hfsp.org en febrero de 2027. Confirmar tambien el requisito de articulo de primera autora en fase de LOI, que no se pudo verificar y que es lo unico que podria descalificarla en su ciclo mas temprano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>W-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Contratos Rio Hortega - edicion AES 2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ISCIII</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2027-02-10 (ventana ~10 feb - 5 mar 2027; publicacion en BOE prevista en diciembre de 2026)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>El esquema mas alcanzable de toda la base de datos para ella: no exige doctorado en ningun momento, y la edicion AES 2027 deberia admitir a quienes terminan la FSE en 2027, que es su caso el 22-05-2027. Presentarse en feb-mar de 2027, siendo aun residente, es la accion concreta que sale de esta pasada.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Ver F-0001. Verificar en el texto de la AES 2027 que el art. 34.2o dice 'durante el ano 2022, o en fecha posterior, incluyendo a los que lo hagan en 2027' y que el plazo de alegaciones de la resolucion provisional cae despues del 22-05-2027. La acogida (un jefe de grupo de un centro publico del SNS) debe estar cerrada a finales de 2026, porque hay cupo por centro y preseleccion interna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Contratos Sara Borrell - edicion AES 2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ISCIII</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2027-02-10 (ventana ~10 feb - 5 mar 2027); su primera edicion realista es la AES 2029</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Su principal objetivo posdoctoral espanol una vez defendida la tesis; como el doctorado debe estar leido antes del plazo, la edicion AES 2028 (~5 de marzo de 2028) es una moneda al aire contra una defensa de febrero de 2028 y la AES 2029 es el objetivo seguro.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Ver F-0002. La ventana rodante de recencia del doctorado (la AES 2026 exigia defensa posterior al 1-1-2022) la mantiene elegible hasta aproximadamente la AES 2032. El grupo receptor debe ser distinto del de su tesis en Murcia y estar en otro centro. PUNTO DE DECISION: si la defensa se adelanta a diciembre de 2027 o enero de 2028, la AES 2028 pasa de moneda al aire a objetivo real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Contratos Miguel Servet - edicion AES 2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ISCIII</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2027-02-11 (ventana ~11 feb - 4 mar 2027)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Inalcanzable durante una decada por la via ordinaria, pero las bases de la AES levantan el techo de fecha de tesis a quienes completaron Rio Hortega o Sara Borrell, que es la razon estrategica para tomar un Rio Hortega en 2027.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Ver F-0003. La AES 2026 exigia tesis leida entre el 1-1-2014 y el 31-12-2021.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Wellcome Early-Career Awards - ronda de julio de 2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Wellcome Trust</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Esquema rodante con varias rondas al ano: proximos plazos ~10-11-2026 y ~06-04-2027, y otra ronda hacia julio de 2027</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>El esquema britanico mejor emparejado con la genetica psiquiatrica (KCL, Cardiff, Edimburgo), y al ser rodante con tres rondas al ano no hay precipicio anual: puede entrar en la primera ronda que sus circunstancias permitan en vez de esperar doce meses. Eso lo hace estructuralmente mas amable con una defensa en febrero de 2028 que cualquier convocatoria anual.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://wellcome.org/research-funding/schemes/early-career-awards</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Ver F-0012. CONFLICTO SIN RESOLVER en la fecha de la ronda de julio de 2026: una fuente dice 21 y otra 22 de julio; wellcome.org devuelve HTTP 403 al fetch automatico y no se pudo dirimir. DOS INCOGNITAS QUE DECIDEN SU PRIMERA RONDA y que la duena debe resolver a mano: si exige el doctorado en la fecha limite o solo al empezar, y si la acogida esta restringida a Reino Unido, Irlanda y paises de renta baja/media, en cuyo caso un centro espanol no vale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>W-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NHMRC Investigator Grants - ronda 2027</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>National Health and Medical Research Council (Australia)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ronda 2028 prevista con apertura ~2-6-2027 y cierre ~28-7-2027 (17:00 AEST); ronda 2029 ~junio-julio de 2028</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Su estancia en QIMR Berghofer es un vinculo institucional australiano vivo, y las Investigator Grants son el vehiculo principal del NHMRC para salario mas investigacion. Merece calendario porque la ronda es a mitad de ano y no choca con los racimos europeos de septiembre y febrero, pero necesita una institucion australiana dispuesta a administrarla, que es una relacion a construir con un ano de antelacion.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://www.nhmrc.gov.au/funding/find-funding/investigator-grants</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Ver F-0016. INELEGIBLE HASTA EL DOCTORADO: Emerging Leadership 1 se evalua en relacion con la oportunidad desde la fecha de concesion del doctorado, asi que un doctorado de febrero de 2028 apunta a la ronda de 2029 (apertura ~junio de 2028) como su primera entrada realista. El NHMRC ya no tiene becas posdoctorales independientes: este esquema es todo el carril.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>W-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BBRF Young Investigator Grant - ciclo 2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brain and Behavior Research Foundation</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Principios de febrero de 2027, con cierre a principios de marzo de 2027</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>70000 dolares en dos anos, sin restriccion geografica, con una solicitud corta y dirigida de lleno a la investigacion en trastornos psiquiatricos, que es su linea 2. No puede usarla hasta ocupar un puesto de formacion investigadora con mentor de psiquiatria en el mismo centro, asi que 2029 es el ciclo realista, pero debe estar en el calendario desde el dia en que empiece un posdoc.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://bbrfoundation.org/grants-prizes/bbrf-young-investigator-grants</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Ver F-0017. La via del titulo de medicina con PGY-IV o mas significa que el doctorado cualificante podria ser su MD y no el PhD: merece la pena preguntar a la BBRF si un primer ano de puesto investigador tras una residencia espanola cuenta como 'advanced post-doctoral fellow'. Una fuente secundaria apunta al 12-3-2027 como cierre del ciclo 2027: sin verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>W-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Postdoctoral Junior Leader - modalidad Incoming, convocatoria 2027</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fundacion la Caixa</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Hacia abril-mayo de 2027 para la Incoming de 2028 (cierre historicamente a finales de julio)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>La modalidad Incoming lleva la misma banda de 2 a 7 anos posdoctorales que la Retaining pero restringe las acogidas a centros Severo Ochoa / Maria de Maeztu, institutos de investigacion sanitaria Carlos III y unidades portuguesas de excelencia. Para una candidata basada en Espana la modalidad correcta suele ser la Retaining; la regla de movilidad de la Incoming no se pudo verificar.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://lacaixafoundation.org/en/postdoctoral-junior-leader-fellowships-incoming-call</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Ver F-0006. Su primera edicion elegible en cualquiera de las dos modalidades es una convocatoria que cierre despues de febrero de 2030. El sitio bloquea el fetch automatico (HTTP 403).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>W-0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ISPG Early Career Investigator Program (ECIP) - ayuda de viaje al WCPG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>International Society of Psychiatric Genetics</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TRAVEL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Portal de resumenes del WCPG 2027 hacia febrero-marzo de 2027; plazo de resumenes y de ECIP hacia mediados de mayo de 2027; congreso a finales de septiembre o principios de octubre de 2027 (sede sin anunciar)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Es la ayuda de congreso mejor emparejada de toda la base de datos: el WCPG es EL congreso de su linea principal (GWAS/PRS de trastornos psiquiatricos) y la elegibilidad del ECIP nombra explicitamente a 'graduate student' junto a las posdoctorales, asi que es elegible COMO DOCTORANDA ACTUAL y sigue siendolo hasta unos cinco anos despues del doctorado, o sea hasta ~2033. El plazo de mediados de mayo de 2027 cae dias antes de que acabe su residencia: sincronizacion perfecta para llegar al mercado posdoctoral con un resumen presentado y un premio en el CV.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://ispg.net/ecip-program/</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>VERIFICADO para la edicion de 2026: congreso en Glasgow del 29 de septiembre al 3 de octubre de 2026; resumenes orales y poster y solicitudes ECIP el 14-5-2026 (el ECIP exige resumen de sesion cientifica presentado a la vez). Quienes recibieron ayuda ECIP entre 2022 y 2025 no podian pedirla en 2026; ella no la ha recibido, asi que no le afecta. Confianza MEDIUM y no HIGH porque el patron de mediados de mayo se apoya solo en la edicion de 2026 y las fechas y sede del WCPG 2027 no estan anunciadas. ELEMENTO APARTE A CORTO PLAZO: el WCPG 2026 es dentro de seis semanas y la inscripcion general podria seguir abierta; merece una comprobacion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>W-0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SRS Trainee Awards del congreso SLEEP (Trainee Merit, Diversity Travel, First-Time Attendee)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sleep Research Society / congreso SLEEP</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TRAVEL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Enero-marzo de 2027 para SLEEP 2027; la propia pagina de la SRS indica que el ciclo del Trainee Merit Award se espera en enero de 2027</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Las doctorandas tienen condicion de trainee y son elegibles, asi que son accionables mientras siga siendo estudiante de doctorado. El Trainee Merit Award cubre aproximadamente la matricula de SLEEP y exige membresia vigente de la SRS mas un resumen no tardio; el Diversity Travel Award llega hasta 2000 dolares para matricula, viaje y alojamiento y no declara requisito de membresia, acogiendo explicitamente a trainees de distintos paises, asi que es el objetivo de mejor relacion valor-esfuerzo para una candidata basada en Espana. El Leadership Development Workshop Award solo se convoca en anos impares, es decir en SLEEP 2027, justo su ventana.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://sleepresearchsociety.org/awards/conference-awards/</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Las fechas y la sede de SLEEP 2027 no figuraban en la pagina. Los congresos SLEEP son en junio, asi que caen despues del fin de residencia del 22-05-2027. Exige visado o ESTA de EE. UU. y un billete de larga distancia, y las ayudas son reembolsos, o sea que adelanta el dinero. Material para el resumen: su linea 3 mas la revision del Journal of Sleep Research.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>W-0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Premio de Investigacion del Instituto de Neurociencias Federico Oloriz (UGR) - edicion 2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Instituto de Neurociencias Federico Oloriz, Universidad de Granada</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PRIZE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mayo de 2027, convocatoria anual con ventana de solo 30 dias naturales</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Un premio real y de baja competencia al que puede optar COMO DOCTORANDA ACTUAL: la convocatoria admite a quien solo esta matriculada en doctorado, es de ambito nacional y no se restringe a la UGR. 1250 euros mas una conferencia invitada son una linea de CV citable para alguien con un expediente todavia fino, y si alguno de sus dos manuscritos se publica en 2026 quedaria dentro de la ventana elegible de las ediciones de 2027 y 2028.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://ineurociencias.ugr.es/instituto/noticias/premio-instituto-neurociencias-2026</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Ver F-0031. VERIFICADO contra el anuncio del instituto: predoc o doctorado posterior al 31-12-2022, articulo publicado en 2023-2025 para la edicion de 2026. Poner recordatorio a primeros de mayo de 2027: la ventana dura 30 dias. Es ademas el caso modelo de una clase entera de premios pequenos de sociedades e institutos espanoles que conviene rastrear de forma sistematica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>W-0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Becas de Investigacion de la SES (Sociedad Espanola de Sueno)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Sueno (SES)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>~noviembre-diciembre de 2026, con plazo ~25 de enero de 2027</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>El unico financiador espanol y en castellano para su linea de sueno: hasta 10000 euros por proyecto de un fondo de 20000, mas una beca especial de 10000 para investigadores jovenes, para proyectos de 1 a 3 anos sobre fisiologia o patologia del sueno. Competencia baja en relacion con todo lo demas de esta rama y financiable desde dentro de Espana mientras sigue atada a Malaga.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://ses.org.es/blog-post/becas-2022-2-5-3-2/</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>LO ACCIONABLE ES EL RELOJ DE LA MEMBRESIA. Fuentes secundarias sobre ediciones recientes indican que hay que ser menor de 45, nacional de la UE o extranjera con residencia en Espana, Y 'ser miembro de la SES desde al menos un ano antes a la convocatoria', con al menos el 70% del equipo formado por socios de la SES. La regla del 70% esta confirmada en la propia web de la SES; la del ano de antiguedad es LIKELY (solo secundaria, el PDF de bases no se abrio). Si es cierta, hacerse socia AHORA es lo que la habilita para la edicion de enero de 2028, y hacerlo antes de ~diciembre de 2026 protege la de enero de 2027. No aparecio requisito de doctorado, lo que la haria una de las poquisimas accesibles antes de defender. La pagina de la SES dice 'Convocatoria abierta' pero el unico plazo que publica es el de enero de 2026: parece no actualizada. Dos convocatorias mas de la SES sin examinar: 'Ayuda para la Investigacion y el Intercambio de Conocimiento' y el 'Premio al Mejor Trabajo Publicado Joaquin Teran y Mari Luz Alonso'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>W-0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ESRS Meetings and Courses Fellowship</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>European Sleep Research Society (ESRS)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>~finales de 2026, con plazo ~31 de enero de 2027</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>LOW-MEDIUM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Es el instrumento propio de desarrollo de carrera de la ESRS, dirigido explicitamente a 'junior candidates in the early stages of their career in sleep research' y abierto a cientificas y clinicas por igual, lo que encaja con una medica que hace genetica del sueno. Financia asistencia a congresos y cursos.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://esrs.eu/grants-awards/meetings-and-courses-fellowship/</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>BLOQUEADO: https://esrs.eu/grants-awards/ devolvio HTTP 403 al fetch automatico el 2026-08-23, confirmando el bloqueo que ya encontro la rutina de positions esta misma semana; intentado una vez y no reintentado. Todo aqui es UNVERIFIED y procede de fragmentos de busqueda: la seleccion la ordena el Comite Cientifico de la ESRS segun los objetivos de aprendizaje de la carta de motivacion, el CV y las publicaciones, teniendo en cuenta la antiguedad; plazo del 31-1-2026 en la ultima edicion. NO se pudo determinar si exige doctorado ni enumerar el resto de ayudas de la ESRS. Una sola visita manual con navegador a https://esrs.eu/grants-awards/ resolveria toda la cartera de la ESRS. La membresia es muy probablemente condicion previa, como en la SRS y la SES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>W-0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>One Mind Rising Star Awards 2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>One Mind</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CAREER_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>~marzo de 2027 (anual)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>300000 dolares para investigacion de inicio de carrera en salud mental: la mayor cuantia individual de esta rama y tematicamente en el centro de su linea 2, con atencion especial a la psiquiatria de precision. Merece seguimiento a largo plazo aunque no pueda entrar en muchos anos.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://onemind.org/what-we-do/one-mind-rising-star-academy/one-mind-rising-star-awards/</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>INELEGIBLE, y por un motivo decisivo: las posdoctorales estan explicitamente excluidas. La elegibilidad son profesoras ayudantes o asociadas dentro de los ocho anos desde su PRIMER NOMBRAMIENTO INDEPENDIENTE, con titulo de doctorado (el MD cuenta). El reloj que importa no es el de su doctorado sino la fecha en que tenga por primera vez una plaza de facultad, que todavia no existe. Revisar solo si accede a un puesto independiente. Confianza LIKELY y no VERIFIED: elegibilidad leida en listados de oficinas de investigacion y en el anuncio de One Mind via busqueda, sin abrir el portal de solicitud.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9254,13 +18094,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -9425,8 +18265,112 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SUB-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SENC (Sociedad Espanola de Neurociencia) - alta como socia</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.senc.es/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Condicion de sociedad miembro de FENS, imprescindible para solicitar las FENS/IBRO-PERC Exchange Fellowships, mas los avisos de premios y congresos de la neurociencia espanola.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Es requisito previo DURO de la unica ayuda con plazo vivo que puede cumplir este otono: la FENS/IBRO-PERC Exchange Fellowship cierra el 15-10-2026 y hay que ser socia ANTES de presentar. De las dos suscripciones de esta pasada, esta es la que tiene reloj.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>URL sin verificar en esta pasada: confirmar la pagina de alta vigente de la SENC antes de actuar. Alternativa equivalente: la membresia individual de FENS. Anadida por la rutina fellowships.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SUB-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ISCIII - avisos de convocatorias / boletin de la AES</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aviso cuando se firma la resolucion de la AES (diciembre) y cuando se abre la ventana de cada actuacion (febrero).</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>La ventana de Rio Hortega dura menos de cuatro semanas y el centro de acogida necesita margen interno; perder la publicacion de diciembre cuesta un ano entero en el esquema de mayor encaje que tiene, y ademas isciii.es bloquea el fetch automatico, asi que el correo vale mas que un rastreo semanal.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Probablemente sea mas fiable pedir que la incluyan en la lista interna de avisos de convocatorias del IIS donde vaya a presentar (IBIMA, en su caso) que el canal general del ISCIII. Anadida por la rutina fellowships.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J3"/>
+  <autoFilter ref="A1:J5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -22,18 +22,18 @@
     <sheet name="readme" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,14 +451,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -590,8 +590,482 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>E-0002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ASHG 2026 Annual Meeting</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Congreso anual</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://ashgmeeting.ashg.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>E-0001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>World Congress of Psychiatric Genetics (WCPG) 2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Congreso anual</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>36</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://ispg.net/wcpg-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>E-0005</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>IGES 2026 Annual Meeting &amp; Education Workshop</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Congreso anual + workshop</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://www.geneticepi.org/2026-annual-meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>T-0002</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Genetic Epidemiology (short course)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Short course</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>142</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>T-0001</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>International Statistical Genetics Workshop (el 'Boulder Workshop')</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://www.colorado.edu/ibg/workshop-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>T-0003</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mendelian Randomization (short course)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Short course</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>189</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>L-0001</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Complex Trait Genetics (CTG) Lab</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://cncr.nl/ctg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>L-0002</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Psychiatric Genetics Group</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://www.qimrb.edu.au/researchers-and-labs/psychiatric-genetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>L-0004</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Generation R - genetica del sueno infantil</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://acamh.onlinelibrary.wiley.com/doi/10.1111/jcpp.13899</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>L-0006</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SGDP Centre / Statistical Genetics Unit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/research/sgu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L2"/>
+  <autoFilter ref="A1:L12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -602,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4581,8 +5055,320 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SRC-0077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>IGES - Annual Meeting &amp; Education Workshop</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.geneticepi.org/2026-annual-meeting</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Reunion anual y workshop educativo de la International Genetic Epidemiology Society: fechas, plazo de resumenes, apoyo de viaje. Publico pequeno y senior de metodologia GWAS/PRS (su linea 1).</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>revisar fechas y plazo de resumenes cada primavera; patron de URL por ano /&lt;ano&gt;-annual-meeting</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>anual</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Anadida por la rutina ecosystem. En 2026 fue adyacente a ASHG en Quebec (18-20 oct).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SRC-0078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SOBP - Society of Biological Psychiatry Annual Meeting</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://sobp.org/</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Reunion anual de psiquiatria biologica con vertiente de genetica/imaging-genetics (su linea 2). Fechas, plazo de resumenes (~nov-dic), becas de viaje.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>navegar a Annual Meeting; el plazo de resumenes se anuncia a finales del ano anterior</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>anual</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Anadida por la rutina ecosystem. 2027: 6-8 may, Chicago. Tarifas en USD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SRC-0079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SLEEP (APSS) - Annual Meeting</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.sleepmeeting.org/</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Mayor reunion de investigacion del sueno (AASM + SRS), con via de genetica/epidemiologia del sueno (su linea 3). Fechas, plazo de resumenes (~primeros de dic), premios de viaje para trainees.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>revisar la convocatoria de resumenes a finales de cada ano</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>anual</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Anadida por la rutina ecosystem. 2027: 5-9 jun, Denver. Tarifas en USD; viaje a EE.UU. caro para una linea 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SRC-0080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>IBG Boulder - International Statistical Genetics Workshop</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.colorado.edu/ibg/workshop-2027</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>El taller nuclear de su tecnica (genetica estadistica, GWAS, Genomic SEM, MR). Fechas, tarifa, plazo y becas ISCEP (Regeneron). 2027 es la edicion PRESENCIAL.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>patron de URL /ibg/workshop-&lt;ano&gt;; tarifa/plazo suelen publicarse entre nov y ene</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>anual</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Anadida por la rutina ecosystem. Su diana de formacion (Fit 5, competencia LOW). Contacto IBGworkshop@colorado.edu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SRC-0081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>University of Bristol - Short courses (Medical School / MRC IEU)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Cursos cortos online de Genetic Epidemiology, Mendelian Randomization, GWAS y PRS (sus lineas 1-2), baratos y de bajo esfuerzo.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>las reservas del programa anual abren ~7-oct; revisar el indice de cursos cada otono</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>anual</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Anadida por la rutina ecosystem. Tarifas en GBP; posibles vouchers de reduccion segun elegibilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SRC-0082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Wellcome Connecting Science - Courses &amp; Conferences</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://coursesandconferences.wellcomeconnectingscience.org/</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Cursos practicos residenciales, entre ellos 'Genetic Analysis of Population-based Association Studies' (GWAS practico, su nucleo), con becas de hasta 50%.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>buscar 'association studies' / 'statistical genetics' en el calendario de cursos; edicion aprox. anual/bienal</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>trimestral</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Anadida por la rutina ecosystem. A 2026-08-24 solo consta la edicion de sep-2024 (cerrada); perseguir convocatoria 2027.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J77"/>
+  <autoFilter ref="A1:J83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4713,7 +5499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8004,8 +8790,178 @@
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Siembra de grupos de investigacion</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>11 grupos nuevos en genetica estadistica de rasgos complejos, GWAS/PRS psiquiatrico y genetica del sueno infantil (EU/EEA, Australia, RU, EE.UU., Espana). 6 con Fit 4-5. 2 anuncios ABIERTOS (Aarhus/Speed, plazo 1-may-2026, VERIFIED; y Max Planck Nijmegen, rodante desde 8-oct-2026, UNVERIFIED) y 1 pista calida (QIMR Berghofer/Medland).</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Siembra del calendario de congresos</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>10 congresos (WCPG, ASHG, ESHG, BGA, IGES, SOBP, ESRS/Sleep Europe, SLEEP, SfN, FENS) con fechas, plazos de resumenes y ayudas de viaje. Reloj vivo: los resumenes late-breaking de ASHG 2026 cierran el 26-ago-2026.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Siembra de formacion</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>6 cursos/talleres. Diana: el International Statistical Genetics Workshop de Boulder (edicion presencial 2027, Fit 5, competencia LOW). Ademas 2 cursos cortos online de Bristol (Genetic Epidemiology, Mendelian Randomization).</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Ampliacion de la superficie de vigilancia</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>6 fuentes nuevas del beat ecosystem: IGES, SOBP, SLEEP/APSS, el IBG Boulder Workshop, los cursos cortos de Bristol y Wellcome Connecting Science.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>subscriptions</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Alertas propuestas</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2 altas TODO (tope por pasada): membresia de la ISPG (avisos WCPG/ECIP) y lista de avisos del IBG Boulder Workshop. Ambas habilitan relojes que se pierden facil.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H79"/>
+  <autoFilter ref="A1:H84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16628,25 +17584,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="52" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
@@ -16655,8 +17611,8 @@
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="52" customWidth="1" min="25" max="25"/>
+    <col width="52" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16791,8 +17747,1416 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Complex Trait Genetics (CTG) Lab</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Danielle Posthuma</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Center for Neurogenomics and Cognitive Research (CNCR), Vrije Universiteit Amsterdam / Amsterdam UMC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Genomica estadistica y psiquiatrica; desarrollo de metodos para variantes comunes+raras; modelizacion fenotipica; conectomica</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>GWAS/WES/WGS, LDSC, MAGMA/FUMA/PoPS, REGENIE, metodos afines a genomic SEM; R, Python, UNIX</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Un anuncio 'Postdoc Statistical Genetics' (BRAINSCAPES) cerro el 18-jun-2025 (academictransfer.com/352365); pagina de empleo viva en cncr.nl/ctg/jobs/ - sin anuncio actual, pero la financiacion Gravitation a 10 anos hasta 2030 implica contratacion recurrente</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>BRAINSCAPES, Programa Gravitation neerlandes 2020-2030 (fuente: anuncio VU/AcademicTransfer); pista larga</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Correo en frio a Posthuma (o via asistente brigitte.borgman@vu.nl) - gancho: MD+PhD en genetica conductual/estadistica con PLINK/R/Python, ofreciendo reforzar la vertiente de genomica psiquiatrica; preguntar por proximas plazas postdoc de BRAINSCAPES</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Produccion continua de referencia en Nature Genetics / Nat Hum Behav sobre metodos GWAS de rasgos complejos (grupo puntero de genetica estadistica)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>De lleno en su linea 1 (genetica estadistica de rasgos complejos) y linea 2 (GWAS psiquiatrico). Taller lider mundial de metodos+aplicacion donde sus PLINK/R y Python asistido por IA son directamente desplegables; UE, sin visado. Primer correo: liderar con el combo MD+PhD y el rango tecnico, citar los dos manuscritos en revision, preguntar si reabrira un postdoc BRAINSCAPES/CTG y ofrecer un breve research statement.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Laboratorio de genetica estadistica de primer nivel mundial; los anuncios postdoc atraen candidaturas internacionales fuertes</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>https://cncr.nl/ctg/</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Abri cncr.nl/ctg/ y el anuncio cerrado de AcademicTransfer yo misma</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>L-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Psychiatric Genetics Group</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sarah Medland</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QIMR Berghofer Medical Research Institute</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>GWAS/PRS psiquiatrico (TDAH, bipolar, depresion, esquizofrenia), genetica de estructura cerebral (ENIGMA), genetica de salud de la mujer</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>GWAS, PRS, modelos de gemelos/familia, imaging genetics; R, pipelines tipo PLINK</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sin anuncio en la pagina del grupo; grupo grande y multi-subvencion (NHMRC/MRFF/NIH/ARC/ERC) = contratacion frecuente - preguntar directamente</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NHMRC, MRFF, NIH, ARC, ERC listados en la pagina del grupo (fuente: qimrb.edu.au)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CALIDO: ya hizo una estancia en QIMR Berghofer (el articulo empirico en Nature Mental Health). Re-contactar a su anfitrion de QIMR / Medland o Lucia Colodro Conde (miembro hispanohablante) - gancho: 'fui visitante aqui, mi articulo basado en QIMR esta en revision en Nature Mental Health, termino el doctorado y busco postdoc'</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Preprint de GWAS multi-ancestral de trastorno por uso de estimulantes (medRxiv, jun 2026); estudios AAA (TEA+TDAH) y Australian Genetics of Bipolar Disorder en curso</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Diana directa en lineas 1-2, y tiene relacion previa + produccion en revision de este mismo instituto - la pista calida mas fuerte del conjunto. El primer correo debe referir su estancia previa y el articulo pendiente, nombrar el trabajo de PRS/psiquiatrico de Medland, y preguntar por plazas postdoc/staff-scientist. Unica salvedad: Australia = necesita patrocinio de visado (marcar, no bloqueante).</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Laboratorio de prestigio, pero la conexion calida reduce materialmente su competencia efectiva</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>https://www.qimrb.edu.au/researchers-and-labs/psychiatric-genetics</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Abri la pagina del grupo de QIMR Berghofer yo misma; su estancia previa en QIMR consta en el brief de la candidata</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>L-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Center for Quantitative Genetics and Genomics (grupo Speed)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Doug Speed</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Aarhus University</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aarhus</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Desarrollo de metodos estadisticos en genetica de rasgos complejos humanos; subtipado/clasificacion de enfermedad a partir de datos geneticos (ecosistema LDAK)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>GWAS, metodos de heredabilidad/PRS, LDAK; R/Stata/Matlab/C, UNIX</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Anuncio postdoc ABIERTO: 'Method development in human statistical genetics, focus on disease classification', plazo 1-may-2026, 2 anos, inicio 1-oct-2026 (Nature Careers job 12856703)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Linea postdoc financiada (plaza de 2 anos anunciada); fuente: anuncio Nature Careers</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Correo directo a doug@qgg.au.dk - gancho: su solida genetica estadistica aplicada (PLINK/R) + la mirada clinica/MD sobre heterogeneidad de enfermedad; el anuncio dice genetica previa 'preferible no requerida', asi que su perfil supera el corte comodamente</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Linea de software LDAK; articulos de metodos de rasgos complejos en curso</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Plaza concreta ABIERTA en su linea 1 (genetica estadistica de rasgos complejos), UE/sin visado, y el marco de clasificacion de enfermedad encaja con una MD que entiende la heterogeneidad clinica. Algo mas orientado a metodos que su nucleo aplicado, asi que el correo debe enfatizar disposicion a hacer desarrollo de metodos ofreciendo a la vez experiencia clinica/de fenotipos psiquiatricos; su Python/R y PLINK cubren la pila. Solicitar antes del 1-may-2026.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rol especializado de desarrollo de metodos estrecha el grupo de candidatos frente a un postdoc generico de GWAS psiquiatrico</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/12856703/</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Abri el anuncio de Nature Careers yo misma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>L-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Generation R - genetica del sueno infantil</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Desana Kocevska (con Generation R / Erasmus MC, epidemiologia de psiquiatria infantil)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Erasmus MC University Medical Center</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Genetica/PRS del sueno infantil, epidemiologia del sueno del desarrollo, trayectorias de sueno materno-infantil (Generation R / Generation R Next)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PRS en cohortes pediatricas, epidemiologia longitudinal/de cohortes, scores derivados de GWAS; R</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>desconocido - sin anuncio; abordar como correo en frio / sondeo de colaboracion</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Generation R es una gran infraestructura de cohorte de nacimiento (bien financiada); subvencion especifica del grupo no confirmada</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Correo en frio a Kocevska - gancho: su review en revision en Journal of Sleep Research + foco en genetica del sueno infantil encajan casi exactamente con este grupo; ofrecer aportar habilidades de genetica estadistica/PRS a los fenotipos de sueno infantil</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>'Are some children genetically predisposed to poor sleep? A polygenic risk study' (J Child Psychol Psychiatry, 2024); trayectorias de sueno materno, Generation R Next (2025, Sleep Medicine)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>El solapamiento mas raro del conjunto: su nicho exacto de linea 3 (genetica del sueno infantil) combinado con metodos PRS (linea 1/2). Muy pocos grupos hacen sueno pediatrico + genetica; este es uno. UE/sin visado. Primer correo: citar su review de sueno, nombrar el articulo de JCPP 2024, proponer extender su trabajo de PRS a fenotipos de sueno mas tempranos (infantiles) que conoce de su revision sistematica.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Area de nicho (genetica del sueno pediatrico) con una comunidad especialista pequena</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>https://acamh.onlinelibrary.wiley.com/doi/10.1111/jcpp.13899</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Dos fuentes secundarias (articulo JCPP + cobertura de Erasmus/prensa); no abri una homepage del grupo, asi que el titulo/estructura actual exactos de la PI quedan sin confirmar</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MRC Centre for Neuropsychiatric Genetics &amp; Genomics</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>James Walters (Director del Centro)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cardiff University</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GWAS psiquiatrico (esquizofrenia, bipolar, TDAH, neurodesarrollo), genomica de CNV/variantes raras, metodos estadisticos/bioinformaticos</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>GWAS, PRS, analisis de CNV, bioinformatica; grandes cohortes de genetica psiquiatrica del Reino Unido</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>El Centro mantiene una pagina de vacantes viva (cardiff.ac.uk/...neuropsychiatric-genetics-genomics/about/current-vacancies) pero no se confirmo plaza actual en esta busqueda</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Financiacion permanente del MRC Centre + multiples subvenciones de proyecto (mayor grupo de genetica psiquiatrica del Reino Unido); fuente: paginas del centro de Cardiff</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Correo en frio a un PI de linea (p.ej. Walters o un lider de PRS/estadistica) - gancho: geneticista estadistica MD+PhD que quiere pasar a GWAS/PRS psiquiatrico; pedir que la avisen de proximas convocatorias postdoc</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Produccion sostenida en Nature Genetics / Biological Psychiatry / Molecular Psychiatry de GWAS psiquiatrico (centro insignia del Reino Unido)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Coincidencia directa con lineas 1-2 y hogar natural para una geneticista estadistica psiquiatrica. Revisar la pagina de vacantes cada semana; si no hay nada abierto, un correo en frio es normal. RU = necesita patrocinio de visado post-Brexit (marcar). El correo debe destacar su independencia en genetica estadistica (PLINK/R) y su formacion clinica.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mayor centro de genetica psiquiatrica del Reino Unido; grupo de candidatos internacional competitivo</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>https://www.cardiff.ac.uk/centre-neuropsychiatric-genetics-genomics</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Solo resultados de busqueda (surgieron paginas de personal senior + vacantes); no abri las paginas del todo - direccion/liderazgo de fuentes secundarias</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>L-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SGDP Centre / Statistical Genetics Unit</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cathryn Lewis (Jefa de Depto / Stat Genetics Unit) y Gerome Breen (genetica psiquiatrica)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MRC Social, Genetic &amp; Developmental Psychiatry Centre, IoPPN, King's College London</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Epidemiologia y estadistica genetica de trastornos psiquiatricos; PRS de depresion/ansiedad/trastornos alimentarios; cohortes GLAD/trastornos alimentarios</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>GWAS, PRS, epidemiologia genetica, metodos estadisticos; R</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>desconocido - sin anuncio confirmado; vale la pena vigilar los tablones ISPG/KCL</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MRC centre + multiples subvenciones; una publicacion reciente en Nature (ene 2026) indica programas activos y financiados (fuente: resultados de busqueda)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Correo en frio a Lewis (Statistical Genetics Unit) o Breen - gancho: geneticista estadistica (PLINK/R) con formacion clinica MD, interesada en PRS de trastornos del animo; su review de depresion + trabajo en revision son relevantes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Articulo en Nature (ene 2026) con Lewis y Breen; trabajo en curso de PRS de depresion</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Coincidencia nuclear en lineas 1-2, con el PRS de depresion como fuerza nombrada - directamente su linea 2. La Statistical Genetics Unit de Lewis es un hogar explicito de genetica estadistica. RU necesita visado (marcar). Primer correo: nombrar la unidad, citar su foco en depresion/salud mental, preguntar por plazas postdoc o co-patrocinio de beca (podria traer su propia beca).</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Centro insignia de genetica psiquiatrica/estadistica del Reino Unido, fuerte demanda de candidatos</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/research/sgu</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Dos fuentes secundarias (perfiles KCL + pagina SGU en resultados); no abri la pagina de la SGU yo misma</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>L-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Grotzinger Lab (genomica psiquiatrica multivariante)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Andrew Grotzinger</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Institute for Behavioral Genetics y Dept of Psychology and Neuroscience, University of Colorado Boulder</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Boulder</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Desarrollo de metodos genomicos multivariantes (Genomic SEM), genetica psiquiatrica y cognitiva transdiagnostica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Genomic SEM, modelizacion de summary-stats de GWAS, PRS; R</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>desconocido - PI de inicio de carrera, IBG tiene pagina de 'positions'; probablemente creciendo/contratando - preguntar directamente</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Autor principal de un articulo en Nature (dic 2025) (5 factores genomicos en 14 trastornos psiquiatricos); programa activo financiado por NIH implicito (fuente: noticias CU Boulder IBG)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Correo en frio a Grotzinger - gancho: geneticista estadistica MD+PhD que quiere aplicar Genomic SEM a fenotipos psiquiatricos transdiagnosticos / de sueno; los PIs junior responden mas a correos en frio y suelen estar montando equipo</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Nature (dic 2025): mapeo del paisaje genetico en 14 trastornos psiquiatricos (s41586-025-09820-3)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Fuerte encaje con lineas 1-2 con un metodo de moda y alta visibilidad (Genomic SEM) que podria aprender rapido dado su fondo de R/estadistica. Laboratorio de inicio de carrera = menor competencia y mayor capacidad de respuesta que los mega-hubs. EE.UU. = patrocinio de visado (marcar). El correo debe proponer una aplicacion concreta de Genomic SEM a un fenotipo que conoce (p.ej. sueno o un rasgo psiquiatrico) y notar que quiza pueda traer financiacion de una beca de la UE.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Laboratorio junior, equipo mas pequeno/nuevo que los hubs consolidados</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>https://www.colorado.edu/behavioral-genetics/andrew-grotzinger</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Perfil CU Boulder IBG + anuncio del articulo en Nature en resultados; no abri la pagina del laboratorio del todo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>L-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Saxena Lab (genomica del sueno y circadiana)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Richa Saxena (con Hassan Dashti)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Center for Genomic Medicine, Massachusetts General Hospital / Harvard Medical School / Broad Institute</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Genetica de rasgos de sueno y circadianos (duracion, siestas, cronotipo), enlaces sueno-cardiometabolico, GWAS de salud del sueno compuesta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>GWAS a gran escala (UK Biobank, etc.), fenotipado por acelerometro/actigrafia, PRS; R/Python</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>desconocido - revisar la pagina 'team/positions' del Saxena Lab; laboratorio grande y conocido con rotacion</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Laboratorio permanente financiado por NIH en MGH/Broad; subvencion 2025-26 especifica no confirmada</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Correo en frio a Saxena o Dashti - gancho: su review en revision en Journal of Sleep Research + interes en genetica del sueno; ofrecer habilidades de genetica estadistica (linea 1) aplicadas al sueno (linea 3)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Trabajo de GWAS de score compuesto de salud del sueno (2025); previo GWAS de referencia de duracion habitual del sueno (Nat Commun)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>El laboratorio de genetica del sueno mas conocido del mundo - encaja con la linea 3 (genetica del sueno) ejecutada con metodos de linea 1. Sueno adulto mas que infantil, asi que el correo debe notar su angulo de genetica del sueno infantil como extension complementaria. Visado EE.UU. (marcar). Buena diana si quiere hacer de la genetica del sueno su titular en vez de la psiquiatrica.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Laboratorio de elite Harvard/Broad de genetica del sueno, alta demanda de candidatos</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>https://saxena.mgh.harvard.edu/</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Perfiles MGH/HMS/Broad + articulo Nat Commun en resultados; no abri el sitio del laboratorio yo misma</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>L-0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Estonian Genome Centre / grupo de genetica estadistica del Estonian Biobank</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Reedik Magi (con Kristi Lall)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Institute of Genomics, University of Tartu</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Tartu</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>GWAS de rasgos complejos, epidemiologia genetica a escala de biobanco, PRS para traslacion clinica, fenotipado de datos de atencion primaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>GWAS de biobanco (&gt;212k EstBB), PRS, meta-analisis; R, herramientas tipo PLINK</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>desconocido - revisar la pagina de empleo de la University of Tartu / Institute of Genomics</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Infraestructura nacional de biobanco + programas UE de medicina personalizada (fuente: articulos de perfil de EstBB 2025)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Correo en frio a Magi/Lall - gancho: geneticista estadistica (PLINK/R) con formacion clinica/de medicina de laboratorio, bien situada para la traslacion de PRS de biobanco a la clinica; preguntar por lineas postdoc</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>'Diverse landscape of genomic research within the Estonian Biobank' (Hum Mol Genet, 2025); caracterizacion de variantes de GWAS de IMC en EstBB (Nat Commun, 2025)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Encaje solido de linea 1 (genetica estadistica de rasgos complejos) en un entorno UE/sin visado con un angulo de traslacion clinica que encaja con su residencia de Medicina de Laboratorio. Menor perfil que los mega-hubs = mejores probabilidades. El correo debe conectar sus habilidades de PRS/PLINK con el trabajo de rasgos complejos a escala de biobanco y su mirada MD/medicina de laboratorio con el despliegue clinico de PRS.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fuerte pero menos saturado globalmente que las insignias RU/NL/EE.UU.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://genomics.ut.ee/en</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Articulos de perfil de EstBB 2025 + perfiles de investigadores en resultados; no abri una pagina del grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>L-0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Grupo de Neurogenetica (Depto de Genetica, UB)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bru Cormand</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Universitat de Barcelona / IBUB / CIBERER</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Genetica de trastornos neuropsiquiatricos/del neurodesarrollo (TDAH, TEA, migrana, uso de sustancias), GWAS + variantes raras + funcional</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>GWAS, secuenciacion de exoma, PRS/solapamiento poligenico, transcriptomica, modelos animales</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>desconocido - los grupos espanoles suelen contratar via convocatorias nacionales (Juan de la Cierva, Margarita Salas) a las que podria co-solicitar</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Grupo de larga trayectoria financiado por MICIN/CIBERER; subvencion actual especifica no confirmada</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Correo en frio a Cormand (en espanol) - gancho: opcion en su pais, sin reubicacion; su interes en TDAH/GWAS psiquiatrico + PLINK/R encaja con su trabajo de solapamiento poligenico; proponer co-solicitar una beca postdoc espanola</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Contribuidor al GWAS de TDAH que identifico 27 loci; trabajo 2025 sobre variantes comunes+raras en TDAH (genes cerebelosos/inmunes)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Plausible con reencuadre: fuerte en genetica psiquiatrica/del neurodesarrollo (linea 2) pero mas molecular/funcional que su nucleo de genetica estadistica pura, asi que ella se encargaria de la parte de estadistica/PRS. Su valor es como su alternativa en Espana/sin reubicacion, alineada con su deseo #2 (permanecer en el sistema espanol) - una co-solicitud de beca aqui la mantiene en el pais haciendo investigacion. El correo debe vender el complemento de genetica estadistica y la via de beca conjunta.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Grupo espanol consolidado; contratacion condicionada a becas nacionales</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>https://www.ub.edu/genetica/</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Perfiles IBUB/UB + ResearchGate y articulos de GWAS de TDAH en resultados; no abri una pagina actual del grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>L-0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Language &amp; Genetics / genomica estadistica (Max Planck)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sin confirmar (Max Planck Institute for Psycholinguistics; probablemente el depto de Simon Fisher)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Max Planck Institute for Psycholinguistics</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Nijmegen</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Genomica estadistica de rasgos relacionados con lenguaje/cognicion, genetica de rasgos complejos</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>GWAS, metodos cuantitativos de genomica estadistica; R/Python</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ABIERTO: plaza de genomica estadistica, candidaturas revisadas de forma rodante desde el 8-oct-2026 hasta cubrir (segun listado del tablon BGA)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Financiacion nuclear Max Planck (bien dotada); subvencion de proyecto especifica no confirmada</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Solicitar la plaza anunciada y/o escribir al PI contratante - gancho: su caja de herramientas de genetica estadistica (PLINK/R, Python asistido por IA) es transferible a rasgos de cognicion/lenguaje</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>No capturado en esta busqueda (la plaza surgio via el tablon de empleo de BGA)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Plausible con reencuadre: plaza de genomica estadistica abierta, financiada, UE/sin visado, pero el foco fenotipico (lenguaje/cognicion) es adyacente a su nucleo mas que psiquiatrico/sueno, asi que necesitaria enmarcar sus metodos como portables. Merece una candidatura dada la convocatoria abierta; menor prioridad que las dianas claramente psiquiatricas/de sueno. Confirmar el PI/depto exacto antes de solicitar.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Convocatoria abierta rodante; el prestigio Max Planck atrae candidatos pero la ventana de revision es amplia</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>https://www.mpi.nl/</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Unica mencion en tablon de empleo (agregacion de anuncios de BGA); PI/depto y subvencion sin confirmar - no abri el anuncio</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z1"/>
+  <autoFilter ref="A1:Z12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16803,24 +19167,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
@@ -16830,8 +19194,8 @@
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="48" customWidth="1" min="25" max="25"/>
+    <col width="52" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16966,8 +19330,1208 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>E-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>World Congress of Psychiatric Genetics (WCPG) 2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Congreso anual</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>International Society of Psychiatric Genetics (ISPG)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Si - ISPG Early Career Investigator Program (ECIP) Travel Award (plazo 2026 14-may, ya pasado)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>La concentracion mas densa del mundo de GWAS/PRS de trastornos psiquiatricos; asisten grupos del PGC. Sede de su linea (2) para contactos y grupos a los que acercarse.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Encaja de lleno con su linea (2): GWAS/PRS psiquiatrico. La mejor sala posible para encontrar grupos de acogida y poner cara a autores del PGC. Contra: el reloj de resumenes y del premio ECIP de 2026 ya cerro (mayo), asi que este ano solo puede asistir/hacer red, no presentar; Reino Unido es viaje barato desde Espana. Mantenerla para el ciclo de resumenes de WCPG 2027.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>https://ispg.net/wcpg-2026/</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Leida la pagina oficial ISPG WCPG 2026. No hay ronda late-breaking. Registro abierto pero sin tabla de tarifas publicada (no verificada).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>E-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ASHG 2026 Annual Meeting</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Congreso anual</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>American Society of Human Genetics (ASHG)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Montreal</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Si - premios de viaje ASHG Trainee/Epstein (no reverificados este ciclo)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>La mayor reunion mundial de genetica humana/estadistica; mucho contenido de genetica estadistica, GWAS y rasgos complejos. Directamente su linea (1).</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Su linea (1), genetica estadistica de rasgos complejos, es la columna vertebral de ASHG. RELOJ VIVO: los resumenes late-breaking abren 10-26 ago 2026 (cierra en ~2 dias); su articulo empirico en Nature Mental Health podria encajar como poster late-breaking si actua ya. Aun sin resumen, es la mejor sala para contactos de metodo. El coste es real (viaje a Canada + tarifa) pero la tarifa trainee es baja.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>https://ashgmeeting.ashg.org/</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Leida la pagina oficial de registro. Resumen regular cerro 18-may-2026; late-breaking 10-26 ago 2026. Early-bird hasta 15-sep-2026: miembro student/trainee 435 USD (~400 EUR), no miembro trainee 775 USD (~710 EUR). Tarifas en USD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>E-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ESHG Conference 2027 (European Human Genetics Conference)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Congreso anual</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>European Society of Human Genetics (ESHG)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2027-06-12</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2027-06-15</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2027-02-04</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2027-02-04</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Si - becas ESHG / apoyo de viaje para jovenes investigadores (no verificado para 2027)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>La principal reunion europea de genetica humana/estadistica; mucho contenido de rasgos complejos y epidemiologia genetica, grupos de la UE a los que podria unirse.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Fuerte encaje para la linea (1) y sus objetivos de reubicacion europea: la sala esta llena de los grupos de la UE a los que realmente se acercaria para un postdoc, y viajar desde Espana es barato. Pista limpia: el plazo de resumenes del 4-feb-2027 esta abierto de par en par, notificaciones a primeros de abril 2027, asi que puede planear un envio real. Algo menos especifico de psiquiatria que WCPG.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://2027.eshg.org/abstracts/</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Fechas/plazo de las paginas oficiales 2027.eshg.org de resumenes y registro via busqueda. Registro abre feb 2027; tarifas aun no publicadas. ESHG 2026 ya celebrado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Behavior Genetics Association (BGA) 2027 Annual Meeting</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Congreso anual</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Behavior Genetics Association (BGA)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Si - premios de viaje BGA para estudiantes/trainees (no verificado para 2027)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>La tribu de la genetica estadistica/conductual: modelos de gemelos, GWAS, PRS de rasgos psiquiatricos y conductuales. Presidenta de programa Sarah Medland (nombre PGC/PRS que le convendria conocer).</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Lo mas 'su gente': BGA es exactamente genetica estadistica/conductual (lineas 1+2), reunion lo bastante pequena para que una doctoranda conozca nombres senior (presidenta de programa 2027 Sarah Medland, anfitrion Scott Vrieze). Alto retorno de visibilidad con competencia moderada. Contra: sede y plazo de resumenes aun por anunciar; revisar de nuevo en otono 2026. BGA 2026 (Amsterdam, junio) ya paso.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>https://bga.org/</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Pagina de futuras reuniones de BGA via busqueda: 29 jun-2 jul 2027, anfitrion Vrieze / presidenta de programa Medland; sede, tarifa y plazo de resumenes TBA. Revisar detalles a finales de 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IGES 2026 Annual Meeting &amp; Education Workshop</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Congreso anual + workshop</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>International Genetic Epidemiology Society (IGES)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Estrie (Esterel Resort), Quebec</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Si - apoyo de viaje/trainee de IGES (no verificado)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Sociedad pequena y centrada en metodos de epidemiologia genetica (metodologia GWAS/PRS, estadistica de rasgos complejos). El workshop educativo se dirige a trainees.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Fuerte encaje de metodos para la linea (1): IGES es donde se discute la metodologia de genetica estadistica en un grupo pequeno y senior, y su workshop educativo esta pensado para alguien de su nivel. El plazo de resumenes (30-may-2026) ya paso y va pegado a ASHG en Quebec, asi que realistamente es objetivo 2027 salvo que ya vaya a ASHG. Registrar y revisar para 2027.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>https://www.geneticepi.org/2026-annual-meeting</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Fechas/plazo de geneticepi.org y listados via busqueda (no fetch directo). Adyacente a ASHG 2026 en Quebec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SOBP 2027 Annual Meeting</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Congreso anual</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Society of Biological Psychiatry (SOBP)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2027-05-06</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2027-05-08</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Si - becas/premios de viaje SOBP (no verificado)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Psiquiatria biologica con una vertiente de genetica/imaging-genetics; solapa su linea (2) pero mas amplia que la genetica estadistica pura.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Encaje plausible via la vertiente de genetica psiquiatrica (linea 2), y oportunidad de conocer grupos de investigacion clinica dado su perfil de MD. Pero es viaje a EE.UU., mas amplio que sus metodos nucleares, y el reloj de resumenes (normalmente ~nov-dic 2026) aun no esta publicado. Menor prioridad que WCPG/ASHG/BGA; registrar y vigilar la convocatoria de resumenes.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>https://sobp.org/</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Fechas (6-8 may 2027, Chicago) de sobp.org via busqueda. Plazo de resumenes aun no anunciado. Tarifas en USD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>E-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sleep Europe 2026 (28th ESRS Congress)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Congreso bienal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>European Sleep Research Society (ESRS)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Maastricht</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Si - becas de viaje/registro ESRS para inicio de carrera (no verificado)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Principal reunion europea de investigacion del sueno; un nicho de genetica/epidemiologia del sueno relevante para su linea (3), sueno infantil.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Plausible via su linea (3), genetica del sueno, y su manuscrito en Journal of Sleep Research: un lugar para encontrar grupos de fenotipos de sueno. Pero es un publico de medicina del sueno mas que de genetica, y el plazo regular de resumenes (~1-abr-2026) ya paso; parece existir una ronda late-breaking pero no pude confirmar su fecha. Viaje barato en la UE es la ventaja. Registrar por los contactos de genetica del sueno.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>https://esrs.eu/sleep-congress/abstracts/</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Fechas de listados ESRS/Congrex via busqueda. La pagina oficial de resumenes devolvio HTTP 403 (bloqueada, un intento) - plazo late-breaking no verificado. Tarifas esperadas en EUR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>E-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SLEEP 2027 (APSS Annual Meeting)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Congreso anual</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Associated Professional Sleep Societies (AASM + Sleep Research Society)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2027-06-05</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2027-06-09</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Si - premios de viaje/merito SRS para trainees (no verificado)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>La mayor reunion de investigacion del sueno (EE.UU.); tiene una via de genetica/epidemiologia del sueno que toca su linea (3).</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Plausible para la linea (3) y el mayor publico de sueno, pero el coste de viaje a EE.UU. es alto para una linea que es la tercera de su lista, y el plazo de resumenes 2027 aun no esta publicado (normalmente ~primeros de dic 2026). Menor prioridad que la opcion europea de sueno; registrar y revisar la convocatoria a finales de 2026.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>https://www.sleepmeeting.org/</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Fechas (5-9 jun 2027, Denver) de sleepmeeting.org/eMedEvents via busqueda. Plazo de resumenes aun no publicado. Tarifas en USD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E-0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Neuroscience 2026 (SfN Annual Meeting)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Congreso anual</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Society for Neuroscience (SfN)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Si - SfN Trainee Professional Development Award (TPDA) (no verificado)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Reunion de neurociencia enorme y amplia; el contenido de genetica estadistica queda diluido entre decenas de miles de asistentes.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Solo registrado: demasiado amplio y grande para su foco estrecho en genetica estadistica, y el viaje a EE.UU. es caro para bajo retorno dirigido. Nota: hay una ventana late-breaking 8-15 sep 2026 si alguna vez quisiera visibilidad neuro general.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://www.sfn.org/meetings/neuroscience-2026</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Fechas y ambas ventanas de resumenes (regular 27 may-10 jun; late-breaking 8-15 sep 2026) de la web oficial sfn.org via busqueda. Tarifas en USD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>E-0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FENS Forum 2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Foro bienal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Federation of European Neuroscience Societies (FENS)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Si - becas de viaje del FENS Forum (confirmadas para 2026)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>El mayor foro de neurociencia de Europa (8.000+); amplio, poco contenido dedicado a genetica estadistica.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Solo registrado: ya paso (6-10 jul 2026, en Barcelona - habria sido barato para ella) y FENS es bienal, asi que la proxima edicion es 2028. Demasiado amplio para sus metodos nucleares. Anotar para 2028 solo si quiere presencia neuro general en casa.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>https://fensforum.org/</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Web oficial fensforum.org via busqueda: resumen regular 5 feb 2026, late-breaking 27 abr 2026 (ambos pasados); evento en jul 2026. Bienal - proximo Forum 2028.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z1"/>
+  <autoFilter ref="A1:Z11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16978,21 +20542,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="51" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -17002,8 +20566,8 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="52" customWidth="1" min="22" max="22"/>
+    <col width="52" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17123,8 +20687,650 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>International Statistical Genetics Workshop (el 'Boulder Workshop')</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Institute for Behavioral Genetics, University of Colorado Boulder</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Boulder, Colorado, USA (presencial)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2027-03-05</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ISG International Scholar &amp; Cultural Exchange Program (ISCEP), financiado por Regeneron Genetics Center, ofrece becas; ademas descuentos de matricula por necesidad via formulario de ayuda financiera. Importes 2027 aun no publicados.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Su diana: de lleno en su tecnica nuclear independiente (genetica estadistica, modelos biometricos/de gemelos, OpenMx, GWAS, Genomic SEM, aleatorizacion mendeliana). 2027 es la edicion PRESENCIAL (2026 fue virtual), que es la version que merece el viaje. La financiacion (ISCEP + descuentos por necesidad) puede cubrir gran parte del coste. Solo 5 dias, bajo esfuerzo para asistir una vez abran fechas/registro.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>https://www.colorado.edu/ibg/workshop-2027</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Fechas leidas en la pagina oficial 2027. Tarifa/plazo 2027 AUN no publicados; como referencia la tarifa academica presencial 2023 fue 600 USD early / 700 late (~560-650 EUR), no academica 1000 USD. El registro suele abrir ~enero; contacto IBGworkshop@colorado.edu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Genetic Epidemiology (short course)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>University of Bristol, Bristol Medical School / MRC IEU</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Short course</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2027-01-27</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2027-02-03</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>desconocido - elegibilidad gratuita/con descuento via la pagina de 'fees and voucher packs' de Bristol; sin importes indicados.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Profundiza su caja de herramientas nuclear de genetica estadistica/GWAS dentro de un marco riguroso de epidemiologia genetica (heredabilidad, asociacion, confusion, contexto de PRS). Online, poca logistica, encaja entre su doctorado y su residencia. La financiacion solo lo cubre si cumple para los vouchers de Bristol; si no, autofinanciado.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1.250 GBP -&gt; ~1.470 EUR (tasa ~1,18). Se imparte 27-29 ene + 1-3 feb 2027. El registro de cuenta abre 23-sep-2026, las reservas abren 7-oct-2026, cierran ~2 semanas antes del inicio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mendelian Randomization (short course)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>University of Bristol, Bristol Medical School / MRC IEU</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Short course</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2027-03-15</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2027-03-19</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>desconocido - elegibilidad gratuita/con descuento via la pagina de 'fees and voucher packs' de Bristol; el personal/PGR de Bristol tiene acceso gratuito autoguiado.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>La MR es una extension natural y de alto valor de sus habilidades de GWAS/PRS para inferencia causal en genetica psiquiatrica/de rasgos complejos (lineas 1-2). Impartido por la unidad lider del campo (MRC IEU). Online, esfuerzo XS. Autofinanciado salvo elegibilidad de voucher.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>880 GBP -&gt; ~1.035 EUR (tasa ~1,18). Las reservas del programa 2026/27 abren 7-oct-2026; cierran ~2 semanas antes del inicio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Genetic Analysis of Population-based Association Studies</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Wellcome Connecting Science (Wellcome Genome Campus)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Practical course</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Wellcome Genome Campus, Hinxton, UK (residencial)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Becas limitadas que ofrecen hasta 50% de reduccion de matricula (segun la ultima edicion).</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Directamente en su nucleo: GWAS practico / analisis de asociacion basado en poblacion - refuerza las habilidades exactas que usa de forma independiente y la situa en una cohorte internacional fuerte. Candidatura selectiva. AUN no hay edicion 2026/2027 confirmada - elemento de vigilancia; residencial en RU.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>https://coursesandconferences.wellcomeconnectingscience.org/event/genetic-analysis-of-population-based-association-studies-20240902/</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Solo la edicion de sep 2024 esta viva (820 GBP incl. alojamiento/comidas -&gt; ~965 EUR; candidaturas cerradas). Se imparte aproximadamente anual/bienal; sin fecha futura publicada. Perseguir la convocatoria de 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CAJAL Course: Neurobiology of Sleep</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CAJAL Advanced Neuroscience Training Programme / Bordeaux School of Neuroscience</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Practical course</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bordeaux, France</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>desconocido - los cursos CAJAL suelen ofrecer becas/exenciones de matricula; no confirmado para este curso. Verificar.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Toca su linea de sueno (#3) pero es neurobiologia de sueno de laboratorio humedo, NO estadistica/genetica - fuera de sus tecnicas; el plazo es 2026-08-27 (a 3 dias), practicamente inviable ahora, y es un bloque de 3 semanas que choca con la residencia. Solo registrar.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>https://cajal-training.org/courses/</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fechas y plazo del 27-ago de la pagina de cursos de CAJAL; tarifa no listada. La pagina del curso individual dio 404.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Statistical Analysis of Genome Scale Data</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cold Spring Harbor Laboratory (CSHL)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Practical course</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cold Spring Harbor, NY, USA (residencial)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4420</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>~la mitad de los trainees reciben ayuda por necesidad; los participantes internacionales pueden solicitar apoyo HHMI.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Prestigioso y fuerte en estadistica genomica/R-Bioconductor, pero su alcance es RNA-seq/ChIP-seq/ATAC-seq mas que su nucleo de GWAS/PRS, y es costoso y residencial en EE.UU. Edicion 2026 ya pasada - vigilar 2027 como opcion de menor prioridad.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://meetings.cshl.edu/courses.aspx?course=C-DATA</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Edicion 2026: 5-19 jun 2026, plazo 20-abr-2026 (ambos PASADOS); 4.790 USD incl. pension completa -&gt; ~4.420 EUR. Recurre anualmente; fechas 2027 aun no publicadas.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
+  <autoFilter ref="A1:W7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18094,12 +22300,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
@@ -18369,8 +22575,112 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SUB-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ISPG - membresia / avisos del WCPG y ECIP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://ispg.net/membership/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Avisos del World Congress of Psychiatric Genetics (plazo de resumenes, registro), del Early Career Investigator Program (premio de viaje + mentoria) y del tablon de empleo de la ISPG.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>El WCPG es la sede central de sus lineas 1-2 y el reloj de resumenes/ECIP se pierde facil (el de 2026 ya cerro en mayo). La membresia canaliza el aviso del ciclo 2027 con margen para preparar un resumen y solicitar el ECIP.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>URL de alta sin verificar en esta pasada. Anadida por la rutina ecosystem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SUB-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IBG Boulder Workshop - lista de avisos de la convocatoria</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.colorado.edu/ibg/workshop-2027</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aviso de apertura de registro, tarifa, plazo y becas ISCEP del International Statistical Genetics Workshop.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Es su formacion diana (Fit 5, competencia LOW) y la edicion 2027 es presencial; la tarifa/plazo aun no estan publicados, asi que el aviso evita perder la ventana de registro (~ene 2027) y de beca ISCEP.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>No hay formulario de alta claro; alternativa: escribir a IBGworkshop@colorado.edu pidiendo aviso de la convocatoria 2027. URL sin verificar como pagina de alta. Anadida por la rutina ecosystem.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J5"/>
+  <autoFilter ref="A1:J7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -30,10 +30,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1076,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>afinada tras definir el perfil, 2026-08-23</t>
+          <t>afinada tras definir el perfil, 2026-08-23. BLOQUEO CONOCIDO: las paginas HTML de isciii.es dan 503, pero los endpoints de PDF de las convocatorias SI descargan (ver SRC-0056). Espejo alternativo: SRC-0085 (IIS Aragon). Disparador canonico de la AES: el extracto del BOE de la segunda quincena de diciembre (SRC-0086).</t>
         </is>
       </c>
     </row>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>afinada tras definir el perfil, 2026-08-23</t>
+          <t>afinada tras definir el perfil, 2026-08-23. BLOQUEO CONFIRMADO 2026-08-24: wellcome.org devuelve 403 al rastreo automatico en dos pasadas seguidas, tambien en su pagina de plazos. No gastar mas llamadas aqui: usar el espejo SRC-0083 (CATCH). Ademas, desde el 29-10-2026 solo admite centros de acogida en Reino Unido y paises de renta baja/media: Espana nunca ha sido elegible.</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,11 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -4006,7 +4010,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4058,7 +4062,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4110,7 +4114,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4318,7 +4322,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4370,7 +4374,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4422,7 +4426,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4474,7 +4478,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4526,7 +4530,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4578,7 +4582,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4682,7 +4686,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5046,7 +5050,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5367,8 +5371,216 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SRC-0083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CATCH (Universidad de Bristol) - espejo de las Wellcome Early-Career Awards</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.catch.ac.uk/research-grants-and-awards/wellcome-early-career-awards/</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>El cuadro de datos de la convocatoria de Wellcome (apertura, cierre con hora, paises de acogida elegibles, duracion e importe), reproducido literalmente del texto de Wellcome.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Leer el cuadro de la convocatoria y comparar semana a semana la linea de cierre y la LISTA DE PAISES elegibles; esa lista cambia el 29-10-2026 y ese cambio altera por si solo si Espana sirve como centro de acogida.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>mensual</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Existe porque wellcome.org devuelve 403 al rastreo automatico dos pasadas seguidas, incluida su pagina de plazos. Al usar espejos universitarios hay que anotar SIEMPRE si la fecha publicada es la del financiador o la interna del centro: es justo la ambiguedad entre el 10 y el 16 de noviembre de 2026. Anadida por la rutina fellowships.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SRC-0084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>JSPS - indice de bases de las becas internacionales (Open Call)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.jsps.go.jp/english/e-fellow/application.html</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>El PDF anual 'FY20XX Application Guideline' con la tabla de plazos de las dos convocatorias del programa Standard [P] y las ventanas de incorporacion.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Seccion '3. APPLICATION DEADLINES...' DENTRO del bloque 'Postdoctoral Fellowship (Standard) [P]' (el PDF repite esa seccion para [PE], [L] y [S]: anclarse al encabezado del bloque). El PDF sigue un patron de URL predecible, .../application_requirements/&lt;ejercicio&gt;/&lt;ejercicio&gt;_applicationguideline_e.pdf, asi que se puede sondear el ejercicio siguiente.</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>mensual</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Lo que hay que cazar aqui es la publicacion del ejercicio FY2028, que es la convocatoria que le encaja. El PDF no se deja resumir automaticamente: extraer el texto en local. Anadida por la rutina fellowships.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SRC-0085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>IIS Aragon - espejo de las resoluciones de la AES del ISCIII</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.iisaragon.es/</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Los PDF de la resolucion de la Accion Estrategica en Salud replicados a los pocos dias de publicarse, que es de donde salen Rio Hortega, Sara Borrell y Miguel Servet.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Buscar en el sitio 'AES_&lt;ano&gt;.pdf' bajo /wp-content/uploads/&lt;ano&gt;/12/, o recorrer su listado de convocatorias cada diciembre buscando 'Accion Estrategica en Salud'.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>mensual</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Rodea el 503 cronico de las paginas HTML de isciii.es. Segunda via, no primera: el disparador canonico sigue siendo el extracto del BOE de diciembre. Anadida por la rutina fellowships.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SRC-0086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BOE - extractos de convocatorias del ISCIII y de la AEI</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.boe.es/buscar/boe.php</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>El anuncio oficial, el mismo dia, de la AES del ISCIII (diciembre) y de las ayudas Juan de la Cierva de la AEI (finales de octubre): las dos convocatorias cuyos dominios propios no se dejan rastrear.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Dos busquedas semanales acotadas a los ultimos 7 dias: "Instituto de Salud Carlos III" "tramitacion anticipada" y "Presidencia de la Agencia Estatal de Investigacion" "Juan de la Cierva".</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Serie verificada de la AES: BOE-B-2023-38433, BOE-B-2024-45526, BOE-B-2025-47164; el de la AES 2027 caera en la segunda quincena de diciembre de 2026. Evita depender de agregadores que esta pasada han demostrado publicar convocatorias reetiquetadas (fibao.es) o fechas sin respaldo (tesify.es). Distinto de SRC-0028, que vigila el BOE por la especialidad de Genetica. Anadida por la rutina fellowships.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J83"/>
+  <autoFilter ref="A1:J87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5499,7 +5711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8960,8 +9172,488 @@
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>F-0007</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>HFSP Postdoctoral Fellowships</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Se deshace el conflicto registrado la semana pasada: el doctorado NO se exige al solicitar. La cita contraria era una alucinacion del resumidor de PDF, no una fuente. Verificado con extraccion local del PDF oficial. Ademas, en fase de LOI vale un preprint.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.hfsp.org/funding/hfsp-funding/postdoctoral-fellowships</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>F-0012</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Wellcome Early-Career Awards</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Espana NO es centro de acogida elegible: solo Reino Unido, Irlanda y paises de renta baja/media, y desde el 29-10-2026 tampoco Irlanda. Techo de 3 anos posdoctorales confirmado; la formacion clinica se descuenta. Corte del 10-11-2026 confirmado; se retira el ~06-04-2027 por falta de respaldo.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://www.catch.ac.uk/research-grants-and-awards/wellcome-early-career-awards/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>F-0002</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Contratos Sara Borrell</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Resuelto a su favor: basta la certificacion universitaria de lectura y aprobacion de la tesis, no hace falta el titulo expedido (art. 41.1.b de la AES 2026). Una defensa en febrero de 2028 llega al cierre de la AES 2028.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>F-0022</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>JSPS Standard Program</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Plazos FY2027 verificados (28-08-2026 y 23-04-2027); ninguno le sirve. Su convocatoria es la primera de FY2028, hacia agosto de 2027. Presenta el anfitrion japones, no ella, y las instituciones cierran internamente con mas de un mes de antelacion.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.jsps.go.jp/english/e-fellow/application.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>F-0024</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>L'Oreal-UNESCO For Women in Science Espana</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Respondida la pregunta abierta: el contrato MIR no sirve, hace falta contrato de investigacion con el centro que presenta, mas 4 anos desde la lectura de la tesis y una estancia previa de 2 anos. No elegible hasta ~2032. Baja de Fit 3 a 2.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://www.forwomeninscience.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>F-0030</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Premio Instituto de Neurociencias Federico Oloriz</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Admite predoctorales matriculadas: es elegible YA. Edicion 2026 cerrada el 05-06-2026, 1.250 EUR, articulo publicado en 2023-2025. Competencia LOW y esfuerzo XS.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://ineurociencias.ugr.es/instituto/noticias/premio-instituto-neurociencias-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>F-0034</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Stanley Center Sklar Program</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cerrada definitivamente: el Broad confirma que la ultima beca Sklar se concedio en 2024. Lo que queda exige ciudadania o residencia estadounidense y ser residente de psiquiatria en dos programas concretos. No volver a revisarla.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.broadinstitute.org/stanley-center-sklar-program</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>F-0004</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Juan de la Cierva</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>La 'convocatoria JDC 2026' no existe: la ultima publicada es la de 2025 (BOE-B-2025-39640, plazo 25-11 a 10-12-2025). fibao.es la reetiqueta como 2026 y tesify.es publica fechas sin respaldo oficial. Se cambia la URL al BOE porque aei.gob.es acumula cuatro 503.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.boe.es/diario_boe/txt.php?id=BOE-B-2025-39640</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>F-0018</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ERC Starting Grant</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>El cambio de ventana es real, no un error de lectura: 2-7 anos rige en las convocatorias de 2026 y 0-10 anos desde las de 2027. Se cuenta desde la defensa certificada. Nueva regla de una StG y una CoG por carrera.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://erc.europa.eu/apply-grant/starting-grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Repaso de la watchlist</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>11 de 14 filas revisadas. Reabiertas dos: la Caixa Junior Leader Incoming 2027 (cierra 23-09-2026, ella no es elegible) y, probablemente, las Becas de Investigacion de la SES. Fechas nuevas en BBRF (05-03-2027) y SLEEP 2027 (Denver, 5-9 de junio). Correccion de etiquetado en la ronda de la NHMRC. Sin revisar: W-0003, W-0004, W-0013 y W-0014.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Ampliacion de la superficie de vigilancia</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>4 fuentes nuevas, todas para rodear dominios que bloquean el rastreo: espejo de Wellcome en CATCH, indice de bases de JSPS, espejo de la AES en el IIS Aragon y el buscador del BOE con las consultas exactas de ISCIII y AEI.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>subscriptions</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Alertas propuestas</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2 altas TODO (tope por pasada): lista de avisos de la Sleep Research Society y alta como socia de la SES, esta ultima porque la membresia es requisito de sus propias becas y podria exigir un ano de antiguedad.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H84"/>
+  <autoFilter ref="A1:H96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13015,7 +13707,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Art. 34 AES 2026, literal: '1o. Estar en posesion del titulo oficial de Especialidad Medica (MIR), Farmaceutica (FIR), o del certificado oficial de especialidad en Biologia (BIR), Quimica (QIR), Bioquimica, Psicologia (PIR), Enfermeria (EIR) o Radiofisica Hospitalaria (RIR).' Y '2o. Haber finalizado el programa de FSE ... durante el ano 2021, o en fecha posterior, incluyendo a los que lo hagan en 2026, siempre que sea con anterioridad a la fecha que se establezca para la finalizacion del plazo de alegaciones a la resolucion provisional de concesion.' NO se menciona el titulo de doctor en ningun punto de los arts. 31-36. No haber disfrutado ya un Rio Hortega.</t>
+          <t>Cita literal, AES 2026 art. 34, requisito 2o: 'Haber finalizado el programa de FSE que habilita para participar en esta actuacion durante el ano 2021, o en fecha posterior, incluyendo a los que lo hagan en 2026, siempre que sea con anterioridad a la fecha que se establezca para la finalizacion del plazo de alegaciones a la resolucion provisional de concesion.' Plazo Rio Hortega 2026 (art. 7.6): del 10 de febrero al 5 de marzo de 2026. Solicita el centro, no la candidata.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -13050,7 +13742,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -13060,24 +13752,24 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Antes de diciembre de 2026: identificar y abordar a un jefe de grupo (IBIMA / Hospital Regional Universitario de Malaga primero, por estar ya alli; una segunda opcion en otro IIS). Cuando aparezca la resolucion AES 2027 en el BOE (previsible en diciembre de 2026), releer el art. 34.2o para confirmar que dice '2022 o posterior, incluyendo a los que lo hagan en 2027' y que la fecha de alegaciones cae despues del 22-05-2027.</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Antes de diciembre de 2026: identificar y abordar a un jefe de grupo (IBIMA / Hospital Regional Universitario de Malaga primero, por estar ya alli; una segunda opcion en otro IIS). Cuando aparezca la resolucion AES 2027 en el BOE (previsible en diciembre de 2026), releer el art. 34.2o para confirmar que dice '2022 o posterior, incluyendo a los que lo hagan en 2027' y que la fecha de alegaciones cae despues del 22-05-2027.</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
@@ -13085,7 +13777,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Rama 2. Tier 1: texto integro de la resolucion de la AES 2026 descargado de isciii.es y extraido localmente (las paginas HTML de isciii.es devuelven HTTP 503 al fetch automatico, pero el endpoint del documento si descarga). Plazos en el art. 7.6; condiciones en los arts. 31-34.</t>
+          <t>Resolucion AES 2026 del ISCIII (19-12-2025), PDF descargado y extraido en local. Las paginas HTML de isciii.es dan 503, pero el endpoint del PDF descarga bien. Espejo alternativo verificado: https://www.iisaragon.es/wp-content/uploads/2025/12/AES_2026.pdf . PENDIENTE: no se ha localizado en el texto que fecha concreta fija la AES para el fin del plazo de alegaciones a la resolucion provisional; ese dato es el que decide si el fin de su residencia (22-05-2027) cae dentro del plazo en la edicion 2027.</t>
         </is>
       </c>
     </row>
@@ -13144,7 +13836,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Art. 40.1.a) literal: 'Haber obtenido el doctorado, entendiendose como tal la fecha de lectura y aprobacion de la tesis doctoral, en fecha posterior al 1 de enero de 2022.' El titulo de doctor o certificacion universitaria con la fecha debe presentarse CON la solicitud (art. 41.1.b), asi que en la practica la tesis debe estar leida antes del plazo: Sara Borrell NO admite 'doctorado antes de empezar'. No haber disfrutado ya un Sara Borrell.</t>
+          <t>Requisito, art. 40.1.a): 'Haber obtenido el doctorado, entendiendose como tal la fecha de lectura y aprobacion de la tesis doctoral, en fecha posterior al 1 de enero de 2022.' Y la clausula que resuelve la duda abierta la semana pasada, art. 41.1.b) (documentacion): 'Titulo de doctor O certificacion emitida por las universidades, con firma verificable, en la que figure indicacion expresa de la fecha de obtencion del grado de doctor.' Es decir: BASTA EL CERTIFICADO DE LECTURA Y APROBACION, no hace falta el titulo expedido ni el pago de tasas.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -13154,7 +13846,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>El paso natural despues de Rio Hortega y el mejor contrato posdoctoral puro de Espana para una medica que quiere un centro investigador con cara asistencial. Punto por punto: (a) el doctorado debe estar leido antes del plazo: con una ETA de febrero de 2028, la AES 2028 (plazo ~5 de marzo de 2028) va al filo y depende de que la defensa ocurra de verdad en febrero y de que la certificacion se emita a tiempo; lo realista es apuntar a la AES 2029, donde una defensa de febrero de 2028 queda comodamente dentro de la ventana. (b) Despues sigue elegible hasta aproximadamente la AES 2032, o sea cuatro intentos reales y no uno. (c) La residencia no estorba: acaba el 22-05-2027, mucho antes de cualquier solicitud. (d) La regla de cambio de grupo le resulta facil: su tesis es de la Universidad de Murcia, asi que cualquier grupo de Malaga, Madrid, Barcelona, Valencia o Granada la cumple sin necesidad de la exencion del ano en el extranjero (sus estancias de Australia y Japon son de ~3 meses cada una y NO servirian para esa exencion). LINEA CON LA QUE ENCABEZAR: GWAS/PRS de trastornos psiquiatricos y de salud mental, porque Sara Borrell se evalua en un instituto de investigacion sanitaria y la genomica psiquiatrica con angulo de traslacion clinica (estratificacion de riesgo, biomarcadores via un servicio de laboratorio) juega a la vez con su titulo de medicina y con sus pipelines de PLINK/R. NO encabezar con neuroimagen ni electrofisiologia: a nivel supervisado seria sobrevenderse en una convocatoria competitiva. TRABAJO: memoria normalizada, CVA-ISCIII y documentacion del grupo, comparable a Rio Hortega pero con mucho mas peso de las publicaciones, que es hoy su punto debil - conseguir que acepten los dos manuscritos antes de solicitar es la preparacion de mayor valor.</t>
+          <t>Sigue siendo de las de mayor encaje (perfil MD+PhD, centro espanol, linea de genetica estadistica encajable en cualquier IIS) y esta pasada resuelve a su favor la pregunta que decidia un ano entero: NO hace falta el titulo de doctor expedido, basta una certificacion universitaria con la fecha de lectura y aprobacion. Elegibilidad punto por punto: doctorado leido despues del 1 de enero de una fecha movil (en la AES 2026 era 01-01-2022, o sea unos 4 anos de ventana), que con defensa en feb-2028 cumple con holgura; acreditacion por certificado, resuelta; centro de acogida espanol, por conseguir. La AES 2028 cerraria hacia el 5 de marzo de 2028, unas dos semanas despues de su defensa prevista: con el certificado en la mano llega, pero el margen es de semanas, asi que la fecha de defensa deja de ser un detalle academico y pasa a ser una decision estrategica. Trabajo: M, con el centro de acogida como parte mas lenta.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -13179,7 +13871,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -13189,24 +13881,24 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Aparcada hasta 2027, pero con un encargo concreto para entonces: pedir al director de tesis que fije la defensa con margen ANTES del cierre de la AES 2028 (~5 de marzo de 2028) y asegurarse de que la universidad emite la certificacion de lectura y aprobacion en dias, no en meses. Ya no hace falta esperar al titulo.</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Aparcar hasta 2027. El punto de decision es si la defensa de febrero de 2028 cae antes del plazo de la AES 2028 (~5 de marzo de 2028): pedir al director de tesis a mediados de 2027 que fije la fecha, porque defender en febrero o en abril de 2028 la mueve un ano entero en este esquema. Mientras tanto, empujar los dos manuscritos hasta la aceptacion.</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
@@ -13214,7 +13906,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Rama 2. Tier 1: resolucion AES 2026, arts. 37-41 y art. 7.6, leidos en el texto completo extraido del PDF oficial del ISCIII.</t>
+          <t>Resolucion AES 2026 del ISCIII, arts. 40 y 41, PDF extraido en local esta pasada.</t>
         </is>
       </c>
     </row>
@@ -13351,7 +14043,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ayudas para contratos Juan de la Cierva (JDC) 2026</t>
+          <t>Ayudas para contratos Juan de la Cierva (JDC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13394,7 +14086,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>DOCTORADO YA CONCEDIDO EN LA FECHA LIMITE, explicitamente no 'en tramite de defensa'. Ventana de recencia de tres anos contada hacia atras desde el cierre. Es por tanto inelegible en las ediciones de 2026 y 2027.</t>
+          <t>Ultima convocatoria realmente publicada: la de 2025 (Resolucion de 29-10-2025, BOE-B-2025-39640), con plazo del 25-11-2025 al 10-12-2025 a las 14:00 para las personas candidatas y hasta el 17-12-2025 para las entidades. Ventana de doctorado de esa edicion: defensa entre el 01-01-2024 y el 31-12-2025 (turno general), ampliable por bajas y cuidados. La fecha que cuenta es la 'fecha del acto de defensa y aprobacion de la tesis doctoral'.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -13404,7 +14096,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>El contrato posdoctoral temprano por defecto en Espana y un encaje real con su investigacion, pero el reloj descarta las ediciones proximas: con defensa en febrero de 2028 no puede tocar ni la convocatoria de 2026 ni la de 2027, y su primer intento es la JDC 2028 (convocatoria ~noviembre de 2028), donde una defensa de febrero de 2028 cae comodamente dentro de una ventana de recencia de tres anos. Despues sigue elegible hasta aproximadamente la edicion de 2030. Punto por punto: (a) doctorado en la fecha limite: falla hasta 2028, pasa desde 2028; (b) la residencia es irrelevante, acaba el 22-05-2027; (c) no hay regla de movilidad tipo MSCA, asi que las fechas sin fijar de sus estancias de Australia y Japon no importan aqui; (d) ciudadania de la UE y base espanola eliminan cualquier obstaculo administrativo. LINEA CON LA QUE ENCABEZAR: genetica estadistica de rasgos complejos, porque la JDC la evaluan paneles de la AEI donde dominan la solidez metodologica y la trayectoria del grupo de acogida, asi que un proyecto intensivo en PLINK/R con un grupo espanol fuerte de genetica estadistica o genomica (CNAG, CRG, ISGlobal, grupos de genetica psiquiatrica de CIBERSAM) es el encuadre mas potente; GWAS/PRS psiquiatrico es la capa de aplicacion natural. RIESGO A VIGILAR: la AEI ha reestructurado el esquema mas de una vez, asi que esta fila hay que reverificarla cada otono, no reutilizarla.</t>
+          <t>Encaje alto por contenido (contrato posdoctoral de la AEI en cualquier centro espanol, compatible con su linea de genetica estadistica) y ventana de aproximadamente dos anos desde la defensa, que con feb-2028 la situa en la convocatoria de 2028 (cierre previsible en diciembre de 2028), no en ninguna anterior. Elegibilidad punto por punto: doctorado en posesion al solicitar, que en 2028 cumpliria; ventana de anos, holgada; centro espanol de acogida, por conseguir. Sigue sin verificarse un extremo: si la AEI admite certificado de defensa o exige titulo expedido en el momento de acreditar (a diferencia del ISCIII, que si lo aclara). Para ella es secundario, porque hasta diciembre de 2028 tiene margen de sobra. Trabajo: M.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -13424,12 +14116,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -13439,32 +14131,32 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Nada hasta 2028. AVISO ANTIRRUIDO, comprobado esta pasada: la 'convocatoria Juan de la Cierva 2026' que circula por internet NO EXISTE. fibao.es reetiqueta como 2026 la convocatoria de 2025 (mismo BOE-B-2025-39640) y tesify.es publica fechas de 2026 sin ningun respaldo oficial. Vigilar solo el BOE: la resolucion de la AEI aparece a finales de octubre.</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>La duena debe abrir https://www.aei.gob.es/convocatorias/buscador-convocatorias en un navegador (el sitio bloquea el fetch automatico con HTTP 503) y confirmar las fechas de la JDC 2026 y la redaccion exacta sobre la fecha del doctorado, que es la que gobernara su intento de 2028.</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>https://www.aei.gob.es/convocatorias/buscador-convocatorias</t>
+          <t>https://www.boe.es/diario_boe/txt.php?id=BOE-B-2025-39640</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Rama 2. Solo Tier 2: paginas de oficinas de investigacion y agregadores espanoles (FIBAO, OTRI UMH, tesify) que coinciden en el calendario AEI 2026 (12 nov - 3 dic 2026). Las paginas propias de la AEI, incluido el 'Calendario previsto de convocatorias', devolvieron 503.</t>
+          <t>aei.gob.es acumula CUATRO URLs con 503 entre esta pasada y la anterior, incluido su endpoint de PDF: el dominio se da por inaccesible al rastreo automatico y se sustituye por el BOE como fuente Tier 1.</t>
         </is>
       </c>
     </row>
@@ -13776,12 +14468,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>'Applicants are not eligible if the doctoral degree has been conferred more than 3 years (36 months) prior to the submission deadline of the Full Proposal', con exenciones por enfermedad, permisos parentales, cuidados y servicio militar. No hay minimo: se admite un doctorado aun no concedido.</t>
+          <t>NO se exige el doctorado al solicitar. Cita literal de las bases oficiales (AY2027, sec. 3.7): 'The applicant must have completed their PhD or a comparable doctoral degree with equivalent research experience (for instance, an MD, medical PhD, or DEng) before starting the fellowship, and before 31 December 2027 at the latest. A completed doctoral degree is not required at the time of application.' Techo por arriba: no elegible si el doctorado se confirio mas de 3 anos (36 meses) antes del cierre de la propuesta completa.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>EL PUNTO DECISIVO: el doctorado NO tiene que estar concedido en la fecha limite. Literal de hfsp.org: 'The applicant must have completed their PhD or a comparable doctoral degree with equivalent research experience (for instance, an MD, medical PhD, or DEng) before starting the fellowship, and before 31 December 2027 at the latest' (fecha que se desplaza un ano por cada ano de convocatoria), y no se exige doctorado completado en el momento de la carta de intencion. Ademas: el proyecto debe suponer un cambio real de direccion investigadora hacia una pregunta interdisciplinar de frontera. LTF es la via para quien tiene doctorado en ciencias de la vida; CDF es para doctorados en fisica/matematicas/informatica con poca experiencia biologica, que no es su caso.</t>
+          <t>Movilidad internacional real (cambio de pais y de campo). Publicacion: en la fase de LOI vale un manuscrito de primera autora publicado, aceptado, en prensa O EN PREPRINT; en la propuesta completa el preprint ya no vale. Ciclo AY2027 (cerrado): LOI iniciada antes del 05-05-2026 y presentada antes del 12-05-2026, propuesta completa 24-09-2026, incorporacion entre 01-04-2027 y 01-01-2028.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -13791,7 +14483,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>El buque insignia cuyo reloj SI encaja con el suyo, y por eso es la pieza central del plan de 2027. Solicitar a la convocatoria del ano 2028 significa una LOI hacia mayo de 2027 -el mismo mes en que acaba la residencia, el 22-05-2027-, propuesta completa hacia septiembre de 2027, decision hacia marzo de 2028 (un mes despues de su defensa prevista) y activacion entre abril de 2028 y enero de 2029, con el doctorado exigido solo antes de empezar y antes del 31 de diciembre de 2028. Todos sus relojes pasan: no hace falta doctorado al presentar, no hay minimo posdoctoral, y el tope de 3 anos se cumple trivialmente porque el titulo ni siquiera estara concedido en la fecha limite. LINEA CON LA QUE ENCABEZAR: genetica estadistica de rasgos complejos reformulada como problema de frontera en un laboratorio que NO sea principalmente de genetica estadistica; HFSP premia entrar en territorio nuevo y penaliza la continuidad con la tesis, asi que el discurso es 'medica + genetica estadistica que se mueve hacia X' (genomica funcional o de celula unica, neurobiologia del sueno, neurociencia computacional), no 'mas GWAS'. Su combinacion MD+PhD y las estancias de QIMR y Japon son justo la evidencia interdisciplinar que HFSP busca. SU DEBILIDAD REAL es el expediente de publicaciones: dos manuscritos de primera autora en revision, y conseguir que ambos se acepten antes de septiembre de 2027 cambia materialmente la solicitud. Elegibilidad punto por punto: nacionalidad espanola -&gt; acogida fuera de Espana; doctorado espanol -&gt; Espana tambien excluida por esa via; las dos estancias de ~3 meses estan holgadamente por debajo del tope acumulado de 12 meses, asi que Australia y Japon siguen siendo paises de acogida validos, pero conviene fijar las fechas exactas antes de contar con ello. TRABAJO: alto (L), identificacion de acogida y proyecto co-escrito, 2-4 semanas de escritura concentrada sobre meses de cortejo; el filtro real es la LOI.</t>
+          <t>CORRECCION DE LA PASADA ANTERIOR: el supuesto conflicto sobre si HFSP exige el doctorado al solicitar NO EXISTIA. El PDF oficial dice exactamente lo contrario de lo que se registro la semana pasada; la frase erronea la fabrico el resumidor automatico de PDF, no una fuente. Verificado extrayendo el texto del PDF en local: 'A completed doctoral degree is not required at the time of application'. Consecuencia para ella: HFSP SI es un buque insignia internacional alcanzable antes de defender. Su ciclo es AY2028 (el AY2027 ya cerro y ademas exigia doctorado antes del 31-12-2027, incompatible con una defensa en feb-2028). Se presenta con la genetica estadistica de rasgos complejos como linea principal y el salto de campo como argumento central, que es justo lo que HFSP premia. Elegibilidad punto por punto: doctorado al solicitar NO se exige (verificado); techo de 3 anos post-doctorado no la afecta (no habra defendido); movilidad, cualquier pais salvo Espana sirve; el requisito de publicacion es el unico que aprieta, y en fase de LOI se satisface CON UN PREPRINT, asi que depositar en bioRxiv/medRxiv uno de los dos manuscritos en revision la vuelve elegible sin depender del calendario de los revisores. Trabajo: L (2-4 semanas) entre LOI y propuesta, mas el tiempo de conseguir laboratorio de acogida, que hay que abrir en enero de 2027 como muy tarde.</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -13816,7 +14508,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -13826,24 +14518,24 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Dos cosas concretas. (1) Depositar como preprint uno de los dos manuscritos de primera autora: satisface el requisito de publicacion en fase de LOI sin esperar a los revisores. (2) De aqui a enero de 2027, preseleccionar de 3 a 5 laboratorios de acogida en el extranjero que supongan cambio real de campo. El calendario del ciclo AY2028 no esta publicado; se espera hacia enero-marzo de 2027 siguiendo el patron del AY2027 (LOI en primavera, propuesta completa en septiembre).</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>De aqui a la primavera de 2027: preseleccionar de 3 a 5 laboratorios de acogida en el extranjero que representen un cambio real de campo y abrir contacto como muy tarde en enero de 2027. Revisar hfsp.org en marzo de 2027 para las fechas de la LOI del ano 2028.</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>https://www.hfsp.org/funding/hfsp-funding/postdoctoral-fellowships</t>
@@ -13851,7 +14543,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Ramas 1 y 5 (fusionadas). Tier 1: pagina de hfsp.org y PDF oficial 'HFSP Fellowships 2027 - Application Guidelines'. CONFLICTO REGISTRADO: la lectura automatica de ese PDF devolvio 'A PhD or equivalent doctorate is required at the time of application', que contradice la pagina web y una segunda fuente independiente. La fila sigue la pagina web, pero la duena deberia leer ella misma las bases del ano 2028 antes de comprometerse.</t>
+          <t>Bases oficiales AY2027 en PDF, texto extraido en local (el resumidor automatico de PDF devolvio una cita INVENTADA e invertida sobre este mismo punto: no aceptar citas de PDF de HFSP sin extraccion local). https://www.hfsp.org/sites/default/files/Sciences/fellows/2027/new/HFSP%20Fellowships%202027%20-%20Application%20Guidelines.pdf</t>
         </is>
       </c>
     </row>
@@ -13917,7 +14609,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>EL PUNTO DECISIVO: el doctorado se exige solo AL EMPEZAR la beca, no en la fecha limite; el FAQ de EMBO dice que se puede solicitar durante el doctorado y 'you must provide us with your PhD degree before the starting date of your fellowship'. SEGUNDA restriccion decisiva: la beca debe iniciarse 'within 9 months of the offer', y eso es lo que fija de verdad su ventana. TERCERA: al menos un articulo de PRIMERA AUTORA aceptado o publicado en revista internacional revisada por pares en el momento de solicitar (vale un preprint de primera autora con revisiones independientes verificables) - hoy NO lo cumple. Movilidad: nada en el laboratorio/instituto/departamento de la tesis, ni volver con el director de tesis este donde este, ni continuar el trabajo doctoral; cambio de pais obligatorio, asi que Espana queda excluida. Desde la ronda de otono de 2027 (solicitudes posteriores al 22-01-2027) ya no se permite volver a solicitar: un solo intento.</t>
+          <t>Cita literal: 'Applicants must have at least one first author publication (research paper) accepted in or published in an international peer reviewed journal at the time of application.' Un preprint SOLO vale si lleva revision por pares publica y en profundidad de un servicio independiente (tipo Review Commons), no un preprint a secas. Doctorado exigido al EMPEZAR, no al solicitar. Quien ya este en el laboratorio de acogida solo puede solicitar si lleva menos de 6 meses viviendo en el pais de acogida. Cierre verificado: viernes 22-01-2027 a las 14:00 CET. Desde la ronda de otono de 2027 se prohiben las resolicitudes.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -13927,7 +14619,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>El instrumento mejor emparejado para un traslado europeo despues de una defensa en febrero de 2028, y sorprendentemente indulgente con el reloj del doctorado: puede solicitar antes de defender. La regla de los 9 meses para incorporarse fija la sincronizacion con precision: una solicitud en el corte de ~julio de 2027 se resolveria hacia noviembre de 2027 y tendria que empezar hacia agosto de 2028, lo que abraza comodamente una defensa de febrero de 2028; una solicitud en el corte del 22-01-2027 se resolveria en primavera de 2027 y caducaria a principios de 2028, demasiado justo para una ETA que puede deslizarse. El objetivo es por tanto el corte de mediados de 2027, con el de enero de 2028 como alternativa. EL BLOQUEO REAL NO ES EL RELOJ SINO LAS PUBLICACIONES: EMBO exige un articulo de primera autora ACEPTADO al presentar, y los dos suyos (revision en Journal of Sleep Research; articulo empirico en Nature Mental Health) siguen en revision. Si ninguno se acepta antes de mediados de 2027 es inelegible, sin matices, asi que perseguir esas decisiones es la accion de mayor valor aqui. LINEA CON LA QUE ENCABEZAR: el trabajo de genetica psiquiatrica derivado de QIMR y la genetica estadistica de rasgos complejos, eligiendo acogida en un entorno molecular, celular o genomico donde ella aporte el lado cuantitativo; el centro de gravedad de EMBO son las ciencias de la vida moleculares, asi que un proyecto puramente epidemiologico de GWAS se lee fuera de mision y necesita un gancho mecanicistico. TRABAJO: L, sobre todo cortejo de acogida mas descripcion conjunta del proyecto. La regla de un solo intento obliga a no quemarlo en un emparejamiento debil.</t>
+          <t>Encaje de fondo alto y un unico requisito que hoy NO cumple, verificado esta pasada palabra por palabra: hace falta un articulo de PRIMERA AUTORA YA ACEPTADO O PUBLICADO en el momento de solicitar. Sus dos manuscritos (revision en Journal of Sleep Research y empirico en Nature Mental Health) siguen en revision, asi que a fecha de hoy es INELEGIBLE, sin matices. La via de rescate NO es un preprint normal: EMBO solo acepta preprints con revision publica independiente. Elegibilidad punto por punto: doctorado al empezar, compatible con defensa en feb-2028 si la incorporacion es posterior; movilidad a Estado miembro de la EMBC, sin problema desde Espana; los 6 meses de residencia previa en el pais de acogida no la afectan; el articulo aceptado es el unico corte real. Linea con la que presentarse: GWAS/PRS de trastornos psiquiatricos. Trabajo: M, unas 3-7 jornadas de escritura una vez haya acogida.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -13952,7 +14644,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -13962,24 +14654,24 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>El cuello de botella es la ACEPTACION de uno de los dos manuscritos: sin eso no hay solicitud posible. Vigilarlo como el hito numero uno. La ronda del 22-01-2027 solo es realista si algo se acepta antes; si no, apuntar a la ronda de otono de 2027 (fecha aun no publicada) teniendo en cuenta que desde esa ronda ya no se permite resolicitar.</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Vigilar la aceptacion de los dos manuscritos de primera autora: son el elemento que condiciona todo. En paralelo, desde principios de 2027 abordar laboratorios de acogida en Estados EMBC (una candidata por laboratorio y ronda, asi que hay que confirmar que nadie mas de ese laboratorio se presenta). Revisar embo.org hacia marzo de 2027 para el corte exacto de mediados de 2027.</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>https://www.embo.org/funding/fellowships-grants-and-career-support/postdoctoral-fellowships/eligibility/</t>
@@ -13987,7 +14679,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Rama 1. Tier 1: paginas de elegibilidad, FAQ y presentacion de las becas posdoctorales de embo.org, leidas el 2026-08-23. La fecha proyectada del corte de mediados de 2027 es LIKELY, no confirmada.</t>
+          <t>https://www.embo.org/funding/fellowships-grants-and-career-support/postdoctoral-fellowships/eligibility/ leida esta pasada; el PDF de guidelines (jun-2026) quedo sin abrir por techo de llamadas.</t>
         </is>
       </c>
     </row>
@@ -14397,12 +15089,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>La institucion de acogida debe estar en el Reino Unido, la Republica de Irlanda o un pais de renta baja o media elegible (excluidas India y China continental). La nacionalidad no es en si una barrera, pero un puesto en el Reino Unido implica patrocinio de visado para una no britanica.</t>
+          <t>Reino Unido y paises de renta baja/media (hasta el 29-10-2026 tambien Irlanda). ESPANA NO ES ELEGIBLE COMO CENTRO DE ACOGIDA, ni antes ni despues del cambio.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OBLIGATORIA: una institucion de acogida elegible debe avalar la solicitud y garantizar el entorno de investigacion; Wellcome espera que se comprometa con su transicion a la independencia. Meses de conversacion previa.</t>
+          <t>Centro de acogida OBLIGATORIO y restringido por pais: solo Reino Unido y paises de renta baja/media. Exige mudanza al Reino Unido.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -14424,12 +15116,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Se informa de hasta tres anos de experiencia posdoctoral al solicitar, con margen por interrupciones, jornada parcial y cambios de disciplina. CONFLICTO A SENALAR: algunas fuentes describen una via de 'doctorado (viva superado) O al menos cuatro anos de experiencia investigadora', y otras una ventana de 5-10 anos posdoctorales; esta ultima corresponde casi con seguridad a los Career Development Awards, un esquema distinto y posterior. Verificar en wellcome.org.</t>
+          <t>Maximo 3 anos de experiencia posdoctoral en la fecha de cierre: 'You may have some postdoctoral experience in your proposed field of study, but no more than three years at the point of the application deadline unless you can demonstrate how other factors have impacted on your research career.' El tiempo fuera de la investigacion (incluida la FORMACION CLINICA) se descuenta expresamente. El doctorado debe estar DEFENDIDO (viva superada) en la fecha de cierre; no vale tesis depositada sin defender.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>La via estandar parece exigir el doctorado (viva superado) al solicitar, es decir concedido en la fecha limite y no al empezar; pero ESTE ES JUSTO EL PUNTO QUE NO SE PUDO VERIFICAR, porque wellcome.org devuelve HTTP 403 al fetch automatico. Rondas multiples al ano: la de julio de 2026 cerro el 21-07-2026 (una fuente dice el 22, conflicto sin resolver) y las siguientes se situan hacia el 10-11-2026 y el 06-04-2027.</t>
+          <t>RESTRICCION DE PAIS DE ACOGIDA, dirimente: 'UK, Republic of Ireland, Low- or middle-income countries (apart from India and mainland China)'. Y desde el 29-10-2026 se estrecha aun mas: solo Reino Unido y paises de renta baja/media de Africa, Asia del Sur y Sudeste Asiatico, es decir Irlanda tambien sale. Ademas, desde el 25-08-2026 el esquema pasa a presentacion CONTINUA con tres cortes al ano (preseleccion en febrero, junio y septiembre), de modo que lo que se registre como 'plazo' son cortes, no cierres duros. Corte inmediato: 10-11-2026.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -14439,7 +15131,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>La opcion britanica mas fuerte para ella, y aquella cuya geografia coincide con donde vive de verdad su campo: KCL/SGDP, el MRC Centre for Neuropsychiatric Genetics and Genomics de Cardiff y Edimburgo son los tres nucleos europeos de genetica psiquiatrica y los tres son acogidas elegibles por Wellcome. Punto por punto: (a) si el techo de tres anos posdoctorales es correcto, su ventana va de la defensa de febrero de 2028 a aproximadamente febrero de 2031 - estrecha, y es la unica ventana donde la incertidumbre de su fecha de defensa muerde de verdad, porque un retraso a finales de 2028 desplaza todas las rondas; (b) la residencia acaba el 22-05-2027, sin choque; (c) como ciudadana de la UE necesita patrocinio de visado britanico, que las universidades elegibles tramitan de forma rutinaria (Global Talent o Skilled Worker): es una senal, no un bloqueo; (d) el problema profundo no es la elegibilidad sino la competitividad, porque estos premios esperan a alguien que ya parezca una futura lider independiente, y con dos manuscritos en revision todavia no lo parece. LINEA CON LA QUE ENCABEZAR: GWAS/PRS de trastornos psiquiatricos y de salud mental, sin ambiguedad - es la linea que se corresponde con los nucleos britanicos, donde sus competencias de PLINK/R son directamente desplegables, y la prioridad de salud mental de Wellcome la hace financiable; su titulo de medicina es un diferenciador real en un campo dominado por no clinicos. PLAN REALISTA: un posdoc ordinario en uno de esos nucleos desde 2028 y despues una candidatura desde dentro.</t>
+          <t>HALLAZGO DE LA PASADA, y corrige el mapa: esta ayuda NO se puede llevar a un centro espanol. Solo admite acogida en el Reino Unido y en paises de renta baja/media, y desde el 29-10-2026 ni siquiera Irlanda. Sigue puntuando 4 porque su contenido es exactamente ella (los hubs britanicos de genetica psiquiatrica -King's/SGDP, Cardiff, Edimburgo- son el destino natural de su linea 1-2 y esta abierta a mudarse), pero deja de ser una opcion 'desde Espana' y pasa a ser una decision de traslado al Reino Unido. Elegibilidad punto por punto: doctorado DEFENDIDO en la fecha de cierre, luego nada antes de feb-2028; techo de 3 anos posdoctorales, que cumple de sobra y ademas su residencia MIR cuenta como tiempo fuera de la investigacion y da margen; acogida britanica, obligatoria y por conseguir. El corte del 10-11-2026 NO es suyo: no tendra doctorado. Trabajo: XL, es una solicitud de programa propio con presupuesto, no una beca de formulario.</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -14449,22 +15141,22 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Esquema insignia de inicio de carrera de Wellcome, abierto internacionalmente a candidaturas acogidas en Reino Unido, Irlanda o paises de renta baja/media; tasas historicas en el mejor de los casos de dos digitos bajos (sin verificar).</t>
+          <t>Esquema insignia britanico, muy competido; ademas exige conseguir antes un centro de acogida en el Reino Unido dispuesto a avalarla.</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -14474,24 +15166,24 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Nada hasta 2028, pero condiciona una decision anterior: si quiere esta via, la acogida tiene que ser BRITANICA, asi que los contactos que abra en 2027 (para HFSP, EMBO o esta) conviene sesgarlos hacia King's/SGDP, Cardiff o Edimburgo. Reverificar en 2027 el modelo de cortes rodantes, que acababa de cambiar.</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>La duena debe abrir https://wellcome.org/research-funding/schemes/early-career-awards en un navegador y resolver dos cosas: si el doctorado se exige en la fecha limite o solo al empezar, y el techo exacto de experiencia posdoctoral. Es el dato que decide si su entrada es la ronda de noviembre de 2027 o las de mediados de 2028.</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>https://wellcome.org/research-funding/schemes/early-career-awards</t>
@@ -14499,7 +15191,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Ramas 2 y 5 (fusionadas). Solo Tier 2, y las fuentes se contradicen entre si sobre la ventana de elegibilidad: se registra el conflicto en vez de resolverlo. wellcome.org es un bloqueo 403 confirmado para el fetch automatico.</t>
+          <t>wellcome.org devuelve 403 al fetch automatico dos pasadas seguidas (tambien su pagina de plazos). Verificado a traves de espejos universitarios britanicos que reproducen el texto de Wellcome: https://www.catch.ac.uk/research-grants-and-awards/wellcome-early-career-awards/ y https://www.law.ox.ac.uk/wellcome-early-career-awards . Cambio de paises elegibles del 29-10-2026 documentado aparte.</t>
         </is>
       </c>
     </row>
@@ -15182,12 +15874,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>La pagina del ERC indica ahora '0-10 years of experience since completion of PhD', contados desde 'the certified date of the successful PhD defence', con prorrogas por permisos parentales, enfermedad, servicio nacional, FORMACION CLINICA, catastrofes, asilo y violencia de genero.</t>
+          <t>CAMBIO REAL DE LAS BASES, no un error de lectura: la ventana historica de 2-7 anos se aplica a las convocatorias de 2026, y desde las convocatorias de 2027 pasa a ser 0-10 anos desde el doctorado ('defended their PhD no more than 10 years before 1 January 2027'). Se cuenta desde la fecha certificada de la defensa, contra una fecha de corte fija por convocatoria. Prorrogas documentadas, entre ellas la FORMACION CLINICA.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Exige doctorado y una trayectoria que la acredite como IP independiente. Con una defensa en febrero de 2028 y sin periodo minimo posdoctoral bajo la regla actual de 0-10 anos seria formalmente elegible desde la convocatoria ERC-2029 y hasta aproximadamente 2038, y sus anos de formacion clinica espanola son ademas causa admitida de prorroga.</t>
+          <t>Ventana 0-10 anos desde la defensa (convocatorias 2027 en adelante). Regla nueva a tener en cuenta: maximo una Starting Grant y una Consolidator Grant por carrera. La convocatoria StG 2027 abrio el 22-07-2026 y cierra el 14-10-2026.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -15197,7 +15889,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>No es una opcion en anos -financia a IP independientes con institucion de acogida y expediente de publicaciones de primera linea, y no tiene ninguna de las dos cosas- pero el reloj merece quedar registrado: seria formalmente elegible desde la convocatoria de 2029 y su formacion clinica cuenta como motivo de prorroga encima de eso.</t>
+          <t>Sigue siendo horizonte lejano (necesita ser investigadora principal con equipo), pero el cambio a 0-10 anos le amplia mucho la ventana futura: su primera convocatoria posible es la de 2029 y conservaria elegibilidad hasta finales de la decada de 2030.</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -15217,12 +15909,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -15232,24 +15924,24 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Nada antes de 2029. Ventana de elegibilidad ya resuelta: 0-10 anos desde la defensa certificada. Al acercarse, comprobar solo la fecha de corte de la convocatoria concreta y la regla de una StG por carrera.</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Nada antes de 2029. Reverificar la ventana de elegibilidad (2-7 frente a 0-10 anos) cuando este a dos anos de solicitar: la respuesta cambia a que convocatorias puede entrar.</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>https://erc.europa.eu/apply-grant/starting-grant</t>
@@ -15257,7 +15949,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Rama 1. Pagina Tier 1 leida directamente, pero la afirmacion de 0-10 anos contradice la ventana historica publicada de 2-7 anos para Starting Grant: se registra como conflicto y no se resuelve. Confirmar en el Information for Applicants de la convocatoria antes de fiarse.</t>
+          <t>https://erc.europa.eu/apply-grant/starting-grant y la nota del ERC sobre las convocatorias 2027; cambio anunciado el 16-04-2026 en el nuevo programa de trabajo.</t>
         </is>
       </c>
     </row>
@@ -15710,7 +16402,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>DOCTORADO NO EXIGIDO EN LA FECHA LIMITE. Literal leido en la pagina 'About the Program (Standard)' de JSPS: las candidatas pueden haber 'obtained a doctoral degree within six years' O bien tener previsto 'receive a Ph.D. by the start date'; no se exige certificado del titulo al solicitar, pero si antes de que empiece la beca. Ademas: ser nacional de un pais con relaciones diplomaticas con Japon; el anfitrion debe ser investigador a tiempo completo en una institucion japonesa elegible; las condiciones deben cumplirse a 1 de abril del ejercicio y mantenerse. El plazo del Open Call Standard NO figuraba en las paginas leidas (esta en appliguidelines.html, no abierta).</t>
+          <t>Cita literal de las bases FY2027: '(2) Persons who, as of April 1, 2027, have obtained a doctoral degree within six years... or who are expected to receive a Ph.D. by the start date of the fellowship period.' Y: 'A person who has been selected as a fellow must submit a diploma or doctoral degree certificate to arrive at JSPS before the start of their fellowship. (Not required when submitting the application).' QUIEN PRESENTA: el investigador anfitrion japones a traves de su institucion; no se admiten solicitudes individuales de la candidata, y las instituciones japonesas suelen cerrar internamente mas de un mes antes. Plazos FY2027 publicados: 28-08-2026 (llegada abr-sep 2027) y 23-04-2027 (llegada sep-nov 2027).</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -15720,12 +16412,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ENCABEZAR CON: las lineas 1 y 2 (genetica estadistica y GWAS/PRS psiquiatrico) como ciencia, y el vinculo japones ya existente como la relacion que hace plausible una acogida. POR QUE ELLA: ya hizo una estancia de ~3 meses en un laboratorio japones de neurociencia, asi que tiene un contacto vivo dentro de la unica estructura que puede presentar la solicitud, que es la institucion anfitriona japonesa. La combinacion MD+PhD se lee bien en los departamentos japoneses de acogida, y una posdoctoral de genetica estadistica no le cuesta equipamiento al laboratorio. RELOJES, PUNTO POR PUNTO: (a) doctorado - es el raro esquema cuya propia redaccion admite a quien 'expects to receive a Ph.D. by the start date', asi que una defensa en febrero de 2028 NO impide una solicitud presentada en 2027 para una beca que empiece despues de la defensa; el certificado se debe antes de empezar, que es exactamente el punto de riesgo si la defensa se retrasa. (b) Residencia - atada a Malaga hasta el 22-05-2027, asi que solo sirven inicios desde mediados de 2027, y un inicio posterior a febrero de 2028 es la construccion segura. (c) La ventana de 6 anos le es irrelevante. (d) Nacionalidad - Espana vale, y el visado lo gestiona JSPS como parte de la beca, con lo que el problema habitual de patrocinio fuera de la UE lo resuelve el propio esquema. (e) Sin regla de movilidad tipo MSCA. SALVEDAD HONESTA: su contacto japones es un laboratorio de electrofisiologia y optogenetica, competencias de nivel supervisado que no puede ejecutar sola; o reformula el proyecto como genetica estadistica en un grupo japones de genetica o genomica psiquiatrica (RIKEN CBS, Tokio, Osaka), lo que implica buscar acogida NUEVA, o plantea un proyecto con sabor genetico en el laboratorio que ya conoce. Esa reformulacion es el trabajo real. TRABAJO: M - plan de investigacion acordado con el anfitrion, CV y lista de publicaciones; la carga administrativa recae en la institucion japonesa, no en ella.</t>
+          <t>Encaje bueno y con puerta de entrada real: tiene contacto vivo del laboratorio japones donde hizo la estancia, y JSPS admite expresamente a quien espera doctorarse antes de la fecha de INICIO, no de solicitud. Pero ninguna de las dos convocatorias FY2027 le sirve, y conviene tenerlo claro para no perseguirlas: la primera cierra el 28-08-2026 (cuatro dias, y necesita anfitrion que presente) y la segunda, del 23-04-2027, da incorporacion entre septiembre y noviembre de 2027, cuando aun no habra defendido (prevista feb-2028) y ademas su MIR corre hasta el 22-05-2027. SU CONVOCATORIA ES LA PRIMERA DE FY2028, previsiblemente hacia agosto de 2027, con incorporacion entre abril y septiembre de 2028: encaja con la defensa de febrero de 2028. Elegibilidad punto por punto: ventana de 6 anos desde el doctorado, holgada; doctorado solo exigido al empezar, verificado; nacionalidad sin restriccion; visado gestionado por JSPS. Trabajo: M para ella, pero el grueso administrativo lo lleva el anfitrion, y por eso hay que avisarle con mucha antelacion.</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -15745,7 +16437,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -15755,24 +16447,24 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Escribir a su antiguo anfitrion japones en la primera mitad de 2027 (no despues): es EL quien presenta la solicitud y su institucion cierra internamente con mas de un mes de antelacion sobre el plazo de JSPS. Objetivo: primera convocatoria de FY2028, esperada hacia agosto de 2027; las bases se publican en una URL de patron predecible (.../application_requirements/&lt;ejercicio&gt;/&lt;ejercicio&gt;_applicationguideline_e.pdf).</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Abrir https://www.jsps.go.jp/english/e-fellow/e-ippan/appliguidelines.html para fijar el plazo del Open Call Standard del ejercicio 2027 y su ventana de inicio; en paralelo, decidir si aborda a su antiguo anfitrion japones o a un grupo japones de genetica estadistica, ya que es el anfitrion quien presenta.</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>https://www.jsps.go.jp/english/e-fellow/e-ippan/index.html</t>
@@ -15780,7 +16472,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Rama 3. Tier 1: paginas 'About the Program (Standard)' e indice de solicitud de JSPS, leidas el 2026-08-23. Confirmacion de la via: 'applications must be submitted to JSPS by a host researcher in Japan via the head of their university or institution'.</t>
+          <t>Bases FY2027 en PDF, texto extraido en local: https://www.jsps.go.jp/file/storage/j-fellow/j-fellow_14/application_requirements/2027/2027_applicationguideline_e.pdf (indice en https://www.jsps.go.jp/english/e-fellow/application.html). Ojo: el mismo PDF repite la tabla de plazos para los programas [PE], [L] y [S]; hay que anclarse al bloque Standard [P].</t>
         </is>
       </c>
     </row>
@@ -15975,17 +16667,17 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>DOCTORADO NO DECLARADO COMO REQUISITO en el texto leido: las condiciones que filtran son ser menor de 40, un proyecto en Ciencias de la Vida y Medioambiente (que incluye explicitamente 'genetica, fisiologia, neurociencia') y un CONTRATO EN VIGOR con el centro de investigacion solicitante, tanto al presentar como durante la ejecucion. Las bases legales completas no se abrieron, asi que la ausencia de requisito de doctorado es una lectura del anuncio, no del articulado.</t>
+          <t>Bases legales (edicion XIX): exige 'Tener suscrito un contrato de investigacion con el Centro de Investigacion para el desarrollo del Proyecto', 'Haber obtenido el doctorado... y que hayan transcurrido al menos cuatro (4) anos desde la lectura de la tesis doctoral', 'Haber realizado al menos una estancia pre o post doctoral de una duracion minima de dos (2) anos' fuera del centro de tesis, y 'Ser una investigadora independiente en fase inicial o independiente'. Lo presenta el centro, no la candidata.</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>ENCABEZAR CON: la linea 1 (genetica estadistica de rasgos complejos) presentada como genetica y neurociencia - la lista de areas elegibles nombra 'genetica' y 'neurociencia' de forma literal, y un proyecto de PRS sobre rasgos psiquiatricos con encuadre de impacto social (salud mental en jovenes) es exactamente la forma que premia este jurado. POR QUE ELLA: mujer menor de 40 en Espana, en un area explicitamente elegible, con un perfil MD+PhD que resulta distintivo ante un jurado no especialista; y es uno de los poquisimos esquemas que no parece exigir el doctorado en mano, algo que importa enormemente con una ETA de febrero de 2028. Punto por punto: (a) doctorado no exigido segun el texto, asi que en principio podria presentarse en la edicion de noviembre de 2026 o en la de noviembre de 2027, es decir ANOS antes de que se abra ninguna otra fila de esta rama; (b) menor de 40, holgadamente; (c) la residencia en Espana hasta el 22-05-2027 juega a favor y no en contra, porque el proyecto debe ejecutarse en un centro espanol; (d) sin barrera de nacionalidad ni regla de movilidad. LA CONDICION QUE HAY QUE RESOLVER, Y ES TODA LA FILA: necesita un contrato en vigor con el centro solicitante. Su contrato de residencia es con el Hospital Regional Universitario de Malaga y su doctorado esta en la Universidad de Murcia, y si alguno de los dos cuenta como 'el centro de investigacion solicitante' con contrato valido es la unica pregunta que decide la elegibilidad: hay que resolverla con las bases legales y con la oficina de investigacion del centro, no adivinarla. Si el instituto del hospital (IBIMA) o la Universidad de Murcia actuan como solicitante, esta pasa a ser una fila fuerte; si no, es inelegible hasta que tenga contrato posdoctoral. TRABAJO: S-M, propuesta corta, CV y narrativa de impacto social, mas el visto bueno institucional.</t>
+          <t>Respuesta a la pregunta abierta de la pasada anterior: un contrato de residencia MIR NO sirve, porque las bases piden un contrato de INVESTIGACION con el centro que presenta la candidatura, y ademas exigen doctorado con 4 anos cumplidos desde la lectura y una estancia previa de 2 anos seguidos fuera (las suyas son de ~3 meses), de modo que no seria elegible hasta ~2032 y la ayuda queda fuera del radar util.</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -16005,12 +16697,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -16020,24 +16712,24 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Ninguna. No volver a perseguirla hasta ~2032. No confundirla con los International Awards / International Rising Talents de la UNESCO (F-0035), que son otro programa, por nominacion de terceros.</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Antes de finales de octubre de 2026: descargar las bases legales de la XX edicion y responder a una pregunta - un contrato MIR de residencia o una matricula de doctorado, satisfacen 'contrato en vigor con el centro de investigacion solicitante'? Preguntar a IBIMA (Malaga) y a la oficina de investigacion de la Universidad de Murcia si alguno actuaria como centro solicitante.</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>https://www.loreal.com/es-es/espana/news/commitment/loreal-unesco-abre-convocatoria-de-premios-for-women-in-science/</t>
@@ -16045,7 +16737,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Rama 3. Tier 1: anuncios de L'Oreal Espana de las ediciones XIX (abierta 24-10-2024, cerrada 04-12-2024) y XX (abierta 23-10-2025, cerrada 17-11-2025), leidos el 2026-08-23. Bases legales no abiertas. La XXI edicion se espera hacia finales de octubre de 2026: LIKELY.</t>
+          <t>Bases legales integras (edicion XIX) extraidas de un espejo universitario: https://sgi.unizar.es/sites/sgi/files/convocatorias/2024/12%204%205023_Bases%20Legales%20Premios%20For%20Women%20in%20Science%202024%202025%20Espa%C3%B1a%20TEXTO.pdf . El PDF equivalente en forwomeninscience.com es un escaneado sin capa de texto, ilegible para el rastreo.</t>
         </is>
       </c>
     </row>
@@ -16744,7 +17436,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Abierto a investigadoras de inicio de carrera de toda Espana, incluidas explicitamente las meramente 'matriculadas en doctorado'. Premia un articulo publicado en neurociencia basica o aplicada de los tres anos anteriores (2023-2025 para la edicion de 2026). La ganadora imparte una conferencia divulgativa. La ventana de solicitud es de solo 30 dias naturales.</t>
+          <t>Edicion 2026 (cerrada): plazo hasta el viernes 5 de junio de 2026, premio unico de 1.250 EUR, sobre un articulo publicado en 2023, 2024 o 2025. Abierta a PREDOCTORALES matriculadas en estudios de doctorado y a posdoctorales con doctorado posterior al 31-12-2022.</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -16754,7 +17446,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Un premio real y de baja competencia al que puede optar COMO DOCTORANDA ACTUAL: la convocatoria admite explicitamente a quien solo esta matriculada en un programa de doctorado, y 1250 euros mas una conferencia invitada son una linea de CV citable y genuina para alguien con un expediente de publicaciones todavia fino. El calendario juega a su favor: sus dos manuscritos de primera autora (la revision en Journal of Sleep Research y el articulo empirico de Nature Mental Health del proyecto de QIMR) estan en revision ahora, asi que si alguno aparece en 2026 quedaria dentro de la ventana elegible de las ediciones de 2027 y 2028. Punto por punto: no exige doctorado terminado; es nacional y ella esta en Espana; no hay acogida que asegurar; el esfuerzo es minimo. LA RESTRICCION: la ventana es de solo 30 dias una vez abierta, hacia mayo, asi que hay que tener el recordatorio puesto. Es ademas el caso modelo de toda una clase de premios pequenos de sociedades e institutos espanoles que merece la pena rastrear sistematicamente en proximas pasadas.</t>
+          <t>Dato nuevo y util de esta pasada: el premio admite PREDOCTORALES matriculadas en programa de doctorado, de modo que es elegible YA, sin esperar a defender. Es dinero pequeno (1.250 EUR) pero de los pocos reconocimientos a los que puede optar ahora mismo, y una linea de curriculo en el ambito de la neurociencia espanola. Elegibilidad punto por punto: matriculada en el doctorado de la Universidad de Murcia, cumple; articulo publicado en 2023-2025 (para la edicion de 2027 se desplazara la ventana), y aqui esta el unico corte real, porque sus dos manuscritos siguen en revision: si alguno se publica antes de la primavera de 2027, tiene con que presentarse. Trabajo: XS, es enviar un articulo ya escrito. Ventana de solo 30 dias naturales, asi que hay que estar atenta en mayo.</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -16779,7 +17471,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -16789,17 +17481,17 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Poner recordatorio a principios de mayo de 2027 y revisar la web del instituto: la ventana dura solo 30 dias. Comprobar antes cual de los dos manuscritos ha salido publicado y en que ano, porque eso determina en que edicion encaja.</t>
+          <t>Vigilar la convocatoria de 2027 a partir de abril (la de 2026 cerro el 05-06-2026 y la ventana dura solo 30 dias). Solo hara falta un articulo publicado dentro de la ventana de anos que fije la nueva edicion.</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -17262,7 +17954,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Inelegible por ciudadania y por via de carrera; el valor real del Stanley Center para ella es como EMPLEADOR (las vacantes del Broad, ya recogidas en SRC-0040), no como financiador.</t>
+          <t>Descartada definitivamente: el propio Broad dice que 'In 2024, the Stanley Center awarded the last Sklar fellowship', y lo que sobrevive son un programa para estudiantes de grado y un premio restringido a residentes de psiquiatria de dos programas concretos de Estados Unidos, ambos con exigencia de ciudadania o residencia permanente estadounidense.</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -17287,7 +17979,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -17297,17 +17989,17 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Descartar como via de financiacion. Mantener el portal de empleo del Broad (SRC-0040) como canal vivo; un correo a sklarprogram@broadinstitute.org zanjaria el estado de la beca si alguna vez merece el esfuerzo.</t>
+          <t>Ninguna. No volver a revisarla semanalmente. El Stanley Center no tiene ninguna convocatoria abierta a la que se pueda presentar por si misma; su unica via alli es el empleo (ofertas de postdoc), que corresponde a la pestana de postdocs.</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -21448,12 +22140,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Portal de LOI ~marzo de 2027, plazo de LOI ~mayo de 2027, propuesta completa ~septiembre de 2027, para la convocatoria del ano 2028 (activacion de abril de 2028 a enero de 2029)</t>
+          <t>Sigue sin publicarse el calendario del ciclo AY2028. Por el patron del AY2027 (LOI iniciada antes del 05-05-2026 y presentada antes del 12-05-2026, propuesta completa el 24-09-2026, incorporacion entre el 01-04-2027 y el 01-01-2028), se espera publicacion hacia enero-marzo de 2027.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21468,7 +22160,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -21478,7 +22170,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Ver F-0007. El laboratorio de acogida debe estar comprometido antes de la LOI y el proyecto debe suponer un cambio real de campo; Espana excluida por nacionalidad y por pais del doctorado. Poner revision en hfsp.org en febrero de 2027. Confirmar tambien el requisito de articulo de primera autora en fase de LOI, que no se pudo verificar y que es lo unico que podria descalificarla en su ciclo mas temprano.</t>
+          <t>Estimacion, no dato: HFSP no ha publicado nada del AY2028. CUIDADO AL VERIFICAR: las fechas que publica hfsp.org para los Research Grants son otras y no valen para las becas posdoctorales. Lo verificado esta pasada es que el doctorado NO se exige al solicitar (ver F-0007).</t>
         </is>
       </c>
     </row>
@@ -21510,7 +22202,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2027-02-10 (ventana ~10 feb - 5 mar 2027; publicacion en BOE prevista en diciembre de 2026)</t>
+          <t>Sin publicar aun. Estimacion por patron: resolucion en la segunda quincena de diciembre de 2026 y plazo de Rio Hortega en febrero de 2027 (fue 12-02/05-03 en 2025 y 10-02/05-03 en 2026).</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -21530,7 +22222,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -21540,7 +22232,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ver F-0001. Verificar en el texto de la AES 2027 que el art. 34.2o dice 'durante el ano 2022, o en fecha posterior, incluyendo a los que lo hagan en 2027' y que el plazo de alegaciones de la resolucion provisional cae despues del 22-05-2027. La acogida (un jefe de grupo de un centro publico del SNS) debe estar cerrada a finales de 2026, porque hay cupo por centro y preseleccion interna.</t>
+          <t>Verificado esta pasada que a 24-08-2026 NO hay nada de la AES 2027 (ni BOE ni ISCIII). El disparador exacto es el extracto en el BOE de la segunda quincena de diciembre (serie BOE-B-2023-38433 / BOE-B-2024-45526 / BOE-B-2025-47164). Espejo que rodea el 503 de isciii.es: https://www.iisaragon.es/wp-content/uploads/2025/12/AES_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -21696,12 +22388,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esquema rodante con varias rondas al ano: proximos plazos ~10-11-2026 y ~06-04-2027, y otra ronda hacia julio de 2027</t>
+          <t>Corte confirmado el 10-11-2026; desde el 25-08-2026 el esquema pasa a presentacion continua con tres cortes al ano (preseleccion en febrero, junio y septiembre). El dato de ~06-04-2027 de la pasada anterior NO tiene respaldo y se retira.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21716,7 +22408,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -21726,7 +22418,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ver F-0012. CONFLICTO SIN RESOLVER en la fecha de la ronda de julio de 2026: una fuente dice 21 y otra 22 de julio; wellcome.org devuelve HTTP 403 al fetch automatico y no se pudo dirimir. DOS INCOGNITAS QUE DECIDEN SU PRIMERA RONDA y que la duena debe resolver a mano: si exige el doctorado en la fecha limite o solo al empezar, y si la acogida esta restringida a Reino Unido, Irlanda y paises de renta baja/media, en cuyo caso un centro espanol no vale.</t>
+          <t>ELLA NO ES ELEGIBLE en ninguno de esos cortes (no tendra doctorado hasta feb-2028) y ademas Espana no vale como centro de acogida: solo Reino Unido y paises de renta baja/media, y desde el 29-10-2026 Irlanda tambien sale. wellcome.org da 403 dos pasadas seguidas: usar espejos de oficinas de investigacion britanicas, distinguiendo siempre si la fecha que publican es la del financiador o la interna del centro.</t>
         </is>
       </c>
     </row>
@@ -21738,7 +22430,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NHMRC Investigator Grants - ronda 2027</t>
+          <t>NHMRC Investigator Grants - ronda con cierre en julio de 2027</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -21758,12 +22450,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ronda 2028 prevista con apertura ~2-6-2027 y cierre ~28-7-2027 (17:00 AEST); ronda 2029 ~junio-julio de 2028</t>
+          <t>Apertura hacia junio de 2027 y cierre hacia finales de julio de 2027. CORRECCION DE ETIQUETADO: lo que la NHMRC llama 'ronda 2027' cerro el 29-07-2026 y financia contratos que empiezan en 2028; la ronda siguiente cierra hacia julio de 2027.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21778,7 +22470,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -21788,7 +22480,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ver F-0016. INELEGIBLE HASTA EL DOCTORADO: Emerging Leadership 1 se evalua en relacion con la oportunidad desde la fecha de concesion del doctorado, asi que un doctorado de febrero de 2028 apunta a la ronda de 2029 (apertura ~junio de 2028) como su primera entrada realista. El NHMRC ya no tiene becas posdoctorales independientes: este esquema es todo el carril.</t>
+          <t>La modalidad Emerging Leadership exige el doctorado ya concedido, asi que con defensa en feb-2028 su primera ronda utilizable es la que cierre hacia julio de 2028. Tiene via de contacto por la estancia en QIMR Berghofer.</t>
         </is>
       </c>
     </row>
@@ -21820,12 +22512,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Principios de febrero de 2027, con cierre a principios de marzo de 2027</t>
+          <t>Apertura en febrero de 2027 y cierre el viernes 05-03-2027; 70.000 USD a dos anos.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21840,7 +22532,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -21850,7 +22542,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ver F-0017. La via del titulo de medicina con PGY-IV o mas significa que el doctorado cualificante podria ser su MD y no el PhD: merece la pena preguntar a la BBRF si un primer ano de puesto investigador tras una residencia espanola cuenta como 'advanced post-doctoral fellow'. Una fuente secundaria apunta al 12-3-2027 como cierre del ciclo 2027: sin verificar.</t>
+          <t>Fechas de 2027 surgidas de busqueda agregada, no de una pagina de la BBRF abierta directamente (sus PDF de bases son form-XObject y no se extraen en el rastreo). Reverificar en enero de 2027.</t>
         </is>
       </c>
     </row>
@@ -21882,12 +22574,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hacia abril-mayo de 2027 para la Incoming de 2028 (cierre historicamente a finales de julio)</t>
+          <t>La convocatoria Incoming 2027 ESTA ABIERTA y cierra el 23-09-2026 a las 14:00 CEST (preseleccion 12-01-2027, entrevistas 24-25 de febrero de 2027, resultados 10-03-2027, incorporacion entre el 01-05-2027 y el 31-12-2027). La de 2028 deberia abrirse hacia junio de 2027 y cerrar hacia septiembre de 2027.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21902,7 +22594,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -21912,7 +22604,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ver F-0006. Su primera edicion elegible en cualquiera de las dos modalidades es una convocatoria que cierre despues de febrero de 2030. El sitio bloquea el fetch automatico (HTTP 403).</t>
+          <t>Reabierta, pero ella NO es elegible: exige doctorado obtenido entre 2 y 7 anos antes del cierre. Con defensa en feb-2028, su primera edicion posible es la convocatoria de 2029 (cierre previsible hacia septiembre de 2028). Hasta 320.100 EUR por un maximo de 3 anos.</t>
         </is>
       </c>
     </row>
@@ -21964,7 +22656,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -21974,7 +22666,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>VERIFICADO para la edicion de 2026: congreso en Glasgow del 29 de septiembre al 3 de octubre de 2026; resumenes orales y poster y solicitudes ECIP el 14-5-2026 (el ECIP exige resumen de sesion cientifica presentado a la vez). Quienes recibieron ayuda ECIP entre 2022 y 2025 no podian pedirla en 2026; ella no la ha recibido, asi que no le afecta. Confianza MEDIUM y no HIGH porque el patron de mediados de mayo se apoya solo en la edicion de 2026 y las fechas y sede del WCPG 2027 no estan anunciadas. ELEMENTO APARTE A CORTO PLAZO: el WCPG 2026 es dentro de seis semanas y la inscripcion general podria seguir abierta; merece una comprobacion.</t>
+          <t>Sin cambios: ispg.net sigue anunciando solo el WCPG 2026 (Glasgow, 29-09 a 03-10-2026); del congreso de 2027 no hay sede, ni fechas, ni portal de resumenes, ni pagina del ECIP.</t>
         </is>
       </c>
     </row>
@@ -22006,7 +22698,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enero-marzo de 2027 para SLEEP 2027; la propia pagina de la SRS indica que el ciclo del Trainee Merit Award se espera en enero de 2027</t>
+          <t>SLEEP 2027 (41o congreso anual de la APSS) confirmado en Denver, Colorado Convention Center, del 5-6 al 9 de junio de 2027. El ciclo de premios de becarias sigue sin publicar; por el precedente de 2026 (resumenes el 08-12-2025, solicitud de premios en enero) se espera ventana en enero de 2027 con resumenes a principios de diciembre de 2026.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -22026,7 +22718,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -22036,7 +22728,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Las fechas y la sede de SLEEP 2027 no figuraban en la pagina. Los congresos SLEEP son en junio, asi que caen despues del fin de residencia del 22-05-2027. Exige visado o ESTA de EE. UU. y un billete de larga distancia, y las ayudas son reembolsos, o sea que adelanta el dinero. Material para el resumen: su linea 3 mas la revision del Journal of Sleep Research.</t>
+          <t>Sede y fechas del congreso VERIFICADAS; el calendario de premios sigue UNVERIFIED. Revisar https://www.sleepmeeting.org/call-for-abstracts/ hacia octubre de 2026 (esa pagina se sirve por JavaScript y llega vacia al rastreo: comprobarla a mano o via el boletin de la SRS).</t>
         </is>
       </c>
     </row>
@@ -22068,7 +22760,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mayo de 2027, convocatoria anual con ventana de solo 30 dias naturales</t>
+          <t>Mayo-junio de 2027 (la edicion 2026 cerro el viernes 05-06-2026), con ventana de solo 30 dias naturales.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -22088,7 +22780,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -22098,7 +22790,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ver F-0031. VERIFICADO contra el anuncio del instituto: predoc o doctorado posterior al 31-12-2022, articulo publicado en 2023-2025 para la edicion de 2026. Poner recordatorio a primeros de mayo de 2027: la ventana dura 30 dias. Es ademas el caso modelo de una clase entera de premios pequenos de sociedades e institutos espanoles que conviene rastrear de forma sistematica.</t>
+          <t>Verificada la edicion 2026: 1.250 EUR, premio unico, articulo publicado en 2023-2025, y abierta a PREDOCTORALES matriculadas, de modo que ella ya es elegible sin haber defendido. Ver F-0030.</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22822,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>~noviembre-diciembre de 2026, con plazo ~25 de enero de 2027</t>
+          <t>POSIBLEMENTE YA ABIERTA: el tablon de Becas y Premios de la SES lista como 'CONVOCATORIA ABIERTA' tres partidas de 2026, entre ellas las Becas de Investigacion SES y la Ayuda para la Investigacion y el Intercambio de Conocimiento. Si se confirma, la estimacion anterior (apertura en noviembre-diciembre de 2026) era erronea.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -22150,7 +22842,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -22160,7 +22852,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>LO ACCIONABLE ES EL RELOJ DE LA MEMBRESIA. Fuentes secundarias sobre ediciones recientes indican que hay que ser menor de 45, nacional de la UE o extranjera con residencia en Espana, Y 'ser miembro de la SES desde al menos un ano antes a la convocatoria', con al menos el 70% del equipo formado por socios de la SES. La regla del 70% esta confirmada en la propia web de la SES; la del ano de antiguedad es LIKELY (solo secundaria, el PDF de bases no se abrio). Si es cierta, hacerse socia AHORA es lo que la habilita para la edicion de enero de 2028, y hacerlo antes de ~diciembre de 2026 protege la de enero de 2027. No aparecio requisito de doctorado, lo que la haria una de las poquisimas accesibles antes de defender. La pagina de la SES dice 'Convocatoria abierta' pero el unico plazo que publica es el de enero de 2026: parece no actualizada. Dos convocatorias mas de la SES sin examinar: 'Ayuda para la Investigacion y el Intercambio de Conocimiento' y el 'Premio al Mejor Trabajo Publicado Joaquin Teran y Mari Luz Alonso'.</t>
+          <t>SIN CONFIRMAR la regla de antiguedad de un ano como socia: no aparece en el texto de ninguna pagina leida, solo en un resumen de buscador. Lo que si esta leido: la edicion 2016/17 exigia proyectos 'liderados por socios de la SES' con al menos el 60% de participantes socios, y la de 2024 subia ese porcentaje al 70%. LA TAREA CONCRETA DE LA PROXIMA PASADA es descargar el PDF de bases desde https://ses.org.es/profesionales/becas-y-premios/ y cerrar dos cosas: el plazo real de la edicion 2026 y si existe antiguedad minima como socia.</t>
         </is>
       </c>
     </row>
@@ -22300,12 +22992,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
@@ -22679,8 +23371,112 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SUB-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sleep Research Society - lista 'Receive SRS Updates' (y membresia de becaria)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://sleepresearchsociety.org/membership/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Avisos de apertura de los premios de la SRS, de los plazos de resumenes y de los Trainee Merit / Diversity Travel Awards del congreso SLEEP, y del Small Research Grant Program.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>El calendario de premios de becarias de la SRS no se publica con antelacion en ninguna pagina rastreable (W-0010 lleva dos pasadas sin fecha), solo llega por correo. Y SLEEP 2027 es en Denver del 5-6 al 9 de junio de 2027, ya terminada su residencia: una ayuda de viaje o un premio de becaria es la via realista para asistir.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>La pagina tiene un formulario de alta verificado (nombre, apellidos, correo). Para la membresia hay tramo de Postdoctoral Fellow / Predoctoral Student en https://members.sleepresearchsociety.org/SRSMembers/Membership/Join/Choose-Membership-Type.aspx (pagina de alta no abierta en esta pasada). Anadida por la rutina fellowships.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SUB-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Sueno (SES) - alta como socia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://ses.org.es/registro/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Comunicaciones de socia y acceso a las convocatorias del tablon de Becas y Premios: Becas de Investigacion SES, Ayuda para la Investigacion y el Intercambio de Conocimiento (movilidad) y el Premio Joaquin Teran y Mari Luz Alonso.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Aqui la suscripcion ES el requisito, no el aviso: las becas de la SES exigen que el proyecto lo lidere una socia y que entre el 60% y el 70% del equipo lo sean, y hay indicios (sin confirmar) de una antiguedad minima de un ano. Si esa antiguedad existe, cada mes que pasa retrasa un ano su elegibilidad. Ademas es el financiador nacional que mejor encaja con la linea de sueno infantil mientras siga en Malaga.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://ses.org.es/hazte-socio/ da 404: la via correcta es /registro/, que lleva al formulario de alta. Ninguna de las dos paginas se abrio en esta pasada (techo de llamadas): confirmar antes de actuar. El tablon https://ses.org.es/profesionales/becas-y-premios/ si esta verificado y es SRC-0066. Anadida por la rutina fellowships.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J7"/>
+  <autoFilter ref="A1:J9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -22,18 +22,18 @@
     <sheet name="readme" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,17 +451,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="52" customWidth="1" min="11" max="11"/>
@@ -538,12 +538,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F-0019</t>
+          <t>F-0037</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FENS/IBRO-PERC Exchange Fellowships</t>
+          <t>Beca Internacional de Intercambio Cientifico Profesional 2026 (Programa de Intercambio Profesional SEMEDLAB)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -553,20 +553,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SHORT_STAY</t>
+          <t>Lab visit / exchange grant</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>hasta 4000</t>
+          <t>hasta 5500 (1000 de viaje en turista + 1500/mes hasta 3 meses)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Antes del 15-10-2026: confirmar u obtener la membresia de SENC o la individual de FENS, escribir a 2 o 3 PI candidatos para la carta de aceptacion, y decidir si la estancia es una rotacion externa de la residencia (necesita visto bueno del tutor, conviene empezar esa conversacion ya) o una estancia posterior al 22-05-2027 solicitada en la ronda del 15 de abril de 2027.</t>
+          <t>URGENTE, 30 dias. 1) Comprobar hoy si es socia de SEMEDLAB y, si no, tramitar el alta. 2) Esta semana, correo al laboratorio receptor pidiendo carta de aceptacion. 3) En paralelo, pedir al jefe de servicio la firma del acuerdo. 4) Enviar antes del 30-09-2026.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://www.fens.org/careers/grants-and-stipends/grant/fens-ibro-perc-exchange-fellowships</t>
+          <t>https://www.fundacionjlc.es/becapremio-convocado/beca-internacional-de-intercambio-cientifico-profesional-2026/</t>
         </is>
       </c>
     </row>
@@ -598,51 +598,55 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>E-0002</t>
+          <t>F-0019</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ASHG 2026 Annual Meeting</t>
+          <t>FENS/IBRO-PERC Exchange Fellowships</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>Fellowships</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Congreso anual</t>
+          <t>SHORT_STAY</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>hasta 4000</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Plazo 15-10-2026 confirmado por dos paginas Tier 1 (FENS e IBRO). RESERVA A TENER EN CUENTA: con el MIR hasta el 22-05-2027, una estancia de 1 a 4 meses tendria que encajarse en su calendario de residencia; conviene decidir antes de invertir en la solicitud.</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://ashgmeeting.ashg.org/</t>
+          <t>https://www.fens.org/careers/grants-and-stipends/grant/fens-ibro-perc-exchange-fellowships</t>
         </is>
       </c>
     </row>
@@ -654,36 +658,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>E-0001</t>
+          <t>F-0054</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>World Congress of Psychiatric Genetics (WCPG) 2026</t>
+          <t>III Convocatoria de Becas Fulbright-Fundacion Seneca de investigacion posdoctoral en los Estados Unidos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>Fellowships</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Congreso anual</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>36</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Regional-bilateral postdoctoral research fellowship (Espana - EE. UU.)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3200 al mes para alojamiento y manutencion + ayuda de desplazamiento</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -691,10 +692,14 @@
           <t>M</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Revisar https://fseneca.es/web/convocatorias en la primera semana de septiembre de 2026, cuando termine el mes inhabil, y capturar las bases de la III convocatoria: ventana de anos post-doctorado y definicion exacta de 'vinculacion con la Region de Murcia'.</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://ispg.net/wcpg-2026/</t>
+          <t>https://fseneca.es/web/convocatorias</t>
         </is>
       </c>
     </row>
@@ -706,12 +711,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>E-0005</t>
+          <t>E-0002</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IGES 2026 Annual Meeting &amp; Education Workshop</t>
+          <t>ASHG 2026 Annual Meeting</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -721,14 +726,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Congreso anual + workshop</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+          <t>Congreso anual</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,7 +755,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://www.geneticepi.org/2026-annual-meeting</t>
+          <t>https://ashgmeeting.ashg.org/</t>
         </is>
       </c>
     </row>
@@ -751,51 +767,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T-0002</t>
+          <t>E-0001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Genetic Epidemiology (short course)</t>
+          <t>World Congress of Psychiatric Genetics (WCPG) 2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Events</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Short course</t>
+          <t>Congreso anual</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>142</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1470</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
+          <t>https://ispg.net/wcpg-2026/</t>
         </is>
       </c>
     </row>
@@ -807,40 +819,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T-0001</t>
+          <t>E-0005</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>International Statistical Genetics Workshop (el 'Boulder Workshop')</t>
+          <t>IGES 2026 Annual Meeting &amp; Education Workshop</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Events</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Congreso anual + workshop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://www.colorado.edu/ibg/workshop-2027</t>
+          <t>https://www.geneticepi.org/2026-annual-meeting</t>
         </is>
       </c>
     </row>
@@ -852,12 +864,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T-0003</t>
+          <t>T-0002</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mendelian Randomization (short course)</t>
+          <t>Genetic Epidemiology (short course)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -872,15 +884,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -896,7 +908,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
         </is>
       </c>
     </row>
@@ -908,20 +920,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L-0001</t>
+          <t>T-0001</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Complex Trait Genetics (CTG) Lab</t>
+          <t>International Statistical Genetics Workshop (el 'Boulder Workshop')</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Groups</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
@@ -937,7 +953,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://cncr.nl/ctg/</t>
+          <t>https://www.colorado.edu/ibg/workshop-2027</t>
         </is>
       </c>
     </row>
@@ -949,36 +965,51 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L-0002</t>
+          <t>T-0003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Psychiatric Genetics Group</t>
+          <t>Mendelian Randomization (short course)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Groups</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Short course</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>182</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XS</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://www.qimrb.edu.au/researchers-and-labs/psychiatric-genetics</t>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
         </is>
       </c>
     </row>
@@ -990,12 +1021,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L-0004</t>
+          <t>L-0001</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Generation R - genetica del sueno infantil</t>
+          <t>Complex Trait Genetics (CTG) Lab</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1019,7 +1050,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://acamh.onlinelibrary.wiley.com/doi/10.1111/jcpp.13899</t>
+          <t>https://cncr.nl/ctg/</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1062,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L-0006</t>
+          <t>L-0002</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SGDP Centre / Statistical Genetics Unit</t>
+          <t>Psychiatric Genetics Group</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1060,12 +1091,94 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
+          <t>https://www.qimrb.edu.au/researchers-and-labs/psychiatric-genetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>L-0004</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Generation R - genetica del sueno infantil</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://acamh.onlinelibrary.wiley.com/doi/10.1111/jcpp.13899</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>L-0006</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SGDP Centre / Statistical Genetics Unit</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>https://www.kcl.ac.uk/research/sgu</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L12"/>
+  <autoFilter ref="A1:L14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1076,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1085,8 +1198,8 @@
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
   </cols>
@@ -2058,12 +2171,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>afinada tras definir el perfil, 2026-08-23. BLOQUEO CONFIRMADO 2026-08-24: wellcome.org devuelve 403 al rastreo automatico en dos pasadas seguidas, tambien en su pagina de plazos. No gastar mas llamadas aqui: usar el espejo SRC-0083 (CATCH). Ademas, desde el 29-10-2026 solo admite centros de acogida en Reino Unido y paises de renta baja/media: Espana nunca ha sido elegible.</t>
+          <t>afinada tras definir el perfil, 2026-08-23. BLOQUEO CONFIRMADO 2026-08-24: wellcome.org devuelve 403 al rastreo automatico en dos pasadas seguidas, tambien en su pagina de plazos. No gastar mas llamadas aqui: usar el espejo SRC-0083 (CATCH). Ademas, desde el 29-10-2026 solo admite centros de acogida en Reino Unido y paises de renta baja/media: Espana nunca ha sido elegible. | 2026-08-31: no reintentado (403 conocido). El conflicto entre el 10-11-2026 y el 16-11-2026 sigue abierto; el 16 aparece como plazo INTERNO en Oxford y en un PDF de UCT, lo que refuerza que el 10 es el del financiador, pero no se ha leido en Tier 1.</t>
         </is>
       </c>
     </row>
@@ -2160,10 +2273,14 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>afinada tras definir el perfil, 2026-08-23</t>
+          <t>afinada tras definir el perfil, 2026-08-23 | 2026-08-31: https://ibro.org/fellowships/ devuelve HTTP 404. La vista con fechas es el calendario de convocatorias, fichado aparte en esta misma pasada. IBRO no financia salarios postdoctorales.</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4127,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>TIER 1 y con diferencia la fuente espanola de mas valor de esta pasada: es el documento que sostiene todo lo que sabemos de Rio Hortega. Las paginas HTML de isciii.es devuelven HTTP 503 al fetch automatico, pero esta URL de documento descarga bien. Es un PDF firmado, asi que WebFetch no puede leerlo: hay que descargar y extraer localmente (no hay pdftotext ni pdfminer en este entorno; funciono un extractor con zlib y expresiones regulares sobre los flujos FlateDecode).</t>
+          <t>TIER 1 y con diferencia la fuente espanola de mas valor de esta pasada: es el documento que sostiene todo lo que sabemos de Rio Hortega. Las paginas HTML de isciii.es devuelven HTTP 503 al fetch automatico, pero esta URL de documento descarga bien. Es un PDF firmado, asi que WebFetch no puede leerlo: hay que descargar y extraer localmente (no hay pdftotext ni pdfminer en este entorno; funciono un extractor con zlib y expresiones regulares sobre los flujos FlateDecode). | 2026-08-31: el PDF de la AES 2026 (111 paginas) se extrajo LOCALMENTE con exito y de el sale la clausula de alegaciones del art. 34.2 que adelanta un ano la elegibilidad de Rio Hortega. RECETA OPERATIVA: el espejo iisaragon.es devuelve 403 a curl sin User-Agent y 200 con -A 'Mozilla/5.0 (X11; Linux x86_64)'; y pypdf necesita que se stubbeen los modulos cryptography.hazmat.* en sys.modules ANTES del import, porque 'import cryptography' provoca un PanicException de pyo3 que no se captura con try/except.</t>
         </is>
       </c>
     </row>
@@ -4218,12 +4335,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>SRC-0019 apunta solo a la raiz de fens.org; esta es la subpagina accionable. Exige ser socia de una sociedad miembro de FENS (la SENC en Espana) para poder solicitar: la membresia es tarea previa, no detalle.</t>
+          <t>SRC-0019 apunta solo a la raiz de fens.org; esta es la subpagina accionable. Exige ser socia de una sociedad miembro de FENS (la SENC en Espana) para poder solicitar: la membresia es tarea previa, no detalle. | 2026-08-31: revisada entera. RESULTADO NEGATIVO Y ESTABLE, que ahorra presupuesto futuro: de los 17 programas listados NINGUNO financia un puesto o un salario postdoctoral; todos son viajes, escuelas, cursos o intercambios cortos. La unica entrada abierta que no es apoyo a cursos es la F-0019. Basta revisarla semestralmente.</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4595,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Las doctorandas tienen condicion de trainee. El Diversity Travel Award parece no exigir membresia, a diferencia del Trainee Merit: es el primer movimiento mas barato.</t>
+          <t>Las doctorandas tienen condicion de trainee. El Diversity Travel Award parece no exigir membresia, a diferencia del Trainee Merit: es el primer movimiento mas barato. | 2026-08-31: fuente clave de esta pasada, permitio pasar W-0010 a VERIFIED sorteando la SPA vacia de sleepmeeting.org. Cita util: 'More information regarding the next cycle of the Trainee Awards can be expected in January of 2027'.</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4647,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>No estaba en sources.tsv. Con puerta de membresia, asi que tiene un plazo de maduracion medido en anos: por eso merece seguimiento ahora y no despues.</t>
+          <t>No estaba en sources.tsv. Con puerta de membresia, asi que tiene un plazo de maduracion medido en anos: por eso merece seguimiento ahora y no despues. | 2026-08-31: AVISO PERMANENTE, EL ROTULO DE ESTE TABLON NO ES FIABLE. Sigue marcando 'CONVOCATORIA ABIERTA' convocatorias de 2026 cuyo plazo vencio el 25-01-2026, segun el PDF de bases extraido localmente. Genero una falsa urgencia en la pasada anterior. El estado se saca SIEMPRE del PDF de bases, nunca de la etiqueta del tablon. PDF de las Becas de Investigacion 2026: https://ses.org.es/wp-content/uploads/2025/11/bases_becas_investigacion_2026-1.pdf</t>
         </is>
       </c>
     </row>
@@ -5579,8 +5696,528 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SRC-0087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>IBRO - Grants Calendar</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://ibro.org/grants/grants-calendar/</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Una sola pagina con la ventana de apertura y cierre de TODOS los programas de IBRO y su estado abierto/cerrado. Es la unica vista de IBRO con fechas: la pagina indice /grants/ lista los programas pero no publica ni un solo plazo. Con una llamada sustituye a diecisiete.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Fetch directo de la URL; leer la tabla y quedarse con las filas cuyo cierre sea posterior a hoy.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Alta en la pasada del 2026-08-31 (rama 1). AVISO: https://ibro.org/fellowships/ devuelve HTTP 404; si alguna rutina la tiene guardada, sustituirla por esta. Verificado ademas que IBRO no financia salarios postdoctorales, solo viajes, cursos e intercambios cortos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SRC-0088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BOJA - Boletin Oficial de la Junta de Andalucia</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.juntadeandalucia.es/boja/</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Extractos y resoluciones completas de las convocatorias de la Consejeria de Universidad, Investigacion e Innovacion, con fechas, numero de ayudas y presupuesto. Es a Andalucia lo que el BOE es al Estado, y Andalucia es donde ella vive y trabaja.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Buscar 'Direccion General de Planificacion de la Investigacion' + 'personal investigador doctor' en la seccion '1. Disposiciones generales'. Alternativa que ya funciono: WebSearch con allowed_domains=['juntadeandalucia.es']. Fichas directas con el patron /boja/AAAA/NNN/X.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Mensual de noviembre a febrero; trimestral el resto del ano</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Alta en la pasada del 2026-08-31 (rama 2). BLOQUEO QUE ESTA FUENTE RODEA: las fichas de juntadeandalucia.es/servicios/sede/tramites/... devuelven 200 con cuerpo vacio porque se renderizan por JavaScript, tanto con WebFetch como con curl. BOJA es HTML plano y si funciona.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SRC-0089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Institutos de Investigacion Sanitaria (Navarrabiomed, IDIS) - convocatorias AES</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.navarrabiomed.es/es/actualidad/convocatorias/</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Reproducen VERBATIM los articulos de requisitos de la AES del ISCIII, con fechas de apertura y cierre en campos estructurados. Resuelven el bloqueo cronico de isciii.es (503 en HTML) sin depender de descargar y extraer PDF.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>site:navarrabiomed.es OR site:idisantiago.es 'Rio Hortega' OR 'Sara Borrell' AES &lt;ano&gt;; o directamente el slug contratos-rio-hortega-aes-&lt;ano&gt;. Espejos equivalentes: idisantiago.es/convocatoria/, idisna.es/convocatorias/, idissc.org/convocatoria/</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Semanal durante enero-marzo (ventana AES); mensual el resto</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Alta en la pasada del 2026-08-31 (rama 2). Desbloquea las filas de mayor Fit de la base (F-0001, F-0002). ADVERTENCIA DE USO: son espejos institucionales; cuando publican un plazo hay que distinguir si es el del financiador o el interno del centro, la misma trampa ya documentada para Wellcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SRC-0090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Sede electronica del ISCIII - anuncios por procedimiento</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://sede.isciii.gob.es/anouncements.jsp</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Las fechas reales de resolucion provisional, definitiva y, sobre todo, la VENTANA EXACTA DE ALEGACIONES de cada actuacion de la AES, que es el dato que decide la elegibilidad de Rio Hortega. Es HTML plano y responde bien mientras isciii.es sigue dando 503.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>El parametro type cambia por procedimiento y convocatoria (CM14, CM21, CM22, CM23, CM25...); fichas en anouncements_detail.jsp?pub=NNNNN. Para descubrir nuevas: site:sede.isciii.gob.es 'Resolucion provisional' 'Contratos Rio Hortega'</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Quincenal de febrero a diciembre</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Alta en la pasada del 2026-08-31 (rama 5). Es la fuente que resolvio la pregunta de las alegaciones de la AES. TRAMPA: el buscador presenta fichas antiguas como si fueran actuales (el primer resultado para 'resolucion provisional Rio Hortega' era la convocatoria de 2022); hay que leer SIEMPRE el ano dentro de la ficha, nunca fiarse del snippet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SRC-0091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Fundacion Seneca (Region de Murcia) - catalogo de convocatorias</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://fseneca.es/web/convocatorias</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>El catalogo anual completo de la Region de Murcia agrupado por programa, con historico desde 2005. Permite saber de un vistazo que programas estan vivos y cuales latentes: asi se detecto que Saavedra Fajardo no esta en 2026 y que la III Fulbright-Seneca si.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Abrir la pestana 'Convocatorias 2026' y la seccion 'Talento Investigador y su Empleabilidad'.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Mensual, con revision obligatoria en la primera semana de septiembre por el fin del mes inhabil</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>MEDIA-ALTA</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Alta en la pasada del 2026-08-31 (rama 2). Tiene grupo de acogida natural alli (Universidad de Murcia) y la competencia es LOW. BLOQUEO Y SOLUCION: fseneca.es devuelve 503 a WebFetch pero 200 a curl con User-Agent de navegador. La pagina del programa Saavedra Fajardo esta publicada con texto Lorem ipsum de relleno: no es un fallo de red, es que el financiador no ha escrito la descripcion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SRC-0092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Fundacion Alicia Koplowitz - ayudas a la investigacion y a la formacion</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://fundacionaliciakoplowitz.org/lineas-de-accion/ayudas-investigacion/</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Las bases anuales en PDF de las ayudas a proyectos (publicadas en enero, cierre en abril) y el indice de las ayudas de formacion. Es la fundacion privada espanola que mejor encaja con su linea infanto-juvenil.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>La URL del PDF es predecible: /wp-content/uploads/AAAA/MM/Bases_...; comprobar la aparicion de la carpeta del ano nuevo. Segunda pagina a vigilar: /lineas-de-accion/ayudas-formacion/</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Trimestral, con pico en enero</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Alta en la pasada del 2026-08-31 (rama 3). PENDIENTE: las 'Ayudas de Formacion' de la misma fundacion no estan fichadas y su pagina no enlaza bases; segun Tier 2 incluyen estancias de 6-12 meses en el extranjero, duracion a la que ya no son ayudas de viaje sino becas de verdad. Es el hueco mas prometedor que dejo abierto la rama 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SRC-0093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Fundacion Jose Luis Castano-SEQC / SEMEDLAB - becas y premios convocados</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.fundacionjlc.es/becas-premios-convocados/</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>La via clinica completa, que estaba sin explorar. En una sola pagina aparecen simultaneamente 8 convocatorias vivas: intercambio internacional, dos ciclos IFCC, becas post-residencia, ayudas a tesis doctoral, ayudas a proyectos y becas de jornadas. Todas restringidas a socias de una sociedad de especialidad espanola: competencia estructuralmente LOW.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Es un indice: abrir la pagina y comparar la lista de slugs /becapremio-convocado/&lt;slug&gt;/ con la de la semana anterior.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Mensual, con revision reforzada en enero y en septiembre</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Alta en la pasada del 2026-08-31 (rama 4). LA FUENTE MAS VALIOSA DE LA PASADA: de aqui salio la unica convocatoria con plazo inminente para la que hoy es elegible. BLOQUEO Y SOLUCION: WebFetch devuelve 503 en varias subpaginas; descargar con curl y extraer localmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SRC-0094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>AEGH - blog de convocatorias</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://aegh.org/blog-2/</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Las cinco lineas de ayuda de la AEGH (estancia profesional, bolsas de viaje, premio joven, becas para acudir al ESHG y nominacion a la national fellowship de la ESHG), que no aparecen en ningun agregador.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Abrir el indice del blog y filtrar los titulos por Convocatoria|Beca|Premio|Bolsas.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Mensual, con revision reforzada en enero-febrero, donde se concentran casi todos los plazos</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Alta en la pasada del 2026-08-31 (rama 4). LIMITACION: la AEGH no publica bases completas en PDF, solo las envia por secretaria@aegh.org, asi que no se pueden preverificar importes ni condiciones de ediciones futuras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SRC-0095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SENC - ayudas y calendarios en PDF</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.senc.es/ayudas-de-la-senc/</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>La SENC publica cada ano dos PDF-calendario (travel grants en diciembre, awards en abril) con numero de ayudas, importe, fecha de apertura y fecha de cierre en una sola tabla: el formato mas denso encontrado en toda la rama.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Extraer del HTML los href que casen con wp-content/uploads/.*(CALENDAR|Call|TRAVEL|Award).*\.pdf y quedarse con los del ano en curso; extraer el texto de los PDF LOCALMENTE, nunca via resumen automatico.</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Dos veces al ano, en diciembre y en abril</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Alta en la pasada del 2026-08-31 (rama 4). Pendiente de abrir: https://www.senc.es/wp-content/uploads/2024/09/Requisitos-solicitudes-de-ayudas-y-becas-SENC.pdf, para saber si la regla de 2 anos consecutivos de antiguedad se aplica tambien a los premios o solo a las ayudas de viaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SRC-0096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>AASM - ficha del congreso SLEEP 2027</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://aasm.org/event/sleep-2027/</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Logistica y calendario de SLEEP 2027 (Denver, cursos 5-6 de junio, sesion general 6-9 de junio, registro en enero de 2027). Sirve de confirmacion cruzada del ciclo de premios de becarias de la SRS.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Fetch directo; leer las fechas del congreso y la apertura de registro.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Alta en la pasada del 2026-08-31 (rama 5). Rodea parcialmente el bloqueo de sleepmeeting.org, que responde 200 pero sirve una SPA vacia; la fecha de apertura de resumenes sigue sin poderse confirmar por ninguna via.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J87"/>
+  <autoFilter ref="A1:J97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5711,7 +6348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9652,8 +10289,254 @@
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Altas de la pasada de descubrimiento</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>26 filas nuevas (F-0037 a F-0062). Cinco ramas en paralelo: buques insignia UE, programas nacionales y autonomicos, fundaciones y financiadores de campo, viajes y premios, y watchlist. Lo urgente: la Beca Internacional de Intercambio Cientifico Profesional de SEMEDLAB, OPEN y con cierre el 30-09-2026, Fit 4 y competencia LOW, la unica convocatoria con plazo inminente para la que hoy es elegible. Lo de mejor encaje: el ISPG ECIP Travel Award, Fit 5 y esfuerzo XS, para el que califica por ser doctoranda.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Rio Hortega (F-0001): se adelanta un ano su primera oportunidad</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Verificado en el PDF oficial de la AES 2026 (art. 34.2) que la FSE debe terminar antes del cierre del plazo de ALEGACIONES a la resolucion provisional, no antes de la solicitud. Con precedentes de la sede del ISCIII (alegaciones del 3 al 16 de octubre en 2025), su fin de residencia del 22-05-2027 cae holgadamente dentro: puede presentarse a la AES 2027 en febrero-marzo de 2027 siendo todavia residente. Hay que preparar la solicitud ya, no en 2028.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://sede.isciii.gob.es/anouncements_detail.jsp?pub=51490</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>MSCA (F-0009): la convocatoria 2026 estaba abierta y la de 2027 puede ser la ultima</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>La fila decia CLOSED y la convocatoria 2026 esta abierta hasta el 09-09-2026 (ella no es elegible). Mas importante: la de 2027 (cierre 08-09-2027) es la ultima de Horizonte Europa y no hay certeza de que exista una PF con estas reglas en 2028. Como la regla exige HABER DEFENDIDO y no tener el titulo expedido, adelantar la defensa a antes de septiembre de 2027 pasa de preferencia de calendario a decision con consecuencias economicas. Fit ajustado de 4 a 3 porque no es elegible para ninguna edicion publicada.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/funding/msca-postdoctoral-fellowships-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>EMBO (F-0008): resueltos los dos pendientes y aparece una via nueva de elegibilidad</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>PDF de guidelines extraido localmente. El doctorado NO se exige al solicitar, asi que puede presentarse siendo doctoranda; el cuello de botella es la publicacion, y su REVISION no serviria porque exigen 'primary research paper'. Via nueva: enviar el empirico a Review Commons o Peer Community In da revisiones publicas verificables y satisface la elegibilidad sin esperar a la revista. La ronda de otono de 2027 cae el 09-07-2027 y es la primera sin derecho a resolicitud.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Repaso de la watchlist</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>11 de 14 filas revisadas (W-0001, W-0002, W-0003, W-0004, W-0005, W-0007, W-0009, W-0010, W-0012, W-0013, W-0014). NINGUNA convocatoria ha reabierto esta semana. Correccion mayor en W-0012: la urgencia de las Becas SES era FALSA, el tablon rotula 'CONVOCATORIA ABIERTA' un plazo vencido el 25-01-2026. W-0014 (One Mind) verificada por primera vez y resulta inelegible estructural. W-0010 pasa a VERIFIED. Sin revisar: W-0006, W-0008 y W-0011. 8 filas nuevas.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Ampliacion de la superficie de vigilancia</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>10 fuentes nuevas y 6 filas con notas actualizadas. Las de mas valor: la sede electronica del ISCIII (unica via a las ventanas de alegaciones de la AES, y responde mientras isciii.es da 503), el indice de la Fundacion Jose Luis Castano-SEQC (de donde salio la unica convocatoria urgente), los espejos de los IIS para la AES y el BOJA para lo andaluz.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>subscriptions</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Alertas propuestas</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2 altas TODO (tope por pasada), ambas de membresia: SEMEDLAB, que es requisito de la convocatoria que cierra el 30-09-2026, y AEGH, cuyo reloj de 2 anos de antiguedad gobierna tres ayudas distintas.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H96"/>
+  <autoFilter ref="A1:H103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10842,7 +11725,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-432</v>
+        <v>-439</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -10988,7 +11871,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -11130,7 +12013,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-115</v>
+        <v>-122</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -11395,7 +12278,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-186</v>
+        <v>-193</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -11787,7 +12670,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -11925,7 +12808,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -12059,7 +12942,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -12189,7 +13072,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -12319,7 +13202,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -13477,16 +14360,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AB63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
@@ -13499,7 +14382,7 @@
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="52" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="52" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
@@ -13680,7 +14563,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>OBLIGATORIA y la solicita el centro, no ella. Necesita un jefe de grupo vinculado a un centro asistencial publico del SNS. Cupos por centro (AES 2026, art. 33.3): centros de un IIS, 14 solicitudes y 8 concesiones; otros centros asistenciales, 8 y 4. Un jefe de grupo con un Rio Hortega AES-2025 activo no puede solicitar. Hay que ganar antes una preseleccion interna: empezar la conversacion en otono de 2026.</t>
+          <t>EXCLUSIVAMENTE entidades sanitarias de titularidad publica con actividad clinico-asistencial; el contrato simultanea investigacion y asistencia. El Hospital Regional Universitario de Malaga / IBIMA encaja de forma directa.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -13707,7 +14590,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Cita literal, AES 2026 art. 34, requisito 2o: 'Haber finalizado el programa de FSE que habilita para participar en esta actuacion durante el ano 2021, o en fecha posterior, incluyendo a los que lo hagan en 2026, siempre que sea con anterioridad a la fecha que se establezca para la finalizacion del plazo de alegaciones a la resolucion provisional de concesion.' Plazo Rio Hortega 2026 (art. 7.6): del 10 de febrero al 5 de marzo de 2026. Solicita el centro, no la candidata.</t>
+          <t>VERIFICADO EN EL PDF OFICIAL DE LA AES 2026, art. 34.2, texto extraido localmente: 'Haber finalizado el programa de FSE que habilita para participar en esta actuacion durante el ano 2021, o en fecha posterior, incluyendo a los que lo hagan en 2026, siempre que sea con anterioridad a la fecha que se establezca para la finalizacion del plazo de alegaciones a la resolucion provisional de concesion.' LA CONVOCATORIA NO FIJA ESA FECHA POR ADELANTADO: se determina al publicarse la resolucion provisional. Precedentes Tier 1 de la sede del ISCIII: Rio Hortega AES 2025, alegaciones 'del 3 al 16 de octubre de 2025'; convocatoria 2022, 'del 19 al 30 de septiembre de 2022'. Rio Hortega va sistematicamente 2-3 meses mas tarde que Sara Borrell y Miguel Servet. Otras condiciones: titulo oficial de especialidad MIR/FIR/BIR/QIR/PIR/EIR/RIR (si extranjero, reconocido u homologado; la mera solicitud de homologacion no vale); no disfrutar ni haber completado antes un Contrato Rio Hortega; se descuentan interrupciones justificadas (maternidad/paternidad, IT por riesgo en el embarazo, IT superior a 3 meses, atencion a dependientes).</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -13742,7 +14625,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -13752,7 +14635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -13762,7 +14645,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Antes de diciembre de 2026: identificar y abordar a un jefe de grupo (IBIMA / Hospital Regional Universitario de Malaga primero, por estar ya alli; una segunda opcion en otro IIS). Cuando aparezca la resolucion AES 2027 en el BOE (previsible en diciembre de 2026), releer el art. 34.2o para confirmar que dice '2022 o posterior, incluyendo a los que lo hagan en 2027' y que la fecha de alegaciones cae despues del 22-05-2027.</t>
+          <t>ADELANTA UN ANO SU PRIMERA OPORTUNIDAD REAL: puede presentarse a la AES 2027 en febrero-marzo de 2027 SIENDO TODAVIA RESIDENTE, y cumplir el requisito al terminar la FSE el 22-05-2027, muy por delante del cierre de alegaciones previsto entre finales de septiembre y mediados de octubre de 2027. Rio Hortega no exige doctorado, asi que su defensa de febrero de 2028 no la bloquea. Preparar la solicitud DESDE YA, no en 2028: hace falta centro sanitario publico que la avale (IBIMA/HRU Malaga) y los cupos por centro son estrictos. Riesgo real: que el Registro Nacional de Especialistas en Formacion refleje su fin de residencia antes de la fecha de alegaciones; es un riesgo de tramite, no de fondo.</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -13777,7 +14660,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Resolucion AES 2026 del ISCIII (19-12-2025), PDF descargado y extraido en local. Las paginas HTML de isciii.es dan 503, pero el endpoint del PDF descarga bien. Espejo alternativo verificado: https://www.iisaragon.es/wp-content/uploads/2025/12/AES_2026.pdf . PENDIENTE: no se ha localizado en el texto que fecha concreta fija la AES para el fin del plazo de alegaciones a la resolucion provisional; ese dato es el que decide si el fin de su residencia (22-05-2027) cae dentro del plazo en la edicion 2027.</t>
+          <t>Resolucion de 19-12-2025 de la AES 2026 (111 paginas), PDF descargado con curl (User-Agent de navegador, obligatorio) y extraido con pypdf. Espejo: https://www.iisaragon.es/wp-content/uploads/2025/12/AES_2026.pdf. Ventanas de alegaciones en https://sede.isciii.gob.es/anouncements_detail.jsp?pub=51490 (Rio Hortega AES 2025).</t>
         </is>
       </c>
     </row>
@@ -14121,7 +15004,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -14131,7 +15014,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -14141,7 +15024,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Nada hasta 2028. AVISO ANTIRRUIDO, comprobado esta pasada: la 'convocatoria Juan de la Cierva 2026' que circula por internet NO EXISTE. fibao.es reetiqueta como 2026 la convocatoria de 2025 (mismo BOE-B-2025-39640) y tesify.es publica fechas de 2026 sin ningun respaldo oficial. Vigilar solo el BOE: la resolucion de la AEI aparece a finales de octubre.</t>
+          <t>CORRECCION DE MATIZ: la JDC 2026 no esta retrasada. La convocatoria mas reciente sigue siendo la de 2025 (BOE-B-2025-39640, extracto de la Resolucion de 29-10-2025, plazo del 25-11-2025 al 17-12-2025 a las 14:00, BDNS 857452). Por el patron de 2025 (extracto en BOE el 31-10-2025), el extracto de la JDC 2026 deberia publicarse a finales de octubre de 2026: su ausencia hoy es lo esperable, no una anomalia. Vigilar el BOE esas semanas. Se mantiene la advertencia sobre fibao.es y tesify.es, que siguen sin respaldo oficial.</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -14473,7 +15356,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Movilidad internacional real (cambio de pais y de campo). Publicacion: en la fase de LOI vale un manuscrito de primera autora publicado, aceptado, en prensa O EN PREPRINT; en la propuesta completa el preprint ya no vale. Ciclo AY2027 (cerrado): LOI iniciada antes del 05-05-2026 y presentada antes del 12-05-2026, propuesta completa 24-09-2026, incorporacion entre 01-04-2027 y 01-01-2028.</t>
+          <t>MATIZ IMPORTANTE QUE LA FILA NO RECOGIA: es cierto que en fase LOI vale un preprint, pero EN FASE DE PROPUESTA COMPLETA ESA OPCION DESAPARECE: el manuscrito debe estar '(i) published in a peer-reviewed journal, (ii) accepted and in press... or (iii) accepted for publication'. El preprint solo compra tiempo hasta el LOI; para septiembre hace falta aceptacion. Confirmado ademas (sec. 3.7, bases AY2027): 'A completed doctoral degree is not required at the time of application'. Referencias AY2027 para calibrar el AY2028: portal 12-03-2026, LOI 12-05-2026, propuesta completa 24-09-2026; doctorado 'before 31 December 2027 at the latest' y no elegible si se confirio antes del 24-09-2023 (ventana de ~3 anos). Trasladado al AY2028, su defensa de febrero de 2028 encajaria comodamente en ambos extremos.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -14508,7 +15391,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -14518,7 +15401,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -14528,7 +15411,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Dos cosas concretas. (1) Depositar como preprint uno de los dos manuscritos de primera autora: satisface el requisito de publicacion en fase de LOI sin esperar a los revisores. (2) De aqui a enero de 2027, preseleccionar de 3 a 5 laboratorios de acogida en el extranjero que supongan cambio real de campo. El calendario del ciclo AY2028 no esta publicado; se espera hacia enero-marzo de 2027 siguiendo el patron del AY2027 (LOI en primavera, propuesta completa en septiembre).</t>
+          <t>El calendario AY2028 SIGUE SIN PUBLICARSE (comprobado en Tier 1: la pagina anuncia todavia el AY2027). Se espera entre enero y marzo de 2027. Depositar un preprint del empirico australiano sigue siendo la accion mas barata y de mayor rendimiento, pero hay que planificar la aceptacion para la propuesta completa de septiembre, no solo el LOI.</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -14590,7 +15473,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -14599,7 +15482,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Hasta 2 anos</t>
+          <t>24 meses (minimo 12; maximo 36 sumando tiempo parcial). Hasta 20% de secondment en otro pais, salvo el pais del doctorado</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -14609,7 +15492,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Cita literal: 'Applicants must have at least one first author publication (research paper) accepted in or published in an international peer reviewed journal at the time of application.' Un preprint SOLO vale si lleva revision por pares publica y en profundidad de un servicio independiente (tipo Review Commons), no un preprint a secas. Doctorado exigido al EMPEZAR, no al solicitar. Quien ya este en el laboratorio de acogida solo puede solicitar si lleva menos de 6 meses viviendo en el pais de acogida. Cierre verificado: viernes 22-01-2027 a las 14:00 CET. Desde la ronda de otono de 2027 se prohiben las resolicitudes.</t>
+          <t>PDF de guidelines extraido localmente (15 paginas, 35.847 caracteres), no por resumen automatico. CINCO reglas, dos de ellas nuevas: (1) PHD NO EXIGIDO AL SOLICITAR: 'Applicants must hold a PhD degree or equivalent at the start of the fellowship, but not necessarily at the time the application is submitted'; si ya lo tiene, elegible dentro de los dos anos previos. ELLA PUEDE SOLICITAR SIENDO AUN DOCTORANDA. (2) PUBLICACION, que es el verdadero cuello de botella: exige 'at least one first (or joint first) author PRIMARY RESEARCH PAPER accepted for publication or published' al presentar; un preprint solo vale con revisiones publicas en profundidad de un servicio independiente y verificable (Peer Community In, Review Commons). OJO: 'primary research paper' significa que su REVISION en Journal of Sleep Research NO SERVIRIA aunque se aceptara; solo cuenta el empirico de Nature Mental Health. (3) Nota explicita sobre MD: 'Candidates with a medical degree (M.D.) may be eligible... provided they hold a PhD (MD-PhD programme)'. (4) MOVILIDAD, buena noticia: maximo 6 meses en el pais de acogida durante los 18 previos; excluido el pais del doctorado (Espana fuera); excluido volver a un laboratorio donde haya trabajado mas de 6 meses, de modo que QIMR Berghofer y el laboratorio japones (~3 meses cada uno) NO quedan vetados como destino. (5) Plazo maximo de incorporacion: ronda de primavera, entre el 1 de julio del ano del premio y el 15 de febrero del siguiente; ronda de otono, entre el 1 de enero y el 15 de agosto del siguiente; solo se empieza dia 1 o dia 15. RIESGO ADICIONAL: 'Applications in which the postdoctoral project is a direct continuation of the PhD project will not be considered', y EMBO excluye trabajo aplicado o clinico sin pregunta biologica clara: tendria que reencuadrar hacia una pregunta biologica distinta de su tesis.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -14644,7 +15527,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -14654,7 +15537,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -14664,7 +15547,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>El cuello de botella es la ACEPTACION de uno de los dos manuscritos: sin eso no hay solicitud posible. Vigilarlo como el hito numero uno. La ronda del 22-01-2027 solo es realista si algo se acepta antes; si no, apuntar a la ronda de otono de 2027 (fecha aun no publicada) teniendo en cuenta que desde esa ronda ya no se permite resolicitar.</t>
+          <t>Sigue INELEGIBLE hoy, y el bloqueo es la publicacion, no el doctorado. Dos vias, y la segunda es nueva y mas rapida: (a) que se acepte el manuscrito de Nature Mental Health antes de un corte; (b) ENVIAR EL EMPIRICO A REVIEW COMMONS O PEER COMMUNITY IN para obtener revisiones publicas verificables sobre el preprint, lo que satisface la elegibilidad sin esperar a la aceptacion de la revista, y no compite con (a). Cortes: 4o viernes de enero y 2o viernes de julio, 14:00. El de otono de 2027 cae el 09-07-2027 y es el PRIMERO SIN DERECHO A RESOLICITUD: solo tendra un disparo, conviene no gastarlo pronto.</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -14679,7 +15562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>https://www.embo.org/funding/fellowships-grants-and-career-support/postdoctoral-fellowships/eligibility/ leida esta pasada; el PDF de guidelines (jun-2026) quedo sin abrir por techo de llamadas.</t>
+          <t>PDF 'Application guidelines' descargado con curl y extraido localmente con pypdf. CORRECCION DE VERSION: el enlace del sitio lo describe como de junio de 2026, pero el pie de las quince paginas dice 'July 2026'. Cierre 22-01-2027 14:00 CET confirmado por el propio PDF.</t>
         </is>
       </c>
     </row>
@@ -14716,11 +15599,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>9</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No publicado en las paginas de la CE leidas (asignaciones de manutencion, movilidad, familia, investigacion y gestion como costes unitarios corregidos por pais). No citar cifras sin consultar el Portal de Financiacion y Licitaciones.</t>
@@ -14738,17 +15632,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>EL PUNTO DECISIVO, Y VA EN SU CONTRA: el doctorado debe estar en su poder EN LA FECHA LIMITE de la convocatoria, no al empezar. La pagina de la MSCA dice que las candidatas 'should have a PhD degree at the time of the deadline for applications. Applicants who have successfully defended their doctoral thesis but who have not yet formally been awarded the doctoral degree will also be considered eligible to apply'. Con una defensa prevista para febrero de 2028 falla el plazo del 09-09-2026 y el del 08-09-2027, y ni siquiera puede acogerse a la concesion de 'defendida pero no expedida', porque no habra defendido en septiembre de 2027. Movilidad: no haber residido ni ejercido su actividad principal en el pais de la beneficiaria mas de 12 meses en los 36 anteriores al plazo.</t>
+          <t>Texto Tier 1: los candidatos 'should have a PhD degree at the time of the deadline for applications', si bien quienes 'have successfully defended their doctoral thesis but who have not yet formally been awarded the doctoral degree will also be considered eligible to apply'. Regla de movilidad textual: no haber residido ni tenido su actividad principal en el pais del beneficiario 'for more than 12 months in the 36 months immediately before the call deadline'. EVALUACION PARA ELLA (Confidence LIKELY por las fechas imprecisas de sus estancias): Espana queda EXCLUIDA como pais de acogida y todos los demas paises quedan disponibles, Australia y Japon incluidos, porque ~3 meses esta muy por debajo del umbral de 12; el margen es tan amplio que ninguna imprecision razonable cambiaria el resultado. INELEGIBLE para la convocatoria 2026, que cierra el 09-09-2026: su defensa esta prevista para febrero de 2028.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>El instrumento le encaja casi perfectamente -ciudadana de la UE, perfil MD+PhD, una linea computacional portatil que cualquier acogida europea puede absorber y una beca de 1-2 anos que podria empezar en 2029- pero la regla del doctorado en la fecha limite hace inalcanzables las dos convocatorias que quedan de Horizonte Europa, y ESE ES EL HALLAZGO MAS IMPORTANTE DE ESTA RAMA. Su primera opcion es una convocatoria de 2028 bajo el programa que suceda a Horizonte Europa (que termina en 2027), asi que el esquema es para planificar, no para solicitar: el riesgo a senalar no es su elegibilidad en 2028 (una defensa en febrero de 2028 supera con margen un plazo de septiembre de 2028, e incluso un retraso de varios meses seguiria pasando) sino si el programa sucesor mantiene el instrumento con el mismo ritmo anual. Sobre movilidad, comprobado punto por punto: ha vivido en Malaga de forma continuada desde el 22-05-2023 salvo dos estancias de ~3 meses, asi que en cualquier ventana de 36 meses que termine en un plazo de 2028 su residencia espanola supera de largo los 12 meses; LA REGLA DE MOVILIDAD DESCARTA DE FACTO UNA ACOGIDA ESPANOLA y deja bien cualquier otro pais de la UE o asociado. Como las dos estancias fueron de solo ~3 meses, tampoco descalifican a Australia ni a Japon como acogida de salida de una Global Fellowship, pero como las fechas exactas no estan fijadas toda esta valoracion de movilidad es LIKELY, no VERIFIED. LINEA CON LA QUE ENCABEZAR: genetica estadistica de rasgos complejos y la linea de GWAS/PRS psiquiatrico, eligiendo una acogida cuyo entorno ERC o de consorcio pueda absorber a una clinica genetista. TRABAJO: pesado (L), propuesta completa de Horizonte Europa mas compromiso de acogida, pero es trabajo de 2028. Registrada como CLOSED porque la convocatoria de 2026 sigue abierta al mundo hasta el 09-09-2026 pero esta cerrada PARA ELLA.</t>
+          <t>El programa es contenido puro suyo y en abstracto seria un 4, pero se baja a 3 porque hay una condicion estructural sin resolver y conviene que la fila lo diga: NO ES ELEGIBLE PARA NINGUNA EDICION PUBLICADA. La convocatoria 2026 cierra el 09-09-2026, mucho antes de su defensa. La de 2027 (HORIZON-MSCA-2027-PF-01-01, lanzamiento 07-04-2027 y cierre 08-09-2027, ambos marcados TBC en origen, 388,57 M EUR) TAMPOCO le llega por cinco meses. Y ahi esta el problema serio: la convocatoria de 2027 es la ultima del actual marco financiero, porque Horizonte Europa cubre 2021-2027, de modo que NO HAY CERTEZA DE QUE EXISTA UNA CONVOCATORIA PF CON ESTAS REGLAS EN 2028 (dependeria del programa sucesor, FP10, sin diseno ni calendario fijados). PALANCA ACCIONABLE: la regla oficial exige HABER DEFENDIDO, no tener el titulo expedido; si adelantara la defensa a antes del 08-09-2027 entraria en la ultima convocatoria de Horizonte Europa. El choque es con el MIR, que termina el 22-05-2027: quedarian ~3,5 meses, apretado pero no imposible si la tesis esta madura. Es una decision con consecuencias economicas concretas, no una preferencia de calendario, y toca hablarla con la direccion de tesis este otono, no en 2027.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -14758,7 +15652,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>399,05 millones de euros para ~1600 ayudas en la convocatoria de 2026 frente a un grupo de solicitantes historicamente mucho mayor (en torno a una de cada siete en ediciones recientes, sin verificar).</t>
+          <t>Convocatoria 2026 con 399,05 M EUR y expectativa de financiar 'nearly 1600 projects' sobre varias veces esa cifra de solicitudes; es el instrumento posdoctoral mas solicitado de Europa</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -14773,34 +15667,34 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>No hay nada que presentar. La accion es estrategica: decidir con la direccion de tesis, este otono, si la defensa puede adelantarse a antes del 08-09-2027 para alcanzar la ultima convocatoria MSCA de Horizonte Europa. Ver W-0015.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Ninguna accion posible antes de 2028. En 2027, vigilar el programa de trabajo del programa sucesor y si la MSCA-PF sobrevive con la misma forma; mientras tanto, fijar los meses exactos de las estancias de QIMR y Japon para poder elevar el calculo de movilidad a VERIFIED. No construir una relacion de acogida sobre la suposicion de que una solicitud en 2027 es posible.</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>https://marie-sklodowska-curie-actions.ec.europa.eu/actions/postdoctoral-fellowships</t>
@@ -14808,7 +15702,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Rama 1. Tier 1: pagina de la accion MSCA (redaccion de elegibilidad), noticia de la convocatoria 2026 (fechas, presupuesto, ~1600 ayudas) y pagina de la convocatoria 2027, con las fechas marcadas TBC por la propia MSCA. Que 2027 sea la ultima convocatoria de este marco financiero procede de una fuente secundaria y NO esta confirmado en la pagina de la MSCA: tratar como LIKELY.</t>
+          <t>Anuncio oficial: la convocatoria 2026 'is open as of 9 April 2026' y 'will close on 9 September 2026'. Fuentes: https://marie-sklodowska-curie-actions.ec.europa.eu/node/1575 y /actions/postdoctoral-fellowships. Convocatoria 2027 en /funding/msca-postdoctoral-fellowships-2027. La afirmacion de que 2027 es la ultima del marco es LIKELY (Tier 2); la pagina oficial no la contiene.</t>
         </is>
       </c>
     </row>
@@ -15735,7 +16629,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>35000 USD al ano hasta dos anos, es decir 70000 USD en total (literal de las bases de 2026; no convertido a euros)</t>
+          <t>hasta 35000 USD anuales durante dos anos = 70000 USD</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -15750,7 +16644,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>EL PUNTO DECISIVO: el titulo de doctorado debe estar ya en su poder al solicitar - 'Applicants must have a doctoral level degree (e.g., M.D. with minimum PGY-IV training, Ph.D., Psy.D., Pharm.D., etc.) and already be employed in research training or a faculty research position.' Es crucial que EL TITULO DE MEDICINA CUENTA como doctorado cualificante siempre que tenga al menos formacion PGY-IV, cosa que alcanza durante su residencia (iniciada el 22-05-2023), asi que aqui la puerta no es estrictamente el doctorado sino EL PUESTO INVESTIGADOR. Exige ademas mentor en el propio centro y que la investigacion sea relevante para trastornos cerebrales y del comportamiento graves.</t>
+          <t>Ciclo 2026 VERIFICADO: apertura miercoles 04-02-2026, cierre miercoles 04-03-2026 a las 23:59 ET. BBRF NO HA PUBLICADO NINGUNA FECHA DE 2027: la fecha 2027-03-05 que llevaba esta fila es una extrapolacion y ademas cae en viernes, cuando el patron de BBRF es cerrar en miercoles. Se retira. ELEGIBILIDAD A VIGILAR (Tier 2, sin confirmar en Tier 1): los postdocs de primer ano son inelegibles y se exige 'M.D. with minimum PGY-IV training' o doctorado mas un puesto de investigacion ya en marcha. Con defensa en febrero de 2028, su primer ano postdoctoral va de febrero de 2028 a febrero de 2029, asi que la primera convocatoria realista seria la de 2029, NO la de 2027.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -15780,39 +16674,39 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Tratar febrero-marzo de 2027 como ventana estimada, nunca como fecha. Descargar y extraer localmente las guidelines en PDF de la BBRF para verificar la exclusion del primer ano postdoctoral y el requisito PGY-IV: si se confirma, W-0007 hay que reprogramarla de 2027 a 2029 y dejamos de vigilar tres anos en balde.</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Nada que presentar antes de 2028. Tratarla como la primera ayuda a escribir en cuanto tenga un posdoc con mentor de psiquiatria en el mismo centro, y releer las bases cada enero (el texto de elegibilidad se reedita anualmente). Merece la pena preguntar a la BBRF por correo si una MD con PGY-IV o mas en un primer ano de puesto investigador cuenta como 'advanced post-doctoral fellow'.</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>https://bbrfoundation.org/grants-prizes/bbrf-young-investigator-grants</t>
@@ -15820,7 +16714,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Rama 1. Tier 1: pagina de ayudas de la BBRF mas el PDF oficial '2026 BBRF YOUNG INVESTIGATOR GRANT Application Guidelines'; el fetch automatico no pudo leer el PDF (es un form-XObject), asi que se descomprimio y se leyo localmente y las citas son literales del documento del financiador.</t>
+          <t>La URL anterior sin el prefijo 'bbrf-' devuelve HTTP 404; corregida. Importe VERIFIED; fechas de 2027 UNVERIFIED.</t>
         </is>
       </c>
     </row>
@@ -15989,14 +16883,18 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -16005,7 +16903,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>De 4 semanas a 4 meses (mas solo con cofinanciacion documentada)</t>
+          <t>Estancia de 4 semanas a 4 meses; dos convocatorias al ano (15 de abril y 15 de octubre); 60% se abona antes de empezar y 40% al entregar el informe</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -16050,27 +16948,27 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Antes del 15-10-2026: confirmar u obtener la membresia de SENC o la individual de FENS, escribir a 2 o 3 PI candidatos para la carta de aceptacion, y decidir si la estancia es una rotacion externa de la residencia (necesita visto bueno del tutor, conviene empezar esa conversacion ya) o una estancia posterior al 22-05-2027 solicitada en la ronda del 15 de abril de 2027.</t>
+          <t>Plazo 15-10-2026 confirmado por dos paginas Tier 1 (FENS e IBRO). RESERVA A TENER EN CUENTA: con el MIR hasta el 22-05-2027, una estancia de 1 a 4 meses tendria que encajarse en su calendario de residencia; conviene decidir antes de invertir en la solicitud.</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -16519,7 +17417,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -16538,7 +17436,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Hace falta un resumen enviado; la ayuda se solicita marcando la casilla correspondiente dentro del formulario de envio de resumenes, asi que esa fecha manda. Notificacion del resultado del resumen a principios de abril de 2027.</t>
+          <t>VIA NACIONAL ADICIONAL DESCUBIERTA, y reduce mucho la competencia: ademas de la solicitud directa a la ESHG, la AEGH (a) concede sus propias 'Becas AEGH para acudir al ESHG' (fueron 3 para el ESHG 2026, Gotemburgo) y (b) NOMINA CANDIDATAS PARA LA 'NATIONAL FELLOWSHIP' DE LA ESHG, que es un cupo por pais. Por la via AEGH la competencia es espanola y no europea. Confianza LIKELY: entradas del blog de la AEGH del 13 y el 15 de enero de 2026 leidas en el indice, no abiertas una a una. PENDIENTE: verificar si el cupo nacional exige tambien 2 anos de antiguedad como socia.</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -16573,27 +17471,27 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Revisar 2027.eshg.org en noviembre de 2026 para la pagina de ayudas; redactar el resumen en enero de 2027 y enviarlo antes del 04-02-2027 con la casilla de ayuda marcada.</t>
+          <t>Verificar en enero de 2027 si la nominacion espanola a la national fellowship de la ESHG exige 2 anos de antiguedad como socia de la AEGH: si no los exige, es un atajo real a un congreso de su linea (ver SUB-0010).</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -17292,7 +18190,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -18264,8 +19162,3301 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>F-0037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Beca Internacional de Intercambio Cientifico Profesional 2026 (Programa de Intercambio Profesional SEMEDLAB)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Lab visit / exchange grant</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Fundacion Jose Luis Castano-SEQC (Fundacion SEMEDLAB) y Sociedad Espanola de Medicina de Laboratorio</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Solicitante en laboratorio espanol; laboratorio receptor obligatoriamente fuera de Espana (cualquier pais)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SI, doble: aceptacion escrita del director del laboratorio receptor mas acuerdo firmado por el jefe del laboratorio espanol de origen</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>30</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>hasta 5500 (1000 de viaje en turista + 1500/mes hasta 3 meses)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Maximo 3 meses; estancia obligatoriamente entre marzo de 2027 y marzo de 2028</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No aplica: no exige doctorado. El corte es de edad, menor de 40 anos</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Socia de SEMEDLAB en el momento de solicitar (esta convocatoria NO exige antiguedad, a diferencia de otras ayudas de la misma Fundacion que piden 1 ano); menor de 40 anos; no haber disfrutado antes de este Programa ni de su version IFCC; documentacion a secretaria@fundacionjlc.es con asunto 'BECAS INTERNACIONALES DE LA FUNDACION'; 5 becas; fallo a finales de noviembre de 2026. NO VERIFICADO si ella ya es socia de SEMEDLAB: es el unico punto que puede tumbar la solicitud.</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Es lo unico con plazo inminente para lo que HOY es elegible, y entra por su puerta menos explotada: la clinica. Por que encaja con ELLA: la ventana de estancia (marzo 2027 - marzo 2028) se solapa casi exactamente con el hueco entre el fin del MIR (22-05-2027) y su defensa prevista (febrero de 2028), asi que cabe de junio de 2027 en adelante sin tocar ni la residencia ni la tesis. Linea a liderar: genetica estadistica aplicada, encajando el proyecto como implantacion de scores poligenicos y pipelines GWAS-PRS en un laboratorio de genomica clinica, que es donde es INDEPENDIENTE; no proponer electrofisiologia ni neuroimagen, que solo maneja supervisada. Elegibilidad punto por punto: edad menor de 40, cumple; trabaja en laboratorio espanol (HRU de Malaga), cumple; laboratorio receptor fuera de Espana, cumple con QIMR Berghofer (contacto ya existente, pero exige visado australiano: anotar, no descartar) o con un laboratorio de genomica clinica europeo, que evita el visado; no beneficiaria previa, previsiblemente cumple; socia de SEMEDLAB, SIN VERIFICAR y decisivo. Reencuadre necesario: el programa habla de laboratorios clinicos y de tecnologias aplicables al laboratorio de origen, asi que la memoria debe argumentar el retorno al laboratorio de Malaga, no el avance de la tesis. Trabajo real: su parte es S (memoria del Anexo 1 con fechas, carta de motivacion al presidente de la Fundacion, CV), 1-2 dias. El cuello de botella NO es el papeleo sino los avales: necesita en menos de 30 dias la aceptacion escrita del director receptor y la firma de su jefe de servicio; una carta de aceptacion internacional suele tardar de 2 a 4 semanas, de modo que el correo al anfitrion sale esta semana o no sale.</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>5 becas para un colectivo cerrado (socias jovenes menores de 40 de una sociedad nacional de especialidad); se evalua calidad de memoria, no curriculo competitivo</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>URGENTE, 30 dias. 1) Comprobar hoy si es socia de SEMEDLAB y, si no, tramitar el alta. 2) Esta semana, correo al laboratorio receptor pidiendo carta de aceptacion. 3) En paralelo, pedir al jefe de servicio la firma del acuerdo. 4) Enviar antes del 30-09-2026.</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>https://www.fundacionjlc.es/becapremio-convocado/beca-internacional-de-intercambio-cientifico-profesional-2026/</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Tier 1, web oficial de la Fundacion Jose Luis Castano-SEQC. El fetch automatico dio 503; el texto se obtuvo con curl y extraccion local, no por resumen automatico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>F-0038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ISPG Early Career Investigator Program (ECIP) Travel Award - World Congress of Psychiatric Genetics</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Conference travel award (society)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>International Society of Psychiatric Genetics (ISPG)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Internacional, sin restriccion de nacionalidad</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>No. Exige abstract aceptado (oral, poster o simposio)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>UNKNOWN (travel stipend, la cuantia no se publica)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Estudiante de grado, ESTUDIANTE DE DOCTORADO, estudiante de medicina, postdoc, o menos de 5 anos desde el doctorado</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Solicitud ECIP presentada junto con un abstract cientifico; excluidas quienes recibieron travel award financiado en 2022, 2023, 2024 o 2025; incluye mentorizacion por una investigadora senior durante el congreso. Requisito de membresia de ISPG NO confirmado. Ciclo 2026 cerrado: el plazo fue el 14-05-2026, el mismo dia que el cierre de abstracts del WCPG 2026 (Glasgow, 29-09 a 03-10-2026). Sede y fechas del WCPG 2027 SIN ANUNCIAR a 2026-08-31.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Es el encaje mas limpio de toda la base con su linea 1-2, y la solicitud mas barata que existe en ella. Por que encaja con ELLA: la definicion de 'early career investigator' de la ISPG incluye explicitamente a doctorandas y a estudiantes de medicina, y el WCPG es EL congreso de genetica psiquiatrica; su manuscrito empirico australiano (primera autora, en revision en Nature Mental Health) es material de abstract directo, y el abstract no exige publicacion previa, que es justo lo que la deja fuera de casi todo lo demas. Linea a liderar: GWAS/PRS de trastornos psiquiatricos y salud mental; la genetica del sueno en lactantes puede entrar como sesgo de fenotipado. Elegibilidad reloj por reloj: doctoranda, cumple sin discusion; no ha recibido travel award de la ISPG entre 2022 y 2025, cumple; tiene abstract, cumple; membresia de ISPG no confirmada como requisito y la cuota junior es barata. La ventana no se le cierra hasta 5 anos despues del doctorado, asi que sirve para el ciclo 2027 y varios mas. Trabajo real: XS, un abstract que ya tiene escrito en forma de manuscrito mas un formulario. Sin anfitrion, sin avales, sin cartas. Lo unico que hay que hacer es no perder el plazo, que cae ~4,5 meses antes del congreso.</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>La ISPG no publica ratio de concesion; se adjudica 'based on merit and need', lo que suele ampliar la base de concesion. MEDIUM es estimacion conservadora, no dato.</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Vigilar ispg.net entre enero y marzo de 2027 el anuncio de sede y fechas del WCPG 2027 (ver W-0009); hacerse socia junior de la ISPG antes de solicitar y tener el abstract preparado con antelacion. El plazo ECIP coincide con el cierre de abstracts, hacia mayo de 2027.</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>https://ispg.net/ecip-program/</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Tier 1 (ispg.net/ecip-program/ y ispg.net/wcpg-2026/). TRAMPA: ispg.net/abstract-submissions/ sirve contenido obsoleto de 2022 con respuesta 200; la informacion viva esta en la pagina del congreso del ano en curso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>F-0039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Excellent Student Rita Levi-Montalcini Award (SENC)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Young researcher / student prize</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Neurociencia (SENC), Comite de Jovenes Investigadores y Formacion</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Espana (socias de la SENC)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>No. Exige abstract al congreso bienal de la SENC como primera autora</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>600 a la ganadora; diploma a las 5 preseleccionadas</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No aplica: RESERVADO A ESTUDIANTES DE DOCTORADO, no a doctoras</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Ser doctoranda; enviar a secretaria.tecnica@senc.es nombre, afiliacion, nombre de la directora o director de tesis y copia del abstract enviado al congreso SENC como primera autora; 5 preseleccionadas dan una charla de 15 minutos en el simposio 'Young investigators building Neuroscience' y el Comite vota la mejor. Edicion 2025: del 10-04-2025 al 10-06-2025. PUNTO A VERIFICAR: si la regla de 2 anos consecutivos de antiguedad como socia, que aparece redactada para las ayudas de viaje, se aplica tambien a los premios.</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Es el caso puro de algo para lo que califica AHORA por ser predoctoral y dejara de calificar despues. Por que encaja con ELLA: el premio esta reservado a doctorandas y el congreso bienal de la SENC de 2027 caeria hacia septiembre de 2027, con ella todavia predoctoral (defensa prevista en febrero de 2028); es probablemente su ULTIMA ventana para este premio. Linea a liderar: aqui conviene el trabajo empirico australiano (neuroimagen mas genetica), porque el auditorio es de neurociencia y no de genetica estadistica; su parte de neuroimagen es supervisada, pero para una charla de 15 minutos eso no es obstaculo y el analisis genetico que si domina es el nucleo del mensaje. Elegibilidad punto por punto: doctoranda matriculada, cumple; abstract como primera autora, lo tiene; carta de la directora de tesis, trivial; socia de la SENC, sin resolver la antiguedad. Trabajo real: XS, un correo con el abstract y los datos, mas 15 minutos de charla si la preseleccionan. Sin anfitrion ni aval externo. Ademas es acumulable: las bases dicen expresamente que los premios son compatibles con las ayudas de viaje de la SENC, asi que puede ir a las dos cosas para el mismo congreso.</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Sociedad nacional; 5 preseleccionadas y una ganadora sobre un colectivo de pocas decenas de doctorandas socias que presentan abstract al bienal</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Hacerse socia de la SENC ya (ver SUB-0003: arranca ademas el reloj de 2 anos de las ayudas de viaje); abrir el PDF 'Requisitos para solicitudes de ayudas y becas SENC' para saber si la regla de 2 anos se aplica tambien a los premios; confirmar fechas y sede del SENC 2027 y vigilar senc.es en abril de 2027.</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>https://www.senc.es/wp-content/uploads/2025/04/1_Rita-Levi-Montalcini-Award-Call-2025.pdf</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Tier 1: PDF oficial de la convocatoria 2025 descargado con curl y extraido localmente con pypdf, no por resumen automatico. Indice de convocatorias en https://www.senc.es/ayudas-de-la-senc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>F-0040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SENC Travel Awards Program (SENC / FENS / ENCODS / SfN)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Conference travel grant (society)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Neurociencia (SENC)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Socias de la SENC (Espana)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>No. Exige abstract como first presenting author y carta de la directora de tesis</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>350 a 1500 segun convocatoria (FENS 2026: 50 ayudas de 450; ENCODS 2026: 15 de 150; SfN 2026: hasta 10 de hasta 1500)</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Doctorandas y postdocs de primeros anos (para postdocs, maximo 4-8 anos desde el doctorado segun convocatoria, con extension de 1 ano por permiso parental o baja grave de 3 meses o mas)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Socia de la SENC con 2 o mas anos consecutivos de antiguedad en el momento de solicitar (excepcion: las doctorandas de primer ano pueden solicitar con 1 ano de membresia, excepcion que ella ya no aprovecha); abstract como primera autora presentadora; EL TRABAJO NO PUEDE ESTAR PREVIAMENTE PUBLICADO; carta de la directora de tesis certificando que cursa el doctorado; una sola travel grant por ano; solicitud por el area privada de socias. Ciclo 2026 cerrado: FENS/ENCODS el 31-01-2026 y SfN el 10-05-2026.</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Encaje real pero bloqueado por reloj de membresia, no por merito. La condicion de 2 anos consecutivos significa que, si se da de alta ahora (agosto de 2026), no sera elegible hasta agosto de 2028: no llega ni al SENC 2027 ni al SfN 2027. No lo pierde, solo lo retrasa, porque tras defender entra por la via de postdoc de primeros anos, abierta hasta 4-8 anos despues del doctorado. Detalle a su favor que conviene registrar: el requisito de que el abstract NO este previamente publicado juega a su favor precisamente porque sus dos manuscritos siguen en revision. La accion util hoy es solo administrativa: alta inmediata para que el contador corra.</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>50 ayudas para FENS 2026 y 15 para ENCODS dentro de una sociedad nacional; el calendario advierte de que a SfN se nomina antes incluso del cierre de abstracts</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Alta como socia de la SENC ya (SUB-0003). Revisar el calendario de travel grants que la SENC publica cada diciembre: el de 2026 se publico el 23-12-2025.</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>https://www.senc.es/wp-content/uploads/2026/01/03_SENC-TRAVEL-GRANTS-PROGRAM_WEB_EN_2026.pdf</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Tier 1: los dos PDF oficiales (programa 2026 y calendario 2026) descargados con curl y extraidos localmente con pypdf. Calendario: https://www.senc.es/wp-content/uploads/2025/12/04_SENC-Travel-Grants-CALENDAR-2026_WEB_EN.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>F-0041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Beca Estancia Profesional AEGH (modalidad junior)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Lab visit / short-stay grant</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Asociacion Espanola de Genetica Humana (AEGH)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Socias de la AEGH (base Espana); centro receptor nacional o internacional</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SI: carta de aceptacion del centro receptor firmada por la investigadora o facultativa responsable</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>hasta 3000 netos (estancia nacional) / hasta 5000 netos (estancia internacional)</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1 a 3 meses; la estancia de la edicion 2026 debia concluir antes del 01-05-2027</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No aplica: corte por edad, junior = menos de 41 anos</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Socia de la AEGH al corriente de pago CON AL MENOS 2 ANOS DE ANTIGUEDAD; justificantes de las dos ultimas cuotas; CV con contribuciones cientificas hechas en Espana; documento acreditativo de edad; carta de aceptacion del centro receptor; memoria breve. Compromiso posterior: certificado de estancia, memoria y presentacion de resultados en el congreso de la AEGH. Edicion 2026 cerrada el 31-03-2026.</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Encaje tematico excelente y competencia minima, pero hay una condicion que resolver y es de calendario, no de merito: la antiguedad de 2 anos como socia. Si se da de alta hoy (agosto de 2026), la primera edicion para la que seria elegible es la de 2028 (plazo hacia marzo de 2028), justo despues de su defensa; no llega a las ediciones de 2027. Por eso el valor de esta fila no es tanto la ayuda como el reloj que dispara: dar de alta la membresia de la AEGH AHORA abre, a partir de 2028, tres ayudas distintas de la misma sociedad (estancia, bolsa de viaje y premio joven) que hoy le estan vedadas por antiguedad. Tematicamente es de las pocas estancias cortas espanolas que aceptan explicitamente perfiles de genetica humana clinica y de investigacion, que es exactamente lo suyo, y no exige publicaciones, lo que neutraliza su punto debil actual.</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Sociedad nacional de especialidad, dos plazas (una junior y una senior) y colectivo elegible pequeno por el filtro de antiguedad</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Dar de alta la membresia de la AEGH esta semana para arrancar el reloj de 2 anos (ver SUB-0010); revisar aegh.org en febrero de 2027 y de 2028.</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>https://aegh.org/convocatoria-de-becas-estancia-profesional-aegh/</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Tier 1, aegh.org. Las bases completas NO se publican en PDF: solo se envian por secretaria@aegh.org.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>F-0042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Premio Joven en Investigacion de la AEGH (XXVI edicion)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Young researcher prize</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Asociacion Espanola de Genetica Humana (AEGH)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Espana (contribuciones cientificas realizadas en Espana)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2000 netos + inscripcion gratuita al congreso nacional + hasta 600 de viaje y alojamiento</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No aplica: corte por edad, 40 anos o menos a 31 de diciembre del ano anterior</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Socia de la AEGH al menos 2 anos consecutivos; 40 anos o menos; formulario de autobaremacion en linea; justificante de cuota; CV y documento de edad; resumen de contribuciones cientificas hechas en Espana; relacion de publicaciones, becas, proyectos financiados y premios con documentacion acreditativa; jurado = Junta Directiva; puede declararse desierto; no se concede dos veces a la misma persona. Edicion XXVI cerrada el 15-02-2026 a las 23:59.</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Diferencia importante frente al Premio Federico Oloriz que ya se conoce: aqui NO se exige un articulo publicado concreto, sino una autobaremacion de trayectoria (publicaciones, becas, proyectos, premios). Eso significa que sus dos manuscritos en revision no la excluyen formalmente, aunque si la dejan floja en el baremo frente a candidatas de hasta 40 anos con carrera hecha. Bloqueo real: los 2 anos de antiguedad como socia, que la dejan fuera hasta la edicion de 2028-2029. Se registra sobre todo porque, junto con la beca de estancia y las bolsas de viaje, refuerza que el alta en la AEGH es una decision con tres retornos distintos.</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Un unico premio y todo el rango de edad hasta 40 anos compitiendo junto: aqui la competencia si es real dentro de una sociedad pequena</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Alta en la AEGH (SUB-0010). Reevaluar cuando sus dos manuscritos esten publicados: es el momento en que este premio sube de fit.</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>https://aegh.org/convocatoria-xxvi-edicion-del-premio-joven-en-investigacion-de-la-aegh/</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Tier 1, aegh.org.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>F-0043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Bolsas de Viaje AEGH (congreso nacional AEGH / Congreso Interdisciplinar en Genetica Humana)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Conference travel grant (society)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Asociacion Espanola de Genetica Humana (AEGH)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Espana</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>No. Exige comunicacion cientifica (oral o poster) como primera o ultima autora</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>inscripcion al congreso + hasta 600 de viaje y alojamiento (3 bolsas)</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No aplica: corte por edad, MENOR DE 35 ANOS, o cualquier edad en situacion de desempleo</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Socia de la AEGH con antiguedad continuada superior a 2 anos; menor de 35 anos o en paro; haber enviado comunicacion al congreso como primera o ultima autora; no haber sido beneficiaria antes. Edicion 2026 cerrada el 15-02-2026 (XXX Congreso AEGH, Granada, 15-17 de abril de 2026).</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Doble reloj y ambos apretados: los 2 anos de antiguedad la dejan fuera hasta 2028, y para entonces el corte de edad de 35 anos puede haber vencido. SU FECHA DE NACIMIENTO NO CONSTA EN EL PERFIL y esa verificacion decide si esta fila vale algo o es papel mojado; si en la convocatoria de 2029 tuviera 35 o mas, solo entraria por la puerta de 'en situacion de desempleo'. Se registra para no redescubrirla y porque el requisito de comunicacion como primera autora si lo cumple sin esfuerzo.</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>3 bolsas y colectivo elegible muy reducido por el doble filtro de antiguedad y edad</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Verificar su edad antes de invertir nada aqui. Alta en la AEGH (SUB-0010).</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>https://aegh.org/convocatoria-de-bolsas-de-viaje-aegh-xxx-congreso-aegh-y-v-congreso-interdisciplinar-en-genetica-humana-del-15-al-17-de-abril-de-2026-granada/</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Tier 1, aegh.org.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>F-0044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ayudas para Tesis Doctoral a Profesionales Jovenes menores de 40 anos (SEMEDLAB)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Doctoral thesis support grant</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Fundacion Jose Luis Castano-SEQC y SEMEDLAB</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Espana; el proyecto puede desarrollarse en un laboratorio clinico nacional o internacional de reconocido prestigio</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SI: documento de aceptacion y apoyo al proyecto del jefe de servicio o responsable del centro, mas aprobacion del CEIC o documento de aceptacion a evaluacion</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>7500 al ano, minimo 1 y maximo 2 anos = hasta 15000; 4 ayudas</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1 a 2 anos</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No aplica: menor de 40 anos en el momento de la convocatoria</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>ESPECIALISTA DEL LABORATORIO CLINICO QUE HAYA OBTENIDO EL TITULO DE ESPECIALISTA CON ANTERIORIDAD AL INICIO DEL PROYECTO; socia de SEMEDLAB con antiguedad minima de 1 ano; matriculada en el Doctorado y con solicitud de realizacion de la Tesis presentada; integracion en un equipo de investigacion; compatible con contrato laboral; INCOMPATIBLE con cualquier otra beca o contrato de investigacion directo. Edicion 2026: ejecucion del 01-07-2026 al 30-06-2027; el plazo de presentacion NO figura en el texto de la convocatoria.</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>El encaje es de calendario y hay que decirlo con precision. Para la edicion 2026 es INELEGIBLE, porque exige tener el titulo de especialista antes del inicio del proyecto y ella no lo obtiene hasta el 22-05-2027. La edicion 2027, con ejecucion previsible de julio de 2027 a junio de 2028, si le encaja: tendria el titulo desde mayo de 2027, seguiria matriculada en el doctorado y su defensa prevista (febrero de 2028) cae dentro del periodo de ejecucion. La condicion de antiguedad de socia (1 ano, no 2) se cumple sola si se da de alta ahora para la beca de intercambio. Aviso de alcance: es una ayuda a la realizacion de la tesis, no un premio ni una ayuda de viaje; se ficha aqui porque es dinero que ella solicita y se lleva a un centro, pero la dueña puede querer moverla.</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>4 ayudas restringidas a especialistas de laboratorio clinico socias de SEMEDLAB menores de 40: un colectivo de pocas decenas de personas en toda Espana</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>VERIFIED para bases y cuantia (HTML crudo por curl); UNVERIFIED para el plazo de presentacion</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Vigilar fundacionjlc.es a comienzos de 2027 para la edicion 2027 y capturar entonces la fecha limite; comprobar la incompatibilidad con cualquier contrato que tenga.</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>https://www.fundacionjlc.es/becapremio-convocado/ayudas-para-tesis-doctoral-a-profesionales-jovenes-menores-de-40-anos-2026/</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Tier 1, Fundacion Jose Luis Castano-SEQC. El WebFetch da 503 en este host: usar curl primero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>F-0045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Beca Post Residencia (Fundacion Jose Luis Castano-SEQC / SEMEDLAB)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Post-residency research fellowship</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Fundacion Jose Luis Castano-SEQC y SEMEDLAB</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Espana</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>de 6000 a 15000; 4 becas</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1 ano</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No aplica: se define por la obtencion del titulo de especialista en el ano natural de la convocatoria</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Dirigida a quienes obtienen el titulo de especialista de Laboratorio Clinico DURANTE EL ANO NATURAL DE LA CONVOCATORIA y se encuentran en desempleo o con contrato a tiempo parcial igual o inferior al 50%. Requisito de antiguedad como socia por verificar. Bases completas de la edicion 2026 no leidas en detalle.</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Su edicion es la de 2027, y encaja con una precision poco comun: obtiene el titulo de especialista el 22-05-2027, dentro del ano natural de esa convocatoria, y el periodo que cubriria (mayo de 2027 a mayo de 2028) es exactamente su hueco entre el fin de la residencia y la defensa prevista. Linea a liderar: genetica estadistica aplicada al laboratorio clinico. Lo que impide subirla de 3 son dos condiciones sin resolver: el requisito de desempleo o de contrato a tiempo parcial igual o inferior al 50%, que choca de frente con el plan de encadenar un contrato de investigacion, y que no se han leido las bases completas. Es una fila de vigilancia con reloj concreto, no una recomendacion todavia.</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>4 becas en un colectivo cerrado de recien especialistas de laboratorio clinico socias de SEMEDLAB</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Capturar las bases de la edicion 2027 en el primer trimestre de 2027 y resolver el requisito de desempleo o parcialidad, que es el que decide si le sirve.</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>https://www.fundacionjlc.es/becapremio-convocado/beca-post-residencia-2026/</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Tier 1 para la existencia y las cifras (indice de la Fundacion JLC); bases completas no leidas. Fila de frontera entre becas y empleo: se queda en fellowships porque es dinero que ella solicita para si.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>F-0046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ayuda para la Investigacion y el Intercambio de Conocimiento (SES)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Short-stay / lab visit grant</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Sueno (SES)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Socias de la SES; estancia en unidad de sueno, preferentemente en Espana</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SI, implicito: unidad de sueno receptora</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>1500 (1 ayuda)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2 meses</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No aplica: no consta limite de edad ni exigencia de doctorado</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Ser socia de la SES; estancia en una unidad de sueno para iniciar un proyecto de investigacion o perfeccionar tecnicas concretas en Medicina del Sueno; antiguedad de membresia requerida NO VERIFICADA; elegibilidad predoctoral no explicitada pero tampoco excluida. Edicion 2026 cerrada el 25-01-2026. OJO: el tablon de la SES la sigue rotulando como 'CONVOCATORIA ABIERTA' con el plazo vencido.</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Toca su tercera linea (genetica del sueno en lactantes y ninos pequenos) y es de las poquisimas ayudas de estancia corta espanolas del ambito del sueno que no exige doctorado. Lo que hay que resolver antes de puntuarla mas alto: la ayuda esta orientada a perfeccionar tecnicas de Medicina del Sueno en una unidad clinica, mientras que lo que ella aporta y necesita es genetica estadistica; solo tiene sentido si la estancia se plantea en una unidad de sueno pediatrica con cohorte fenotipada, donde su valor anadido sea el analisis genetico de datos que la unidad ya tiene. Es dinero pequeno (1500 EUR) y una sola plaza. NOTA DE COORDINACION: esto NO es F-0026 (las ayudas de la ESRS, sociedad europea); es la sociedad espanola.</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Una sola ayuda pero colectivo elegible pequeno (socias de la SES) y cuantia baja, que disuade</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Revisar ses.org.es en diciembre de 2026 para la edicion 2027; escribir a secretaria.tecnica@ses.org.es para confirmar si admite predoctorales y que antiguedad de socia exige.</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>https://ses.org.es/profesionales/becas-y-premios/</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Tier 1, ses.org.es. Pagina concreta: https://ses.org.es/blog-post/becas-2022-2-3-2-2/ y bases en https://ses.org.es/wp-content/uploads/2025/11/bases_-beca-estancia-en-unidad-de-sueno-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>F-0047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ayudas EIDUM-CMN para estancias de movilidad de doctorandas (Universidad de Murcia)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Short-stay mobility grant (universidad propia)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Escuela Internacional de Doctorado de la Universidad de Murcia (EIDUM) / CMN</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Doctorandas matriculadas en la Universidad de Murcia; estancias nacionales o extranjeras</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SI, implicito: institucion receptora</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Estancias comprendidas entre el 1 de septiembre y el 30 de agosto del ano siguiente</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No aplica: exclusivo de doctorandas</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Estar matriculada en un programa de doctorado de la UM; finalidad orientada a obtener la Mencion Internacional o a desarrollar la tesis en cotutela. La convocatoria se publica anualmente entre enero y febrero; la de 2026 (R-190_2026) ya esta resuelta.</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Cubre el hueco de las estancias breves para doctorandas por la via mas barata de todas: su propia universidad, sin competencia externa y sin exigencia de publicaciones. El encaje de calendario es bueno: la convocatoria de enero-febrero de 2027 cubre estancias de septiembre de 2027 a agosto de 2028, otra vez el hueco entre el fin del MIR y la defensa. Condicion a resolver: la ayuda esta orientada a la Mencion Internacional, que exige un minimo de 3 meses en el extranjero y planificarse antes del deposito de la tesis; si quiere la Mencion, la decision hay que tomarla en 2026, no en 2027. Cuantia sin verificar, asi que puede ser simbolica; en principio combinable con la beca de intercambio de SEMEDLAB si las fechas no se solapan.</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Convocatoria interna de una sola universidad, restringida a sus propias doctorandas</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Preguntar en EIDUM por la convocatoria de 2027 y por los requisitos de Mencion Internacional; decidir en otono de 2026 si va a por la Mencion, porque condiciona el calendario de deposito.</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>https://www.um.es/web/eidum/informacion-academica/guia/becas-y-empleabilidad/becas-movilidad</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Tier 1, um.es. La pagina confirma nombre, finalidad y cadencia anual, pero no importe ni plazo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>F-0048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Becas de Investigacion SES (incluye beca especial para investigadores jovenes)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Research project grant (sociedad cientifica nacional)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Sueno (SES)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Espana; IP con nacionalidad UE o extracomunitaria con residencia en Espana</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ninguno obligatorio; se valora trabajar en centro de sueno acreditado por CEAMS-FESMES</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>hasta 10000 por beca; dotacion total 20000 + 10000 adicionales para la beca de investigadores jovenes</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1 a 3 anos</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Ninguna: no se exige doctorado. Unico limite temporal: menos de 35 anos para la modalidad de investigadores jovenes</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>IP 'miembro de la SES desde al menos un ano antes a la convocatoria' (VERIFICADO en las bases, texto literal); 70% o mas del equipo socios de la SES; equipo multidisciplinar; 'en el caso de tratarse de un medico residente, debera estar realizando el ultimo ano de la especialidad'; no haber sido premiada como IP en los dos anos anteriores; no se conceden dos becas a personas del mismo grupo u hospital; memoria de 4000 palabras o menos sobre fisiologia o patologia del sueno; pago 75% al inicio y 25% al final. Edicion 2026 CERRADA el 25-01-2026, pese a que el tablon la rotula 'CONVOCATORIA ABIERTA'.</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Encaje tematico y de etapa casi exacto, y es de las poquisimas convocatorias que contemplan explicitamente a un medico residente en el equipo. La linea a liderar es la genetica del sueno en lactantes y ninos pequenos, que cae de lleno en 'fisiologia o patologia del sueno' y es su linea con manuscrito de primera autora en revision (Journal of Sleep Research); se puede defender sin tocar nada de lo supervisado. Relojes: no hay ventana post-doctorado, asi que su defensa de febrero de 2028 es irrelevante aqui; edad previsiblemente menor de 35, lo que la mete en la modalidad joven (LIKELY, sin confirmar); nacionalidad UE con residencia en Espana, cumplida; ninguna regla de movilidad. EL RELOJ QUE SI MANDA ES OTRO: la antiguedad como socia. No consta que lo sea, y las bases exigen un ano antes de la convocatoria; si se da de alta en septiembre de 2026 llega tarde a la edicion 2027 (apertura hacia noviembre de 2026) y entra justo para la de 2028. Se pierde ademas una coincidencia afortunada: la clausula del residente en ultimo ano la cumpliria exactamente en la convocatoria de enero de 2027, porque su ultimo ano de MIR va del 22-05-2026 al 22-05-2027. Solicitud: memoria de 4000 palabras, CV, presupuesto y formulario; no exige carta de anfitrion ni centro comprometido, se presenta desde su propio hospital, asi que no hay que negociar con nadie de antemano. Trabajo real: 3-7 dias concentrados.</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Dotacion de 30000 EUR con maximo de 10000 por beca implica del orden de 3 concesiones anuales, repartidas entre los socios de una sociedad nacional pequena. La SES no publica tasa de exito: base inferida, no dato.</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>1) Darse de alta como socia de la SES YA, en septiembre de 2026 (SUB-0008): es el unico paso que abre la puerta y cada semana de retraso corre contra el ano de antiguedad. 2) Escribir a secretaria.tecnica@ses.org.es para resolver dos ambiguedades: si el ano de antiguedad se cuenta hasta la apertura o hasta el cierre, y si la clausula del medico residente en ultimo ano se aplica a la IP o solo a los colaboradores. 3) Volver al tablon en noviembre de 2026 para la edicion 2027.</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>https://ses.org.es/wp-content/uploads/2025/11/bases_becas_investigacion_2026-1.pdf</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>PDF Tier 1 descargado con curl y extraido con pypdf, no por resumen automatico. Texto literal del plazo: 'El plazo de solicitud: Desde la apertura de la convocatoria hasta al 25 de enero de 2026'. CONTRADICE al tablon https://ses.org.es/becas-y-premios/, que a 2026-08-31 la sigue rotulando 'CONVOCATORIA ABIERTA'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>F-0049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ayudas a Proyectos de Investigacion en Psiquiatria, Psicologia y Neurociencias Infanto-Juveniles o Neuropediatria (Fundacion Alicia Koplowitz, XXI convocatoria)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Research project grant (fundacion privada)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Fundacion Alicia Koplowitz</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Espana</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SI: Instituto de Investigacion Sanitaria (IIS) o centro de investigacion espanol acreditado, receptor unico de la ayuda; la IP debe estar vinculada a esa entidad los dos anos</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>hasta 50000 por ayuda; TRES ayudas</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2 anos</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Ninguna: las bases no exigen doctorado ni fijan ventana post-doctoral ni edad</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>IP unico y ESPANOL; 'El investigador Principal no podra estar cursando la residencia MIR ni PIR'; una sola solicitud por investigador, tambien como colaborador; prohibida la financiacion simultanea de otras fuentes para el mismo proyecto; memoria cientifica en castellano de 5 folios o menos; CV de la IP y de tres colaboradores; acuerdo de colaboracion firmado; informe del CEIC; gastos de personal 40% o menos y NUNCA remuneracion de la IP; la ayuda no crea relacion contractual ni laboral. Edicion 2026 cerrada el 30-04-2026; fallo en octubre de 2026; inicio de la ayuda 01-11-2026.</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>El encaje tematico es de los mejores de toda la base: 'Neurociencias Infanto-Juveniles' describe literalmente su tercera linea (genetica del sueno en lactantes y ninos pequenos), y la segunda (GWAS/PRS de trastornos psiquiatricos) entra por la puerta de la psiquiatria infanto-juvenil si acota el fenotipo a poblacion infantil. No exige doctorado, no hay ventana de anos, no hay reglas de movilidad: los relojes no la penalizan. Lo que la bloquea es una condicion dura y otra estructural. DURA: la clausula MIR/PIR la deja inelegible como IP en la convocatoria de 2027 (cierre hacia abril de 2027, con el MIR vivo hasta el 22-05-2027); la primera edicion para la que puede firmar como IP es la de 2028, ya post-MIR y post-defensa. ESTRUCTURAL: exige vinculacion con un IIS acreditado durante los dos anos y no paga su salario, asi que no resuelve su financiacion personal; es dinero de proyecto, no un postdoc. Si es accionable ya de otra forma: nada en las bases excluye a una residente como COLABORADORA, asi que puede entrar en la solicitud de 2027 de un grupo espanol y llegar a 2028 con el aval del centro y el CV construido. La solicitud es pesada y el CEIC es el cuello de botella: hay que arrancarlo con meses de antelacion.</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Texto de las bases: 'convoca TRES (3) Ayudas a la Investigacion' para toda Espana y para tres areas tematicas a la vez; es la fundacion de referencia del campo en el pais y lleva 21 convocatorias</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>No accionable como IP hasta 2028. Accion de este curso: buscar vinculacion con un IIS acreditado (IBIMA en Malaga es el natural desde su hospital) y ofrecerse como colaboradora en un equipo que presente a la convocatoria de 2027.</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>https://fundacionaliciakoplowitz.org/lineas-de-accion/ayudas-investigacion/</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>PDF Tier 1 de bases (6 paginas) descargado con curl y extraido con pypdf; requisitos citados literalmente. Bases: https://fundacionaliciakoplowitz.org/wp-content/uploads/2026/01/Bases_Ayudas-Proyectos_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>F-0050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Research Stay Grant for Interdisciplinary Training in Neuroscience (CINET)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Postdoctoral mobility fellowship (fundacion privada)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Fundacion Tatiana Perez de Guzman el Bueno - Centro Internacional de Neurociencia y Etica (CINET)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Cualquier nacionalidad y cualquier edad. Residentes en Espana salen a un centro extranjero; quien lleve 2 o mas anos fuera puede venir a un centro espanol</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SI: admision o compromiso de admision del centro de acogida para el periodo solicitado</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ANNOUNCED</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>40000 brutos anuales + 4000 de instalacion + hasta 1200 de viaje + seguro medico y de accidentes</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>12 meses</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Ninguna declarada: exige el titulo de doctora, sin ventana de anos (pendiente de confirmar en bases)</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Doctorado; residencia en Espana en el momento de solicitar para la modalidad de salida; admision del centro extranjero; la estancia debe ser de formacion INTERDISCIPLINAR en neurociencia y areas afines (biologia humana, bioetica, psicologia, filosofia, fisica, historia). Criterios de valoracion conocidos: aportacion a la formacion interdisciplinar 30% y prestigio internacional del centro receptor 20%. Ultima edicion documentada: 2025. Calendario de la edicion 2026/2027 SIN CONFIRMAR: web bloqueada.</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Es lo mas parecido a un postdoc de movilidad que ha aparecido fuera de los buques insignia: 12 meses con 40000 EUR brutos mas instalacion y viaje, sin ventana de anos post-doctorado, sin limite de edad y sin restriccion de nacionalidad, un perfil de requisitos rarisimamente permisivo que evita los tres filtros que suelen dejarla fuera. Linea a liderar: genetica estadistica de rasgos psiquiatricos (GWAS/PRS), su unica tecnica de nivel independiente. El envoltorio interdisciplinar no hay que fabricarlo: su doctorado esta inscrito en un programa de Psicologia (Anatomia Humana y Psicobiologia) y su titulo es de Medicina, asi que la combinacion medicina-psicologia-genetica estadistica es literalmente el cruce que CINET puntua; no necesita apoyarse en electrofisiologia ni neuroimagen, que son las supervisadas. Relojes: el unico requisito temporal es tener el doctorado, lo que la situa en la edicion de 2028; como se sale desde Espana hacia fuera, su residencia continua en Malaga desde 2023 juega a favor y las dos estancias de ~3 meses no la afectan. Si exige anfitrion comprometido antes de solicitar, con carta de admision: son de 3 a 6 meses de conversacion, asi que el contacto con el grupo receptor (QIMR Berghofer, donde ya estuvo, o un grupo europeo de genetica psiquiatrica) debe abrirse a lo largo de 2027, no en el mes de la solicitud. Se queda en 4 y no en 5 porque no se han podido leer las bases: importes y condiciones son LIKELY y el calendario esta sin verificar.</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Ni el numero de becas concedidas ni la tasa de exito aparecen en las fuentes accesibles</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Reintentar cinetcenter.com en la pasada de octubre por otra via; si sigue bloqueado, escribir a CINET pidiendo bases y calendario de la edicion 2027, y buscar el PDF republicado por webs universitarias (medicina.us.es adjunta el suyo).</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>https://www.cinetcenter.com/convocatoria/research-stay-grant-for-interdisciplinary-training-in-neuroscience-2/</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Dos fuentes Tier 2 independientes que concuerdan: anuncio de la Facultad de Medicina de la Universidad de Sevilla (edicion 2025) y ficha de becas.com. BASES TIER 1 NO LEIDAS: fundaciontatiana.com y cinetcenter.com devuelven contenido vacio al fetch y HTTP 202 con 273 bytes a curl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>F-0051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SRSF Small Research Grant</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Small research grant (fundacion de sociedad cientifica)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sleep Research Society Foundation (SRSF)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Sin restriccion geografica declarada; exige afiliacion institucional en el momento de solicitar</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Afiliacion institucional (no anfitrion concreto)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>aprox. 4300 (5000 USD; el financiador fija la cifra en dolares, la conversion es orientativa)</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>12 meses</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Hasta 10 anos desde el titulo terminal (PhD, MD, DO) y nivel de Assistant Professor o inferior; se admiten excepciones documentadas por formacion clinica, permisos parentales o cuidado de dependientes</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Ser miembro en regla de la Sleep Research Society, de la AASM o con membresia dual EN EL MOMENTO DE PRESENTAR; estar matriculada en un programa de grado o posgrado, o dentro de la ventana de 10 anos; afiliacion institucional. Ciclo 2026 cerrado el 31-08-2026 a las 23:59 CT; notificacion 30-11-2026; periodo de financiacion enero-diciembre de 2027.</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Elegible reloj por reloj: su MD de 2019 arranca la ventana de 10 anos, que llega hasta 2029, y la excepcion explicita por formacion clinica cubre el MIR aunque hiciera falta; no hay requisito de nacionalidad ni de institucion estadounidense declarado, y no exige doctorado. La linea a presentar seria sueno infantil, donde tiene manuscrito propio. Se queda en 3 por dos razones honestas: el importe (5000 USD) es dinero semilla, no financiacion de carrera ni salario, y hay una condicion sin resolver, que no consta que sea socia de la SRS ni de la AASM y la membresia se exige ya al solicitar, no despues. El objetivo real es la edicion de 2027.</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>La SRSF no publica numero de ayudas concedidas ni tasa de exito</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Valorar el coste de la cuota de socia de la SRS antes de junio de 2027 (ver SUB-0007) y preparar la solicitud para el cierre previsto hacia el 31-08-2027.</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>https://sleepresearchsociety.org/foundation/small-research-grant/</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Tier 1, sleepresearchsociety.org.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>F-0052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Contratacion laboral de personal investigador doctor (Linea 2, EIDIA Horizonte 2027) - contratos postdoctorales Junta de Andalucia</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Regional postdoctoral contract (early postdoc)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Consejeria de Universidad, Investigacion e Innovacion - Junta de Andalucia</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Andalucia. Sin restriccion de nacionalidad ni de residencia previa detectada en el extracto</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SI: grupo de investigacion de un agente del Sistema Andaluz del Conocimiento. Solicita la ENTIDAD; la candidata cumplimenta los Anexos I y I-BIS en la Oficina Virtual y los envia al representante legal</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>9011925 para 65 ayudas, aprox. 138645 por contrato (~46000/ano). El importe por contrato es DERIVADO por division, no leido</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hasta 3 anos</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>'Perfeccionar las capacidades adquiridas durante una primera etapa de formacion postdoctoral'. La ventana exacta de anos esta en la Orden de bases de 24-10-2023, NO abierta. UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Grado de doctor acreditado con titulo o certificacion academica con indicacion expresa de la fecha de obtencion (misma puerta que Sara Borrell). NO se detecto requisito de movilidad internacional, a diferencia de Beatriu de Pinos y de Madrid. Requiere aceptacion del Consejo de Departamento o grupo receptor. Edicion 2026: del 05-01-2026 al 28-01-2026 18:00 (ampliado por incidencias tecnicas, fecha final exacta no verificada); propuesta provisional de seleccionados el 09-07-2026.</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Es la unica via autonomica encontrada que NO tiene requisito de movilidad exterior, y por tanto la unica compatible con su historial de residencia continua en Espana desde 2023. Encaja con su etapa exacta ('primera etapa de formacion postdoctoral') y con su base geografica: hace el MIR en el Hospital Regional Universitario de Malaga, asi que UMA e IBIMA son centros de acogida naturales con los que ya tiene proximidad fisica e institucional. Linea a liderar: genetica estadistica y GWAS-PRS de trastornos psiquiatricos, que es su tecnica independiente y no depende de infraestructura humeda. RELOJES: exige doctorado YA obtenido, con certificacion de fecha admitida. La edicion que abre en enero de 2027 le queda fuera. La edicion de enero de 2028 cae SEMANAS ANTES de su defensa prevista (febrero de 2028): con el patron 05-28 de enero, la pierde por muy poco. La primera edicion realmente suya es la de enero de 2029, salvo que adelante la defensa a diciembre de 2027. ES UN CASO DONDE LA INCERTIDUMBRE DE UNOS MESES EN LA FECHA DE DEFENSA DECIDE LA ELEGIBILIDAD, y merece tenerlo en cuenta al negociar el calendario de deposito. Trabajo real: memoria de linea investigadora, CV y aval del grupo; esfuerzo moderado, pero la solicitud la firma la universidad, lo que impone un plazo interno adelantado (en la UMA fue el 30-01 y en la UPO el 23-01). Anfitrion: si, hace falta grupo receptor comprometido con acuerdo de Consejo de Departamento, cerrado en diciembre, un mes antes.</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>65 contratos para toda Andalucia y todas las areas; convocatoria regional, no estatal, lo que reduce mucho el volumen de competidores frente a Juan de la Cierva</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>VERIFIED para fechas, numero de ayudas, importe global y duracion (extracto en BOJA num. 246 de 23/12/2025 y ficha de la UMA). UNVERIFIED para la ventana de anos post-doctorado y para la fecha final de la ampliacion</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>En noviembre de 2026, abrir la Orden de bases de 24-10-2023 en BOJA y extraer el articulo de requisitos de la candidata (ventana de anos desde el doctorado y posible antiguedad maxima). Es el dato que convierte esta fila en un Fit 4 firme o la degrada.</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>https://www.juntadeandalucia.es/boja/2025/246/10</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Extracto Tier 1 en BOJA leido directamente. Confirmado por dos espejos universitarios independientes (UMA y UPO). OJO: los plazos de UMA (30-01) y UPO (23-01) son INTERNOS del centro; el del financiador es el 28-01-2026 a las 18:00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>F-0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Programa Saavedra Fajardo - contratos posdoctorales de atraccion (Region de Murcia)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Regional postdoctoral contract</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Fundacion Seneca - Agencia de Ciencia y Tecnologia de la Region de Murcia</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Region de Murcia como destino</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SI: universidades y centros publicos de investigacion de la Region de Murcia (UMU, UPCT, CEBAS-CSIC, IMIB-Arrixaca)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>UNVERIFIED. Referencia: mas de 1 M EUR asignados al programa en la edicion 2023-2024</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>5 anos, segun nota de prensa institucional de la edicion 2024</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>'Jovenes doctores en una etapa de formacion postdoctoral temprana'; ventana exacta UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Doctorado obtenido; incorporacion a un grupo de un agente del sistema murciano. Es un programa de ATRACCION de talento internacional, por lo que muy probablemente lleva requisito de movilidad: NO VERIFICADO y decisivo para ella. PROGRAMA APARENTEMENTE LATENTE: la ultima apertura documentada es del 23-10-2023 y el catalogo 'Talento Investigador y su Empleabilidad (2026)' de la Fundacion Seneca NO lo incluye.</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Es plausible por una razon concreta: hace la tesis en el Programa de Doctorado en Psicologia de la Universidad de Murcia, asi que tiene grupo receptor natural y director que la conoce, y el IMIB-Arrixaca aparece entre los centros de acogida historicos. Su linea de genetica estadistica de rasgos complejos y de sueno en lactantes tiene ademas anclaje real en Murcia (el grupo de cronobiologia de la UMU figura entre los beneficiarios historicos, con un contrato sobre cronodisrupcion). Pero hay dos condiciones sin resolver que impiden subirla de 3: el programa lleva dos anos sin convocarse y puede estar descatalogado, y siendo de 'atraccion' es probable que exija haber estado fuera de la Region o del pais, requisito que su residencia continua en Malaga no cumple. Relojes: exigiria doctorado obtenido, luego no antes de 2028. Trabajo real: memoria mas aval del grupo, esfuerzo medio. Anfitrion: imprescindible, pero es el que menos le costaria conseguir de todo el radar, porque ya esta dentro de la casa.</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>6 contratos en la edicion 2024 y 39 beneficiarios historicos acumulados, dentro de una unica comunidad autonoma pequena</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>LIKELY para el estado latente (catalogo oficial 2026 leido y el programa no figura). UNVERIFIED para requisitos, importe y duracion: la propia pagina del programa esta publicada con texto Lorem ipsum de relleno</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Preguntar directamente a la Fundacion Seneca (seneca@fseneca.es) si Saavedra Fajardo tendra edicion en 2027 y cuales son los requisitos de movilidad. Es un correo y desbloquea una convocatoria de competencia LOW con anfitrion natural: la mejor relacion coste/informacion de la rama.</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>https://www.fseneca.es/web/talento/sf</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Pagina del programa vacia (Lorem ipsum) salvo el listado de 39 beneficiarios historicos. Catalogo 2026 verificado en https://fseneca.es/web/convocatorias. fseneca.es da 503 a WebFetch pero 200 a curl con User-Agent de navegador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>F-0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>III Convocatoria de Becas Fulbright-Fundacion Seneca de investigacion posdoctoral en los Estados Unidos</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Regional-bilateral postdoctoral research fellowship (Espana - EE. UU.)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Fundacion Seneca (Region de Murcia) y Comision Fulbright Espana</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Personal docente o investigador vinculado a universidades y organismos de investigacion de la Region de Murcia; destino EE. UU.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SI: universidad o centro de investigacion estadounidense. CARTA DE INVITACION PREVIA IMPRESCINDIBLE para poder solicitar</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ANNOUNCED</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3200 al mes para alojamiento y manutencion + ayuda de desplazamiento</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>minimo 9 y maximo 12 meses continuados, sin renovacion ni extension</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>'Jovenes doctores'; sin ventana numerica verificada</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Doctorado obtenido; vinculacion con universidad u organismo de investigacion de la Region de Murcia; carta de invitacion de la institucion estadounidense. VENTAJA CLAVE: al ir por el canal Fulbright, el visado J-1 lo gestiona el programa, lo que resuelve exactamente la barrera que hace que la NIH F32 (F-0015) sea Fit 1 para ella. Figura en el catalogo 2026 de la Fundacion Seneca pero a 2026-08-31 no hay convocatorias abiertas: agosto es mes inhabil. En la I convocatoria la apertura fue 'a partir del 3 de septiembre'.</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Es la unica via a EE. UU. encontrada que NO tropieza con la ciudadania: Fulbright patrocina el visado, mientras que la NRSA F32 exige ciudadania o residencia permanente. Para sus lineas 1 y 2 EE. UU. concentra los consorcios de referencia, y 9-12 meses de trabajo computacional en un grupo del PGC serian un salto real de CV para alguien sin publicaciones destacadas todavia. Lo que hay que reencuadrar, y por eso no sube de 3: su vinculacion con Murcia es de doctoranda y al terminar la tesis en 2028 puede haber caducado, asi que hay que confirmar si vale la afiliacion al programa de doctorado o exige contrato vigente; 9-12 meses no es un postdoc completo sino una estancia larga, de modo que compite con la opcion de un contrato Sara Borrell (F-0002), que si es carrera; y exige doctorado, luego no antes de 2028. Trabajo real: solicitud Fulbright estandar, moderada, pero la carta de invitacion previa es requisito de admision, no un adorno, y conseguirla en un grupo estadounidense de primer nivel lleva tipicamente de 3 a 6 meses de correspondencia: habria que empezar a escribir a PIs a mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Convocatoria restringida a una sola comunidad autonoma y a un punado de plazas; ediciones anteriores del programa Region de Murcia-Fulbright se movieron en el orden de 3 a 5 becas</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Revisar https://fseneca.es/web/convocatorias en la primera semana de septiembre de 2026, cuando termine el mes inhabil, y capturar las bases de la III convocatoria: ventana de anos post-doctorado y definicion exacta de 'vinculacion con la Region de Murcia'.</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>https://fseneca.es/web/convocatorias</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Tier 1 para la existencia de la convocatoria en el catalogo 2026. Importe, duracion y requisito de carta de invitacion proceden de notas institucionales sobre ediciones anteriores, no de las bases de la III.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>F-0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ikerbasque Research Fellows 2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Regional tenure-track fellowship</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Ikerbasque - Basque Foundation for Science</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Pais Vasco como destino; cualquier nacionalidad</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>SI: institucion de investigacion vasca (universidades, BERC, IIS); se exige carta de acogida</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>46195 al ano brutos + hasta 4000 de mudanza internacional + 10000 de start-up</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>5 anos (tenure track hacia PI)</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Doctorado entre 2015-01-01 y 2023-12-31, es decir entre ~3 y ~11 anos post-doctorado</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>INELEGIBLE HOY: exige doctorado ya obtenido dentro de la ventana y experiencia internacional acreditada. Con doctorado en febrero de 2028, la primera edicion cuya ventana la incluiria seria aproximadamente la de 2031.</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Es un tenure track de 5 anos dirigido a postdocs ya consolidados, muy por encima de su etapa; se registra como objetivo de medio plazo y para no redescubrirlo.</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>15 plazas para todas las areas, evaluadas por mas de 100 evaluadores externos de 20 paises</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Revisar de nuevo en 2029-2030, no antes.</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>https://www.ikerbasque.net/en/calls/research-fellows-2026-1</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Tier 2. El PDF de especificaciones (https://calls.ikerbasque.net/images/stories/2026_ikerbasque_rf_call_specs.pdf) es el Tier 1 pendiente de extraer localmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>F-0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ayudas de Atraccion de Talento Investigador Cesar Nombela 2026 (Comunidad de Madrid)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Regional incoming-talent postdoctoral contract</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid - Direccion General de Investigacion e Innovacion</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid como destino; cualquier nacionalidad</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SI: universidades madrilenas, Fundaciones IMDEA, OPI, Fundaciones de Investigacion Biomedica y entidades sanitarias. Solicita la entidad</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>UNVERIFIED (no aparece en la ficha de sede)</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>5 anos</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Doctorado obtenido entre 2016-01-01 y 2023-12-31</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>INELEGIBLE por dos motivos acumulativos: la ventana de doctorado 2016-2023, y el requisito de 'haber tenido un vinculo profesional remunerado con entidades de investigacion extranjeras de al menos 2 anos en los ultimos 5'. Sus dos estancias de ~3 meses suman ~6 meses. Edicion 2026 cerrada el 09-07-2026 (Orden 2355/2026 de 11 de junio).</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Requiere 2 anos de vinculo remunerado con entidades extranjeras en los ultimos 5, requisito que su trayectoria clinica en Espana hace estructuralmente inalcanzable a corto plazo.</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Programa insignia de la Comunidad de Madrid con contratos de 5 anos y todas las areas compitiendo</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>VERIFIED para plazo, ventana de doctorado, requisito de 2 anos en el extranjero y duracion; UNVERIFIED para importe</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Ninguna a corto plazo. Sirve de referencia de lo que exigen las convocatorias autonomicas de atraccion: el umbral es 2 anos fuera.</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>https://sede.comunidad.madrid/ayudas-becas-subvenciones/ayudas-atraccion-talento-investigador-2</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Tier 1, sede electronica de la Comunidad de Madrid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>F-0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ajuts postdoctorals Beatriu de Pinos (BP 2025)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Regional incoming-mobility postdoctoral fellowship</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AGAUR - Generalitat de Catalunya</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Cataluna como destino; candidata de cualquier nacionalidad pero procedente del extranjero</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SI: universidad o centro de investigacion catalan, que confirma la solicitud provisional</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>149396 (salario) + 12000 (dotacion)</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>3 anos</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Doctorado obtenido entre 2018-01-01 y 2023-12-31, ampliable a 2016 por causas justificadas</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>INELEGIBLE por tres barreras independientes: minimo 2 anos de experiencia postdoctoral FUERA de Espana; regla de movilidad de no haber residido ni trabajado en Espana mas de 12 meses en los 3 anos anteriores; y su doctorado sera de 2028, fuera de la ventana. Edicion cerrada el 04-02-2026.</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Programa de atraccion de talento desde el extranjero: su residencia continuada en Espana la excluye por la regla de movilidad y su fecha de doctorado queda fuera de la ventana.</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Programa emblematico de Cataluna, historicamente cofinanciado por MSCA-COFUND</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Ninguna. Solo reevaluar si algun dia acumulara 2 o mas anos de postdoc fuera de Espana.</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>https://agaur.gencat.cat/en/beques-i-ajuts/convocatories-per-temes/Ajuts-postdoctorals-Beatriu-de-Pinos-BP-2025</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Tier 2. Registrada para no redescubrirla y para dejar escrita la razon de la inelegibilidad, que es estructural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>F-0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BGA Early Career Award (antes Fuller and Scott Award)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Career prize</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Behavior Genetics Association</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Global (requiere ser miembro de la BGA en regla)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Premio puntual, se entrega en la reunion anual</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Dentro de 7 anos desde el 'terminal degree' (Ph.D., M.D.). LA DEFINICION ES AMBIGUA Y CRITICA PARA ELLA</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Miembro de la BGA en regla; dentro de 7 anos del titulo terminal; se otorga por nominacion (carta breve y CV a behaviorgeneticsassociation@gmail.com). Para el ciclo 2026 el plazo fue el 01-03-2026 (Tier 2). AMBIGUEDAD GRAVE: la BGA enumera 'Ph.D., M.D.' como titulos terminales; si su MD de 2019 cuenta, su reloj expiro en 2026; si cuenta el PhD de febrero de 2028, tendria hasta 2035.</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Es un premio a contribuciones ya destacadas y ella no tiene aun publicaciones, asi que se registra solo para no redescubrirlo y para dejar anotada la ambiguedad del reloj MD/PhD.</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Premio unico anual de una sociedad internacional; los galardonados historicos son profesores consolidados</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Un correo a behaviorgeneticsassociation@gmail.com preguntando si el reloj de 7 anos se cuenta desde el MD o desde el PhD. Es barato y aclara ademas su elegibilidad para F-0028.</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567677</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Pagina Tier 1 de premios de la BGA (confirma el renombrado y la lista de premios, pero NO publica plazos ni importes). La regla de los 7 anos y el plazo del 01-03-2026 vienen de resumen de busqueda Tier 2 sin confirmar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>F-0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>IBRO Rising Stars Awards</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Start-up / laboratory establishment award</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>International Brain Research Organization (IBRO)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Global (por confirmar)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Investigadora principal estableciendo laboratorio propio</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Descrito por IBRO como apoyo sustancial 'for early career investigators setting up new laboratories': etapa de PI independiente, no postdoctoral. No figura en el calendario de convocatorias vigente.</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Es una ayuda de arranque de laboratorio propio, varios escalones por encima de su etapa; se registra para no volver a mirarla.</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Sin datos publicados</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Ninguna. No reabrir salvo que consiga plaza de PI (horizonte posterior a 2032).</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>https://ibro.org/grant/rising-stars-awards/</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Aparece en el indice Tier 1 de programas de IBRO; no figura en el calendario de convocatorias 2026, asi que no se pudo confirmar ventana ni importe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>F-0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Tatiana Foundation Young Investigator Award (SENC)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Young researcher prize</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SENC / Fundacion Tatiana Perez de Guzman el Bueno</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Espana (socias de la SENC)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>3000 + conferencia plenaria en el congreso bienal + entrada al Comite de Jovenes Investigadores durante 2 anos</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Doctorado obtenido hace 8 anos o menos</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Requiere DOCTORADO OBTENIDO hace 8 anos o menos, socia activa de la SENC, haber trabajado en institucion espanola el ultimo ano, comunicacion al bienal y 2 cartas de recomendacion de socias. Edicion 2025 cerrada el 10-06-2025.</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>INELEGIBLE hoy porque exige el titulo de doctora, que no tendra hasta 2028; se registra para reevaluarlo en la edicion de 2029.</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Premio unico de la sociedad nacional de neurociencia con conferencia plenaria asociada</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Reevaluar en 2029, cuando lleve un ano largo de doctora.</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>https://www.senc.es/wp-content/uploads/2025/04/1_Tatiana-Foundation-Young-Investigator-Award_Call_2025.pdf</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Tier 1: PDF de la convocatoria 2025 extraido localmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>F-0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Premios de Innovacion Cientifica para Jovenes Investigadores (Fundacion Pfizer, XXVII edicion)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Young researcher prize</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Fundacion Pfizer</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Espana</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>15000 por categoria (basica y clinica)</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No aplica: hasta 40 anos</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Exige un trabajo YA PUBLICADO en revista cientifica. Estado y plazo de la edicion vigente UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Exige trabajo ya publicado y sus dos manuscritos siguen en revision, el mismo corte que la deja fuera del Premio Federico Oloriz.</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Premio nacional de referencia con una sola plaza por categoria</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Verificar la pagina oficial en fundacionpfizer.org cuando alguno de sus manuscritos se publique; antes no merece presupuesto.</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>https://www.fundacionpfizer.org/</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Solo Tier 2: no se abrio pagina oficial. La URL es la raiz del sitio, no la de la convocatoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>F-0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Premios Extraordinarios de Doctorado (Universidad de Murcia)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Thesis prize</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Universidad de Murcia</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Universidad de Murcia</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No aplica: se resuelve por bloques de cursos tras la defensa</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Exige tesis ya defendida con sobresaliente cum laude y propuesta por unanimidad del tribunal; la convocatoria cubre las tesis leidas en los dos cursos anteriores. La ultima cerro el 24-10-2025.</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Solo accesible tras la defensa: con defensa en febrero de 2028 la convocatoria que le corresponde caeria hacia el otono de 2029, y depende de algo que se decide el dia del tribunal, no en una solicitud.</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Numero limitado de premios por rama de conocimiento entre todas las tesis de dos cursos</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Nada hasta 2029. Lo unico accionable es que el tribunal proponga el cum laude por unanimidad el dia de la defensa.</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>https://www.um.es/web/eidum/tramitacion-tesis/pex</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Tier 1, um.es.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB37"/>
+  <autoFilter ref="A1:AB63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22033,16 +26224,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
@@ -22160,7 +26351,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -22170,7 +26361,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Estimacion, no dato: HFSP no ha publicado nada del AY2028. CUIDADO AL VERIFICAR: las fechas que publica hfsp.org para los Research Grants son otras y no valen para las becas posdoctorales. Lo verificado esta pasada es que el doctorado NO se exige al solicitar (ver F-0007).</t>
+          <t>Sin cambios: el calendario AY2028 sigue sin publicarse y la pagina de HFSP anuncia todavia el AY2027. Se mantiene la expectativa de publicacion entre enero y marzo de 2027, con LOI hacia mayo de 2027. MATIZ NUEVO Y RELEVANTE (ver F-0007): el preprint solo satisface el requisito de publicacion en fase LOI; en la propuesta completa de septiembre hace falta aceptacion.</t>
         </is>
       </c>
     </row>
@@ -22207,7 +26398,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>LIKELY para las fechas; el REQUISITO pasa a VERIFIED</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -22222,7 +26413,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -22232,7 +26423,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Verificado esta pasada que a 24-08-2026 NO hay nada de la AES 2027 (ni BOE ni ISCIII). El disparador exacto es el extracto en el BOE de la segunda quincena de diciembre (serie BOE-B-2023-38433 / BOE-B-2024-45526 / BOE-B-2025-47164). Espejo que rodea el 503 de isciii.es: https://www.iisaragon.es/wp-content/uploads/2025/12/AES_2026.pdf</t>
+          <t>HALLAZGO DE LA PASADA. Requisito verificado textualmente en el PDF oficial de la AES 2026 (art. 34.2), extraido localmente: la FSE debe finalizar 'con anterioridad a la fecha que se establezca para la finalizacion del plazo de alegaciones a la resolucion provisional de concesion'. La convocatoria no fija esa fecha por adelantado. Precedentes Tier 1 de la sede del ISCIII: Rio Hortega AES 2025, alegaciones 'del 3 al 16 de octubre de 2025' (pub=51490, publicada el 02-10-2025); convocatoria 2022, 'del 19 al 30 de septiembre de 2022'; Sara Borrell y Miguel Servet AES 2025, 'del 11 al 24 de julio de 2025'. Rio Hortega va sistematicamente 2-3 meses mas tarde. Para la AES 2027 cabe esperar el cierre de alegaciones entre finales de septiembre y mediados de octubre de 2027, y el 22-05-2027 cae holgadamente dentro. CONSECUENCIA: LA AES 2027 ES SU PRIMERA EDICION POSIBLE Y SE PREPARA YA, no en 2028. Cabo suelto: no se localizo la resolucion provisional de Rio Hortega AES 2026; puede que aun no este publicada, lo que encajaria con el patron de octubre.</t>
         </is>
       </c>
     </row>
@@ -22284,7 +26475,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -22294,7 +26485,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ver F-0002. La ventana rodante de recencia del doctorado (la AES 2026 exigia defensa posterior al 1-1-2022) la mantiene elegible hasta aproximadamente la AES 2032. El grupo receptor debe ser distinto del de su tesis en Murcia y estar en otro centro. PUNTO DE DECISION: si la defensa se adelanta a diciembre de 2027 o enero de 2028, la AES 2028 pasa de moneda al aire a objetivo real.</t>
+          <t>Sin cambios en la estimacion de reapertura: la AES 2027 no esta publicada y nada indica desviacion de la ventana ~10 de febrero a 5 de marzo de 2027. Ancla Tier 1 nueva del calendario interno: resolucion provisional de la AES 2025 publicada el 10-07-2025 con alegaciones 'del 11 al 24 de julio de 2025, ambos inclusive' (sede del ISCIII, pub=51471). Confirmado que su primera edicion realista sigue siendo la AES 2029, porque exige doctorado y defiende en febrero de 2028.</t>
         </is>
       </c>
     </row>
@@ -22346,7 +26537,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -22356,7 +26547,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ver F-0003. La AES 2026 exigia tesis leida entre el 1-1-2014 y el 31-12-2021.</t>
+          <t>Sin cambios. Mismo ancla Tier 1: resolucion provisional de la AES 2025 del 10-07-2025, alegaciones 'del 11 al 24 de julio de 2025, ambos inclusive' (sede del ISCIII, pub=51470). Sigue fuera de su alcance por trayectoria: Miguel Servet exige varios anos posdoctorales.</t>
         </is>
       </c>
     </row>
@@ -22408,7 +26599,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -22418,7 +26609,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ELLA NO ES ELEGIBLE en ninguno de esos cortes (no tendra doctorado hasta feb-2028) y ademas Espana no vale como centro de acogida: solo Reino Unido y paises de renta baja/media, y desde el 29-10-2026 Irlanda tambien sale. wellcome.org da 403 dos pasadas seguidas: usar espejos de oficinas de investigacion britanicas, distinguiendo siempre si la fecha que publican es la del financiador o la interna del centro.</t>
+          <t>Sin cambios y el conflicto sigue vivo. Confirmado por Tier 2 el paso a presentacion continua desde el 25-08-2026 con preseleccion en febrero, junio y septiembre. La fecha 16-11-2026 aparece explicitamente como PLAZO INTERNO DE INSTITUCION en paginas de Oxford y en un PDF de convocatoria interna de UCT, lo que refuerza que el 10-11-2026 es el del financiador, pero no se ha podido leer en una pagina Tier 1: wellcome.org sigue dando 403 y no se reintento. La lectura mas probable es que ambas fechas son correctas en su ambito.</t>
         </is>
       </c>
     </row>
@@ -22512,12 +26703,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Apertura en febrero de 2027 y cierre el viernes 05-03-2027; 70.000 USD a dos anos.</t>
+          <t>Ventana estimada de febrero a marzo de 2027; BBRF NO HA PUBLICADO NINGUNA FECHA DE 2027. Se retira el 05-03-2027 de la pasada anterior: era una extrapolacion y ademas cae en viernes, cuando el patron de BBRF es cerrar en miercoles. Ciclo 2026 verificado: 04-02-2026 a 04-03-2026 23:59 ET.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>LIKELY para la ventana, UNVERIFIED para la fecha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22532,7 +26723,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -22542,7 +26733,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Fechas de 2027 surgidas de busqueda agregada, no de una pagina de la BBRF abierta directamente (sus PDF de bases son form-XObject y no se extraen en el rastreo). Reverificar en enero de 2027.</t>
+          <t>AVISO DE REPROGRAMACION PROBABLE: fuentes Tier 2 indican que los postdocs de primer ano son inelegibles y que se exige 'M.D. with minimum PGY-IV training' o doctorado mas un puesto de investigacion en marcha. Con defensa en febrero de 2028, su primer ano postdoctoral va de febrero de 2028 a febrero de 2029, asi que la primera convocatoria realista seria la de 2029 y no la de 2027. Verificar en las guidelines en PDF antes de seguir vigilando esta fila tres anos en balde.</t>
         </is>
       </c>
     </row>
@@ -22656,7 +26847,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -22666,7 +26857,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sin cambios: ispg.net sigue anunciando solo el WCPG 2026 (Glasgow, 29-09 a 03-10-2026); del congreso de 2027 no hay sede, ni fechas, ni portal de resumenes, ni pagina del ECIP.</t>
+          <t>Sin cambios: sede y fechas del WCPG 2027 SIGUEN SIN ANUNCIAR, verificado en dos paginas Tier 1 de ispg.net; la unica futura listada es el WCPG 2026 (Glasgow, 29 de septiembre a 3 de octubre de 2026) y no hay rastro de ECIP 2027. VENTANA DE VIGILANCIA CONCRETA: la sede del congreso siguiente suele anunciarse durante el congreso anterior, asi que la semana del 29 de septiembre de 2026 es el momento natural para que aparezca. El ECIP queda fichado ademas como fila propia en fellowships (Fit 5, la solicitud mas barata de la base).</t>
         </is>
       </c>
     </row>
@@ -22703,7 +26894,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED para la ventana de enero de 2027</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22718,7 +26909,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -22728,7 +26919,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sede y fechas del congreso VERIFICADAS; el calendario de premios sigue UNVERIFIED. Revisar https://www.sleepmeeting.org/call-for-abstracts/ hacia octubre de 2026 (esa pagina se sirve por JavaScript y llega vacia al rastreo: comprobarla a mano o via el boletin de la SRS).</t>
+          <t>Cita literal de la Sleep Research Society: 'The application period for SLEEP 2026 is closed. More information regarding the next cycle of the Trainee Awards can be expected in January of 2027.' Fuente Tier 1 nueva que sortea el bloqueo de sleepmeeting.org: https://sleepresearchsociety.org/awards/conference-awards/. Dato adicional util: el Leadership Development Workshop Award se convoca en anos IMPARES, es decir existe en SLEEP 2027 y no existio en 2026; el Grant Writing Workshop Award es de anos pares. AASM confirma la logistica de SLEEP 2027 (Denver, cursos 5-6 de junio, sesion general 6-9 de junio, registro en enero de 2027). SIGUE SIN CONFIRMAR la fecha de apertura del envio de resumenes: la hipotesis de principios de diciembre de 2026 es UNVERIFIED y sleepmeeting.org es el unico sitio que la publicaria.</t>
         </is>
       </c>
     </row>
@@ -22822,12 +27013,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>POSIBLEMENTE YA ABIERTA: el tablon de Becas y Premios de la SES lista como 'CONVOCATORIA ABIERTA' tres partidas de 2026, entre ellas las Becas de Investigacion SES y la Ayuda para la Investigacion y el Intercambio de Conocimiento. Si se confirma, la estimacion anterior (apertura en noviembre-diciembre de 2026) era erronea.</t>
+          <t>Apertura hacia noviembre-diciembre de 2026 y cierre hacia el 25-01-2027, por el patron de la edicion 2026.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22842,7 +27033,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -22852,7 +27043,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>SIN CONFIRMAR la regla de antiguedad de un ano como socia: no aparece en el texto de ninguna pagina leida, solo en un resumen de buscador. Lo que si esta leido: la edicion 2016/17 exigia proyectos 'liderados por socios de la SES' con al menos el 60% de participantes socios, y la de 2024 subia ese porcentaje al 70%. LA TAREA CONCRETA DE LA PROXIMA PASADA es descargar el PDF de bases desde https://ses.org.es/profesionales/becas-y-premios/ y cerrar dos cosas: el plazo real de la edicion 2026 y si existe antiguedad minima como socia.</t>
+          <t>CORRECCION IMPORTANTE: LA URGENCIA DE LA PASADA ANTERIOR ERA FALSA. Las bases en PDF, descargadas con curl y extraidas localmente, dicen literalmente 'El plazo de solicitud: Desde la apertura de la convocatoria hasta al 25 de enero de 2026'. La edicion 2026 esta CERRADA desde enero, pese a que el tablon de la SES la sigue rotulando 'CONVOCATORIA ABIERTA' a 31-08-2026. NO habia ningun reloj corriendo. El rotulo del tablon de la SES queda marcado como NO FIABLE para todas las pasadas futuras: el estado se saca del PDF, nunca de la etiqueta. RESUELTA TAMBIEN LA REGLA DE ANTIGUEDAD, que pasa de UNVERIFIED a VERIFIED: 'Ser miembro de la SES desde al menos un ano antes a la convocatoria de la beca'. La convocatoria pasa a tener fila propia en fellowships con Fit 4.</t>
         </is>
       </c>
     </row>
@@ -22904,7 +27095,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -22914,7 +27105,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BLOQUEADO: https://esrs.eu/grants-awards/ devolvio HTTP 403 al fetch automatico el 2026-08-23, confirmando el bloqueo que ya encontro la rutina de positions esta misma semana; intentado una vez y no reintentado. Todo aqui es UNVERIFIED y procede de fragmentos de busqueda: la seleccion la ordena el Comite Cientifico de la ESRS segun los objetivos de aprendizaje de la carta de motivacion, el CV y las publicaciones, teniendo en cuenta la antiguedad; plazo del 31-1-2026 en la ultima edicion. NO se pudo determinar si exige doctorado ni enumerar el resto de ayudas de la ESRS. Una sola visita manual con navegador a https://esrs.eu/grants-awards/ resolveria toda la cartera de la ESRS. La membresia es muy probablemente condicion previa, como en la SRS y la SES.</t>
+          <t>Sin cambios y sigue sin verificar. Via indirecta intentada sin reintentar esrs.eu (403 conocido): los snippets de buscador de la pagina oficial siguen mostrando el ciclo cerrado con plazo del 31 de enero de 2026, lo que es coherente con un plazo hacia el 31 de enero de 2027, pero es cache de Tier 1 leida de segunda mano, no una pagina abierta. Se mantiene LOW-MEDIUM y el dato queda UNVERIFIED por tercera pasada consecutiva.</t>
         </is>
       </c>
     </row>
@@ -22946,42 +27137,506 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>~marzo de 2027 (anual)</t>
+          <t>Convocatoria hacia febrero-abril de 2027 con cierre a finales de abril de 2027. CORRECCION: el ciclo 2026 cerro el 27-04-2026 a las 21:00 PT, no en marzo como estimaba la siembra.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>300000 dolares para investigacion de inicio de carrera en salud mental: la mayor cuantia individual de esta rama y tematicamente en el centro de su linea 2, con atencion especial a la psiquiatria de precision. Merece seguimiento a largo plazo aunque no pueda entrar en muchos anos.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://onemind.org/what-we-do/one-mind-rising-star-academy/one-mind-rising-star-awards/</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>VERIFICADA POR PRIMERA VEZ EN TIER 1 Y LA FILA CAMBIA DE NATURALEZA: NO LE SIRVE, NI EN 2027 NI PREVISIBLEMENTE NUNCA A CORTO PLAZO. Exige institucion u organizacion ESTADOUNIDENSE, nombramiento independiente como Assistant o Associate Professor con hasta 8 anos desde ese nombramiento, y nominacion institucional firmada por un cargo del decanato o de programas de investigacion. Nada de eso le aplica ni le aplicara en el horizonte de este radar. Datos del ciclo 2026: notificacion 13-08-2026, inicio mas temprano 01-01-2027, 300.000 USD en 3 anos, cinco premios. SE RECOMIENDA DEJAR DE GASTAR PRESUPUESTO EN ELLA cada pasada: queda documentada como inelegible estructural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>W-0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MSCA Postdoctoral Fellowships - convocatoria 2027 (HORIZON-MSCA-2027-PF-01-01) y el acantilado posterior</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Comision Europea / REA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Postdoctoral fellowship</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lanzamiento 2027-04-07 y cierre 2027-09-08, ambos marcados TBC en la propia pagina oficial; 388,57 M EUR. Es la ULTIMA convocatoria del marco financiero actual (Horizonte Europa cubre 2021-2027) y no hay certeza de que exista una PF con estas reglas en 2028: dependeria de FP10, sin diseno ni calendario fijados.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Decide si su primera MSCA posible existe siquiera. Con defensa en febrero de 2028 no llega al cierre del 08-09-2027; si adelantara la defensa a antes de esa fecha entraria, porque la regla exige haber defendido y no tener el titulo expedido. Es la unica pieza del radar que puede cambiar el calendario de su tesis.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/funding/msca-postdoctoral-fellowships-2027</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>La afirmacion de que 2027 es la ultima del marco procede de Tier 2 (Horizon Europe NCP Portal, enlargement-infohub) y NO aparece en la pagina oficial de la MSCA: es coherente con que Horizonte Europa cubra 2021-2027, pero es una inferencia. Confirmarla en el programa de trabajo antes de que nadie tome decisiones sobre la fecha de defensa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>W-0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EMBO Postdoctoral Fellowships - ronda de otono de 2027</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMBO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Postdoctoral fellowship</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Corte el 2027-07-09 a las 14:00 CEST. Los cortes son el 4o viernes de enero y el 2o viernes de julio; el segundo viernes de julio de 2027 es el dia 9.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Es la PRIMERA ronda sin derecho a resolicitud ('Effective from the Autumn 2027 selection round, i.e. for all applications submitted after January 22, 2027, 14:00 CET, re-applications will no longer be permitted'). Solo tendra un disparo en la vida, asi que conviene no gastarlo antes de tener la publicacion resuelta.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://www.embo.org/funding/fellowships-grants-and-career-support/postdoctoral-fellowships/</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Regla VERIFIED en el PDF de guidelines extraido localmente; la fecha concreta es aritmetica determinista sobre la regla. El desbloqueo real no es esta fecha sino la publicacion: ver F-0008 y la via Review Commons / Peer Community In.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>W-0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Becas de Investigacion SES - edicion 2027</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Sueno (SES)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Research project grant</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Apertura hacia noviembre-diciembre de 2026 y cierre hacia el 2027-01-25 (las bases de 2026 se subieron en noviembre de 2025 con cierre el 25 de enero).</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Su reloj no es el plazo sino la MEMBRESIA: las bases exigen ser socia de la SES desde al menos un ano antes de la convocatoria. Si se da de alta en septiembre de 2026 NO llega a la edicion de 2027 y entra justo para la de 2028. Ademas, en la edicion de enero de 2027 cumpliria exactamente la clausula del medico residente en ultimo ano, y esa coincidencia se pierde por la antiguedad.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://ses.org.es/becas-y-premios/</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AVISO PERMANENTE: el tablon de la SES NO retira el rotulo 'CONVOCATORIA ABIERTA' al vencer el plazo. El estado hay que sacarlo siempre del PDF de bases, nunca de la etiqueta. Fue esa etiqueta la que genero la falsa urgencia de la pasada anterior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>W-0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Convocatorias anuales de la AEGH (estancia profesional, bolsas de viaje y premio joven)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Asociacion Espanola de Genetica Humana (AEGH)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Travel grants, short stays and prizes</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Premio joven y bolsas de viaje: convocatoria a mediados de enero de 2027, cierre hacia el 2027-02-15. Beca de estancia profesional: convocatoria hacia febrero de 2027, cierre hacia el 2027-03-31.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Tres ayudas distintas de la misma sociedad, todas con competencia LOW o MEDIUM, y todas cerradas por el mismo requisito: 2 anos de antiguedad como socia. Darse de alta ahora las abre a partir de 2028. Es una decision con tres retornos.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://aegh.org/blog-2/</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>La AEGH no publica bases completas en PDF: solo las envia por secretaria@aegh.org. Verificar tambien si la nominacion espanola a la national fellowship de la ESHG (ver F-0023) exige la misma antiguedad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>W-0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Convocatorias anuales de la SENC (travel grants y premio Rita Levi-Montalcini)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Neurociencia (SENC)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Travel grants and student prize</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Calendario de travel grants publicado hacia finales de diciembre de 2026 (el de 2026 salio el 23-12-2025), con FENS/ENCODS cerrando el 31 de enero y SfN abriendo el 10 de abril. Premio Rita Levi-Montalcini: apertura hacia el 10-04-2027 y cierre hacia el 10-06-2027, asociado al congreso bienal de 2027.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>300000 dolares para investigacion de inicio de carrera en salud mental: la mayor cuantia individual de esta rama y tematicamente en el centro de su linea 2, con atencion especial a la psiquiatria de precision. Merece seguimiento a largo plazo aunque no pueda entrar en muchos anos.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>https://onemind.org/what-we-do/one-mind-rising-star-academy/one-mind-rising-star-awards/</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>INELEGIBLE, y por un motivo decisivo: las posdoctorales estan explicitamente excluidas. La elegibilidad son profesoras ayudantes o asociadas dentro de los ocho anos desde su PRIMER NOMBRAMIENTO INDEPENDIENTE, con titulo de doctorado (el MD cuenta). El reloj que importa no es el de su doctorado sino la fecha en que tenga por primera vez una plaza de facultad, que todavia no existe. Revisar solo si accede a un puesto independiente. Confianza LIKELY y no VERIFIED: elegibilidad leida en listados de oficinas de investigacion y en el anuncio de One Mind via busqueda, sin abrir el portal de solicitud.</t>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>El premio Rita Levi-Montalcini esta RESERVADO A DOCTORANDAS y el bienal de 2027 caeria hacia septiembre de 2027, con ella todavia predoctoral: es probablemente su ultima ventana. Las travel grants, en cambio, exigen 2 anos de antiguedad como socia y no las alcanza hasta agosto de 2028.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://www.senc.es/ayudas-de-la-senc/</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Pendiente: abrir el PDF 'Requisitos para solicitudes de ayudas y becas SENC' para saber si la regla de 2 anos consecutivos se aplica tambien a los premios o solo a las ayudas de viaje. De eso depende que su mejor premio de predoctoral sea accesible en 2027. Fechas y sede del congreso bienal SENC 2027 sin confirmar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>W-0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Contratos postdoctorales de la Junta de Andalucia (Linea 2, EIDIA) - edicion 2027</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Consejeria de Universidad, Investigacion e Innovacion - Junta de Andalucia</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Regional postdoctoral contract</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Apertura hacia el 2026-12-20 y cierre hacia el 2027-01-28. El patron oscila entre diciembre y febrero (Res. 17-12-2025 para la edicion 2026; Res. 21-02-2024 para la de 2024).</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Es la unica via autonomica sin requisito de movilidad exterior, y por tanto la unica compatible con su historial. La edicion decisiva para ella es la de enero de 2029; la de enero de 2028 cae semanas antes de su defensa prevista y la pierde por muy poco.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://www.juntadeandalucia.es/boja/</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Antes de la edicion de 2027 hay que abrir la Orden de bases de 24-10-2023 en BOJA y extraer la ventana de anos post-doctorado, que es el dato que aun falta. Las fichas de sede de juntadeandalucia.es devuelven cuerpo vacio (render por JavaScript): usar BOJA, que es HTML plano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>W-0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ayudas a Proyectos de la Fundacion Alicia Koplowitz - convocatoria 2027</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Fundacion Alicia Koplowitz</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Research project grant</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bases publicadas hacia enero de 2027 y cierre hacia el 2027-04-30 (XXI convocatoria consecutiva; las bases de 2026 se publicaron en enero con cierre el 30 de abril).</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>El encaje tematico con neurociencias infanto-juveniles es de los mejores de la base, pero la clausula 'El investigador Principal no podra estar cursando la residencia MIR ni PIR' la deja fuera como IP en 2027, con el MIR vivo hasta el 22-05-2027. Su primera edicion como IP es la de 2028. Puede entrar como colaboradora en 2027.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://fundacionaliciakoplowitz.org/lineas-de-accion/ayudas-investigacion/</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Las URL de los PDF de bases son predecibles: /wp-content/uploads/AAAA/MM/Bases_... Pendiente para otra pasada: las 'Ayudas de Formacion' de la misma fundacion, cuya pagina no enlaza bases pero que segun Tier 2 incluyen estancias de 6-12 meses en el extranjero, duracion a la que ya no son ayudas de viaje sino becas de verdad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>W-0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>III Convocatoria de Becas Fulbright-Fundacion Seneca de investigacion posdoctoral en EE. UU.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Fundacion Seneca (Region de Murcia) y Comision Fulbright Espana</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bilateral postdoctoral fellowship</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Septiembre de 2026, inminente: figura ya en el catalogo 2026 de la Fundacion Seneca y agosto es mes inhabil para presentar solicitudes; en la I convocatoria la apertura fue 'a partir del 3 de septiembre'.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Es la unica via a EE. UU. que sortea la barrera de ciudadania que hunde la NIH F32 (F-0015), porque el visado J-1 lo gestiona Fulbright. Exige doctorado, asi que no antes de 2028, pero las bases de esta III convocatoria fijan la ventana de anos y la definicion de 'vinculacion con la Region de Murcia', que es lo que decide si le sirve.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://fseneca.es/web/convocatorias</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Revisar en la primera semana de septiembre de 2026, cuando termine el mes inhabil. fseneca.es da 503 a WebFetch pero 200 a curl con User-Agent de navegador.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L15"/>
+  <autoFilter ref="A1:L23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22992,7 +27647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23475,8 +28130,112 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SUB-0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SEMEDLAB / Fundacion Jose Luis Castano-SEQC - alta como socia</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.fundacionjlc.es/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Avisos de las 8 convocatorias anuales de la Fundacion (intercambio internacional, ciclos IFCC, beca post-residencia, ayudas a tesis doctoral, ayudas a proyectos) y, sobre todo, ACCESO: casi todas exigen ser socia.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PRIORIDAD MAXIMA Y CON RELOJ DE 30 DIAS: la Beca Internacional de Intercambio Cientifico Profesional cierra el 30-09-2026, exige ser socia EN EL MOMENTO DE SOLICITAR y es la unica convocatoria con plazo inminente para la que hoy es elegible. Sin el alta, esa oportunidad muere sola. Contacto: secretaria@fundacionjlc.es, tel. 93 446 26 70.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Propuesta en la pasada del 2026-08-31 (rama 4). La rutina NO se suscribe en su nombre. Comprobar primero si ya es socia: varias filas de fellowships cambian de Fit segun la respuesta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SUB-0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AEGH (Asociacion Espanola de Genetica Humana) - alta como socia</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://aegh.org/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Avisos de las cinco lineas de ayuda de la AEGH y de sus bases completas, que NO se publican en web y solo se envian por secretaria@aegh.org.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Aqui la membresia no es solo un canal de informacion, es el RELOJ DE ELEGIBILIDAD: tres ayudas de la AEGH (beca de estancia profesional, bolsas de viaje y premio joven) exigen 2 anos de antiguedad continuada. Dandose de alta ahora quedan abiertas a partir de 2028; cada semana de retraso resta una semana a esa fecha. Ademas la AEGH nomina para la national fellowship de la ESHG (F-0023), donde la competencia es espanola y no europea.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Propuesta en la pasada del 2026-08-31 (rama 4). La rutina NO se suscribe en su nombre.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:J11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -23,17 +23,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6216,8 +6216,528 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SRC-0097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>MSCA - paginas oficiales de convocatoria por ano (Postdoctoral Fellowships)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/node/1496</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>El calendario completo de cada edicion de las MSCA Postdoctoral Fellowships (lanzamiento, plazo, notificacion, firma y arranque de proyectos) y el presupuesto, en HTML plano legible por un agente. Es la unica via hallada que publica las fechas que el Funding and Tenders Portal esconde tras JavaScript.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Una pagina por edicion: node/1495 = PF 2026, node/1496 = PF 2027 (canonical node/876). Leer el bloque de fechas y anotar siempre si llevan la marca (TBC).</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Alta en la pasada 2026-09-07 (rama 1). VERIFICADO ese dia: PF 2027 = lanzamiento 07-04-2027, plazo 08-09-2027, notificacion feb-2028, firma abr-2028, arranque may-2028, 388,57 M EUR, con TODAS las fechas marcadas (TBC). Complementa a SRC-0011, que apunta solo a la raiz del dominio, y sortea el bloqueo por JavaScript de SRC-0072. Consecuencia directa para la candidata: con defensa estimada en feb-2028 NO llega al plazo del 08-09-2027, asi que su primera MSCA-PF alcanzable es la edicion de 2028.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SRC-0098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>MSCA COFUND 2027 - pagina de convocatoria</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/funding/msca-cofund-2027</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Las instituciones que en 2027 piden cofinanciacion para montar programas propios de becas postdoctorales. Los programas seleccionados arrancan en enero de 2028 y sacan sus primeras convocatorias de becarios en 2028-2029, justo la ventana de la candidata.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Seguir la convocatoria (lanzamiento previsto 08-12-2026, plazo 06-04-2027) y sobre todo la lista de proyectos COFUND seleccionados que deberia publicarse hacia septiembre de 2027; de ahi salen los programas a los que ella si se presenta.</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Alta en la pasada 2026-09-07 (rama 1). NO ABIERTA DIRECTAMENTE: las fechas vienen del resumen de una busqueda, no de una lectura de la pagina, hay que verificarlas antes de actuar. Es un canal indirecto: ella no solicita el COFUND, solicita las becas de los programas COFUND, y por eso la senal util llega con un ano de retraso sobre la convocatoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SRC-0099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>FIMABIS / IBIMA-Plataforma BIONAND - convocatorias de empleo (portal RFGI-SSPA)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.rfgi.es/ConvocatoriasPropiasFIMABIS/es/Convocatorias/DesgloseEstadoTipoConvocatoria/FIMAB_EM</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Convocatorias de empleo temporal de investigacion del instituto de investigacion sanitaria de su propio hospital en Malaga: titulado superior, investigador postdoctoral, tecnico, bioinformatica y bioestadistica</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tipo de convocatoria FIMAB_EM (Ofertas de empleo); filtrar por estado Abiertas</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Unica via oficial que enlaza ibima.eu/es/trabaja-con-nosotros. La pagina indice se abre bien pero el listado de convocatorias requiere navegar dentro del portal; no basta con un fetch de la raiz. Verificada viva el 2026-09-07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SRC-0100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CNIO - ofertas de empleo</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.cnio.es/acerca-del-cnio/ofertas-de-empleo/</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Ofertas del Centro Nacional de Investigaciones Oncologicas por categorias (jefes de grupo, investigadores cientificos, postdoctorales, tecnicos, unidades clinicas)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Revisar las secciones de investigadores y de titulados superiores; buscar bioinformatica y biologia computacional</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Verificada el 2026-09-07: se abre sin bloqueo y lista bien las ofertas, pero el 2026-09-07 no habia ninguna de bioinformatica, genomica ni genetica estadistica (solo predoctoral, dos tecnicos de laboratorio, un titulado superior de oncohematologia pediatrica IdiPAZ-CNIO y un tecnico de gestion). Sin bolsa permanente ni autocandidatura. Rendimiento bajo para su perfil: la genetica del CNIO es oncologica, no psiquiatrica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SRC-0101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>IMIM - Hospital del Mar Research Institute, ofertes de treball</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.imim.es/ofertes/ofertes-treball/</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Oferta publica, convocatorias temporales, bolsas de trabajo y convocatorias externas del IMIM, que tiene grupo de genetica psiquiatrica en el PRBB de Barcelona</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Seccions Convocatories temporals y Borses de treball; buscar genetica, bioinformatica y salut mental</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>BLOQUEO CONFIRMADO 2026-09-07: HTTP 403 al fetch automatico tanto en www.imim.es/ofertes/ofertes-treball/ como en el host real del listado www.researchmar.net/ofertes/ofertas-empleo/. En navegador funciona. No volver a gastar llamadas en fetch: usar navegador o buscador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SRC-0102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CIBER (consorcio, incluye CIBERSAM) - empleo</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.ciberisciii.es/empleo</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Ofertas de empleo del consorcio CIBER, incluidas plazas de estadistica y epidemiologia en grupos de CIBERSAM y contratos indefinidos de personal propio</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Listado de ofertas de empleo del consorcio; filtrar por area tematica CIBERSAM</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Quincenal</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Sustituye a la URL de ofertas que daba 404. BLOQUEO CONFIRMADO 2026-09-07: el dominio ciberisciii.es devuelve HTTP 403 al fetch automatico (probado en /ofertas-de-empleo). La ruta viva /empleo procede de fuentes Tier 2 (Sociedad Espanola de Epidemiologia, LinkedIn de CIBER) y no ha podido abrirse: UNVERIFIED. Consultar en navegador o vigilar los reboteos en seepidemiologia.es.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SRC-0103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Epidemiologia - ofertas de empleo</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://seepidemiologia.es/</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Reboteo de ofertas de empleo espanolas de epidemiologia y bioestadistica, incluidas convocatorias del CIBER y de institutos de investigacion sanitaria que no salen en agregadores</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Seccion de ofertas de empleo; buscar CIBER, bioestadistica, genetica</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Quincenal</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Fuente NUEVA, detectada el 2026-09-07 al rastrear la via viva de empleo del CIBER: publicaba una convocatoria de contrato indefinido en CIBER para perfiles de medicina o de matematicas/estadistica con master en salud publica o ciencia de datos, que es literalmente el perfil de Ana. No abierta por esta rama (solo vista en resultados de busqueda): validar la URL exacta de la seccion de ofertas en la proxima pasada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SRC-0104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SERGAS - seleccion temporal de FEA y listas de contratacion (Galicia)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.sergas.gal/Recursos-Humanos/Emprego-publico-Seleccion-temporal?idioma=es</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Las convocatorias de seleccion temporal de facultativo especialista de area por hospital y area sanitaria, con fecha de publicacion y plaza, mas el acceso a las listas generales de contratacion. Es el mecanismo permanente de entrada al SERGAS, paralelo a la OPE.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Abrir la pagina y filtrar el listado por FEA y por las categorias de laboratorio (Analisis Clinicos, Bioquimica Clinica, y en el futuro Laboratorio Clinico o Genetica). Complemento: /Recursos-Humanos/OFERTAS_FEA_GENERAL y /Recursos-Humanos/Listaxes-de-contratacion</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Mensual, con revision reforzada en marzo y abril (plazo ordinario de inscripcion en listas)</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Alta en la pasada del 2026-09-07 (rama 4). Amplia el mapa de CCAA a Galicia, que no estaba cubierta. AVISO DE URL: sergas.es responde 301 a sergas.gal; usar directamente el dominio .gal para evitar la redireccion. El catalogo gallego sigue sin recoger la categoria Laboratorio Clinico del RD 101/2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SRC-0105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Osakidetza - contratacion temporal (bolsas de trabajo del Servicio Vasco de Salud)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.osakidetza.euskadi.eus/contratacion-temporal/webosk00-procon/es/</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Las resoluciones de apertura de plazo de inscripcion en las bolsas de contratacion temporal por categoria, con fechas literales de apertura y cierre, y los cambios de denominacion de categoria. Aqui se detecto que Osakidetza ya ha creado la lista de Laboratorio Clinico en sustitucion de Analisis Clinicos y Bioquimica Clinica.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Buscar en la pagina las resoluciones del ano en curso y quedarse con las categorias de laboratorio y genetica; la inscripcion se hace en el area privada de lanpoltsa.osakidetza.eus; consultas por correo a 2021lp-lc@osakidetza.eus</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Trimestral, con revision reforzada en junio-julio, que es cuando abrio el plazo de 2026</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Alta en la pasada del 2026-09-07 (rama 4). Amplia el mapa de CCAA al Pais Vasco. Es el primer servicio autonomico visto que aplica la denominacion Laboratorio Clinico del RD 101/2025. PENDIENTE: la pagina rotula la categoria como FEM-Tecnico/a de Laboratorio Clinico y no queda claro si es facultativo o tecnico de FP; resolverlo por correo antes de junio de 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SRC-0106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Amgen R&amp;D Postdoctoral Fellows Program - portal de postdocs</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://careers.amgen.com/en/Postdoctoral</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Programa recurrente de postdocs de Amgen (3 anos ampliables a 4) en I+D, incluida la sede de Amgen deCODE genetics en Reykjavik, con plazas de genetica estadistica y genomica computacional.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Enlace 'Postdoctoral-jobs' del portal; alternativamente careers.amgen.com/en/search-jobs con la palabra 'genetics'.</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Descubierta el 2026-09-07 a partir del anuncio de deCODE en jobRxiv. La pagina general del programa carga bien, pero solo lista como sedes Thousand Oaks, San Francisco, Burnaby y Copenhague, sin mencionar Reykjavik pese a existir la plaza islandesa: hay que mirar el buscador de empleo, no la pagina del programa. Las fichas concretas viven en Workday (amgen.wd1.myworkdayjobs.com), sin comprobar si se dejan leer automaticamente.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J97"/>
+  <autoFilter ref="A1:J107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6348,7 +6868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10535,8 +11055,1268 @@
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>P-0018</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Clinical Research Fellow (Psychological Medicine)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Rama 2 (tablones academicos). Leido en la pagina de resultados de jobs.ac.uk (busqueda 'psychiatric genetics', 2026-09-07); no se abrio el anuncio individual, de ahi LIKELY y no VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DST268/clinical-research-fellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>P-0019</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow in Neurogenetics</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Rama 2. Aparece en el buscador de Science Careers (query 'statistical genetics', 2026-09-07); la pagina de detalle devuelve HTTP 403 al fetch, un solo intento, no verificado.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://jobs.sciencecareers.org/job/679674/postdoctoral-fellow-in-neurogenetics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>P-0020</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow - Statistical Genetics and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Rama 5 (buzon y novedad), barrido de jobRxiv (SRC-0035) el 2026-09-07. Anuncio leido en jobRxiv (publicado 2026-08-22) y confirmado de forma independiente por researchersjob.com y por la pagina del programa de postdocs de Amgen; no se abrio la ficha del portal Workday de Amgen, de ahi LIKELY y no VE</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://jobrxiv.org/job/postdoctoral-fellow-statistical-genetics-and-artificial-intelligence/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>P-0021</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Postdoctoral Scholar/Researcher in Statistical Genetics - Young Lab</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Rama 5 (buzon y novedad), barrido de jobRxiv (SRC-0035) el 2026-09-07. Solo se leyo la ficha agregada de jobRxiv, que declara el anuncio caducado; no se abrio ninguna pagina de UCLA, por eso UNVERIFIED y por eso el nombre del PI no se afirma.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://jobrxiv.org/?post_type=job_listing&amp;p=117072</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>P-0022</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Clinical Research Associate (farmacogenomica clinica)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Rama 5 (buzon y novedad), tablon de empleo de la ISPG (SRC-0030) el 2026-09-07. Los datos proceden del anuncio reproducido en el tablon de la ISPG; no se abrio el portal Oracle de la universidad, por eso UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://iaejup.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/UOA-Careers/job/3142/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>P-0004</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Postdoctoral Researcher in Psychiatric and Genetic Epidemiology (ERC StressGene)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Last_Verified=2026-09-07; Source_Note=Rama 1 (EURAXESS). 2026-09-07: reabierta la URL del anuncio 557315 y confirmado que ya no existe, devuelve la lista generica de busqueda de EURAXESS. Matiz importante: en esta pasada CUALQUIER URL de euraxess.ec.europa.eu/jobs devolvio esa misma lista generica a</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/557315</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>P-0007</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Postdoc in method development in human statistical genetics (classification of complex traits)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Status=CLOSED; Deadline=2026-05-01; Start_Date=2026-10-01; Confidence=LIKELY; Last_Verified=2026-09-07; Fit_Rationale=Tema exactamente su linea 1, genetica estadistica de rasgos complejos humanos, y el grupo de Doug Speed construye LDAK y SumHer, herramientas que ella ya usa aguas abajo, lo que da u</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/12856703/postdoc-position-in-method-development-in-human-statistical-genetics-with-a-focus-on-classificat-/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>P-0006</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Scientist in host genetics and data integration for liver cancer risk prediction</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Status=OPEN; Deadline=2026-09-11; Confidence=VERIFIED; Last_Verified=2026-09-07; Source_Note=Rama 2, 2026-09-07: sigue listado y activo en jobs.ac.uk (ref DSR614, cierre 11 Sep, 39.424-47.779 GBP). Aparece en tres busquedas distintas (statistical genetics, polygenic, genetic epidemiology).</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSR614/postdoctoral-research-scientist-in-host-genetics-and-data-integration-for-liver-cancer-risk-predication-and-early-detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>P-0013</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Associate in Epidemiology and Health Data Science</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Status=CLOSED; Confidence=VERIFIED; Last_Verified=2026-09-07; Source_Note=Rama 2, 2026-09-07: anuncio DSM851 de QMUL Wolfson Institute of Population Health visto en jobs.ac.uk con fecha de cierre 06 Sep 2026, ya pasada. Convocatoria agotada.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSM851/postdoctoral-research-associate-in-epidemiology-and-health-data-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>P-0012</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Junior Research Data Scientist</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Status=CLOSED; Confidence=LIKELY; Last_Verified=2026-09-07; Source_Note=Rama 2, 2026-09-07: plazo 03-09-2026 vencido y no reaparece en ninguna de las cinco busquedas tematicas de jobs.ac.uk. Base = plazo vencido, no se abrio la pagina del anuncio.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSR260/junior-research-data-scientist</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>P-0015</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Clinical Research Associate (IoPPN)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Status=CLOSED; Confidence=LIKELY; Last_Verified=2026-09-07; Source_Note=Rama 2, 2026-09-07: plazo 27-08-2026 vencido; no figura ya en las busquedas de jobs.ac.uk. Base = plazo vencido.</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/154086-clinical-research-associate</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>P-0016</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Clinical Research Fellow (IoPPN)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status=CLOSED; Confidence=LIKELY; Last_Verified=2026-09-07; Source_Note=Rama 2, 2026-09-07: plazo 01-09-2026 vencido. OJO: KCL Psychological Medicine tiene ahora un Clinical Research Fellow con cierre 18-09-2026 (DST268) que podria ser su reedicion; se registra como fila nueva y queda por confirmar </t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/155765-clinical-research-fellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>P-0014</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Research Assistant (Moondance Dementia Laboratory)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confidence=UNVERIFIED; Last_Verified=2026-09-07; Source_Note=Rama 2, 2026-09-07: NO CONFIRMADO. El portal eploy de Cardiff responde en https://cardiffuniweb.eploy.net/vacancies/ pero solo devuelve la pagina 1 de 3 y la paginacion (?page=2) reenvia a la 1, asi que no se pudo ver el listado completo. </t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://cardiffuniweb.eploy.net/vacancies/vacancy-search-results.aspx?culture=en-GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>P-0002</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Scientist in Statistical Genomics / Genetic Epidemiology</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Status=ROLLING; Deadline=; Start_Date=2026-12-01 (negociable); Salary_EUR_Year=73999-91055 bruto (incl. 8% de paga de vacaciones), segun experiencia; Duration=3 anos; Confidence=LIKELY; Last_Verified=2026-09-07; Next_Action=En Q4 2027, con la defensa a la vista, escribir a Beate St Pourcain (beate.s</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://recruitingapp-5569.de.umantis.com/Vacancies/496/Description/2?lang=eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>J-0007</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Convocatorias de empleo FIMABIS / IBIMA-Plataforma BIONAND (portal RFGI-SSPA)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rama 3 (instituciones). Ruta descubierta abriendo https://ibima.eu/es/trabaja-con-nosotros/, que enlaza este portal como su unica via de ofertas publicas; portal abierto y confirmado vivo el 2026-09-07. Las convocatorias individuales no se listan sin navegar por el portal (contenido cargado tras la </t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://www.rfgi.es/ConvocatoriasPropiasFIMABIS/es/Convocatorias/DesgloseEstadoTipoConvocatoria/FIMAB_EM</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>J-0008</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Seleccion temporal de FEA del SERGAS (listas de contratacion, Galicia)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Rama 4 (mas alla de la academia), carril 2 sistema publico. Pagina Tier 1 abierta y leida el 2026-09-07 tras redireccion 301 de sergas.es a sergas.gal. La ventana anual 1-marzo/30-abril procede de la pagina general de contratacion temporal de la Xunta (Tier 2) y queda marcada como LIKELY dentro de l</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://www.sergas.gal/Recursos-Humanos/Emprego-publico-Seleccion-temporal?idioma=es</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>J-0009</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Bolsa de trabajo temporal de Osakidetza - categoria Laboratorio Clinico (sustituye a Analisis Clinicos y Bioquimica Clinica)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Rama 4 (mas alla de la academia), carril 2 sistema publico. Pagina Tier 1 de Osakidetza abierta y leida el 2026-09-07: las fechas 06-07-2026 y 27-07-2026 y la Resolucion 1060/2026 son literales de la pagina. La naturaleza de la categoria (facultativo frente a tecnico) queda expresamente sin verifica</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://www.osakidetza.euskadi.eus/contratacion-temporal/webosk00-procon/es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>J-0003</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Via transitoria al titulo de especialista en Genetica Medica y en Genetica de Laboratorio (dos reales decretos separados, aun sin publicar)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Name=Via transitoria al titulo de especialista en Genetica Medica y en Genetica de Laboratorio (dos reales decretos separados, aun sin publicar); Status=PENDING; Open_Date=; Deadline=; Requirements_Key=Serian dos titulos y dos reales decretos distintos: Genetica Medica reservada a titulados en Medic</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://www.sanidad.gob.es/normativa/audiencia/home.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SRC-0097</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>MSCA - paginas oficiales de convocatoria por ano (Postdoctoral Fellowships)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>El calendario completo de cada edicion de las MSCA Postdoctoral Fellowships (lanzamiento, plazo, notificacion, firma y arranque de proyectos) y el presupuesto, en HTML plano legible por un agente. Es la unica via hallada que publica las fechas que el Funding and Tenders Portal esconde tras JavaScrip</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/node/1496</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>SRC-0098</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>MSCA COFUND 2027 - pagina de convocatoria</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Las instituciones que en 2027 piden cofinanciacion para montar programas propios de becas postdoctorales. Los programas seleccionados arrancan en enero de 2028 y sacan sus primeras convocatorias de becarios en 2028-2029, justo la ventana de la candidata.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/funding/msca-cofund-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>SRC-0099</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>FIMABIS / IBIMA-Plataforma BIONAND - convocatorias de empleo (portal RFGI-SSPA)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Convocatorias de empleo temporal de investigacion del instituto de investigacion sanitaria de su propio hospital en Malaga: titulado superior, investigador postdoctoral, tecnico, bioinformatica y bioestadistica</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://www.rfgi.es/ConvocatoriasPropiasFIMABIS/es/Convocatorias/DesgloseEstadoTipoConvocatoria/FIMAB_EM</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>SRC-0100</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>CNIO - ofertas de empleo</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Ofertas del Centro Nacional de Investigaciones Oncologicas por categorias (jefes de grupo, investigadores cientificos, postdoctorales, tecnicos, unidades clinicas)</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://www.cnio.es/acerca-del-cnio/ofertas-de-empleo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SRC-0101</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>IMIM - Hospital del Mar Research Institute, ofertes de treball</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Oferta publica, convocatorias temporales, bolsas de trabajo y convocatorias externas del IMIM, que tiene grupo de genetica psiquiatrica en el PRBB de Barcelona</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://www.imim.es/ofertes/ofertes-treball/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SRC-0102</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>CIBER (consorcio, incluye CIBERSAM) - empleo</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Ofertas de empleo del consorcio CIBER, incluidas plazas de estadistica y epidemiologia en grupos de CIBERSAM y contratos indefinidos de personal propio</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://www.ciberisciii.es/empleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SRC-0103</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Epidemiologia - ofertas de empleo</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Reboteo de ofertas de empleo espanolas de epidemiologia y bioestadistica, incluidas convocatorias del CIBER y de institutos de investigacion sanitaria que no salen en agregadores</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://seepidemiologia.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SRC-0104</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>SERGAS - seleccion temporal de FEA y listas de contratacion (Galicia)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Las convocatorias de seleccion temporal de facultativo especialista de area por hospital y area sanitaria, con fecha de publicacion y plaza, mas el acceso a las listas generales de contratacion. Es el mecanismo permanente de entrada al SERGAS, paralelo a la OPE.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://www.sergas.gal/Recursos-Humanos/Emprego-publico-Seleccion-temporal?idioma=es</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SRC-0105</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Osakidetza - contratacion temporal (bolsas de trabajo del Servicio Vasco de Salud)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Las resoluciones de apertura de plazo de inscripcion en las bolsas de contratacion temporal por categoria, con fechas literales de apertura y cierre, y los cambios de denominacion de categoria. Aqui se detecto que Osakidetza ya ha creado la lista de Laboratorio Clinico en sustitucion de Analisis Cli</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://www.osakidetza.euskadi.eus/contratacion-temporal/webosk00-procon/es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SRC-0106</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Amgen R&amp;D Postdoctoral Fellows Program - portal de postdocs</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Programa recurrente de postdocs de Amgen (3 anos ampliables a 4) en I+D, incluida la sede de Amgen deCODE genetics en Reykjavik, con plazas de genetica estadistica y genomica computacional.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://careers.amgen.com/en/Postdoctoral</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>subscriptions</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SUB-0011</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>EU Funding and Tenders Portal - busqueda guardada con aviso por correo</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Aviso por correo cuando cambia el estado de los topics vigilados (Forthcoming a Open) y cuando aparecen los topics del programa marco sucesor de Horizonte Europa.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-search</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>subscriptions</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SUB-0012</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>jobs.ac.uk - alerta por correo de busqueda guardada</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Correo con los anuncios nuevos que casan con palabras clave guardadas (statistical genetics, psychiatric genetics, polygenic, GWAS, genetic epidemiology)</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/jobs-by-email</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H103"/>
+  <autoFilter ref="A1:H133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10942,7 +12722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD18"/>
+  <dimension ref="A1:AD23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10950,15 +12730,15 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="52" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="52" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
@@ -11303,12 +13083,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3 years</t>
+          <t>3 anos</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>73999-91055 bruto (incl. 8% holiday bonus), segun experiencia</t>
+          <t>73999-91055 bruto (incl. 8% de paga de vacaciones), segun experiencia</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -11329,7 +13109,7 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>PhD en genomica estadistica, epidemiologia genetica, bioestadistica o campo cuantitativo afin; metodos omicos para arquitectura genetica de fenotipos humanos; R, Python, Perl, shell. Deseable: SEM, meta-analisis, neuroimagen. SIN PLAZO FIJO: revision continua a partir del 2026-10-08 hasta cubrir.</t>
+          <t>PhD en genomica estadistica, epidemiologia genetica, bioestadistica o campo cuantitativo afin; metodos omicos para arquitectura genetica de fenotipos humanos; R, Python, Perl, shell. Deseable: SEM, meta-analisis, neuroimagen. SIN PLAZO FIJO: revision continua de candidaturas a partir del 2026-10-08 y hasta cubrir la plaza. Encuadre en el consorcio EAGLE.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -11359,39 +13139,39 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>En Q4 2027, con la defensa a la vista, escribir a Beate St Pourcain (beate.stpourcain@mpi.nl) preguntando por la siguiente vacante del grupo y ofreciendo su perfil MD+PhD con GWAS/PRS; la edicion actual empieza en diciembre de 2026 y le es inaplicable.</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>No aplicar: arranque dic-2026 y PhD ya defendido, ambos fuera de su ventana. Anadir a St Pourcain y al grupo Population Genetics of Human Communication a la lista de contactos y escribirle en Q1-Q2 2027 preguntando por aperturas para finales de 2027 / 2028; vigilar la pagina de vacantes cada ciclo.</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>https://recruitingapp-5569.de.umantis.com/Vacancies/496/Description/2?lang=eng</t>
@@ -11399,7 +13179,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Rama 5 (novedad). Localizado en el tablon de empleo de la ISPG y VERIFICADO en el portal propio de la Max Planck Society, que muestra publicacion el 2026-08-12. No lo indexa ninguno de los agregadores que cubren las otras ramas.</t>
+          <t>Rama 5 (buzon y novedad) reverifico la fila en el tablon de la ISPG (SRC-0030) el 2026-09-07: sigue publicada, ahora con salario (EUR 73.999,91-91.055,27), inicio 01-12-2026 negociable, contrato de 3 anos, revision desde el 08-10-2026 hasta cubrir, encuadre EAGLE sobre correlatos geneticos de la conducta social desde la infancia, y contactos beate.stpourcain@mpi.nl y secretariat.genetics@mpi.nl. No se abrio el portal umantis de solicitud, de ahi LIKELY.</t>
         </is>
       </c>
     </row>
@@ -11618,34 +13398,34 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Registrar el grupo, no el anuncio. Hacia mediados de 2027 comprobar si StressGene o su ERC sucesor sigue reclutando y escribir al grupo de Unnur Valdimarsdottir con una nota de encaje de una pagina; mientras tanto mantener el centro en la lista de posibles acogidas MSCA-PF, que es la via que si encaja con una defensa en feb 2028.</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Registrar el grupo, no el anuncio. Hacia mediados de 2027 comprobar si StressGene o su ERC sucesor sigue reclutando y escribir al grupo de Unnur Valdimarsdottir con una nota de encaje de una pagina; mientras tanto mantener el centro en la lista de posibles acogidas MSCA-PF, que es la via que si encaja con una defensa en feb 2028.</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>https://euraxess.ec.europa.eu/jobs/557315</t>
@@ -11653,7 +13433,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Rama 1 (EURAXESS). Hallado con busqueda restringida al dominio euraxess.ec.europa.eu; la URL del puesto ahora redirige a la busqueda generica, es decir, el anuncio ha expirado.</t>
+          <t>Rama 1 (EURAXESS). 2026-09-07: reabierta la URL del anuncio 557315 y confirmado que ya no existe, devuelve la lista generica de busqueda de EURAXESS. Matiz importante: en esta pasada CUALQUIER URL de euraxess.ec.europa.eu/jobs devolvio esa misma lista generica al fetch automatico, asi que el enlace roto no es diagnostico por si solo; aun asi, un anuncio de 2026 no seguiria vivo. El valor de la fila es el grupo, no la vacante.</t>
         </is>
       </c>
     </row>
@@ -11725,7 +13505,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-439</v>
+        <v>-445</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -11871,7 +13651,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -11910,34 +13690,34 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>No aplicar: no puede incorporarse antes de mediados de 2027. En su lugar, crear una alerta guardada en jobs.ac.uk con University of Oxford + statistical genetics / genetic epidemiology y revisar NDM Experimental Medicine en Q4 2027. Si quiere un gancho ya, escribir a Azim Ansari en otono de 2027 (no antes) con el articulo de Nature Mental Health una vez aceptado, preguntando si estos puestos se repiten.</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>No aplicar: no puede incorporarse antes de mediados de 2027. En su lugar, crear una alerta guardada en jobs.ac.uk con University of Oxford + statistical genetics / genetic epidemiology y revisar NDM Experimental Medicine en Q4 2027. Si quiere un gancho ya, escribir a Azim Ansari en otono de 2027 (no antes) con el articulo de Nature Mental Health una vez aceptado, preguntando si estos puestos se repiten.</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>https://www.jobs.ac.uk/job/DSR614/postdoctoral-research-scientist-in-host-genetics-and-data-integration-for-liver-cancer-risk-predication-and-early-detection</t>
@@ -11945,7 +13725,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Rama 2, jobs.ac.uk (SRC-0002), anuncio abierto y fechas leidas directamente el 2026-08-23. Es el unico postdoc real de genetica estadistica que devolvieron tres consultas distintas de jobs.ac.uk esta semana.</t>
+          <t>Rama 2, 2026-09-07: sigue listado y activo en jobs.ac.uk (ref DSR614, cierre 11 Sep, 39.424-47.779 GBP). Aparece en tres busquedas distintas (statistical genetics, polygenic, genetic epidemiology).</t>
         </is>
       </c>
     </row>
@@ -12013,7 +13793,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-122</v>
+        <v>-128</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -12027,7 +13807,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Topic is her research line 1 stated plainly - statistical genetics of human complex traits - and Doug Speed's group (LDAK, SumHer) builds tools she already uses downstream, which makes for a credible cold-contact hook. Denmark is EU: no visa, English-working group, and a two-year contract rather than the one-year Dutch norm. The honest brake is the phrase method development: this post is about writing and benchmarking new estimators, not applying GWAS/PRS pipelines, and her independent level is pipeline execution in PLINK/R with AI-assisted Python. She would be below the bar unless she spends the next 18 months deliberately building methods evidence - a small public repo, a simulation study, a methods section she owns end to end in the Nature Mental Health paper - which is a legitimate thing to plan for and is why this is kept at 3 rather than dropped. No salary published; Danish postdoc pay is above any floor (none set). CONFLICTING SOURCES, unreconciled: branch 1 read a deadline of 2026-05-01 (hence CLOSED here), while branch 2's Nature Careers listing showed no deadline and appeared live; both agree on a 2026-10-01 start, which is consistent with a spring deadline. Nature Careers blocks automated fetching (HTTP 400), so neither could open the source page. Either way the dates are far ahead of her Feb 2028 (ETA) defence.</t>
+          <t>Tema exactamente su linea 1, genetica estadistica de rasgos complejos humanos, y el grupo de Doug Speed construye LDAK y SumHer, herramientas que ella ya usa aguas abajo, lo que da un gancho creible para un contacto en frio. Dinamarca es UE: sin visado, grupo que trabaja en ingles (su C2) y contrato de dos anos en vez del ano tipico holandes. El freno honesto es la expresion method development: el puesto consiste en escribir y evaluar estimadores nuevos, no en ejecutar pipelines GWAS/PRS, y su nivel independiente es ejecucion de pipelines en PLINK/R con Python asistido por IA; entraria por debajo del liston salvo que dedique los proximos 18 meses a construir evidencia metodologica (un repositorio publico, un estudio de simulacion, una seccion de metodos suya de principio a fin en el articulo de Nature Mental Health), que es un plan legitimo y por eso la fila se queda en 3 y no se descarta. Sin salario publicado; el sueldo postdoctoral danes supera cualquier suelo, y no hay suelo. CONFLICTO DE FUENTES RESUELTO EL 2026-09-07: la rama 1 habia leido plazo 2026-05-01 y la rama 2 lo vio vivo y sin plazo en Nature Careers; una segunda fuente independiente (el anuncio difundido por el propio centro en LinkedIn y sus resumenes) confirma plazo 1 de mayo con incorporacion el 1 de octubre de 2026, y las fichas de Nature Careers suelen sobrevivir al cierre sin mostrar plazo, que es la explicacion economica de la discrepancia. Como la fecha de incorporacion ya paso, el puesto esta cerrado con independencia de como se resuelva el detalle. Dato nuevo y util: la plaza cuelga de un proyecto ERC de Speed sobre metodos estadisticos para clasificar enfermedades, o sea financiacion plurianual y contratacion previsiblemente recurrente. Ella NO podia presentarse en ningun caso: la residencia MIR no termina hasta el 22-05-2027 y la defensa se estima en febrero de 2028.</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -12047,39 +13827,39 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Conflicto cerrado, no reabrirlo. En la primavera de 2027 revisar si el proyecto ERC de Doug Speed vuelve a sacar plaza, y sobre todo escribirle a doug@qgg.au.dk en el primer trimestre de 2028, ya con la tesis defendida, para proponerle ser anfitrion de una MSCA-PF en la convocatoria de 2028; la de 2027, con plazo el 08-09-2027, le queda fuera por calendario.</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Ninguna sobre el anuncio, y confirmar el estado real (abierto o cerrado) abriendo la ficha de Nature Careers en un navegador, porque las dos ramas discrepan. Tratarlo como objetivo de competencias: durante el proximo ano producir un resultado con sabor metodologico al que poder apuntar; despues vigilar las vacantes de QGG desde la primavera de 2027 y considerar el grupo de Doug Speed como acogida MSCA-PF para 2028.</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>https://www.nature.com/naturecareers/job/12856703/postdoc-position-in-method-development-in-human-statistical-genetics-with-a-focus-on-classificat-/</t>
@@ -12087,7 +13867,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Ramas 1 y 2 (misma plaza, fusionada; ver el conflicto de fechas en Fit_Rationale). Nature Careers bloquea el fetch automatico (HTTP 400) y la pagina de vacantes de AU TECH no mostraba el puesto, por eso UNVERIFIED.</t>
+          <t>Ramas 1 y 2 (misma plaza, fusionada). Conflicto de fechas cerrado por la rama 1 el 2026-09-07 con una segunda fuente independiente. nature.com sigue bloqueando el fetch (HTTP 400) y en esta pasada fallaron ademas qgg.au.dk/en/about-qgg/vacancies (HTTP 404) y www.au.dk (HTTP 403), asi que la confianza sube a LIKELY y no a VERIFIED.</t>
         </is>
       </c>
     </row>
@@ -12278,7 +14058,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-193</v>
+        <v>-199</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -12656,7 +14436,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -12670,7 +14450,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -12704,39 +14484,39 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Sin solicitud. Se conserva como prueba de que KCL SGDP / NIHR BioResource Maudsley contrata personal cuantitativo con regularidad: crear una alerta en jobs.ac.uk con King's College London + Social, Genetic para anuncios de grado postdoc a partir de finales de 2027.</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Sin solicitud. Se conserva como prueba de que KCL SGDP / NIHR BioResource Maudsley contrata personal cuantitativo con regularidad: crear una alerta en jobs.ac.uk con King's College London + Social, Genetic para anuncios de grado postdoc a partir de finales de 2027.</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>https://www.jobs.ac.uk/job/DSR260/junior-research-data-scientist</t>
@@ -12744,7 +14524,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Rama 2, jobs.ac.uk (SRC-0002), anuncio abierto y fechas leidas directamente el 2026-08-23.</t>
+          <t>Rama 2, 2026-09-07: plazo 03-09-2026 vencido y no reaparece en ninguna de las cinco busquedas tematicas de jobs.ac.uk. Base = plazo vencido, no se abrio la pagina del anuncio.</t>
         </is>
       </c>
     </row>
@@ -12794,7 +14574,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -12808,7 +14588,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -12847,34 +14627,34 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Sin accion. Se conserva solo para dejar constancia de que el Wolfson Institute of Population Health combina a veces epidemiologia de historia clinica con puntuaciones poligenicas, un nicho MD + genetica estadistica plausible que conviene revisar en 2027.</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Sin accion. Se conserva solo para dejar constancia de que el Wolfson Institute of Population Health combina a veces epidemiologia de historia clinica con puntuaciones poligenicas, un nicho MD + genetica estadistica plausible que conviene revisar en 2027.</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>https://www.jobs.ac.uk/job/DSM851/postdoctoral-research-associate-in-epidemiology-and-health-data-science</t>
@@ -12882,7 +14662,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Rama 2, jobs.ac.uk (SRC-0002), anuncio abierto y fechas leidas directamente el 2026-08-23; lo devolvio la consulta polygenic, no statistical genetics.</t>
+          <t>Rama 2, 2026-09-07: anuncio DSM851 de QMUL Wolfson Institute of Population Health visto en jobs.ac.uk con fecha de cierre 06 Sep 2026, ya pasada. Convocatoria agotada.</t>
         </is>
       </c>
     </row>
@@ -12942,7 +14722,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -12976,39 +14756,39 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Sin accion. Lo util es la URL de vacantes de Cardiff que si funciona: revisarla desde mediados de 2027 buscando plazas de Research Associate en genetica estadistica del MRC CNGG.</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Sin accion. Lo util es la URL de vacantes de Cardiff que si funciona: revisarla desde mediados de 2027 buscando plazas de Research Associate en genetica estadistica del MRC CNGG.</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>https://cardiffuniweb.eploy.net/vacancies/vacancy-search-results.aspx?culture=en-GB</t>
@@ -13016,7 +14796,7 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Rama 3. Portal eploy propio de Cardiff (Tier 1), vacante ref 442. cardiff.ac.uk/jobs devuelve HTTP 403 al fetch automatico; jobs.cardiff.ac.uk redirige (302) a esta URL de eploy, que si funciona. Solo se leyo la pagina 1 de 3 y no aparecio ningun puesto del MRC CNGG.</t>
+          <t>Rama 2, 2026-09-07: NO CONFIRMADO. El portal eploy de Cardiff responde en https://cardiffuniweb.eploy.net/vacancies/ pero solo devuelve la pagina 1 de 3 y la paginacion (?page=2) reenvia a la 1, asi que no se pudo ver el listado completo. En esa pagina 1 no hay nada de Moondance ni del MRC Centre for Neuropsychiatric Genetics; si hay un 'Research Assistant/Associate (Statistics)' del Centre for Trials Research, ref 459, con cierre 17-09-2026, la MISMA fecha de P-0014: posible confusion de identidad, sin resolver.</t>
         </is>
       </c>
     </row>
@@ -13062,7 +14842,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -13072,7 +14852,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -13106,39 +14886,39 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Sin accion. Se registra para dejar constancia de que el IoPPN si anuncia puestos de investigacion de via clinica, un carril que merece vigilancia por su titulo de medicina a partir de mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Sin accion. Se registra para dejar constancia de que el IoPPN si anuncia puestos de investigacion de via clinica, un carril que merece vigilancia por su titulo de medicina a partir de mediados de 2027.</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>https://www.kcl.ac.uk/jobs/154086-clinical-research-associate</t>
@@ -13146,7 +14926,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Rama 3. Visto en la busqueda de vacantes propia de KCL (Tier 1); la vista de listado dio titulo, facultad, ubicacion y cierre, pero no salario. URL reconstruida desde la ruta relativa del listado, no abierta individualmente: enlace provisional.</t>
+          <t>Rama 2, 2026-09-07: plazo 27-08-2026 vencido; no figura ya en las busquedas de jobs.ac.uk. Base = plazo vencido.</t>
         </is>
       </c>
     </row>
@@ -13192,7 +14972,7 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -13202,7 +14982,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -13236,39 +15016,39 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Sin accion mas alla de anotar el patron: el IoPPN mantiene un flujo constante de puestos de clinico-investigador. Revisar desde mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Sin accion mas alla de anotar el patron: el IoPPN mantiene un flujo constante de puestos de clinico-investigador. Revisar desde mediados de 2027.</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>https://www.kcl.ac.uk/jobs/155765-clinical-research-fellow</t>
@@ -13276,7 +15056,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Rama 3. Visto en la busqueda de vacantes propia de KCL (Tier 1), 106 vacantes en total. URL reconstruida desde la ruta relativa del listado: enlace provisional. Ningun puesto del SGDP Centre era visible en la primera pagina de resultados.</t>
+          <t>Rama 2, 2026-09-07: plazo 01-09-2026 vencido. OJO: KCL Psychological Medicine tiene ahora un Clinical Research Fellow con cierre 18-09-2026 (DST268) que podria ser su reedicion; se registra como fila nueva y queda por confirmar si es el mismo puesto.</t>
         </is>
       </c>
     </row>
@@ -13403,8 +15183,702 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P-0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Clinical Research Fellow (Psychological Medicine)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Department of Psychological Medicine, IoPPN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Clinical research fellowship (post asalariado)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>53000</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>12</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Titulo de medicina; investigacion clinica en salud mental; probable exigencia de registro GMC en RU</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>(a) Encaja por el lado MD del combo: es un puesto de medico investigador en Psychological Medicine del IoPPN, el entorno britanico mas fuerte en genetica psiquiatrica (SGDP a un pasillo), y ahi su perfil MD+PhD en genetica estadistica de rasgos complejos vale mas que un CV bibliometrico corto. (b) Candidatura tipica: CV, carta, dos referencias y entrevista clinica; trabajo real S, pero el plazo del 18-09-2026 lo hace irrelevante en la practica. (c) Salario publicado 45.943 GBP anuales sin London Weighting (~53.000 EUR al cambio aproximado; la cifra oficial es la libra). (d) Sin problema de visado por nacionalidad UE solo a medias: RU ya no es libre circulacion, haria falta Skilled Worker visa, y un Clinical Research Fellow suele exigir registro GMC, que ella no tiene. (e) NO PUEDE PRESENTARSE: sigue en residencia MIR hasta el 22-05-2027 y su tesis no se defiende hasta feb-2028. El valor de la fila es el canal: KCL IoPPN saca Clinical Research Fellow de forma recurrente (P-0016 cerro el 01-09-2026 y este anuncio aparece con plazo 18-09-2026), asi que conviene volver a mirarlo en 2027.</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>IoPPN es destino de primer nivel en salud mental y el puesto admite a cualquier medico con interes investigador en RU</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>En marzo de 2027 revisar jobs.ac.uk con el filtro de empleador KCL y comprobar si esta convocatoria se ha repetido con plazo compatible con mayo-2027</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DST268/clinical-research-fellow</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Rama 2 (tablones academicos). Leido en la pagina de resultados de jobs.ac.uk (busqueda 'psychiatric genetics', 2026-09-07); no se abrio el anuncio individual, de ahi LIKELY y no VERIFIED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P-0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow in Neurogenetics</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>National Institute on Aging (NIH)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bethesda, Maryland</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Postdoc intramural NIH</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Doctorado (o MD) y experiencia en genetica/genomica; anuncio dice salario acorde a experiencia</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>(a) Es genetica humana computacional en el intramural del NIH, adyacente a su linea 1 (genetica estadistica de rasgos complejos): las cohortes de neurogenetica del NIA trabajan con GWAS y scores poligenicos, que es exactamente lo que ella maneja de forma independiente con PLINK y R. No exige neuroimagen ni electrofisiologia autonomas, que es donde su formacion es solo supervisada. (b) Candidatura NIH intramural: CV, carta de investigacion y tres cartas de referencia, y el proceso es rodante mas que por plazo; esfuerzo real M por las cartas y el research statement. (c) Condiciones no publicadas mas alla de 'commensurate with experience': no se inventa cifra. (d) Requiere patrocinio de visado J-1 o similar, que el NIH tramita de forma rutinaria para postdocs extranjeros: es friccion, no barrera. (e) NO PUEDE PRESENTARSE AHORA: fin de residencia 22-05-2027 y defensa prevista feb-2028; ademas la pagina del anuncio devuelve 403 al fetch automatico y no se pudo leer nombre del laboratorio ni PI, asi que la fila queda UNVERIFIED a proposito. Su valor es marcar el intramural del NIA como canal permanente que hay que abrir a mano en 2027.</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>No se pudo abrir el anuncio; sin datos de numero de plazas ni de perfil buscado</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Abrir a mano en navegador el anuncio 679674 de Science Careers antes de 2026-10-31 para capturar laboratorio, PI y correo de contacto, y guardarlos como gancho para escribir en Q3 2027</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>https://jobs.sciencecareers.org/job/679674/postdoctoral-fellow-in-neurogenetics/</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Rama 2. Aparece en el buscador de Science Careers (query 'statistical genetics', 2026-09-07); la pagina de detalle devuelve HTTP 403 al fetch, un solo intento, no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P-0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow - Statistical Genetics and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Amgen deCODE genetics</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Amgen R&amp;D Postdoctoral Fellows Program</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>no nombrado en el anuncio</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Reykjavik</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Postdoc (empleada a tiempo completo de Amgen)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4 anos (el programa Amgen contrata 3 anos ampliables a un cuarto)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>no publicado (sin fecha de cierre anunciada)</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Doctorado COMPLETADO antes de la fecha de inicio en estadistica, genetica humana, informatica, bioinformatica o matematicas; conocimiento profundo de genetica estadistica, bioestadistica o genomica computacional; publicaciones peer-reviewed y comunicaciones en congresos; Python o R; entornos HPC</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Encaja de lleno con su linea 1 (genetica estadistica de rasgos complejos) y su linea 2 (GWAS/PRS): es un puesto metodologico sobre datos geneticos y biomedicos de escala poblacional en deCODE, justo donde ella trabaja sola con PLINK, R y pipelines GWAS/PRS; el componente de IA/machine learning es lo unico realmente nuevo y es aprendible desde su base. Islandia pertenece al EEE, asi que como ciudadana de la UE no necesita visado ni patrocinio: ventaja concreta frente a las plazas equivalentes de EEUU. Esfuerzo de candidatura medio (CV, carta, research statement en ingles C2 y referencias) por el portal Workday de Amgen; el punto debil real es el CV bibliometrico, porque el anuncio pide explicitamente logro cientifico demostrado con publicaciones peer-reviewed y ella tiene dos manuscritos en revision como primera autora y ninguna publicacion destacada, de modo que presentarse sin al menos uno aceptado seria debil. Salario no publicado. NO PUEDE presentarse a esta edicion: exige el doctorado completado ANTES de la fecha de inicio y su defensa es febrero de 2028 (ETA), ademas de que la residencia MIR no acaba hasta el 22-05-2027. El valor de la fila es el canal: el programa de postdoc de Amgen R&amp;D es recurrente y deCODE saca plazas de genetica estadistica de forma repetida, asi que es un objetivo real para 2028. Sin PI nombrado; la via de contacto util es el portal de Amgen mas un correo al grupo de genetica estadistica de deCODE cuando tenga fecha de defensa cerrada.</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>deCODE es uno de los destinos de referencia mundial en genetica estadistica y el anuncio pide expresamente publicaciones peer-reviewed y logro cientifico demostrado; el programa Amgen recluta a escala global.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>En Q3 2027, con la tesis depositada, mirar el portal careers.amgen.com (busqueda Postdoctoral) para la edicion siguiente y escribir al grupo de genetica estadistica de deCODE presentando su combo MD+PhD y sus pipelines GWAS/PRS.</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>https://jobrxiv.org/job/postdoctoral-fellow-statistical-genetics-and-artificial-intelligence/</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Rama 5 (buzon y novedad), barrido de jobRxiv (SRC-0035) el 2026-09-07. Anuncio leido en jobRxiv (publicado 2026-08-22) y confirmado de forma independiente por researchersjob.com y por la pagina del programa de postdocs de Amgen; no se abrio la ficha del portal Workday de Amgen, de ahi LIKELY y no VERIFIED. CONFLICTO A VIGILAR: la pagina del programa Amgen R&amp;D solo lista Thousand Oaks, San Francisco, Burnaby y Copenhague como sedes de postdocs, no Reykjavik, mientras el anuncio situa la plaza en Amgen deCODE genetics (Reykjavik); no se pudo reconciliar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P-0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Postdoctoral Scholar/Researcher in Statistical Genetics - Young Lab</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>University of California Los Angeles (UCLA)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Young Lab, Human Genetics</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>no nombrado en el anuncio (grupo Young Lab; verosimilmente Alexander S. Young, sin confirmar)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>no publicado en EUR; USD 69.073-82.836 al ano segun el anuncio</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>no publicado; el anuncio aparece marcado como caducado en jobRxiv a 2026-09-07</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>No detallados en el anuncio recuperado; puesto de genetica estadistica en genetica humana</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Es un laboratorio de genetica estadistica de genetica humana en UCLA, exactamente su linea 1 y su linea 2 (metodos de GWAS/PRS), y el tipo de grupo donde su trabajo independiente con PLINK y R vale mas que su lista de publicaciones. La plaza concreta esta CERRADA (anuncio de febrero de 2026 marcado como caducado), asi que HOY NO PUEDE presentarse; ademas, aunque estuviera abierta, no podria: la residencia MIR la ata hasta el 22-05-2027 y su defensa es febrero de 2028 (ETA), y un postdoc estadounidense exige doctorado ya defendido. Implicacion de movilidad: EEUU requiere visado J-1 o H-1B con patrocinio de la universidad, tramite que UCLA hace de rutina pero que alarga meses el calendario. El valor de la fila es el canal y el gancho personal: es un grupo pequeno que contrata por convocatoria abierta en UCLA Recruit y que responde bien al contacto directo. Esfuerzo de candidatura tipico en EEUU: CV, research statement, tres cartas de referencia y a menudo un ejemplo de codigo o de analisis, es decir dias de trabajo real, no horas. Salario publicado en el rango USD 69.073-82.836.</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Postdoc de genetica estadistica en una universidad estadounidense de primer nivel, con candidaturas internacionales y sin restriccion de nacionalidad.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>En Q1 2028, con fecha de defensa fijada, escribir al Young Lab de UCLA (via la pagina del grupo) ofreciendo su combo MD+PhD y su experiencia en GWAS/PRS, y vigilar UCLA Recruit por si reabre la plaza.</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>https://jobrxiv.org/?post_type=job_listing&amp;p=117072</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Rama 5 (buzon y novedad), barrido de jobRxiv (SRC-0035) el 2026-09-07. Solo se leyo la ficha agregada de jobRxiv, que declara el anuncio caducado; no se abrio ninguna pagina de UCLA, por eso UNVERIFIED y por eso el nombre del PI no se afirma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P-0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Clinical Research Associate (farmacogenomica clinica)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>University of Alberta</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Department of Psychiatry, Faculty of Medicine &amp; Dentistry</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>no nombrado en el anuncio</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Edmonton</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Research &amp; Research Support (hibrido)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1 ano inicial</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>no publicado en EUR; CAD 76.135-85.660 al ano segun el anuncio</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gestion de proyectos de farmacogenomica clinica, diseno de estudios, analisis de datos y preparacion de publicaciones</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Puesto de apoyo a la investigacion de 1 ano en farmacogenomica clinica en Canada, con inicio inmediato imposible para ella (residencia hasta el 22-05-2027), visado con patrocinio necesario y contenido alejado de GWAS/PRS: se registra solo para no redescubrirlo y para dejar mapeado el canal del Department of Psychiatry de la Universidad de Alberta.</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Sin datos publicados sobre numero de candidaturas ni sobre restricciones de residencia en Canada.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Ninguna accion antes de 2027; si en Q3 2027 interesa el carril farmacogenomico canadiense, revisar el portal de empleo de la Universidad de Alberta.</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>https://iaejup.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/UOA-Careers/job/3142/</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Rama 5 (buzon y novedad), tablon de empleo de la ISPG (SRC-0030) el 2026-09-07. Los datos proceden del anuncio reproducido en el tablon de la ISPG; no se abrio el portal Oracle de la universidad, por eso UNVERIFIED.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD18"/>
+  <autoFilter ref="A1:AD23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13415,7 +15889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB7"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13429,7 +15903,7 @@
     <col width="52" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="52" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
@@ -13852,7 +16326,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Via transitoria al titulo de especialista en Genetica Medica y en Genetica de Laboratorio - seguimiento normativo</t>
+          <t>Via transitoria al titulo de especialista en Genetica Medica y en Genetica de Laboratorio (dos reales decretos separados, aun sin publicar)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13895,7 +16369,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Aun sin publicar: el real decreto que debe contener la disposicion transitoria no esta en el BOE a 2026-08-23. Las fuentes profesionales anticipan acceso directo para especialistas y no especialistas que acrediten prestacion de servicios durante un numero de anos todavia sin concretar; ni baremo ni plazo publicados.</t>
+          <t>Serian dos titulos y dos reales decretos distintos: Genetica Medica reservada a titulados en Medicina y Genetica de Laboratorio abierta a Medicina, Farmacia, Biologia, Quimica y Veterinaria, ambas de cuatro anos; la disposicion transitoria de acceso excepcional se anuncia siguiendo el modelo de Pediatria y Urgencias, es decir acreditando prestacion de servicios en el area, requisito de anos de ejercicio que ella NO tendra al terminar la residencia en mayo de 2027</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -13905,7 +16379,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Not a vacancy but the gate to the whole of career lane 2, and the brief names it explicitly as something this routine tracks. STATUS AT 2026-08-23, established by opening the Ministry's own pages: there is no open window and none announced with dates, because the real decreto is not yet in the BOE. Documented chronology: the SNS Human Resources Commission approved creating both specialties on 2024-12-05; the Ministry formally announced the approval on 2025-06-13 (Genetica Medica reserved to medical graduates, Genetica de Laboratorio open to Medicine, Pharmacy, Biology, Chemistry and Veterinary, both four years, handled as two separate reales decretos); the prior public consultation on the Genetica de Laboratorio draft was published on 2025-07-01; in March 2026 the Ministry described the RD as ready and pending public hearing. CHECKED DIRECTLY THIS RUN: the official audiencia e informacion publica listing shows NO Genetica project open, so the hearing stage did not open between March and August 2026 and the RD cannot be in the BOE. Why this matters to her specifically: she is an MD, so Genetica Medica would be open to her, and a transitional route would let her hold the genetics title without repeating MIR - the difference between her clinical lane being laboratory medicine only and being clinical genetics. The window, when it opens, will be short (months from entry into force), which is why it is worth a standing BOE alert rather than a weekly check. UNRESOLVED CONFLICT, recorded rather than silently decided: the AEGH page contains text suggesting a real decreto reached the Council of Ministers and the BOE, but gives no date or disposition number, and most likely refers to the RD on Formacion Sanitaria Especializada rather than the Genetica ones.</t>
+          <t>Sigue siendo la fila de mayor consecuencia del carril clinico: si la via transitoria se abre, una MD con residencia de Medicina de Laboratorio y doctorado en genetica estadistica obtiene el titulo de especialista en genetica sin repetir cuatro anos de residencia. ESTADO A 07-09-2026, VERIFICADO HOY Y NEGATIVO: el listado de audiencia e informacion publica del Ministerio de Sanidad tiene un unico proyecto abierto, el real decreto de personas en situacion de electrodependencia (24-07-2026 a 11-09-2026); no hay ningun proyecto de Genetica en tramite de audiencia. Tampoco aparece en el BOE ningun real decreto que establezca los titulos de especialista en Genetica Medica o en Genetica de Laboratorio: la unica norma reciente del ambito sigue siendo el RD 101/2025, de 18 de febrero (BOE-A-2025-3189), que crea Laboratorio Clinico. La tramitacion lleva veinte meses de anuncios sin acto administrativo: diciembre de 2024 aval de la Comision de RRHH del Consejo Interterritorial, junio de 2025 resolucion favorable de la Direccion General de Ordenacion Profesional, 01-07-2025 consulta publica previa (PDF 01.07.25_CPP_PRD_Especialidad_en_Genetica_laboratorio.pdf en sanidad.gob.es/normativa/docs), diciembre de 2025 la directora general dice que saldran a audiencia en breve, febrero-marzo de 2026 el Ministerio lo da por a punto y la AEGH anuncia que veran la luz en julio. Estamos en septiembre de 2026 y no han salido, con lo que la primera convocatoria MIR de estas especialidades en 2027 se da por muy comprometida. Consecuencia practica para ella: aunque el RD se publicara manana, el plazo de solicitud de la via transitoria caeria previsiblemente en 2027-2028 y le exigiria acreditar anos de servicio en genetica que no tendra; el encaje de perfil es total pero la elegibilidad real es dudosa y hay que leer la disposicion transitoria palabra por palabra en cuanto se publique el borrador.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -13915,12 +16389,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>No hay convocatoria: sin texto publicado no hay ni baremo ni concurrencia que estimar</t>
+          <t>No hay convocatoria ni criterios publicados: no se puede estimar</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>M</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -13930,34 +16404,34 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Revisar cada semana sanidad.gob.es/normativa/audiencia/home.htm hasta que aparezcan los dos proyectos de real decreto de Genetica; el dia que aparezca el borrador, leer su disposicion transitoria y comprobar si exige anos de ejercicio en genetica y si admite la residencia de Laboratorio Clinico como merito; en paralelo, buscar en el BOE por titulo cada mes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Dar de alta una alerta del BOE con 'Genetica Medica' y 'Genetica de Laboratorio' (ver SUB-0001) y vigilar semanalmente el listado de audiencia publica de Sanidad, que da semanas de margen sobre el BOE y publica ya el texto de la disposicion transitoria. La proxima pasada: intentar la busqueda de legislacion del BOE por titulo con 'Genetica' para cerrar el conflicto de la pagina de la AEGH.</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>https://www.sanidad.gob.es/normativa/audiencia/home.htm</t>
@@ -13965,7 +16439,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Rama 4. Listado oficial de audiencia e informacion publica de Sanidad abierto el 2026-08-23: ningun proyecto de Genetica, solo el de electrodependencia. Nota de prensa del Ministerio de 2025-06-13 (id=6697) y consulta publica previa de 2025-07-01 como respaldo documental.</t>
+          <t>Rama 4, pasada del 2026-09-07. Verificado en Tier 1: listado de audiencia publica del Ministerio de Sanidad (SRC-0055) abierto y leido hoy, con un solo proyecto vivo y ninguno de Genetica. La ausencia en el BOE se comprobo por busqueda acotada al dominio boe.es (el formulario GET de boe.es/buscar/legislacion.php devuelve 'Los valores de busqueda enviados son incorrectos', bloqueo nuevo que conviene anotar): esa parte es LIKELY, no VERIFIED. CONFLICTO AEGH: SIGUE ABIERTO Y NO LO CIERRO. Abri hoy aegh.org y su portada NO contiene ninguna afirmacion de aprobacion en Consejo de Ministros ni de publicacion en BOE; solo un anuncio del Secretario de Estado de que las especialidades podrian ver la luz en julio. Es decir, no he podido reproducir el texto conflictivo ni localizar la pagina exacta que lo contiene. La hipotesis de la pasada anterior sigue en pie y ahora tiene un candidato concreto: el RD 203/2025, de 18 de marzo (BOE-A-2025-5405), que modifica el RD 589/2022 sobre formacion sanitaria especializada, si fue aprobado en Consejo de Ministros y publicado en BOE, y es la norma que la nota de prensa 6637 del Ministerio presenta como aprobada. No hay prueba de que sea el referente del texto de la AEGH, asi que el conflicto queda escrito, no resuelto.</t>
         </is>
       </c>
     </row>
@@ -14348,8 +16822,406 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>J-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Convocatorias de empleo FIMABIS / IBIMA-Plataforma BIONAND (portal RFGI-SSPA)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FIMABIS - Fundacion Publica Andaluza para la Investigacion de Malaga en Biomedicina y Salud (gestora de IBIMA-Plataforma BIONAND)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Investigacion biomedica publica (Sistema Sanitario Publico de Andalucia)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Convocatorias temporales por proyecto (personal tecnico e investigador)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>No publicado en el portal general; cada convocatoria fija categoria y retribucion</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Varia por convocatoria (titulado superior, investigador postdoctoral, tecnico); IBIMA declara perfiles de bioinformatica, bioestadistica y ciencia de datos en salud, y tiene ECAI de Bioinformatica coordinada por Juan Antonio Garcia Ranea y grupos de neurociencia/psiquiatria (Patricia Moreno Peral, Antonia Serrano Criado)</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>(a) Encaje: es su propio ecosistema local. Ana esta destinada en el Hospital Regional Universitario de Malaga hasta el 22-05-2027 y IBIMA es el instituto de investigacion sanitaria de ese hospital, con ECAI de Bioinformatica y grupos de neurociencia/psiquiatria; sus pipelines GWAS/PRS con PLINK y R encajan en los perfiles de bioinformatica/bioestadistica que el instituto declara contratar. El combo MD + doctorado en curso es exactamente lo que valoran los IIS para puestos de investigador con anclaje clinico. (b) Candidatura: cada convocatoria pide CV baremado, titulacion y a veces memoria; el esfuerzo real por convocatoria es de horas, no dias, porque el baremo es administrativo. (c) Condiciones: no hay retribucion publicada en la pagina general; se fija en cada convocatoria. (d) Sin visado ni mudanza: es su ciudad. (e) Gancho: escribir a la ECAI de Bioinformatica (Garcia Ranea) o a un grupo de salud mental ofreciendo genetica estadistica aplicada a cohortes propias del instituto, antes de que salga convocatoria. AVISO DE CALENDARIO: mientras siga en la residencia MIR no puede ocupar un contrato de investigacion a tiempo completo; el uso realista de este canal empieza en la primavera de 2027 y las convocatorias son de plazo corto, asi que el valor es vigilarlo, no presentarse hoy.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Convocatorias locales de un IIS andaluz con baremo administrativo; concurrencia menor que la de un portal internacional pero con candidatos locales ya vinculados al instituto</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>En marzo de 2027 revisar semanalmente el portal RFGI (tipo FIMAB_EM) y, antes, en Q4 2026, escribir a la ECAI de Bioinformatica de IBIMA (Juan Antonio Garcia Ranea) presentandose como MD residente de Laboratorio Clinico con pipelines GWAS/PRS propios y disponibilidad a partir de junio de 2027</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>https://www.rfgi.es/ConvocatoriasPropiasFIMABIS/es/Convocatorias/DesgloseEstadoTipoConvocatoria/FIMAB_EM</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Rama 3 (instituciones). Ruta descubierta abriendo https://ibima.eu/es/trabaja-con-nosotros/, que enlaza este portal como su unica via de ofertas publicas; portal abierto y confirmado vivo el 2026-09-07. Las convocatorias individuales no se listan sin navegar por el portal (contenido cargado tras la pagina indice), asi que no se ha verificado ninguna convocatoria concreta. La pagina de transparencia de la Junta de Andalucia para FIMABIS devuelve HTTP 403 al fetch automatico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>J-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Seleccion temporal de FEA del SERGAS (listas de contratacion, Galicia)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Servizo Galego de Saude (SERGAS) - Conselleria de Sanidade, Xunta de Galicia</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sistema publico de salud (SNS, Galicia)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Santiago de Compostela (sede); plazas en las siete areas sanitarias gallegas</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Nombramiento estatutario temporal por lista de seleccion temporal; via paralela y permanente a la OPE</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>No publicado en la pagina; retribucion de FEA segun tablas del SERGAS</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Titulo de especialista de la categoria correspondiente; el catalogo del SERGAS sigue usando FEA Analisis Clinicos/Bioquimica Clinica y no recoge todavia ni Laboratorio Clinico ni Genetica; ademas de las listas generales hay convocatorias puntuales por area sanitaria resueltas por meritos, entrevista o prueba teorico-practica</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Encaja porque es exactamente el carril clinico espanol de primera clase: nombramiento estatutario de FEA en la especialidad de laboratorio que ella tendra el 22-05-2027, sin exigir doctorado defendido (su defensa es febrero de 2028) y sin visado ni mudanza fuera de la UE. Galicia amplia el mapa mas alla de Andalucia, Madrid, Cataluna, Valencia y Murcia y funciona con dos mecanismos: listas generales de seleccion temporal, cuyo plazo ordinario de inscripcion es del 1 de marzo al 30 de abril de cada ano segun la pagina general de contratacion temporal de la Xunta (Tier 2, LIKELY, no confirmado en la propia pagina del SERGAS), y convocatorias sueltas por area sanitaria publicadas de forma continua (verificadas hoy: Embriologo/a RHA con 6 plazas del 31-08-2026, FEA Radiodiagnostico-Neurorradioloxia del 21-08-2026, FEA Cirugia General del 10-08-2026). El esfuerzo real es documental, no competitivo: inscripcion telematica, autobaremo y acreditacion de meritos; no piden carta de motivacion ni charla. NO puede inscribirse ahora: hasta el 22-05-2027 no tiene titulo de especialista, asi que su ventana util es el plazo de marzo-abril de 2028, o antes una convocatoria puntual de area que admita nombramiento inmediato posterior a esa fecha. Riesgo documentado: al no existir aun la categoria Laboratorio Clinico en el catalogo gallego, habra que comprobar que el titulo del RD 101/2025 se admite en la categoria de Analisis Clinicos/Bioquimica Clinica.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Lista abierta a cualquier especialista del Estado, pero el baremo premia servicios prestados en el SERGAS y el conocimiento de gallego, lo que la deja por debajo de las candidatas locales en la parte de meritos</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>En marzo de 2027 abrir sergas.gal/Recursos-Humanos/Emprego-publico-Seleccion-temporal y confirmar en la propia resolucion el plazo anual de inscripcion en listas; preparar la documentacion en abril de 2027 e inscribirse en el plazo de marzo-abril de 2028, ya con el titulo</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>https://www.sergas.gal/Recursos-Humanos/Emprego-publico-Seleccion-temporal?idioma=es</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Rama 4 (mas alla de la academia), carril 2 sistema publico. Pagina Tier 1 abierta y leida el 2026-09-07 tras redireccion 301 de sergas.es a sergas.gal. La ventana anual 1-marzo/30-abril procede de la pagina general de contratacion temporal de la Xunta (Tier 2) y queda marcada como LIKELY dentro de la fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>J-0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bolsa de trabajo temporal de Osakidetza - categoria Laboratorio Clinico (sustituye a Analisis Clinicos y Bioquimica Clinica)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Osakidetza - Servicio Vasco de Salud</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sistema publico de salud (SNS, Pais Vasco)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Vitoria-Gasteiz (sede); plazas en las OSI del Pais Vasco</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bolsa de contratacion temporal (lista de contratacion de personal estatutario)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>-41</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>La Resolucion 1060/2026 abrio el plazo de inscripcion el 06-07-2026 y lo cerro el 27-07-2026; la lista nueva de Laboratorio Clinico sustituye expresamente a las de Analisis Clinicos y Bioquimica Clinica; inscripcion por el area privada de lanpoltsa.osakidetza.eus; Osakidetza declara que la bolsa queda permanentemente abierta a nuevas altas cuando se preve agotamiento de listas; AMBIGUEDAD NO RESUELTA: el rotulo leido es FEM-Tecnico/a de Laboratorio Clinico y no he podido determinar si la categoria es de facultativo especialista o de tecnico de formacion profesional</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Interesa por dos motivos. Primero, es el unico servicio autonomico de los ya mapeados que ha adoptado la denominacion LABORATORIO CLINICO del RD 101/2025 (BOE 19-02-2025), justo el titulo que ella tendra el 22-05-2027, mientras Madrid, Valencia y Murcia siguen con Analisis Clinicos: confirma que el cambio de nomenclatura ya esta bajando a las CCAA y marca a Osakidetza como el canal donde su titulo encajara sin traduccion. Segundo, es un mecanismo de bolsa, no una oposicion, con esfuerzo documental bajo y sin visado. La razon de que el Fit sea 3 y no 4 es una condicion sin resolver, no la competencia: la categoria aparece rotulada como FEM-Tecnico/a de Laboratorio Clinico y no he podido confirmar si es la lista de facultativos especialistas (encaje pleno) o la de tecnicos de laboratorio de FP (encaje nulo). No puede presentarse en ningun caso a esta edicion: el plazo cerro el 27-07-2026 y ademas hasta el 22-05-2027 no tendra el titulo. Sin salario publicado en la pagina. Contacto util ya identificado: 2021lp-lc@osakidetza.eus, indicando en el asunto ACTUALIZACION y la categoria.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>No se publica numero de inscritas ni de nombramientos por categoria</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Antes de junio de 2027 escribir a 2021lp-lc@osakidetza.eus preguntando (a) si la lista de Laboratorio Clinico es de facultativo especialista y (b) cuando se abre el proximo plazo de alta, dado que la bolsa se declara permanentemente abierta; revisar la pagina de contratacion temporal cada trimestre a partir de enero de 2027</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>https://www.osakidetza.euskadi.eus/contratacion-temporal/webosk00-procon/es/</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Rama 4 (mas alla de la academia), carril 2 sistema publico. Pagina Tier 1 de Osakidetza abierta y leida el 2026-09-07: las fechas 06-07-2026 y 27-07-2026 y la Resolucion 1060/2026 son literales de la pagina. La naturaleza de la categoria (facultativo frente a tecnico) queda expresamente sin verificar.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB7"/>
+  <autoFilter ref="A1:AB10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15473,7 +18345,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -15613,7 +18485,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -16894,7 +19766,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -17417,7 +20289,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -18190,7 +21062,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -19205,7 +22077,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -27647,12 +30519,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
@@ -28234,8 +31106,112 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SUB-0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EU Funding and Tenders Portal - busqueda guardada con aviso por correo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-search</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aviso por correo cuando cambia el estado de los topics vigilados (Forthcoming a Open) y cuando aparecen los topics del programa marco sucesor de Horizonte Europa.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>El portal es una aplicacion JavaScript: ni la pagina ni su API de busqueda son accesibles a un agente (api.tech.ec.europa.eu devuelve HTTP 405 a una peticion GET). La suscripcion es la unica forma de que la informacion llegue sin que ella entre a mano cada mes, y el topic que de verdad le importa, la MSCA-PF de 2028 bajo un programa marco que todavia no existe, se anunciara aqui antes que en ningun otro sitio.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Requiere cuenta EU Login. Guardar la busqueda de topics con el texto MSCA y los estados Forthcoming y Open, y activar la notificacion por correo. Propuesta por la rama 1 en la pasada 2026-09-07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SUB-0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>jobs.ac.uk - alerta por correo de busqueda guardada</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/jobs-by-email</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Correo con los anuncios nuevos que casan con palabras clave guardadas (statistical genetics, psychiatric genetics, polygenic, GWAS, genetic epidemiology)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Es el tablon que mejor responde al fetch automatico y el unico que en esta pasada dio resultados utiles; el volumen semanal en sus temas es de 3-9 anuncios, manejable por correo, y adelanta los plazos que la rutina se pierde entre lunes.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Rama 2. El filtro por empleador de jobs.ac.uk (/search/employer/&lt;slug&gt;/jobs) devuelve HTTP 500 al fetch automatico, de ahi que la alerta por palabras clave sea el sustituto.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J11"/>
+  <autoFilter ref="A1:J13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-445</v>
+        <v>-446</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-128</v>
+        <v>-129</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-199</v>
+        <v>-200</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>

--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -22,18 +22,18 @@
     <sheet name="readme" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$172</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -731,15 +731,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-12</v>
+        <v>8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>715</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -752,7 +752,11 @@
           <t>M</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Reloj vivo a 8 dias: la inscripcion anticipada cierra el 15-sep-2026 a las 17:00 ET. Hacerse socia trainee de ASHG antes de inscribirse baja la cuota casi a la mitad; despues del 15-sep solo queda tarifa late/onsite.</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>https://ashgmeeting.ashg.org/</t>
@@ -804,7 +808,11 @@
           <t>M</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>La inscripcion sigue ABIERTA a 22 dias del congreso: si va, registrarse esta semana en https://ispg.societyconference.com/v2/ y escribir a info@ispg.net pidiendo la cuota Student/Post-Doc y si hay opcion virtual, porque el portal no muestra tarifas.</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>https://ispg.net/wcpg-2026/</t>
@@ -864,12 +872,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T-0002</t>
+          <t>T-0007</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Genetic Epidemiology (short course)</t>
+          <t>Advanced Mendelian Randomization</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -879,20 +887,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Short course</t>
+          <t>Curso corto avanzado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>730</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -902,13 +910,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>XS</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>No reservar todavia: hacer primero el MR introductorio (T-0003) en marzo-2027 y buscar la edicion de finales de 2027 cuando Bristol publique el programa 2027-28</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/advanced-mr/</t>
         </is>
       </c>
     </row>
@@ -920,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T-0001</t>
+          <t>T-0002</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>International Statistical Genetics Workshop (el 'Boulder Workshop')</t>
+          <t>Genetic Epidemiology (short course)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -935,25 +947,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Workshop</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+          <t>Short course</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>128</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Las reservas del programa 2026-27 abren el 2026-10-07 a mediodia (hora britanica), con registro previo de interes desde el 2026-09-23: poner alarma, porque estos cursos se llenan</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://www.colorado.edu/ibg/workshop-2027</t>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
         </is>
       </c>
     </row>
@@ -965,12 +992,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T-0003</t>
+          <t>T-0001</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mendelian Randomization (short course)</t>
+          <t>International Statistical Genetics Workshop (el 'Boulder Workshop')</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -980,36 +1007,33 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Short course</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2027-03-01</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>175</v>
-      </c>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>550</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>XS</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Escribir a IBGworkshop@colorado.edu preguntando por la cuota 2027, la fecha de apertura de inscripcion, el plazo y si habra opcion virtual; vigilar la pagina cada semana porque la inscripcion suele abrirse sin previo aviso</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
+          <t>https://www.colorado.edu/ibg/workshop-2027</t>
         </is>
       </c>
     </row>
@@ -1021,36 +1045,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L-0001</t>
+          <t>T-0003</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Complex Trait Genetics (CTG) Lab</t>
+          <t>Mendelian Randomization (short course)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Groups</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Short course</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>175</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Reservar en cuanto abran las reservas el 2026-10-07 a mediodia; es la puerta de entrada obligatoria al curso avanzado de MR</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://cncr.nl/ctg/</t>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
         </is>
       </c>
     </row>
@@ -1062,25 +1105,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L-0002</t>
+          <t>T-0009</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Psychiatric Genetics Group</t>
+          <t>Molecular Epidemiology</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Groups</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Curso corto</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1088,10 +1135,14 @@
           <t>S</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Solo si sobra presupuesto y tiempo: va justo despues del MR introductorio (15-19 mar 2027), semana siguiente</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.qimrb.edu.au/researchers-and-labs/psychiatric-genetics</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
         </is>
       </c>
     </row>
@@ -1103,25 +1154,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L-0004</t>
+          <t>T-0008</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Generation R - genetica del sueno infantil</t>
+          <t>Machine Learning with Omics Data</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Groups</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Curso corto</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1129,10 +1184,14 @@
           <t>S</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Abrir la ficha del curso cuando se publiquen cuota y programa, y decidir junto con el resto de la oferta de Bristol de 2027</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://acamh.onlinelibrary.wiley.com/doi/10.1111/jcpp.13899</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1203,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L-0006</t>
+          <t>L-0001</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SGDP Centre / Statistical Genetics Unit</t>
+          <t>Complex Trait Genetics (CTG) Lab</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1173,12 +1232,429 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
+          <t>https://cncr.nl/ctg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>L-0002</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Psychiatric Genetics Group</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Abrir el portal qimrberghofer.turborecruit.com.au y filtrar por genetica/postdoc; si no hay nada, mandar el correo en frio de todas formas (es la pista mas calida del conjunto y no depende de que haya anuncio).</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://www.qimrb.edu.au/researchers-and-labs/psychiatric-genetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>L-0004</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Generation R - genetica del sueno infantil</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Confirmar en Tier 1 el cargo y la sede actual de Kocevska (pagina de personal del NIN, grupo Van Someren, y buscador de investigadores de Erasmus MC) e identificar al PI senior de la linea de sueno infantil antes de escribir.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://acamh.onlinelibrary.wiley.com/doi/10.1111/jcpp.13899</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>L-0006</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SGDP Centre / Statistical Genetics Unit</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Escribir a Cathryn Lewis (Statistical Genetics Unit) planteando co-patrocinio de beca postdoc, dado que la unidad no publica vacantes propias.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>https://www.kcl.ac.uk/research/sgu</t>
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>L-0012</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Grupo de genetica estadistica psiquiatrica de Wouter Peyrot (proyecto ERC PersonalRiskProfile)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Escribir correo en frio a Peyrot antes de fin de 2026 presentando disponibilidad desde mediados de 2027 y pidiendo una videollamada de 20 minutos; en paralelo, localizar su direccion institucional exacta en pure.amsterdamumc.nl y revisar la bolsa de empleo de Amsterdam UMC por si sale la plaza del ERC.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://www.amsterdamumc.org/en/research/institutes/amsterdam-public-health/news/wouter-peyrot-awarded-erc-starting-grant-for-personalized-genetic-risk-profiles-in-psychiatry-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>L-0013</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Grupo de Kelli Lehto, Instituto de Genomica (proyecto ERC AT-TENSION)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Correo en frio a Kelli Lehto con CV y las dos fechas de disponibilidad; preguntar si AT-TENSION prevee contratar en 2027 y ofrecer la vertiente de fenotipado clinico. Confirmar antes su direccion institucional en la ficha de personal de ut.ee.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://ut.ee/en/news/erc-grant-helps-explore-innovative-approaches-improve-diagnosis-adhd-adults</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>L-0014</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Grupo de Psiquiatria Infantil y Genetica del Comportamiento de Christel Middeldorp</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Preparar un correo en frio con una propuesta de una pagina sobre genetica del sueno en primera infancia dentro de sus cohortes; antes, verificar en pure.amsterdamumc.nl su financiacion vigente y sus publicaciones de 2025-2026 sobre sueno.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://www.amsterdamumc.org/en/research/researchers/christel-middeldorp.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>E-0011</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BGA 2028 - 58th Annual Meeting of the Behavior Genetics Association</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Revisar la pagina de BGA Future Meetings en enero-2028 para fechas exactas y plazo de resumenes; apuntarla ya como objetivo post-tesis.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567675</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>E-0014</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>XXXV Reunion Anual de la Sociedad Espanola de Sueno (SES 2027)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Consultar congreso-ses.com/ses2027 en octubre-2026 para fechas exactas de marzo-2027, plazo de comunicaciones y cuota de residente; si cae en marzo, hay que pedir dias en el hospital con antelacion.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://congreso-ses.com/ses2027/bienvenida</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>E-0015</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Jornada AEGH 2027 (Asociacion Espanola de Genetica Humana)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Mirar aegh.org/congresos-y-jornadas-aegh a finales de 2026 para ver que sede gano la candidatura y que fechas tiene la Jornada 2027.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://aegh.org/congresos-y-jornadas-aegh/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L14"/>
+  <autoFilter ref="A1:L23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1189,7 +1665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2325,7 +2801,11 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -2373,7 +2853,11 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -2421,7 +2905,11 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -2469,7 +2957,11 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>afinada tras definir el perfil, 2026-08-23</t>
@@ -2571,7 +3063,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2621,7 +3113,11 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>añadida tras definir el perfil, 2026-08-23</t>
@@ -4751,7 +5247,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5219,7 +5715,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5271,7 +5767,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5323,7 +5819,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5375,7 +5871,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5427,7 +5923,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5479,7 +5975,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -6736,8 +7232,840 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SRC-0107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ERC - listas oficiales de investigadores principales financiados (Starting, Consolidator y Advanced Grants)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://erc.europa.eu/apply-grant/starting-grant</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>PDF anual con nombre del PI, institucion de acogida, pais, acronimo, titulo del proyecto y panel de TODOS los proyectos financiados. Un PI con ERC recien concedido va a contratar doctorandos y postdocs en los doce a dieciocho meses siguientes y normalmente aun no lo ha anunciado en ningun portal de empleo, asi que es la ventana de competencia mas baja que existe.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Descargar el PDF de resultados del ano (patron de URL erc.europa.eu/system/files/AAAA-MM/erc-AAAA-{stg,cog,adg}-results-*.pdf), extraer el texto y filtrar por las palabras clave genet, genom, polygenic, GWAS, psychiatr, mental health, depress, sleep, biobank, heritab, ADHD, autism. Prestar atencion a los paneles LS2 (genetica y genomica), LS5 (neurociencia) y tambien SH4 (psicologia), donde caen proyectos de genetica del comportamiento.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Trimestral: StG suele publicarse en septiembre, CoG a finales de noviembre y AdG a mitad de ano.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Los PDF del ERC no se dejan leer por el lector automatico de paginas: hay que descargarlos y extraer el texto localmente (descomprimir los flujos del PDF), que es como he sacado a Palamara y a Lehto en esta pasada. La convocatoria StG 2026 deberia publicarse hacia septiembre de 2026: revisarla en la proxima pasada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SRC-0108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ISPG (International Society of Psychiatric Genetics) - junta directiva y comites</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://ispg.net/board-of-directors/</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Nombres y roles de quince personas que dirigen hoy la genetica psiquiatrica mundial, con etiquetas utilisimas para filtrar: representante clinico, representante de ciencia computacional, representantes de carrera temprana y responsable del programa de investigadores noveles. Es un mapa de PIs activos y de con quien hablar segun el perfil.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Revisar la lista completa cada semestre; cruzar los nombres nuevos con los grupos ya fichados en la tabla y perfilar a los que no esten. Priorizar los cargos de Clinical Representative y Early Career Representative, que son los que mejor entienden una candidatura MD que empieza.</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Semestral (la junta rota anualmente).</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>En esta pasada esta unica pagina ha producido cuatro filas (Middeldorp, McIntosh, Huckins y Sanchez-Roige). La pagina no publica afiliaciones: hay que buscar cada nombre aparte. Complementarla en pasadas futuras con las juntas de BGA e IGES, que no me ha dado tiempo a abrir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SRC-0109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BGA - Future Meetings (Behavior Genetics Association)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567675</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Sedes y anyos de las proximas reuniones anuales de la BGA antes de que existan webs de congreso (asi aparecio Tartu 2028)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Leer la lista completa; contrastar con la pagina hermana BGA Current Meeting (module_id=558771), que es donde se publican fechas, plazo de resumenes y becas de la edicion inmediata</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Fuente Tier 1 que no se habia usado antes en esta rama; es la unica que anticipa sedes BGA con dos anyos de margen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SRC-0110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ASHG - Future &amp; Past Annual Meetings</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.ashg.org/meetings/future-past/</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Ciudad y fechas de las reuniones anuales de ASHG hasta 2034 (2027 Nashville, 2028 San Diego, 2029 Boston...)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Leer la tabla de futuras; para plazos de resumenes usar ashg.org/deadlines-events</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Permite planificar viajes caros con anyos de antelacion; los plazos concretos viven en otra pagina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SRC-0111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Congreso SES - webs por edicion (Sociedad Espanola de Sueno)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://congreso-ses.com/ses2027/bienvenida</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Sede, fechas, plazo de comunicaciones y cuotas (con tarifa de residente) de la reunion anual espanola del sueno</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Cambiar el anyo en la ruta: /ses2026/, /ses2027/...; revisar las secciones Comunicaciones y Cuotas de Inscripcion</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Opcion mas barata de su linea 3: sin vuelo ni visado; la web de 2027 ya existe aunque todavia sin fechas exactas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SRC-0112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Bristol Medical School - catalogo de cursos cortos</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Programa anual completo con fechas exactas de Genetic Epidemiology, Mendelian Randomization, Advanced MR, Molecular Epidemiology, Machine Learning with Omics Data y Causal Inference in Epidemiology</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Revisar el listado entero; filtrar por epidemiologia genetica, inferencia causal y datos multiomicos</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Mensual, con revision obligatoria a finales de septiembre y el dia de apertura de reservas</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Es la fuente Tier 1 que resuelve T-0002 y T-0003 de una sola visita. Ojo con las redirecciones: la ruta antigua /medical-school/study/short-courses/ redirige a /medical-school/short-courses-and-cpd/short-courses/. Reservas 2026-27: apertura 2026-10-07 a mediodia, registro de interes desde 2026-09-23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SRC-0113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>EMBL-EBI Training (eventos y cursos online)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.ebi.ac.uk/training/events/</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Cursos gratuitos y de pago sobre puntuaciones poligenicas y el PGS Catalog, GWAS, bioinformatica de datos omicos y programacion</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Filtrar por 'polygenic', 'GWAS', 'statistical genetics', 'Python'</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Localizado un curso online sobre puntuaciones poligenicas y el PGS Catalog que no he llegado a abrir; pendiente de verificar formato, coste y si es autoformativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SRC-0114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Summer Schools in Europe (agregador)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.summerschoolsineurope.eu/</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Escuelas de verano europeas de genetica estadistica, epidemiologia y ciencia de datos, todas dentro de la UE y por tanto sin visado</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Buscar 'genetics', 'genomics', 'epidemiology', 'risk prediction', 'bioinformatics'</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Trimestral, intensificando entre enero y abril, que es cuando abren los plazos</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Fuente Tier 2 nueva en esta pasada: por aqui aparecio la escuela de verano de Tartu, que no habia salido en ninguna busqueda anterior. Util justo para la ventana posterior a mayo-2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SRC-0115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>AEGH - Asociacion Espanola de Genetica Humana, seccion de cursos</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://aegh.org/cursos-3/</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Formacion acreditada en genetica clinica, diagnostico genetico y bioinformatica en Espana, conectada con su via de Medicina de Laboratorio</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Cursos cortos y de formacion continuada; descartar masteres y titulos propios, que estan fuera de alcance</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Via espanola sin coste de viaje y compatible con la residencia. En la revision de hoy solo se ven cursos introductorios y programas largos (masteres, expertos universitarios) fuera de alcance; ninguno con fechas 2027 publicadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SRC-0116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PGC Video Textbook (Psychiatric Genomics Consortium)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://pgcanalytics.github.io/pgcvideotextbook/welcome.html</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Formacion autoformativa y gratuita en genetica psiquiatrica: control de calidad, GWAS, puntuaciones poligenicas y analisis de rutas</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Recurso fijo, no hay convocatoria: revisar solo si anuncian talleres en directo</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>El PGC NO tiene un programa de 'analyst training' con convocatoria y fechas, al contrario de lo que sugeria la pista de la pasada anterior: lo que existe es este video-libro gratuito. Sirve como repaso barato antes del Boulder Workshop, pero no es un curso con plaza ni certificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SRC-0117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Max Planck Institute for Psycholinguistics - pagina de vacantes</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.mpi.nl/career-education/vacancies</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Todas las plazas del MPI Nijmegen, incluido el Departamento de Language &amp; Genetics (grupos de Simon Fisher y Beate St Pourcain): postdocs y doctorados de genomica estadistica y epidemiologia genetica</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Revisar el listado completo; buscar 'Statistical Genomics', 'Genetic Epidemiology', 'Language and Genetics'</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Fuente NUEVA, no usada en pasadas anteriores. Es la Tier 1 que confirma la plaza de L-0011. Aviso: la URL corta www.mpi.nl/page/vacancies da 404; la buena es esta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SRC-0118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>QIMR Berghofer - portal de seleccion TurboRecruit</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://qimrberghofer.turborecruit.com.au</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Las vacantes reales de QIMR Berghofer (la pagina institucional /careers no lista nada, solo redirige aqui): postdocs y research officers, incluido el grupo de genetica psiquiatrica de Sarah Medland</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Filtrar por genetics / postdoctoral / research officer</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Fuente NUEVA. Critica porque L-0002 es la pista mas calida del conjunto y hasta ahora se vigilaba la pagina equivocada. No llegue a abrirla esta semana por presupuesto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SRC-0119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Cardiff University - portal oficial de vacantes</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://cardiffuniweb.eploy.net/vacancies/vacancy-search-results.aspx?culture=en-GB</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Todas las vacantes de Cardiff, incluidas las del MRC Centre for Neuropsychiatric Genetics &amp; Genomics, que en la pagina del propio Centro no se pueden leer de forma automatica</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Buscar genetics / genomics / psychiatry / bioinformatics / research associate</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Fuente NUEVA y necesaria: cardiff.ac.uk/centre-neuropsychiatric-genetics-genomics y su subpagina de vacantes devuelven 403 a acceso automatico. El listado esta paginado (3 paginas) y la paginacion por parametro de URL no funciono, hay que recorrerla a mano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>SRC-0120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Saxena Lab (MGH/Broad) - pagina de oportunidades</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://saxena.mgh.harvard.edu/our-lab/jobs-in-the-lab/</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Plazas del laboratorio de genomica del sueno y circadiana de Richa Saxena</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Pagina unica, leer entera</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Fuente NUEVA. Hoy dice 'Coming Soon!' (sin plazas), pero la pagina esta montada para publicar, asi que un cambio aqui es senal fiable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>SRC-0121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Institute for Behavioral Genetics (CU Boulder) - Positions</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://www.colorado.edu/ibg/join-ibg/positions</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Postdocs y plazas del IBG, incluidos los tres programas de formacion federales (NIMH, NIDA, NIA) y el entorno de Andrew Grotzinger</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Pagina unica, leer entera; atender a si las becas exigen ciudadania/residencia estadounidense</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Quincenal</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Fuente NUEVA. La pagina esta desactualizada (conserva un anuncio con plazo de dic-2024), asi que sirve para detectar programas de financiacion mas que plazas frescas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SRC-0122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Institute of Genomics, University of Tartu - ofertas de empleo</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://genomics.ut.ee/en/content/job-offers</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Plazas del Estonian Genome Centre / Institute of Genomics: grupos de genomica neuropsiquiatrica, epidemiologia genomica y genomica de enfermedad humana</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Seguir el enlace de 'academic job offers' al listado de la Universidad de Tartu</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Quincenal</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Fuente NUEVA. Es un indice, no un listado: las ofertas reales viven en el portal de empleo de la Universidad de Tartu al que apunta.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J107"/>
+  <autoFilter ref="A1:J123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6868,7 +8196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12315,8 +13643,1646 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>L-0012</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Grupo de genetica estadistica psiquiatrica de Wouter Peyrot (proyecto ERC PersonalRiskProfile)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Es el encaje mas limpio de toda la pasada: linea 1 y linea 2 de ella a la vez (genetica estadistica de rasgos complejos aplicada a GWAS/PRS psiquiatricos), tecnicas exactamente las que despliega sola (PLINK, R, algo de Python) y cero exigencia de neuroimagen o electrofisiologia. Culturalmente es el </t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://www.amsterdamumc.org/en/research/institutes/amsterdam-public-health/news/wouter-peyrot-awarded-erc-starting-grant-for-personalized-genetic-risk-profiles-in-psychiatry-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>L-0013</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Grupo de Kelli Lehto, Instituto de Genomica (proyecto ERC AT-TENSION)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Linea 2 pura (GWAS/PRS de salud mental) con la metodologia exacta que ella despliega sola y ni una sola tecnica que no domine. Es un grupo pequeno y en construccion alrededor de un ERC fresco, lo que da dos ventajas raras a la vez: financiacion asegurada varios anos y competencia mas baja que en los</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://ut.ee/en/news/erc-grant-helps-explore-innovative-approaches-improve-diagnosis-adhd-adults</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>L-0014</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Grupo de Psiquiatria Infantil y Genetica del Comportamiento de Christel Middeldorp</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Es el unico grupo de la pasada que toca a la vez las lineas 2 y 3 de ella: genetica de la psicopatologia infantil, con cohortes de desarrollo y modelos de gemelos, que es el sustrato natural donde meter la genetica del sueno en lactantes y ninos pequenos. Las tecnicas son las suyas (GWAS, PRS, longi</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://www.amsterdamumc.org/en/research/researchers/christel-middeldorp.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>L-0015</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Division of Psychiatry / grupo de psiquiatria biologica de Andrew McIntosh (Generation Scotland, UKRI Mental Health Platform)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Linea 2 en su version mas potente: es uno de los grupos que define el GWAS de la depresion a escala mundial, con Generation Scotland detras y el paper de Cell de 2025 como prueba de que ahi se publica en la primera division. Las tecnicas nucleares (GWAS, PRS, metilacion) son las que ella despliega s</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://www.research.ed.ac.uk/en/persons/andrew-mcintosh</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>L-0016</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Grupo de metodos estadisticos genomicos de Pier Francesco Palamara (proyecto ERC ARGgen)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Da de lleno en la linea 1 declarada como preferente (genetica estadistica de rasgos complejos) y con dinero recien concedido, que es justo el momento en que un PI contrata y todavia nadie ha anunciado nada. Ninguna tecnica del grupo cae en su zona supervisada: no hay neuroimagen ni electrofisiologia</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://erc.europa.eu/system/files/2025-12/erc-2025-cog-results_ls.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>L-0017</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Huckins Lab (genomica psiquiatrica computacional)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Linea 2 con una vuelta de tuerca metodologica util: es genetica psiquiatrica computacional donde el PRS clasico se extiende hacia lo multi-omico, asi que ella entra con lo que ya sabe (GWAS/PRS en PLINK y R) y sale sabiendo algo que hoy no sabe. Cero exigencia de tecnicas de su zona supervisada. Es </t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://medicine.yale.edu/profile/laura-huckins/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>L-0018</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Development and Neurodiversity Lab (DIVE), estudios de gemelos BATSS y EASE</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Es el unico grupo que he encontrado esta semana que trabaja exactamente en la linea 3 de ella, genetica del sueno en lactantes, y no en sueno adulto reetiquetado: mide calidad del sueno, capacidad de calmarse y llanto a los 2 y 5 meses en una cohorte de gemelos propia y ya recogida, y ademas usa pun</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://acamh.onlinelibrary.wiley.com/doi/10.1002/jcv2.70023</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>L-0019</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Sanchez-Roige Lab</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Encaje plausible pero condicionado: la metodologia es exactamente la suya (GWAS y PRS a escala de biobanco sobre fenotipos psiquiatricos) y el laboratorio es grande, bien conectado con el PGC y con financiacion NIH declarada, pero el fenotipo central (uso de sustancias e impulsividad) no es ninguna </t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://www.sanchezroigelab.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>L-0001</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Complex Trait Genetics (CTG) Lab</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Last_Updated, Last_Verified, Openings_Known, Source_Note</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://cncr.nl/ctg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>L-0002</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Psychiatric Genetics Group</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Contact_Route, Last_Updated, Last_Verified, Next_Action, Openings_Known, Source_Note</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://www.qimrb.edu.au/researchers-and-labs/psychiatric-genetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>L-0003</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Center for Quantitative Genetics and Genomics (grupo Speed)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Contact_Route, Funding_Status, Last_Updated, Last_Verified, Next_Action, Openings_Known, Source_Note</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/12856703/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>L-0004</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Generation R - genetica del sueno infantil</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Contact_Route, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Openings_Known, PI, Source_Note</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://acamh.onlinelibrary.wiley.com/doi/10.1111/jcpp.13899</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>L-0005</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>MRC Centre for Neuropsychiatric Genetics &amp; Genomics</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Funding_Status, Last_Updated, Last_Verified, Next_Action, Openings_Known, Source_Note</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://www.cardiff.ac.uk/centre-neuropsychiatric-genetics-genomics</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>L-0006</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>SGDP Centre / Statistical Genetics Unit</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action, Openings_Known, PI, Source_Note</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/research/sgu</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>L-0007</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Grotzinger Lab (genomica psiquiatrica multivariante)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Last_Updated, Last_Verified, Next_Action, Openings_Known, Recent_Output, Source_Note, URL</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://www.colorado.edu/ibg/andrew-grotzinger</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>L-0008</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Saxena Lab (genomica del sueno y circadiana)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Contact_Route, Last_Updated, Last_Verified, Next_Action, Openings_Known, Recent_Output, Source_Note</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://saxena.mgh.harvard.edu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>L-0009</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Estonian Genome Centre / grupo de genetica estadistica del Estonian Biobank</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action, Openings_Known, Research_Lines, Source_Note</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://genomics.ut.ee/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>L-0010</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Grupo de Neurogenetica (Depto de Genetica, UB)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://www.ub.edu/genetica/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>L-0011</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Population Genetics of Human Communication (PGHC) - Departamento de Language &amp; Genetics, Max Planck</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Competition_Basis, Competition_Level, Confidence, Contact_Route, Fit_1_5, Fit_Rationale, Funding_Status, Last_Updated, Last_Verified, Name, Next_Action, Openings_Known, PI, Recent_Output, Research_Lines, Source_Note, Techniques, URL</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://www.mpi.nl/career-education/vacancies/vacancy/3-year-postdoctoral-research-scientist-position-statistical-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>E-0011</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>BGA 2028 - 58th Annual Meeting of the Behavior Genetics Association</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Es la sala natural de su linea 1 (genetica estadistica de rasgos complejos) y cae en la UE, sin visado y con vuelo barato via Tallin/Helsinki, en 2028: con la tesis defendida en feb-2028 y sus dos primeros autores ya publicados llegaria en posicion de pedir charla oral en vez de poster. La sede es e</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567675</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>E-0012</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>ASHG 2027 - 77th Annual Meeting of the American Society of Human Genetics</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Es el escaparate mundial de sus lineas 1 y 2: sesiones de genetica estadistica, GWAS y PRS a diario y todo el ecosistema de consorcios psiquiatricos en el mismo pasillo. Octubre-2027 cae cinco meses despues de acabar la residencia (22-may-2027), asi que por primera vez podria ir sin gastar dias de l</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://www.ashg.org/meetings/future-past/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>E-0013</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>World Sleep 2027 - Congress of the World Sleep Society</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Es el foro mas grande de su linea 3 (sueno infantil) y el unico donde su revision en Journal of Sleep Research y el trabajo de genetica del sueno se leen ante la comunidad completa, no ante un subgrupo. Septiembre-2027 esta ya fuera de la residencia, asi que el reloj le juega a favor; pesa en contra</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://worldsleepsociety.org/world-sleep-2027-in-montreal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>E-0014</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>XXXV Reunion Anual de la Sociedad Espanola de Sueno (SES 2027)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Congreso nacional, barato y sin vuelo, con seccion pediatrica donde su revision de sueno en lactantes encaja; el contenido genetico es escaso, por eso no pasa de plausible.</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://congreso-ses.com/ses2027/bienvenida</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>E-0015</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Jornada AEGH 2027 (Asociacion Espanola de Genetica Humana)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Reunion nacional barata que cruza sus dos identidades (residente de Medicina de Laboratorio y genetista) y sirve para red de contactos en Espana, aunque el peso de genetica estadistica de rasgos complejos es bajo.</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://aegh.org/congresos-y-jornadas-aegh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>E-0001</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>World Congress of Psychiatric Genetics (WCPG) 2026</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action, Source_Note, Travel_Grant_Available</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://ispg.net/wcpg-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>E-0002</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>ASHG 2026 Annual Meeting</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Cost_EUR, Deadline, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://ashgmeeting.ashg.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>E-0004</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Behavior Genetics Association (BGA) 2027 Annual Meeting</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, City, Confidence, Country, End_Date, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Source_Note, Start_Date</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://bga.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>E-0007</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Sleep Europe 2026 (28th ESRS Congress)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, City, Confidence, End_Date, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://esrs.eu/sleep-congress/abstracts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>E-0008</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>SLEEP 2027 (APSS Annual Meeting)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, End_Date, Last_Updated, Last_Verified, Next_Action, Source_Note, Start_Date</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://www.sleepmeeting.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>E-0009</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Neuroscience 2026 (SfN Annual Meeting)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>columnas: Abstract_Deadline, Change_Flag, Confidence, Deadline, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://www.sfn.org/meetings/neuroscience-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>T-0007</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Advanced Mendelian Randomization</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Cierra de lleno el hueco de aleatorizacion mendeliana avanzada que ella no domina sola (metodos robustos a pleiotropia, MR multivariante, MR intrafamiliar, multiancestral, sesgo de colisionador), pero exige haber hecho antes el curso introductorio de MR (T-0003, marzo-2027), asi que su edicion reali</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/advanced-mr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>T-0008</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Machine Learning with Omics Data</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Toca su hueco de bioinformatica de datos omicos y ademas cae en junio de 2027, ya fuera de la residencia, pero no es genetica estadistica nuclear y no he podido leer cuota ni programa detallado.</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>T-0009</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Molecular Epidemiology</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Datos omicos y multiomicos con enfoque causal, util para su hueco de bioinformatica omica, pero cae en plena residencia y solapa parcialmente con el curso de epidemiologia genetica que ya tiene fichado.</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>T-0010</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>From Genetic Variants to Risk Prediction (UniTartu Summer School)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escuela de verano en la UE (sin visado), barata y practica, que cubre control de calidad, PCA/UMAP, GWAS, puntuaciones poligenicas y flujos de trabajo reproducibles en R/Python y Unix, es decir refuerza su parte de programacion y buenas practicas; pero gran parte del contenido GWAS/PRS ya lo maneja </t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://ut.ee/en/content/genetic-variants-risk-prediction</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>T-0001</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>International Statistical Genetics Workshop (el 'Boulder Workshop')</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Cost_EUR, End_Date, Fit_Rationale, Funding_Available, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://www.colorado.edu/ibg/workshop-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>T-0002</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Genetic Epidemiology (short course)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, City_or_Online, Confidence, Cost_EUR, End_Date, Funding_Available, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>T-0003</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Mendelian Randomization (short course)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, City_or_Online, Confidence, Cost_EUR, End_Date, Funding_Available, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>T-0004</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Genetic Analysis of Population-based Association Studies</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://coursesandconferences.wellcomeconnectingscience.org/event/genetic-analysis-of-population-based-association-studies-20240902/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>T-0005</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>CAJAL Course: Neurobiology of Sleep</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Cost_EUR, End_Date, Funding_Available, Last_Updated, Last_Verified, Next_Action, Source_Note, Start_Date</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://cajal-training.org/courses/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H133"/>
+  <autoFilter ref="A1:H172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25339,14 +28305,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="52" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
@@ -25364,7 +28330,7 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="52" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="52" customWidth="1" min="25" max="25"/>
     <col width="52" customWidth="1" min="26" max="26"/>
@@ -25545,7 +28511,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Un anuncio 'Postdoc Statistical Genetics' (BRAINSCAPES) cerro el 18-jun-2025 (academictransfer.com/352365); pagina de empleo viva en cncr.nl/ctg/jobs/ - sin anuncio actual, pero la financiacion Gravitation a 10 anos hasta 2030 implica contratacion recurrente</t>
+          <t>Confirmado en cncr.nl/ctg/jobs/ el 2026-09-07: NO hay plaza postdoc ni de doctorado anunciada. La pagina solo ofrece practicas de grado/master (contacto Gerda Berkhout) y avisa de que no quedan plazas de practicas para primavera/verano 2026; remite a los listados VU-CNCR para lo demas. La financiacion Gravitation hasta 2030 sigue implicando contratacion recurrente, asi que el correo en frio sigue siendo la via.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -25595,22 +28561,22 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="W2" t="inlineStr"/>
@@ -25626,7 +28592,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Abri cncr.nl/ctg/ y el anuncio cerrado de AcademicTransfer yo misma</t>
+          <t>Abri yo misma cncr.nl/ctg/jobs/ el 2026-09-07 (Tier 1): sin vacantes cientificas listadas.</t>
         </is>
       </c>
     </row>
@@ -25673,7 +28639,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sin anuncio en la pagina del grupo; grupo grande y multi-subvencion (NHMRC/MRFF/NIH/ARC/ERC) = contratacion frecuente - preguntar directamente</t>
+          <t>Revisado qimrb.edu.au/careers el 2026-09-07 (Tier 1): la pagina institucional NO lista vacantes, deriva todo al portal de seleccion qimrberghofer.turborecruit.com.au. No pude abrir ese portal esta semana, asi que no hay confirmacion ni desmentido de plazas en el grupo de Medland. La via del correo en frio a su antiguo anfitrion sigue siendo la principal.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -25683,7 +28649,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>CALIDO: ya hizo una estancia en QIMR Berghofer (el articulo empirico en Nature Mental Health). Re-contactar a su anfitrion de QIMR / Medland o Lucia Colodro Conde (miembro hispanohablante) - gancho: 'fui visitante aqui, mi articulo basado en QIMR esta en revision en Nature Mental Health, termino el doctorado y busco postdoc'</t>
+          <t>Re-contactar a su anfitrion de QIMR / Sarah Medland o Lucia Colodro Conde (miembro hispanohablante) - gancho: 'fui visitante aqui, mi articulo basado en QIMR esta en revision en Nature Mental Health, termino el doctorado y busco postdoc'. En paralelo vigilar el portal real de vacantes, qimrberghofer.turborecruit.com.au, que es donde QIMR publica de verdad.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -25723,30 +28689,34 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Abrir el portal qimrberghofer.turborecruit.com.au y filtrar por genetica/postdoc; si no hay nada, mandar el correo en frio de todas formas (es la pista mas calida del conjunto y no depende de que haya anuncio).</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>https://www.qimrb.edu.au/researchers-and-labs/psychiatric-genetics</t>
@@ -25754,7 +28724,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Abri la pagina del grupo de QIMR Berghofer yo misma; su estancia previa en QIMR consta en el brief de la candidata</t>
+          <t>Abri qimrb.edu.au/careers yo misma el 2026-09-07; de ahi sale la direccion del portal de seleccion, que no llegue a abrir.</t>
         </is>
       </c>
     </row>
@@ -25801,17 +28771,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Anuncio postdoc ABIERTO: 'Method development in human statistical genetics, focus on disease classification', plazo 1-may-2026, 2 anos, inicio 1-oct-2026 (Nature Careers job 12856703)</t>
+          <t>OJO, DATO CADUCADO CORREGIDO: el plazo del 1-may-2026 YA PASO. El anuncio sigue apareciendo indexado en la pagina oficial de vacantes de Aarhus (international.au.dk, 'Postdoc position in method development in human statistical genetics, with a focus on classification of complex diseases'), con inicio 1-oct-2026 o lo antes posible y duracion de 2 anos, pero NO pude abrir la pagina de vacantes del centro (qgg.au.dk/en/vacancies devuelve 404), asi que no se si sigue viva o es un residuo. Hay que preguntarlo directamente.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Linea postdoc financiada (plaza de 2 anos anunciada); fuente: anuncio Nature Careers</t>
+          <t>DATO NUEVO: la plaza esta financiada principalmente por una ERC Consolidator Grant de Doug Speed para clasificar enfermedades complejas a partir de datos geneticos. Una ERC CoG son 5 anos, asi que aunque esta convocatoria concreta este cerrada es muy probable que haya mas rondas de contratacion en el mismo proyecto.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Correo directo a doug@qgg.au.dk - gancho: su solida genetica estadistica aplicada (PLINK/R) + la mirada clinica/MD sobre heterogeneidad de enfermedad; el anuncio dice genetica previa 'preferible no requerida', asi que su perfil supera el corte comodamente</t>
+          <t>Correo directo a doug@qgg.au.dk - gancho: su genetica estadistica aplicada (PLINK/R) mas la mirada clinica/MD sobre heterogeneidad de enfermedad, que es justo el objeto de su ERC. Como el plazo publicado ya paso, el correo debe preguntar explicitamente si la plaza sigue abierta y si habra nuevas incorporaciones al proyecto ERC en 2027-2028.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -25846,35 +28816,39 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Escribir a doug@qgg.au.dk preguntando por el estado de la plaza y por futuras rondas de la ERC CoG, indicando su disponibilidad (mediados de 2027 / feb-2028).</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>https://www.nature.com/naturecareers/job/12856703/</t>
@@ -25882,7 +28856,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Abri el anuncio de Nature Careers yo misma</t>
+          <t>El anuncio original de Nature Careers se abrio en la pasada anterior. Esta semana: qgg.au.dk/en/vacancies da 404 y la existencia continuada del anuncio en international.au.dk mas el detalle de la ERC Consolidator vienen de resultados de busqueda, no de abrir la pagina - por eso baja a LIKELY.</t>
         </is>
       </c>
     </row>
@@ -25899,7 +28873,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Desana Kocevska (con Generation R / Erasmus MC, epidemiologia de psiquiatria infantil)</t>
+          <t>Desana (Desi) Kocevska - ATENCION, CORRECCION PENDIENTE DE CONFIRMAR: las fuentes secundarias la describen como investigadora POSTDOCTORAL en el Netherlands Institute for Neuroscience (Amsterdam), grupo Sleep &amp; Cognition de Eus van Someren, con afiliacion secundaria a Erasmus MC (Psiquiatria Infantil y del Adolescente). Si es postdoc y no jefa de grupo, NO puede contratar: seria una puerta de entrada y una posible colaboradora, no la PI que ofrece la plaza.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -25929,7 +28903,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>desconocido - sin anuncio; abordar como correo en frio / sondeo de colaboracion</t>
+          <t>desconocido - y ademas la premisa de la fila esta en duda. No hay anuncio. Antes de tratarla como grupo contratante hay que averiguar quien es el PI senior con capacidad de contratar en la linea de sueno infantil (dentro de Generation R / Erasmus MC, o el grupo de Van Someren en el NIN).</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -25939,7 +28913,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Correo en frio a Kocevska - gancho: su review en revision en Journal of Sleep Research + foco en genetica del sueno infantil encajan casi exactamente con este grupo; ofrecer aportar habilidades de genetica estadistica/PRS a los fenotipos de sueno infantil</t>
+          <t>Correo en frio a Kocevska como CONTACTO CIENTIFICO, no como jefa de grupo - gancho: su review en revision en Journal of Sleep Research encaja casi exactamente con el articulo de JCPP 2024 de Kocevska. Pedirle orientacion sobre quien lidera la linea de genetica del sueno pediatrico en Rotterdam/Amsterdam y si ve encaje para una postdoc; ese correo cuesta poco y puede abrir la puerta al PI real.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -25954,7 +28928,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>El solapamiento mas raro del conjunto: su nicho exacto de linea 3 (genetica del sueno infantil) combinado con metodos PRS (linea 1/2). Muy pocos grupos hacen sueno pediatrico + genetica; este es uno. UE/sin visado. Primer correo: citar su review de sueno, nombrar el articulo de JCPP 2024, proponer extender su trabajo de PRS a fenotipos de sueno mas tempranos (infantiles) que conoce de su revision sistematica.</t>
+          <t>El solapamiento cientifico mas raro del conjunto y por eso mantengo el 5: su nicho exacto de linea 3 (genetica del sueno infantil) ejecutado con metodos PRS de linea 1/2, en un entorno UE sin visado y sobre una infraestructura de cohorte de nacimiento enorme (Generation R). Muy pocos grupos en el mundo hacen sueno pediatrico mas genetica y este es uno. PERO el encaje estructural es peor de lo que decia esta ficha: Kocevska parece ser postdoc, no jefa de grupo, asi que el primer acercamiento no debe pedirle una plaza sino conocimiento y contacto - citar su review de sueno, nombrar el articulo de JCPP 2024, proponer extender el trabajo de PRS a fenotipos de sueno mas tempranos (lactantes) que ella conoce de su revision sistematica, y preguntar quien dirige esa linea y si habria via para una postdoc o para co-solicitar una beca.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -25974,35 +28948,39 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Confirmar en Tier 1 el cargo y la sede actual de Kocevska (pagina de personal del NIN, grupo Van Someren, y buscador de investigadores de Erasmus MC) e identificar al PI senior de la linea de sueno infantil antes de escribir.</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>https://acamh.onlinelibrary.wiley.com/doi/10.1111/jcpp.13899</t>
@@ -26010,7 +28988,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Dos fuentes secundarias (articulo JCPP + cobertura de Erasmus/prensa); no abri una homepage del grupo, asi que el titulo/estructura actual exactos de la PI quedan sin confirmar</t>
+          <t>Intentado el 2026-09-07: erasmusmc.nl/en/research/researchers/kocevska-desana devuelve 404 y no aparece ficha propia en nin.nl. Solo fuentes secundarias (ResearchGate la da como postdoc en el NIN / grupo Van Someren, articulos con doble afiliacion). Por eso baja de LIKELY a UNVERIFIED: el dato de 'grupo con PI propia' que daba esta fila NO esta sostenido.</t>
         </is>
       </c>
     </row>
@@ -26057,12 +29035,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>El Centro mantiene una pagina de vacantes viva (cardiff.ac.uk/...neuropsychiatric-genetics-genomics/about/current-vacancies) pero no se confirmo plaza actual en esta busqueda</t>
+          <t>Revisado el 2026-09-07 en el portal oficial de vacantes de Cardiff (cardiffuniweb.eploy.net, el ATS propio de la universidad): NINGUNA plaza de genetica, genomica, psiquiatria o bioinformatica en la primera pagina de resultados (28 vacantes, pagina 1 de 3; la paginacion no me dejo pasar de ahi). Lo unico proximo de lejos es 'Research Assistant/Associate (Statistics)', cierre 17-sep-2026, sin escuela identificada - merece una mirada antes de esa fecha. La pagina de vacantes del propio Centro bloquea el acceso automatico (HTTP 403).</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Financiacion permanente del MRC Centre + multiples subvenciones de proyecto (mayor grupo de genetica psiquiatrica del Reino Unido); fuente: paginas del centro de Cardiff</t>
+          <t>Financiacion permanente del MRC Centre mas multiples subvenciones de proyecto (mayor grupo de genetica psiquiatrica del Reino Unido). DATO NUEVO (fuente secundaria, por confirmar): el 'Brain and Genomics Hub', iniciativa nacional de investigacion en enfermedad mental grave liderada por Cardiff junto con otras universidades, tiene puestos asociados al Centro - es la via mas probable de contratacion a corto plazo.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -26107,30 +29085,34 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mirar la vacante 'Research Assistant/Associate (Statistics)' antes del 17-sep-2026 y averiguar de que escuela es; investigar el Brain and Genomics Hub y quien contrata en el. La pagina de vacantes del Centro hay que abrirla a mano (bloquea bots).</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>https://www.cardiff.ac.uk/centre-neuropsychiatric-genetics-genomics</t>
@@ -26138,7 +29120,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Solo resultados de busqueda (surgieron paginas de personal senior + vacantes); no abri las paginas del todo - direccion/liderazgo de fuentes secundarias</t>
+          <t>El 2026-09-07 abri el portal oficial de vacantes de Cardiff (Tier 1) y confirme que no hay nada de genetica en la pagina 1 de 3. Las paginas del Centro (cardiff.ac.uk/centre-neuropsychiatric-genetics-genomics y su subpagina de vacantes) devuelven 403 a acceso automatico: intentado dos veces, no insisto. Por eso sigue en LIKELY y no sube a VERIFIED.</t>
         </is>
       </c>
     </row>
@@ -26155,7 +29137,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cathryn Lewis (Jefa de Depto / Stat Genetics Unit) y Gerome Breen (genetica psiquiatrica)</t>
+          <t>Cathryn Lewis (lidera la Statistical Genetics Unit; su cargo actual es Head of School of Mental Health &amp; Psychological Sciences - CORREGIDO, esta ficha decia 'Jefa de Depto') y Gerome Breen (genetica psiquiatrica)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -26185,7 +29167,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>desconocido - sin anuncio confirmado; vale la pena vigilar los tablones ISPG/KCL</t>
+          <t>Revisada la pagina de la Statistical Genetics Unit (kcl.ac.uk/research/sgu) el 2026-09-07: NO hay seccion de vacantes ni plazas listadas. La unidad existe y esta activa, pero la contratacion no se anuncia aqui - hay que ir a la bolsa de empleo de KCL y a los tablones ISPG. El correo en frio o el co-patrocinio de beca siguen siendo la via realista.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -26230,35 +29212,39 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Escribir a Cathryn Lewis (Statistical Genetics Unit) planteando co-patrocinio de beca postdoc, dado que la unidad no publica vacantes propias.</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>https://www.kcl.ac.uk/research/sgu</t>
@@ -26266,7 +29252,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Dos fuentes secundarias (perfiles KCL + pagina SGU en resultados); no abri la pagina de la SGU yo misma</t>
+          <t>Abri yo misma kcl.ac.uk/research/sgu el 2026-09-07 (Tier 1): confirma a Lewis al frente de la Statistical Genetics Unit y su cargo de Head of School of Mental Health &amp; Psychological Sciences. Gerome Breen NO aparece en esa pagina concreta - su vinculo al SGDP viene de otras fuentes y queda sin reconfirmar.</t>
         </is>
       </c>
     </row>
@@ -26313,7 +29299,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>desconocido - PI de inicio de carrera, IBG tiene pagina de 'positions'; probablemente creciendo/contratando - preguntar directamente</t>
+          <t>Revisada la pagina de plazas del IBG (colorado.edu/ibg/join-ibg/positions) el 2026-09-07: no hay postdoc especifico del laboratorio de Grotzinger. Lo que hay es una beca postdoctoral del programa de formacion NIMH T32 y la mencion de tres programas de formacion federales (NIMH, NIDA, NIA) que financian postdocs. AVISO IMPORTANTE: las becas T32 del NIH suelen exigir ciudadania o residencia permanente estadounidense - hay que confirmarlo, porque si es asi esa via le queda cerrada y solo le sirve un postdoc pagado con fondos de proyecto. La pagina ademas esta desactualizada (mantiene un anuncio de profesorado con plazo de dic-2024).</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -26328,7 +29314,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Nature (dic 2025): mapeo del paisaje genetico en 14 trastornos psiquiatricos (s41586-025-09820-3)</t>
+          <t>Nature (dic 2025): mapeo del paisaje genetico en 14 trastornos psiquiatricos (s41586-025-09820-3). DATO NUEVO: Grotzinger es el galardonado 2026 del Spence Award de la APS (premio a investigadores jovenes destacados), senal de laboratorio en ascenso y con visibilidad.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -26363,38 +29349,42 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Correo en frio directo a Andrew.Grotzinger@colorado.edu (correo publicado en fuentes del IBG) proponiendo una aplicacion concreta de Genomic SEM; preguntar de paso si sus fondos de proyecto permiten contratar a alguien sin ciudadania estadounidense, porque la via T32 probablemente no.</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://www.colorado.edu/behavioral-genetics/andrew-grotzinger</t>
+          <t>https://www.colorado.edu/ibg/andrew-grotzinger</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Perfil CU Boulder IBG + anuncio del articulo en Nature en resultados; no abri la pagina del laboratorio del todo</t>
+          <t>CORRECCION: la URL que traia esta ficha (colorado.edu/behavioral-genetics/andrew-grotzinger) devuelve 404 el 2026-09-07, igual que colorado.edu/lab/grotzinger. La nueva URL sale de resultados de busqueda y aun no la he abierto. Si abri (Tier 1) la pagina de plazas del IBG, de donde salen los datos de T32 y programas de formacion. Sigue en LIKELY porque no he abierto ninguna pagina propia del laboratorio.</t>
         </is>
       </c>
     </row>
@@ -26441,7 +29431,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>desconocido - revisar la pagina 'team/positions' del Saxena Lab; laboratorio grande y conocido con rotacion</t>
+          <t>Revisada la pagina de oportunidades del propio laboratorio (saxena.mgh.harvard.edu/our-lab/jobs-in-the-lab/) el 2026-09-07: literalmente dice 'Coming Soon!' - NO hay ninguna plaza publicada. La homepage si invita a escribir ('We are looking for talented, enthusiastic researchers to join us'), asi que la via es el correo en frio, no esperar un anuncio. Merece vigilancia semanal porque la pagina esta preparada para publicar.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -26451,12 +29441,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Correo en frio a Saxena o Dashti - gancho: su review en revision en Journal of Sleep Research + interes en genetica del sueno; ofrecer habilidades de genetica estadistica (linea 1) aplicadas al sueno (linea 3)</t>
+          <t>Correo en frio a Richa Saxena o Hassan Dashti (Saxena Lab, 185 Cambridge St, 5th Floor, Boston MA 02114) - gancho: su review en revision en Journal of Sleep Research mas interes en genetica del sueno; ofrecer habilidades de genetica estadistica (linea 1) aplicadas al sueno (linea 3). La propia web pide que la gente interesada escriba, asi que un correo en frio aqui esta explicitamente invitado.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Trabajo de GWAS de score compuesto de salud del sueno (2025); previo GWAS de referencia de duracion habitual del sueno (Nat Commun)</t>
+          <t>GWAS de siesta diurna con 123 regiones del genoma asociadas; trabajo sobre trabajo por turnos de noche, riesgo genetico y diabetes tipo 2 en UK Biobank; sueno y infarto de miocardio; 'Timing of Food Intake'. Cuatro lineas activas: genetica del sueno, genetica circadiana, genetica de complicaciones del embarazo y nexo sueno/circadiano-enfermedad (neurologica y cardiometabolica).</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -26486,35 +29476,39 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vigilar semanalmente la pagina de oportunidades del laboratorio; en paralelo mandar el correo en frio, que la web lo pide expresamente.</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>https://saxena.mgh.harvard.edu/</t>
@@ -26522,7 +29516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Perfiles MGH/HMS/Broad + articulo Nat Commun en resultados; no abri el sitio del laboratorio yo misma</t>
+          <t>Abri yo misma la homepage del Saxena Lab y su pagina de empleo el 2026-09-07 (Tier 1). Sube de LIKELY a VERIFIED.</t>
         </is>
       </c>
     </row>
@@ -26559,7 +29553,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GWAS de rasgos complejos, epidemiologia genetica a escala de biobanco, PRS para traslacion clinica, fenotipado de datos de atencion primaria</t>
+          <t>GWAS de rasgos complejos, epidemiologia genetica a escala de biobanco (&gt;200.000 participantes en el Estonian Biobank), PRS para traslacion clinica, fenotipado de datos de atencion primaria. DATO NUEVO util: el instituto tiene grupos propios de 'Neuropsychiatric genomics' y de 'Bioinformatics and genomic epidemiology' ademas del de genomica de enfermedad humana - el de genomica neuropsiquiatrica es diana directa de su linea 2 y no estaba en esta ficha.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -26569,7 +29563,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>desconocido - revisar la pagina de empleo de la University of Tartu / Institute of Genomics</t>
+          <t>Revisadas genomics.ut.ee/en y su pagina de ofertas de empleo (genomics.ut.ee/en/content/job-offers) el 2026-09-07: la pagina de empleo es un indice que reenvia a los listados de la Universidad de Tartu (ofertas academicas y de gestion por separado), sin postdoc de genetica estadistica visible. Lo unico anunciado en abierto son 'PhD positions 2026'. Sin plaza postdoc confirmada: via de correo en frio.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -26614,35 +29608,39 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Identificar quien lidera el grupo de Neuropsychiatric genomics del Institute of Genomics (es mejor diana para su linea 2 que Magi solo) y escribir a ese PI y a Magi/Lall; revisar tambien el listado academico de empleo de la Universidad de Tartu al que apunta la pagina del instituto.</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>https://genomics.ut.ee/en</t>
@@ -26650,7 +29648,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Articulos de perfil de EstBB 2025 + perfiles de investigadores en resultados; no abri una pagina del grupo</t>
+          <t>Abri yo misma genomics.ut.ee/en y genomics.ut.ee/en/content/job-offers el 2026-09-07 (Tier 1). Sube a VERIFIED en cuanto a institucion, grupos y estado de vacantes. Salvedad honesta: el cargo actual de Reedik Magi NO lo he reconfirmado en una ficha personal - no aparece en la portada.</t>
         </is>
       </c>
     </row>
@@ -26742,35 +29740,39 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Localizar la pagina actual del grupo de Cormand (probablemente via el directorio de la Facultat de Biologia de la UB, el IBUB o CIBERER) y sustituir la URL rota antes de escribirle. No mandar el correo con esta ficha sin verificar.</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
           <t>https://www.ub.edu/genetica/</t>
@@ -26778,7 +29780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Perfiles IBUB/UB + ResearchGate y articulos de GWAS de TDAH en resultados; no abri una pagina actual del grupo</t>
+          <t>CORRECCION: la URL que traia esta ficha (ub.edu/genetica) devuelve HTTP 404 el 2026-09-07, o sea que el enlace publicado esta roto. No me dio el presupuesto para buscar la pagina de sustitucion, asi que la fila baja a UNVERIFIED hasta que alguien abra una pagina Tier 1 del grupo. El resto de la fila sigue apoyandose solo en fuentes secundarias de la pasada anterior.</t>
         </is>
       </c>
     </row>
@@ -26790,12 +29792,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Language &amp; Genetics / genomica estadistica (Max Planck)</t>
+          <t>Population Genetics of Human Communication (PGHC) - Departamento de Language &amp; Genetics, Max Planck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sin confirmar (Max Planck Institute for Psycholinguistics; probablemente el depto de Simon Fisher)</t>
+          <t>Beate St Pourcain (lidera el grupo Population Genetics of Human Communication, dentro del Departamento de Language and Genetics que dirige Simon Fisher) - CORREGIDO: esta ficha decia 'sin confirmar, probablemente el depto de Simon Fisher'</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -26815,103 +29817,1131 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Genomica estadistica de rasgos relacionados con lenguaje/cognicion, genetica de rasgos complejos</t>
+          <t>Genetica de poblaciones y epidemiologia genetica del comportamiento social y la comunicacion humana, con enfasis en el CAMBIO DEL DESARROLLO desde la primera infancia; trayectorias de salud mental, condiciones del neurodesarrollo y fenotipos cerebrales; trabajo sobre cohortes de nacimiento a traves del consorcio EAGLE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>GWAS, metodos cuantitativos de genomica estadistica; R/Python</t>
+          <t>GWAS, epidemiologia genetica del desarrollo, analisis de datos omicos de arquitectura genetica de fenotipos humanos, cohortes longitudinales de nacimiento (EAGLE); R, Python, Perl, shell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ABIERTO: plaza de genomica estadistica, candidaturas revisadas de forma rodante desde el 8-oct-2026 hasta cubrir (segun listado del tablon BGA)</t>
+          <t>CONFIRMADA Y ABIERTA: 'Postdoctoral Research Scientist Position in Statistical Genomics/Genetic Epidemiology', 3 anos, jornada completa (39 h/semana), Departamento de Language and Genetics, grupo PGHC, supervisada por Beate St Pourcain. Candidaturas revisadas de forma rodante desde el 8-oct-2026 hasta cubrir. Inicio previsto 1-dic-2026, NEGOCIABLE. Piden doctorado en genomica estadistica, epidemiologia genetica, bioestadistica o bioinformatica (o estar a punto de obtenerlo) y solvencia computacional en R, Python, Perl o shell. AVISO DE CALENDARIO: el inicio en dic-2026 es incompatible con su disponibilidad (mediados de 2027 como pronto, feb-2028 para puestos que exigen el doctorado terminado); hay que preguntar hasta donde llega ese 'negociable'.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Financiacion nuclear Max Planck (bien dotada); subvencion de proyecto especifica no confirmada</t>
+          <t>Financiacion nuclear Max Planck; la plaza es un contrato de 3 anos ya presupuestado dentro del Departamento de Language and Genetics</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Solicitar la plaza anunciada y/o escribir al PI contratante - gancho: su caja de herramientas de genetica estadistica (PLINK/R, Python asistido por IA) es transferible a rasgos de cognicion/lenguaje</t>
+          <t>Consultas cientificas informales a Beate St Pourcain (beate.stpourcain [at] mpi.nl); consultas generales a la secretaria del Departamento de Language &amp; Genetics (secretariat.genetics [at] mpi.nl). Se puede escribir ANTES del 8-oct-2026 para sondear la fecha de inicio.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No capturado en esta busqueda (la plaza surgio via el tablon de empleo de BGA)</t>
+          <t>Programa del grupo PGHC sobre correlatos geneticos del comportamiento social desde la primera infancia y trayectorias de salud mental, con participacion en el consorcio EAGLE (Early Genetics and Lifecourse Epidemiology)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Sube de 3 a 4 porque al abrir el anuncio el encaje resulta mucho mejor de lo que parecia: no es 'genetica del lenguaje' sin mas, es epidemiologia genetica del desarrollo sobre cohortes de nacimiento (EAGLE), con trayectorias de salud mental y condiciones del neurodesarrollo entre los fenotipos. Eso toca a la vez su linea 1 (genetica estadistica de rasgos complejos, que es literalmente el titulo del puesto), su linea 2 (salud mental/neurodesarrollo) y su linea 3 (fenotipos infantiles medidos desde la primera infancia, el mismo tipo de cohorte que ha revisado para el Journal of Sleep Research). Requisitos tecnicos exactamente los suyos: R, Python, shell, analisis de datos omicos - nada que necesite electrofisiologia ni neuroimagen, que son sus tecnicas supervisadas y no desplegables. Paises Bajos, UE, sin visado, contrato de 3 anos con financiacion nuclear Max Planck: colchon estable, sin depender de que le concedan una beca. El unico problema serio es el calendario: inicio 1-dic-2026 frente a una disponibilidad de mediados de 2027 en el mejor caso, y este puesto exige doctorado (feb-2028). Por eso el primer acercamiento no debe ser una candidatura ciega sino un correo a St Pourcain antes del 8-oct-2026 que diga tres cosas: que su perfil MD mas genetica estadistica encaja con la parte de fenotipado clinico y salud mental del proyecto, que su revision sistematica de genetica del sueno en lactantes le da conocimiento directo de fenotipos de primera infancia en cohortes tipo EAGLE, y la pregunta directa de si el inicio puede desplazarse a 2027-2028 o si convendria mas apuntar a la siguiente plaza del grupo.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Convocatoria abierta rodante y sin plazo de cierre, lo que reparte las candidaturas en el tiempo; el prestigio Max Planck atrae candidatos pero el perfil pedido (genomica estadistica sobre cohortes del desarrollo) es especializado</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Escribir a beate.stpourcain@mpi.nl ANTES del 8-oct-2026 preguntando si la fecha de inicio admite desplazarse a 2027-2028 y presentando el perfil; segun la respuesta, decidir si solicitar esta plaza o esperar a la siguiente.</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>https://www.mpi.nl/career-education/vacancies/vacancy/3-year-postdoctoral-research-scientist-position-statistical-0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Abri yo misma el anuncio completo en mpi.nl el 2026-09-07 (Tier 1). Sube de UNVERIFIED a VERIFIED: la plaza que la pasada anterior solo vio en el tablon BGA existe, es real, y el PI NO es Simon Fisher sino Beate St Pourcain dentro de su departamento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L-0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Grupo de genetica estadistica psiquiatrica de Wouter Peyrot (proyecto ERC PersonalRiskProfile)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wouter Peyrot</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Amsterdam UMC, Departamento de Psiquiatria (con doble afiliacion al Departamento de Complex Trait Genetics de la VU Amsterdam)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Paises Bajos</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Genetica estadistica de trastornos psiquiatricos: analisis cross-disorder, prediccion poligenica (PRS, DDx-PRS), integracion de variantes comunes y raras con historia familiar y patrones cross-ancestry, e impacto del emparejamiento selectivo y la seleccion natural. Objetivo declarado del ERC: identificar personas con riesgo elevado de enfermedad mental grave para prevencion personalizada.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Pipelines de genetica estadistica sobre biobancos y datos del PGC; desarrollo de metodos (R, Python, linea de comandos); PRS multi-rasgo. No exige neuroimagen ni electrofisiologia.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Ninguna plaza concreta anunciada en la pagina institucional; el ERC Starting Grant de 1,5 M EUR implica contrataciones de doctorandos y postdocs en el arranque del proyecto. Sin verificar: consultar la bolsa de empleo de Amsterdam UMC.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ERC Starting Grant de 1,5 millones de euros para el proyecto PersonalRiskProfile, segun la nota oficial de Amsterdam UMC (amsterdamumc.org, Amsterdam Public Health) leida el 2026-09-07. Colchon de varios anos.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Correo en frio directo a Wouter Peyrot (buscar la direccion en su ficha de Amsterdam UMC o en pure.amsterdamumc.nl; no la he verificado, no la inventes). Gancho: es psiquiatra con formacion en matematicas que hace genetica estadistica, exactamente el perfil hibrido de ella; presentarse como MD con residencia de Medicina de Laboratorio y tesis en genetica estadistica de rasgos complejos, mencionar el manuscrito en revision en Nature Mental Health del proyecto QIMR y ofrecerse para la parte de PRS multi-trastorno de PersonalRiskProfile. Ruta calida alternativa: Danielle Posthuma (L-0001) comparte departamento en la VU.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>DDx-PRS (distinguir trastornos psiquiatricos con puntuaciones poligenicas, preprint en medRxiv y publicacion posterior); trabajo continuado en el Cross-Disorder Working Group del PGC, del que es co-chair en 2026.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Es el encaje mas limpio de toda la pasada: linea 1 y linea 2 de ella a la vez (genetica estadistica de rasgos complejos aplicada a GWAS/PRS psiquiatricos), tecnicas exactamente las que despliega sola (PLINK, R, algo de Python) y cero exigencia de neuroimagen o electrofisiologia. Culturalmente es el mejor espejo posible: Peyrot es medico psiquiatra que hizo el salto a la genetica estadistica, asi que entiende de primera mano el itinerario MD que quiere hacer ella y no lo leera como una carrera rara. El colchon de financiacion es fresco (ERC StG recien concedido), lo que significa plantilla por construir y no una plantilla llena. Ademas es co-chair 2026 del Cross-Disorder del PGC, o sea puerta de entrada a la red donde se hacen los papers que ella quiere firmar. Movilidad libre por ciudadania UE. El primer acercamiento debe decir tres cosas: (1) soy MD y termino residencia el 22-may-2027, con doctorado previsto para feb-2028, asi que puedo entrar antes como investigadora predoctoral o incorporarme ya doctorada segun lo que necesite el proyecto; (2) manejo pipelines GWAS/PRS de forma independiente y traigo un empirico de primera autora en revision en Nature Mental Health del proyecto australiano; (3) propuesta concreta, no generica: la capa clinica de PersonalRiskProfile (fenotipado y valor predictivo real en consulta) es donde una medica aporta lo que un bioinformatico no.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Grupo con ERC recien concedido en un tema de moda (prediccion poligenica en psiquiatria) y en Amsterdam, uno de los tres o cuatro polos mundiales de genetica de rasgos complejos. Atraera candidaturas de toda Europa. Contrapeso real: el perfil MD con residencia de laboratorio es escaso en esa cola de candidatos.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Escribir correo en frio a Peyrot antes de fin de 2026 presentando disponibilidad desde mediados de 2027 y pidiendo una videollamada de 20 minutos; en paralelo, localizar su direccion institucional exacta en pure.amsterdamumc.nl y revisar la bolsa de empleo de Amsterdam UMC por si sale la plaza del ERC.</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://www.amsterdamumc.org/en/research/institutes/amsterdam-public-health/news/wouter-peyrot-awarded-erc-starting-grant-for-personalized-genetic-risk-profiles-in-psychiatry-1</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Tier 1: nota oficial de Amsterdam UMC sobre el ERC Starting Grant, leida el 2026-09-07. Perfiles institucionales complementarios en amsterdamumc.org/en/research/researchers/wouter-peyrot.htm y research.vumc.nl. El encargo de la rama lo senalaba como pendiente de la pasada del 2026-08-24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>L-0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Grupo de Kelli Lehto, Instituto de Genomica (proyecto ERC AT-TENSION)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kelli Lehto</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Institute of Genomics, University of Tartu (Biobanco de Estonia)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Tartu</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Causas geneticas y ambientales de los rasgos de TDAH en adultos, solapamiento genetico con otros trastornos mentales, e interaccion de estres, estilo de vida y pandemia sobre la sintomatologia a lo largo de la edad y el sexo. Desarrollo de una herramienta de cribado que combina autoinforme, historia clinica electronica, datos geneticos y aprendizaje automatico.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>GWAS y puntuaciones poligenicas sobre cinco grandes biobancos (Estonia, Noruega, Paises Bajos, Suecia y Reino Unido); epidemiologia genetica longitudinal; historia clinica electronica vinculada; machine learning. Sin neuroimagen ni electrofisiologia.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>No hay plaza publicada verificada. El ERC Starting Grant es de 2025 y arranca con equipo por formar: es el momento tipico de contratar doctorandos y postdocs.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ERC Starting Grant de 1,5 millones de euros, proyecto AT-TENSION, panel SH4, confirmado en la lista oficial de investigadores principales de las ERC Starting Grants 2025 (erc.europa.eu, erc-2025-stg-results-all-domains.pdf) que he descargado y leido el 2026-09-07, y en la nota de la Universidad de Tartu.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Correo en frio a Kelli Lehto (profesora asociada del Institute of Genomics; direccion en la ficha de personal de ut.ee, no verificada). Gancho: AT-TENSION necesita gente que sepa unir fenotipo clinico y genetica estadistica sobre biobancos, y ella es medica que ya trabaja con pipelines GWAS/PRS. Mencionar explicitamente el multi-biobanco: la experiencia con datos del proyecto QIMR encaja con el trabajo entre cohortes.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Proyecto AT-TENSION (Attention on inattention: dissecting the causal mechanisms of adult ADHD features), concedido en la convocatoria ERC StG 2025 y difundido por la Universidad de Tartu y ERR en 2025.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Linea 2 pura (GWAS/PRS de salud mental) con la metodologia exacta que ella despliega sola y ni una sola tecnica que no domine. Es un grupo pequeno y en construccion alrededor de un ERC fresco, lo que da dos ventajas raras a la vez: financiacion asegurada varios anos y competencia mas baja que en los polos grandes, porque Tartu no es el primer destino que se le ocurre a un candidato de Londres o Amsterdam. Encaje adicional poco obvio: AT-TENSION construye un cribado clinico a partir de historia clinica electronica y datos geneticos, y eso es literalmente el terreno de una especialista en Medicina de Laboratorio; ella puede ofrecer criterio sobre calidad y significado de las variables clinicas, no solo codigo. Ciudadania UE, sin visado. El Biobanco de Estonia esta ya en la tabla via Reedik Magi (L-0009), pero es otro PI, otra linea y otro dinero, y ademas ese solapamiento juega a favor: dos puertas en la misma institucion. El primer acercamiento debe pedir concretamente la parte psiquiatrica-clinica del proyecto (definicion de fenotipos de TDAH adulto a partir de registros sanitarios y validacion del cribado) y declarar las fechas: disponible desde mediados de 2027 sin doctorado terminado, doctorada en feb-2028.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>ERC recien concedido y muy publicitado (Tartu, ERR, EurekAlert), lo que atrae solicitudes; pero Estonia recibe menos candidaturas espontaneas que Amsterdam, Londres o Boston y el grupo es de tamano medio-pequeno.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Correo en frio a Kelli Lehto con CV y las dos fechas de disponibilidad; preguntar si AT-TENSION prevee contratar en 2027 y ofrecer la vertiente de fenotipado clinico. Confirmar antes su direccion institucional en la ficha de personal de ut.ee.</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://ut.ee/en/news/erc-grant-helps-explore-innovative-approaches-improve-diagnosis-adhd-adults</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Tier 1: lista oficial de PIs de las ERC Starting Grants 2025 (https://erc.europa.eu/system/files/2025-09/erc-2025-stg-results-all-domains.pdf) descargada y extraida localmente el 2026-09-07, entrada LEHTO Kelli, University of Tartu, EE, AT-TENSION, panel SH4; mas nota institucional de la Universidad de Tartu. Tier 2 de apoyo: ERR y EurekAlert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>L-0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Grupo de Psiquiatria Infantil y Genetica del Comportamiento de Christel Middeldorp</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Christel Middeldorp</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Amsterdam UMC, catedra de Psiquiatria Infantil y Adolescente y Atencion Psicosocial (institutos Amsterdam Public Health y Amsterdam Reproduction &amp; Development)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Paises Bajos</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Influencias geneticas y familiares sobre las trayectorias de sintomas psiquiatricos en la infancia y la adolescencia; asociaciones de genoma completo en psicopatologia infantil y trastornos de ansiedad; estudios longitudinales y de gemelos; modelos de atencion integrada a familias.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Genetica del comportamiento (modelos de gemelos), GWAS y puntuaciones poligenicas en cohortes de desarrollo, epidemiologia longitudinal. No exige neuroimagen ni electrofisiologia.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>No verificado. Catedra consolidada con doctorandos rotando; conviene preguntar directamente.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>UNKNOWN. Su ficha institucional de Amsterdam UMC no detalla proyectos ni cuantias; no he localizado una fuente Tier 1 de financiacion vigente y no la invento. Verificar en pure.amsterdamumc.nl o preguntandole.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Correo en frio a Christel Middeldorp a traves de su ficha de Amsterdam UMC o de Pure. Gancho doble y muy fuerte: es MD PhD igual que ella (medica que hace genetica del comportamiento) y ademas es la representante clinica de la junta de la ISPG, o sea que evaluar a una medica que quiere entrar en genetica psiquiatrica es exactamente su papel institucional. Proponer la interseccion sueno infantil y psicopatologia del desarrollo, que es el hueco entre su linea 2 y su linea 3.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Publicaciones sobre asociaciones de genoma completo en psicopatologia infantil, ansiedad y salud mental en la adolescencia, incluida la relacion entre caracteristicas del ciclo menstrual y salud mental en la adolescencia temprana.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Es el unico grupo de la pasada que toca a la vez las lineas 2 y 3 de ella: genetica de la psicopatologia infantil, con cohortes de desarrollo y modelos de gemelos, que es el sustrato natural donde meter la genetica del sueno en lactantes y ninos pequenos. Las tecnicas son las suyas (GWAS, PRS, longitudinal) y no hay ninguna barrera de neuroimagen ni electrofisiologia. El encaje cultural es el argumento decisivo: Middeldorp es medica con doctorado que hizo carrera en genetica del comportamiento y ocupa el asiento clinico en la junta de la ISPG; para ella el itinerario MD hacia la genetica estadistica no es una rareza que haya que justificar, es su propia biografia. Amsterdam concentra ademas a Peyrot y a Posthuma (L-0001), asi que una sola visita puede convertirse en tres conversaciones. El primer acercamiento debe llevar una propuesta escrita, no una pregunta abierta: los dos manuscritos en revision (la revision en Journal of Sleep Research y el empirico en Nature Mental Health) como carta de presentacion, y una idea concreta de proyecto sobre determinantes geneticos del sueno en los primeros anos dentro de sus cohortes longitudinales, senalando que ella aporta la mirada clinica y el pipeline GWAS/PRS. Advertencia honesta: la financiacion vigente no esta verificada, asi que hay que preguntar por el colchon antes de invertir mucho.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Catedra visible en un polo competitivo, pero la interseccion sueno infantil y genetica esta menos poblada que la genetica psiquiatrica de adultos, y el perfil medico reduce la cola de competidores comparables. Competition_Basis parcialmente inferido, no medido.</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Preparar un correo en frio con una propuesta de una pagina sobre genetica del sueno en primera infancia dentro de sus cohortes; antes, verificar en pure.amsterdamumc.nl su financiacion vigente y sus publicaciones de 2025-2026 sobre sueno.</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>https://www.amsterdamumc.org/en/research/researchers/christel-middeldorp.htm</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Tier 1: ficha institucional de investigadora de Amsterdam UMC leida el 2026-09-07. Localizada a traves de la junta directiva de la ISPG (ispg.net/board-of-directors), donde figura como Clinical Representative: angulo de comites de sociedades, no usado en la pasada anterior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>L-0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Division of Psychiatry / grupo de psiquiatria biologica de Andrew McIntosh (Generation Scotland, UKRI Mental Health Platform)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Andrew McIntosh</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>University of Edinburgh, School of Neurological and Cardiovascular Sciences; director de la UKRI Mental Health Platform</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Edimburgo</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Causas geneticas y ambientales del trastorno depresivo mayor; mecanismos y consecuencias causales de la depresion; genetica de esquizofrenia y trastorno bipolar; investigacion en cohortes poblacionales.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>GWAS, metilacion del ADN, puntuaciones de riesgo poligenico, epidemiologia genetica en cohortes poblacionales; participacion en ENIGMA (neuroimagen consorciada, pero como una linea entre varias, no como requisito de entrada).</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Su ficha declara que acepta candidaturas de doctorado en riesgo genetico y ambiental de la depresion, heterogeneidad de la enfermedad, patrones longitudinales de inicio y mecanismos de resiliencia psicologica. No verificada ninguna plaza postdoctoral concreta.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Direccion de la UKRI Mental Health Platform (plataforma nacional financiada por UKRI) segun su perfil oficial de la Universidad de Edimburgo, leido el 2026-09-07. Cuantia y fechas no verificadas.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Correo en frio a Andrew McIntosh via su perfil de research.ed.ac.uk. Gancho: es psiquiatra y co-chair del grupo de trabajo de Depresion Mayor del PGC; presentarse como medica que hace GWAS/PRS y preguntar por las vias de entrada a la UKRI Mental Health Platform, mencionando la disponibilidad desde mediados de 2027. Si la respuesta es que solo hay doctorado, no es un no: ella puede entrar antes de defender la tesis solo en puestos que no exijan doctorado.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Estudio de 2025 en Cell que identifica 697 asociaciones e implica tipos celulares y farmacoterapias en la depresion a traves de grupos ancestrales.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Linea 2 en su version mas potente: es uno de los grupos que define el GWAS de la depresion a escala mundial, con Generation Scotland detras y el paper de Cell de 2025 como prueba de que ahi se publica en la primera division. Las tecnicas nucleares (GWAS, PRS, metilacion) son las que ella despliega sola. El descuento respecto de un 5 es honesto y doble: primero, no he verificado ninguna plaza ni cuantia concreta de contratacion, solo la direccion de la plataforma UKRI y la apertura declarada a doctorandos; segundo, parte del grupo trabaja con neuroimagen via ENIGMA, y aunque no parece requisito de entrada, ella no puede desplegar RM sola el dia 1 y conviene decirlo antes que ocultarlo. Encaje cultural bueno: McIntosh es medico psiquiatra, no le sorprendera una candidata MD. Reino Unido no requiere visado dificil pero si patrocinio, hay que senalarlo. El primer acercamiento debe ser breve y concreto: MD con residencia de Medicina de Laboratorio hasta may-2027, tesis en genetica estadistica con defensa prevista feb-2028, pipeline GWAS/PRS propio, dos manuscritos de primera autora en revision, y pregunta directa sobre si la UKRI Mental Health Platform contrata perfiles clinicos-computacionales en 2027.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Grupo de altisima visibilidad (Highly Cited Researcher, paper en Cell 2025, plataforma nacional UKRI) en un pais de destino preferente para candidatos internacionales.</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vigilar la pagina de vacantes de la UKRI Mental Health Platform y de la Universidad de Edimburgo durante el otono de 2026; enviar correo en frio a McIntosh preguntando por perfiles clinico-computacionales y por si el grupo patrocina visado.</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>https://www.research.ed.ac.uk/en/persons/andrew-mcintosh</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Tier 1: perfil oficial de investigador de la Universidad de Edimburgo (research.ed.ac.uk) leido el 2026-09-07. Localizado via la junta directiva de la ISPG, donde figura como vicepresidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>L-0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Grupo de metodos estadisticos genomicos de Pier Francesco Palamara (proyecto ERC ARGgen)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pier Francesco Palamara</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>University of Oxford</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Oxford</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Metodos genealogicos y estadisticos para el analisis genomico a gran escala (proyecto ARGgen): inferencia de grafos de recombinacion ancestral y su uso para el estudio de rasgos complejos en biobancos.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Desarrollo de metodos y software de genetica estadistica, inferencia genealogica, analisis de biobancos a escala; programacion intensiva (C++, Python, R). Fuerte componente metodologico y computacional.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>No verificada ninguna plaza publicada. Un ERC Consolidator concedido en noviembre de 2025 implica contratacion de postdocs y doctorandos durante 2026-2027.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ERC Consolidator Grant 2025, panel LS2, proyecto ARGgen, confirmado en la lista oficial de investigadores principales del dominio LS publicada por el ERC el 28-11-2025 (erc-2025-cog-results_ls.pdf), descargada y leida el 2026-09-07. Cuantia no detallada en esa lista (el techo tipico de un Consolidator son 2 millones de euros); no la afirmo.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Correo en frio al PI en Oxford (direccion en su pagina del Departamento de Estadistica o del Big Data Institute; no verificada, buscarla antes). Gancho: ARGgen es metodologia pura de genetica estadistica de rasgos complejos, que es su linea 1; ofrecer el angulo de aplicacion biomedica y el fenotipado clinico que un grupo de metodos suele tener flojo, y declarar el nivel real de programacion (PLINK y R independientes, Python intermedio) sin inflarlo.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Concesion del ERC Consolidator ARGgen (noviembre de 2025). No he revisado su produccion reciente por limite de presupuesto.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Da de lleno en la linea 1 declarada como preferente (genetica estadistica de rasgos complejos) y con dinero recien concedido, que es justo el momento en que un PI contrata y todavia nadie ha anunciado nada. Ninguna tecnica del grupo cae en su zona supervisada: no hay neuroimagen ni electrofisiologia, todo es estadistica y computacion. El descuento respecto de un 5 tiene una causa concreta y no es la competencia: es un grupo de desarrollo de METODOS, y el nivel de programacion que exige el dia a dia (C++ o Python avanzado para software de inferencia genealogica) esta por encima del PLINK y R independientes mas algo de Python que ella declara. Es un encaje fuerte pero condicionado: entraria como la persona que aplica los metodos a fenotipos biomedicos y aporta criterio clinico, no como la que escribe el motor. El primer acercamiento debe ser explicito en eso para no venderse como lo que no es, y debe preguntar si ARGgen prevee un perfil de aplicacion clinica ademas de los perfiles de metodos. Reino Unido: hace falta patrocinio de visado, senalarlo. Disponibilidad desde mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Oxford mas ERC Consolidator mas genetica estadistica metodologica: atrae candidaturas de matematicos y estadisticos con perfil computacional muy superior al suyo en programacion.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Localizar la pagina oficial del grupo en Oxford (Departamento de Estadistica o Big Data Institute) y su correo; solo entonces decidir si merece un correo en frio o si conviene priorizar los grupos con componente clinico. Guardar como referencia para posibles colaboraciones metodologicas.</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://erc.europa.eu/system/files/2025-12/erc-2025-cog-results_ls.pdf</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Tier 1: lista oficial de PIs de las ERC Consolidator Grants 2025, dominio LS, publicada por el ERC (fecha del documento 28-11-2025), descargada y extraida localmente el 2026-09-07: entrada PALAMARA, Pier Francesco, University of Oxford, UK, ARGgen, panel LS2. La URL apunta al PDF oficial porque aun no he verificado la pagina del grupo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>L-0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Huckins Lab (genomica psiquiatrica computacional)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Laura Huckins</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Yale School of Medicine, Departamento de Psiquiatria</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>New Haven, Connecticut</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Imputacion transcriptomica (prediccion de expresion genica a partir de datos de referencia de eQTL para tests de asociacion con rasgos) y prediccion multi-omica de rasgos psiquiatricos; genetica de los trastornos de la conducta alimentaria (co-preside el grupo de trabajo de Eating Disorders del PGC); susceptibilidad y resiliencia genetica al TEPT segun el tipo de trauma.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Metodologia estadistica sobre datos geneticos y multi-omicos, GWAS y derivados, imputacion transcriptomica; trabajo computacional puro, sin neuroimagen ni electrofisiologia.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>No verificada ninguna plaza concreta en la ficha institucional.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Financiacion declarada en su perfil oficial de Yale: Klarman Family Foundation, National Institute of Mental Health y National Institute of Environmental Health Sciences. Cuantias y fechas no detalladas en esa pagina.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Correo en frio a laura.huckins@yale.edu (direccion publicada en su perfil oficial de Yale). Gancho: es la representante de Ciencia Computacional en la junta de la ISPG y co-chair de un grupo de trabajo del PGC; presentarse como MD con pipeline GWAS/PRS propio y preguntar por vias de incorporacion en 2027-2028, mencionando de entrada que se necesitaria patrocinio de visado J-1 o H-1B.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Trabajo en imputacion transcriptomica y prediccion multi-omica; Theodore Reich Early Career Award (2023); miembro de la Connecticut Academy of Science &amp; Engineering (2023).</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Linea 2 con una vuelta de tuerca metodologica util: es genetica psiquiatrica computacional donde el PRS clasico se extiende hacia lo multi-omico, asi que ella entra con lo que ya sabe (GWAS/PRS en PLINK y R) y sale sabiendo algo que hoy no sabe. Cero exigencia de tecnicas de su zona supervisada. Es ademas una PI joven, premiada como early career en 2023, con financiacion NIMH y NIEHS declarada en su propia pagina de Yale: laboratorio en expansion y no una catedra saturada, lo que suele significar mentoria real. Su posicion en la junta de la ISPG como representante computacional y su co-presidencia en el PGC abren red mas alla del laboratorio. Dos frenos honestos que impiden el 5: hace falta patrocinio de visado para Estados Unidos, y las lineas concretas del laboratorio (conducta alimentaria y TEPT) no son ninguna de las tres preferencias declaradas por ella, aunque el metodo si lo sea. El primer acercamiento debe apoyarse en el metodo, no en el fenotipo: decir que le interesa la extension multi-omica de la prediccion poligenica, adjuntar el empirico de primera autora en revision en Nature Mental Health y preguntar sin rodeos por la disponibilidad de patrocinio de visado, que es la condicion que decide si merece la pena seguir.</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Yale y financiacion NIH atraen candidatos, pero la especialidad concreta (imputacion transcriptomica en trastornos de la conducta alimentaria y TEPT) es un nicho con menos candidatos que la depresion o la esquizofrenia. Estimacion, no medida.</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Correo en frio a laura.huckins@yale.edu en el primer trimestre de 2027 preguntando por incorporaciones postdoctorales para 2027-2028 y por patrocinio de visado; guardar la respuesta sobre visado porque sirve para calibrar toda la rama estadounidense.</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://medicine.yale.edu/profile/laura-huckins/</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Tier 1: perfil oficial de Yale School of Medicine leido el 2026-09-07, incluida la direccion de correo y la lista de financiadores. Localizada via la junta directiva de la ISPG (Computational Science Representative).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>L-0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Development and Neurodiversity Lab (DIVE), estudios de gemelos BATSS y EASE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Terje Falck-Ytter (PI del laboratorio); Charlotte Viktorsson (investigadora postdoctoral que lidera la linea de sueno infantil)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Uppsala University, Departamento de Psicologia (con vinculo al Karolinska Institutet)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Suecia</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Influencias geneticas y ambientales sobre el sueno, la capacidad de calmarse y la duracion del llanto en lactantes de 2 y 5 meses; desarrollo cerebral y conductual temprano y emergencia de condiciones del neurodesarrollo (autismo). Cohorte BATSS (Babytwins Study Sweden): 177 pares de gemelos monocigoticos y 134 dicigoticos seguidos entre los 5 y los 36 meses.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Modelos clasicos de gemelos para descomposicion genetica y ambiental; puntuaciones poligenicas derivadas de GWAS de ritmo circadiano, insomnio, sueno corto y sueno largo; ademas EEG, eye tracking, observacion directa y cuestionarios.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>No verificado.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>UNKNOWN. No he abierto una fuente Tier 1 de financiacion; la web de Wiley donde esta el articulo devolvio 403 en el unico intento y no he consultado la ficha de proyectos de Uppsala. No invento cuantias.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Correo en frio a Charlotte Viktorsson (ficha de personal de uu.se, referencia N19-2904) con copia o mencion a Terje Falck-Ytter. Gancho muy especifico: la revision de primera autora en revision en Journal of Sleep Research es sobre este mismo terreno, asi que el correo puede abrir con una lectura critica de su articulo de 2026 en JCPP Advances y una propuesta de aportar la capa de genetica estadistica (PRS) que el laboratorio usa pero no tiene como nucleo.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Viktorsson y cols., Genetic and environmental influences on sleep quality, ability to settle, and crying duration in 2- and 5-month-old infants: a longitudinal twin study, JCPP Advances, 2026 (doi 10.1002/jcv2.70023; PubMed 41815772). Antes: A comparison of sleep and settle behaviours across twins and singletons at 5 months of age, Infant and Child Development, 2025. La Universidad de Uppsala difundio los resultados sobre llanto y sueno en julio de 2025.</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Es el unico grupo que he encontrado esta semana que trabaja exactamente en la linea 3 de ella, genetica del sueno en lactantes, y no en sueno adulto reetiquetado: mide calidad del sueno, capacidad de calmarse y llanto a los 2 y 5 meses en una cohorte de gemelos propia y ya recogida, y ademas usa puntuaciones poligenicas de rasgos de sueno, que es su tecnica independiente. Para una tesis que termina en esta area, entrar en BATSS significa datos longitudinales de primera infancia listos para analizar, que es justo lo que casi nadie tiene. El motivo para no darle un 5 es de tecnica y de honestidad: el laboratorio es de neurodesarrollo y su instrumental central es EEG y eye tracking, y ella no puede desplegar electrofisiologia sola el dia 1, asi que solo encaja si el puesto se define alrededor del analisis genetico-estadistico de los datos ya recogidos. Tampoco he podido verificar financiacion, asi que hay riesgo de que no haya dinero para contratar. El primer acercamiento debe ser tecnico y concreto: proponer llevar los PRS de sueno de BATSS mas alla de la descomposicion gemelar, ofreciendo su pipeline GWAS/PRS, y preguntar de frente si hay financiacion y si aceptarian una perfil que aporte genetica estadistica y mirada clinica pediatrica en lugar de electrofisiologia.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>No hay plaza publicada ni datos sobre numero de solicitudes; el nicho de sueno en lactantes es pequeno, lo que sugiere competencia baja, pero es una conjetura y la registro como desconocida.</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Abrir a mano la ficha de personal de Charlotte Viktorsson en uu.se y la pagina del laboratorio DIVE para verificar correo y financiacion (la version automatica del articulo en Wiley da 403); despues, correo en frio con propuesta de analisis de PRS de sueno en BATSS. Muy recomendable citar este articulo en la revision del Journal of Sleep Research si aun esta a tiempo.</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://acamh.onlinelibrary.wiley.com/doi/10.1002/jcv2.70023</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Tier 1 parcial: nota de la propia Universidad de Uppsala sobre el estudio de llanto y sueno (uu.se/en/news/2025/2025-07-14-why-your-infant-is-crying) y registro del articulo en PubMed 41815772. El texto completo en Wiley devolvio HTTP 403 en el unico intento permitido, por eso el nivel de confianza es LIKELY y no VERIFIED: quedan por confirmar a mano la lista completa de autores, la financiacion y la afiliacion exacta de cada firmante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>L-0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sanchez-Roige Lab</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sandra Sanchez-Roige</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>University of California San Diego, Departamento de Psiquiatria (vinculada al Institute for Genomic Medicine)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>San Diego, California</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Factores causales de los trastornos psiquiatricos y de fenotipos dimensionales, en especial trastornos por uso de sustancias y rasgos de alta impulsividad; psiquiatria de precision combinando genetica, genomica y bioinformatica medica en humanos y organismos modelo.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>GWAS a gran escala sobre 23andMe, UK Biobank, Million Veteran Program, PGC y el Externalizing Consortium; procesamiento de lenguaje natural aplicado a historia clinica en trastornos por uso de sustancias; metabolomica.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>La web del laboratorio tiene una seccion Join the Team, pero el contenido recuperado no detalla plazas concretas: no puedo afirmar que haya vacante abierta.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Colaboraciones y financiacion declaradas en la web del laboratorio con NIH (NIDA y NIAAA) y 23andMe; sin cuantias ni fechas verificadas.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Correo en frio a sanchezroige@ucsd.edu (direccion publicada en un documento de la consorcio de genetica del NIDA; confirmar en la web del laboratorio antes de escribir). Gancho: la PI es espanola y hace carrera en genetica psiquiatrica en Estados Unidos, asi que conoce de primera mano el paso desde Espana; escribir en ingles pero mencionar la formacion en la Complutense y en Murcia, y preguntar directamente por patrocinio de visado y por si aceptan perfiles clinicos.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Publicaciones recientes sobre envejecimiento metabolomico en condiciones de salud mental, perspectivas de curso vital en genetica psiquiatrica, procesamiento de lenguaje natural en trastornos por uso de sustancias y relacion entre anorexia nerviosa y descuento por demora.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Plausible con reencuadre: plaza de genomica estadistica abierta, financiada, UE/sin visado, pero el foco fenotipico (lenguaje/cognicion) es adyacente a su nucleo mas que psiquiatrico/sueno, asi que necesitaria enmarcar sus metodos como portables. Merece una candidatura dada la convocatoria abierta; menor prioridad que las dianas claramente psiquiatricas/de sueno. Confirmar el PI/depto exacto antes de solicitar.</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Encaje plausible pero condicionado: la metodologia es exactamente la suya (GWAS y PRS a escala de biobanco sobre fenotipos psiquiatricos) y el laboratorio es grande, bien conectado con el PGC y con financiacion NIH declarada, pero el fenotipo central (uso de sustancias e impulsividad) no es ninguna de sus tres lineas preferentes, y ademas hace falta patrocinio de visado para Estados Unidos. Lo registro sobre todo por dos razones practicas: es una PI espanola que ya hizo ese camino y puede dar consejo aunque no haya plaza, y su laboratorio es una puerta al Externalizing Consortium. Merece un correo corto, no una candidatura elaborada.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Convocatoria abierta rodante; el prestigio Max Planck atrae candidatos pero la ventana de revision es amplia</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Laboratorio conocido en genetica de adicciones con financiacion NIH; no hay datos publicos sobre volumen de solicitudes.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>https://www.mpi.nl/</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Unica mencion en tablon de empleo (agregacion de anuncios de BGA); PI/depto y subvencion sin confirmar - no abri el anuncio</t>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Correo breve de contacto en frio pidiendo quince minutos de conversacion sobre como se salta de Espana a la genetica psiquiatrica en Estados Unidos; revisar la pagina Join the Team del laboratorio antes de escribir para ver si hay convocatoria abierta.</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://www.sanchezroigelab.org/</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Tier 1 parcial: pagina principal del laboratorio leida el 2026-09-07 (lineas, colaboraciones y financiadores); la seccion de vacantes no se pudo leer en detalle y la direccion de correo procede de un documento del consorcio de genetica del NIDA, no de la web del laboratorio, por eso la confianza es LIKELY. Localizada via la junta directiva de la ISPG (Early Career Representative).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z12"/>
+  <autoFilter ref="A1:Z20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26922,7 +30952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -26947,9 +30977,9 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="52" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="48" customWidth="1" min="25" max="25"/>
+    <col width="52" customWidth="1" min="25" max="25"/>
     <col width="52" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
@@ -27139,7 +31169,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Si - ISPG Early Career Investigator Program (ECIP) Travel Award (plazo 2026 14-may, ya pasado)</t>
+          <t>SI pero CERRADO: ECIP Travel Awards del Early Career Investigator Program, plazo 14-may-2026 (https://ispg.net/wcpg-2026/)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -27174,30 +31204,34 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>La inscripcion sigue ABIERTA a 22 dias del congreso: si va, registrarse esta semana en https://ispg.societyconference.com/v2/ y escribir a info@ispg.net pidiendo la cuota Student/Post-Doc y si hay opcion virtual, porque el portal no muestra tarifas.</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>https://ispg.net/wcpg-2026/</t>
@@ -27205,7 +31239,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Leida la pagina oficial ISPG WCPG 2026. No hay ronda late-breaking. Registro abierto pero sin tabla de tarifas publicada (no verificada).</t>
+          <t>Tier 1, ispg.net/wcpg-2026 el 2026-09-07: 'Registration for WCPG 2026 is now OPEN', sin fecha de cierre publicada y sin mencion alguna a asistencia virtual/online. Plazos ya vencidos: simposios 19 y 26-mar-2026, orales/posters y ECIP 14-may-2026, premios Reich y Todd 31-may-2026, registro obligatorio de ponentes 1-jul-2026. Las cuotas quedan UNVERIFIED: el portal ispg.societyconference.com/v2 solo devuelve 'Loading...' (carga por JavaScript) y la pagina ispg.net/registration muestra todavia contenido de WCPG 2022 Florencia. Categoria Student/Post-Doc incluye residentes, con verificacion documental al inscribirse. Sede: Scottish Event Campus, Glasgow, 29-sep a 3-oct-2026.</t>
         </is>
       </c>
     </row>
@@ -27257,12 +31291,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>715</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -27302,30 +31336,34 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Reloj vivo a 8 dias: la inscripcion anticipada cierra el 15-sep-2026 a las 17:00 ET. Hacerse socia trainee de ASHG antes de inscribirse baja la cuota casi a la mitad; despues del 15-sep solo queda tarifa late/onsite.</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>https://ashgmeeting.ashg.org/</t>
@@ -27333,7 +31371,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Leida la pagina oficial de registro. Resumen regular cerro 18-may-2026; late-breaking 10-26 ago 2026. Early-bird hasta 15-sep-2026: miembro student/trainee 435 USD (~400 EUR), no miembro trainee 775 USD (~710 EUR). Tarifas en USD.</t>
+          <t>Tier 1, ashgmeeting.ashg.org/attend/register el 2026-09-07. Cuotas en USD: no socio trainee 775 anticipada / 825 late; socio student-trainee 435 anticipada / 460 late; no socio 1.250 / 1.400. Cost_EUR 715 = 775 USD al cambio aproximado 0,92 (si se hace socia, ~400 EUR). Ventana anticipada 13-ago a 15-sep-2026 17:00 ET; despues late/onsite. No hay inscripcion de un solo dia ni opcion virtual anunciada. El plazo de resumenes late-breaking (26-ago-2026) ya paso, asi que el unico reloj que queda es el de inscripcion.</t>
         </is>
       </c>
     </row>
@@ -27482,8 +31520,16 @@
           <t>Behavior Genetics Association (BGA)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>2027-06-29</t>
@@ -27514,7 +31560,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Lo mas 'su gente': BGA es exactamente genetica estadistica/conductual (lineas 1+2), reunion lo bastante pequena para que una doctoranda conozca nombres senior (presidenta de programa 2027 Sarah Medland, anfitrion Scott Vrieze). Alto retorno de visibilidad con competencia moderada. Contra: sede y plazo de resumenes aun por anunciar; revisar de nuevo en otono 2026. BGA 2026 (Amsterdam, junio) ya paso.</t>
+          <t>Sede ya confirmada y con un detalle que la afecta directamente: la program chair de 2027 es Sarah Medland (QIMR Berghofer), la institucion del proyecto de su manuscrito empirico en Nature Mental Health, asi que presentar alli pone su trabajo delante del grupo con el que ya colabora y del nucleo de la genetica del comportamiento. Ademas cae del 29-jun al 2-jul-2027, cinco semanas despues de terminar la residencia (22-may-2027): es el primer congreso grande de su linea 1 al que puede ir sin pelear por dias de libranza. Contra: EE.UU. implica ESTA y vuelo caro para una residente sin presupuesto de laboratorio.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -27529,35 +31575,39 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vigilar bga.org (BGA Current Meeting) a partir de enero-2027: plazo de resumenes, web del congreso y plazo de student travel awards siguen como TBA.</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>https://bga.org/</t>
@@ -27565,7 +31615,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Pagina de futuras reuniones de BGA via busqueda: 29 jun-2 jul 2027, anfitrion Vrieze / presidenta de programa Medland; sede, tarifa y plazo de resumenes TBA. Revisar detalles a finales de 2026.</t>
+          <t>Tier 1: pagina oficial BGA Current Meeting el 2026-09-07: '2027 BGA Annual Meeting, Minneapolis, Minnesota, USA, 29 June - 2 July 2027', local host Scott Vrieze, program chair Sarah Medland. Siguen TBA: plazo de resumenes, web, programa, cuotas y plazo de becas de estudiante y de early career award. La pagina de Future Meetings de la BGA anuncia ademas Tartu (Estonia) para 2028.</t>
         </is>
       </c>
     </row>
@@ -27890,30 +31940,34 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ya no hay via para presentar en 2026: solo cabe ir de oyente (cuota sin verificar) o esperar al proximo Sleep Europe, que por bienalidad tocaria en 2028. Dejar de gastar intentos en la pagina de resumenes de esrs.eu.</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>https://esrs.eu/sleep-congress/abstracts/</t>
@@ -27921,7 +31975,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Fechas de listados ESRS/Congrex via busqueda. La pagina oficial de resumenes devolvio HTTP 403 (bloqueada, un intento) - plazo late-breaking no verificado. Tarifas esperadas en EUR.</t>
+          <t>El intento anterior devolvio HTTP 403 en la pagina oficial de resumenes; en esta pasada se recupero su contenido a traves del buscador (esrs.eu/sleep-congress/abstracts) sin abrirla directamente, de ahi LIKELY. Sede confirmada: Maastricht (MECC), Paises Bajos, 20-23 oct 2026 (no Amsterdam). Plazo ordinario de resumenes 1-abr-2026 CERRADO y ventana de late breaking abstracts 1-jun a 31-jul-2026 17:00 CEST tambien CERRADA. Cuotas de inscripcion no verificadas.</t>
         </is>
       </c>
     </row>
@@ -27958,7 +32012,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2027-06-05</t>
+          <t>2027-06-06</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -28006,30 +32060,34 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>La convocatoria de resumenes de SLEEP 2027 aun no esta abierta: revisar sleepmeeting.org/call-for-abstracts en noviembre-2026, porque en la edicion 2026 el plazo cerro el 8-dic-2025 y el de 2027 caera previsiblemente en el mismo tramo.</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>https://www.sleepmeeting.org/</t>
@@ -28037,7 +32095,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Fechas (5-9 jun 2027, Denver) de sleepmeeting.org/eMedEvents via busqueda. Plazo de resumenes aun no publicado. Tarifas en USD.</t>
+          <t>CONFLICTO DE FECHAS: la ficha de aasm.org/event/sleep-2027 da 6-9 jun 2027 en Denver (Colorado Convention Center) frente al 5-jun-2027 que teniamos registrado; adopto 6-9 jun y lo dejo senalado. sleepmeeting.org solo muestra todavia contenido de SLEEP 2026 (plazo de resumenes 8-dic-2025), y su pagina call-for-abstracts devolvio contenido vacio al abrirla el 2026-09-07: la fecha de resumenes 2027 sigue sin publicar y no se inventa.</t>
         </is>
       </c>
     </row>
@@ -28130,30 +32188,34 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Reloj vivo a 8 dias, pero es solo la ventana de late-breaking (8 a 15-sep-2026, cierre a las 17:00 EDT, sin prorroga) y exige ser socia de la SfN: con Fit 2 lo razonable es dejarlo pasar salvo que quiera datos nuevos en sala; no requiere ninguna accion mas.</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>https://www.sfn.org/meetings/neuroscience-2026</t>
@@ -28161,7 +32223,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Fechas y ambas ventanas de resumenes (regular 27 may-10 jun; late-breaking 8-15 sep 2026) de la web oficial sfn.org via busqueda. Tarifas en USD.</t>
+          <t>Tier 1, sfn.org (paginas de late-breaking abstracts y call for abstracts) el 2026-09-07: la convocatoria ordinaria fue 27-may a 10-jun-2026 y las notificaciones salieron a principios de agosto; el 15-sep-2026 que teniamos registrado corresponde al cierre de los late-breaking, no al plazo general. Congreso 14-18 nov 2026 en el Walter E. Washington Convention Center, Washington DC.</t>
         </is>
       </c>
     </row>
@@ -28285,8 +32347,564 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>E-0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BGA 2028 - 58th Annual Meeting of the Behavior Genetics Association</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Behavior Genetics Association (BGA)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tartu</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PROBABLE (la BGA da student travel awards y early career award cada anyo; plazo TBA)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Genetica estadistica y del comportamiento, gemelos, GWAS/PRS de rasgos complejos y psiquiatricos</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Es la sala natural de su linea 1 (genetica estadistica de rasgos complejos) y cae en la UE, sin visado y con vuelo barato via Tallin/Helsinki, en 2028: con la tesis defendida en feb-2028 y sus dos primeros autores ya publicados llegaria en posicion de pedir charla oral en vez de poster. La sede es el Instituto de Genomica de la Universidad de Tartu (Biobanco de Estonia), grupo de referencia en PRS y biobancos poblacionales: es la ocasion mas barata que tendra de sentarse con ese equipo y con el nucleo BGA.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Revisar la pagina de BGA Future Meetings en enero-2028 para fechas exactas y plazo de resumenes; apuntarla ya como objetivo post-tesis.</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567675</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Tier 1: pagina oficial BGA Future Meetings consultada el 2026-09-07: lista 2028 Tartu (Estonia) con fecha TBA y 2029 TBA. Sin fechas ni cuotas publicadas todavia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>E-0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ASHG 2027 - 77th Annual Meeting of the American Society of Human Genetics</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>American Society of Human Genetics (ASHG)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nashville</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2027-10-26</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2027-10-30</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>UNVERIFIED (ASHG suele tener trainee/international travel awards; no comprobado para 2027)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Genetica humana en todas sus ramas; la mayor reunion mundial del campo (7.000-8.500 asistentes)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Es el escaparate mundial de sus lineas 1 y 2: sesiones de genetica estadistica, GWAS y PRS a diario y todo el ecosistema de consorcios psiquiatricos en el mismo pasillo. Octubre-2027 cae cinco meses despues de acabar la residencia (22-may-2027), asi que por primera vez podria ir sin gastar dias de libranza; a cambio es el destino mas caro de la lista (vuelo transatlantico + cuota de ~700 EUR sin descuento de socio) y necesita ESTA por ser ciudadana UE. Con dos primeros autores ya publicados para entonces, es el sitio donde buscar postdoc a la vez que presenta.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vigilar ashg.org/meetings/future-past y la pagina de deadlines en marzo-2027: el plazo de resumenes de ASHG suele caer a comienzos de junio del anyo del congreso.</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://www.ashg.org/meetings/future-past/</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Fechas 26-30 oct 2027 en Nashville (TN) coincidentes en la pagina de ASHG Future &amp; Past Annual Meetings y en varios agregadores (eMedEvents, life-sciences-usa, showsbee) el 2026-09-07; no abri la pagina oficial linea a linea, de ahi LIKELY. Sin cuotas ni plazo de resumenes publicados aun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>E-0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>World Sleep 2027 - Congress of the World Sleep Society</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>World Sleep Society</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Montreal</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2027-09-10</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2027-09-15</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>UNVERIFIED (la World Sleep Society ha dado becas para jovenes investigadores en ediciones previas; no publicado para 2027)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Medicina e investigacion del sueno a escala mundial, &gt;3.000 asistentes de 80+ paises</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Es el foro mas grande de su linea 3 (sueno infantil) y el unico donde su revision en Journal of Sleep Research y el trabajo de genetica del sueno se leen ante la comunidad completa, no ante un subgrupo. Septiembre-2027 esta ya fuera de la residencia, asi que el reloj le juega a favor; pesa en contra el coste (vuelo transatlantico, cuota aun no publicada) y que Canada exige eTA a ciudadanos UE. Ventana util ya abierta: las propuestas de simposio se admiten desde el 15-ago-2026 hasta el 20-ene-2027, o sea que podria proponer un simposio de genetica del sueno pediatrico en vez de limitarse a un poster.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Decidir antes de dic-2026 si propone simposio (cierre 20-ene-2027) y vigilar worldsleepcongress.com para la apertura del envio de resumenes individuales.</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://worldsleepsociety.org/world-sleep-2027-in-montreal/</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Tier 1: worldsleepsociety.org (2026-09-07) confirma 10-15 sep 2027 en el Palais des Congres de Montreal. La ventana de simposios 15-ago-2026 a 20-ene-2027 procede de la pagina worldsleepsociety.org/shape-the-scientific-program-2027 via buscador; el plazo de resumenes ordinarios y las cuotas no estan publicados todavia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>E-0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>XXXV Reunion Anual de la Sociedad Espanola de Sueno (SES 2027)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Sueno (SES)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Logrono</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Espana</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Medicina del sueno espanola: neurofisiologia, neumologia, pediatria y psicologia del sueno</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Congreso nacional, barato y sin vuelo, con seccion pediatrica donde su revision de sueno en lactantes encaja; el contenido genetico es escaso, por eso no pasa de plausible.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Consultar congreso-ses.com/ses2027 en octubre-2026 para fechas exactas de marzo-2027, plazo de comunicaciones y cuota de residente; si cae en marzo, hay que pedir dias en el hospital con antelacion.</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>https://congreso-ses.com/ses2027/bienvenida</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Tier 1: la web oficial del congreso (consultada 2026-09-07) confirma Logrono y presidencia del comite organizador (Dra. Alejandra Roncero Lazaro), pero no publica todavia fechas exactas, plazo de comunicaciones ni cuotas; el mes (marzo-2027) procede de fuentes secundarias, de ahi LIKELY. Precedentes: Granada 5-7 mar 2026, Santiago 24-26 abr 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>E-0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Jornada AEGH 2027 (Asociacion Espanola de Genetica Humana)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Asociacion Espanola de Genetica Humana (AEGH)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Espana</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Genetica humana clinica y de laboratorio en Espana</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Reunion nacional barata que cruza sus dos identidades (residente de Medicina de Laboratorio y genetista) y sirve para red de contactos en Espana, aunque el peso de genetica estadistica de rasgos complejos es bajo.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mirar aegh.org/congresos-y-jornadas-aegh a finales de 2026 para ver que sede gano la candidatura y que fechas tiene la Jornada 2027.</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>https://aegh.org/congresos-y-jornadas-aegh/</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>La web de la AEGH (2026-09-07) confirma que en 2027 toca Jornada AEGH porque en 2026 se celebra el V Congreso Interdisciplinar en Genetica Humana, y que la presentacion de candidaturas de sede se cerraba a finales de octubre de 2025; sede y fechas siguen sin anunciarse en la pagina, por eso UNVERIFIED.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z11"/>
+  <autoFilter ref="A1:Z16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28297,13 +32915,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="51" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -28319,7 +32937,7 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="52" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="52" customWidth="1" min="22" max="22"/>
     <col width="52" customWidth="1" min="23" max="23"/>
@@ -28479,10 +33097,14 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ISG International Scholar &amp; Cultural Exchange Program (ISCEP), financiado por Regeneron Genetics Center, ofrece becas; ademas descuentos de matricula por necesidad via formulario de ayuda financiera. Importes 2027 aun no publicados.</t>
+          <t>ISCEP (patrocinio de Regeneron Genetics Center) sigue vivo, PERO solo para nacionales y residentes de paises de renta baja o media-baja: ella, como espanola, NO es elegible. No consta ninguna otra exencion de cuota general.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -28492,7 +33114,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Su diana: de lleno en su tecnica nuclear independiente (genetica estadistica, modelos biometricos/de gemelos, OpenMx, GWAS, Genomic SEM, aleatorizacion mendeliana). 2027 es la edicion PRESENCIAL (2026 fue virtual), que es la version que merece el viaje. La financiacion (ISCEP + descuentos por necesidad) puede cubrir gran parte del coste. Solo 5 dias, bajo esfuerzo para asistir una vez abran fechas/registro.</t>
+          <t>Es su diana de formacion: el temario 2027 se centra en modelado genetico latente e incluye modelos de gemelos, OpenMx, genomic SEM y aleatorizacion mendeliana, justo los metodos avanzados de genetica estadistica que hoy no despliega sola. Cae 1-5 mar 2027, aun dentro de la residencia (termina el 22-may-2027), asi que exigiria permiso. La financiacion NO la cubre: la beca ISCEP excluye a los paises de renta alta, de modo que cuota, vuelos y alojamiento a EEUU corren por su cuenta.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -28512,30 +33134,34 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Escribir a IBGworkshop@colorado.edu preguntando por la cuota 2027, la fecha de apertura de inscripcion, el plazo y si habra opcion virtual; vigilar la pagina cada semana porque la inscripcion suele abrirse sin previo aviso</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>https://www.colorado.edu/ibg/workshop-2027</t>
@@ -28543,7 +33169,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Fechas leidas en la pagina oficial 2027. Tarifa/plazo 2027 AUN no publicados; como referencia la tarifa academica presencial 2023 fue 600 USD early / 700 late (~560-650 EUR), no academica 1000 USD. El registro suele abrir ~enero; contacto IBGworkshop@colorado.edu.</t>
+          <t>Pagina oficial de la edicion 2027 y pagina oficial del ISCEP leidas el 2026-09-07. Confirmadas fechas 1-5 marzo 2027 en Boulder, Colorado, presencial; el foco anunciado es el modelado genetico latente (modelos de gemelos, OpenMx, genomic SEM, MR). La cuota 2027 NO esta publicada: los 550 EUR son una estimacion a partir de la tarifa academica de 600 USD de la edicion 2024 y hay que confirmarla. Tampoco hay plazo de solicitud publicado ni confirmacion de opcion virtual (existe una pagina de recursos online con materiales de ediciones pasadas). La pagina menciona un programa de inscripcion temprana para quien necesite visado. El aviso del ISCEP 2027 estaba previsto para mayo de 2026 y las condiciones publicadas dejan fuera a los paises de renta alta.</t>
         </is>
       </c>
     </row>
@@ -28570,7 +33196,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Online en directo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -28590,12 +33216,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>desconocido - elegibilidad gratuita/con descuento via la pagina de 'fees and voucher packs' de Bristol; sin importes indicados.</t>
+          <t>No consta beca ni exencion; coste integro a su cargo</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -28625,30 +33251,34 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Las reservas del programa 2026-27 abren el 2026-10-07 a mediodia (hora britanica), con registro previo de interes desde el 2026-09-23: poner alarma, porque estos cursos se llenan</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
@@ -28656,7 +33286,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.250 GBP -&gt; ~1.470 EUR (tasa ~1,18). Se imparte 27-29 ene + 1-3 feb 2027. El registro de cuenta abre 23-sep-2026, las reservas abren 7-oct-2026, cierran ~2 semanas antes del inicio.</t>
+          <t>Ficha oficial del curso y catalogo de Bristol leidos el 2026-09-07. Confirmado: 27-29 de enero y 1-3 de febrero de 2027, seis dias lectivos a jornada completa, formato online en directo, 1.250 GBP (~1.450 EUR), reservas cerradas hasta dos semanas antes del inicio (2027-01-13, coincide con lo ya fichado). Temario: tipos de datos geneticos, estructura poblacional, heredabilidad, GWAS y GWAS multiancestral, construccion y uso de puntuaciones poligenicas, anotacion funcional, estudios de expresion y metilacion y MR. No menciona explicitamente LDSC ni fine-mapping. Ojo: seis dias a jornada completa en plena residencia exigen permiso, aunque hay acceso a grabaciones durante 5 meses.</t>
         </is>
       </c>
     </row>
@@ -28683,7 +33313,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Online en directo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -28703,12 +33333,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>desconocido - elegibilidad gratuita/con descuento via la pagina de 'fees and voucher packs' de Bristol; el personal/PGR de Bristol tiene acceso gratuito autoguiado.</t>
+          <t>No consta beca ni exencion; coste integro a su cargo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -28738,30 +33368,34 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Reservar en cuanto abran las reservas el 2026-10-07 a mediodia; es la puerta de entrada obligatoria al curso avanzado de MR</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
@@ -28769,7 +33403,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>880 GBP -&gt; ~1.035 EUR (tasa ~1,18). Las reservas del programa 2026/27 abren 7-oct-2026; cierran ~2 semanas antes del inicio.</t>
+          <t>Ficha oficial leida el 2026-09-07. Confirmado: 15-19 de marzo de 2027, cinco dias, online en directo, 880 GBP (~1.020 EUR), reservas cerradas dos semanas antes (2027-03-01, coincide con lo ya fichado). No exige experiencia previa en MR, pero si epidemiologia etiologica, regresion multivariable y soltura con Stata 17+ o R: ella cumple. Acceso a materiales y grabaciones 5 meses.</t>
         </is>
       </c>
     </row>
@@ -28839,30 +33473,34 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Volver a mirar en enero-2027; si para entonces no hay convocatoria 2027, bajar la cadencia de revision a trimestral y no redescubrirlo</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>https://coursesandconferences.wellcomeconnectingscience.org/event/genetic-analysis-of-population-based-association-studies-20240902/</t>
@@ -28870,7 +33508,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Solo la edicion de sep 2024 esta viva (820 GBP incl. alojamiento/comidas -&gt; ~965 EUR; candidaturas cerradas). Se imparte aproximadamente anual/bienal; sin fecha futura publicada. Perseguir la convocatoria de 2027.</t>
+          <t>Corregido un dato de la pasada anterior: ademas de la edicion de sep-2024 hubo una edicion el 2025-09-01, de modo que el curso siguio vivo hasta 2025 (histórico: 2019, 2020 virtual, 2022, 2023, 2024, 2025). Revisado el listado oficial de cursos de Wellcome Connecting Science el 2026-09-07: los unicos cursos listados son Accelerating Translation of Biodata to Impact (22-24 sep 2026) y Scalable Genomics and Pangenomics (11-16 oct 2026), ambos con plazo cerrado. NO hay convocatoria 2026 ni 2027 de este curso publicada a dia de hoy.</t>
         </is>
       </c>
     </row>
@@ -28915,10 +33553,14 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>desconocido - los cursos CAJAL suelen ofrecer becas/exenciones de matricula; no confirmado para este curso. Verificar.</t>
+          <t>Estipendios de la Boehringer Ingelheim Foundation y de la FENS (para la edicion 2026, ya cerrada)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -28948,30 +33590,34 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>No revisar hasta junio-2027 por si anuncian una edicion posterior; en cualquier caso es laboratorio humedo fuera de su tecnica</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>https://cajal-training.org/courses/</t>
@@ -28979,7 +33625,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Fechas y plazo del 27-ago de la pagina de cursos de CAJAL; tarifa no listada. La pagina del curso individual dio 404.</t>
+          <t>Pagina oficial de CAJAL leida el 2026-09-07: edicion 2026 del 19 de noviembre al 8 de diciembre de 2026 en la Bordeaux School of Neuroscience, plazo cerrado el 27 de agosto, 4.500 EUR con matricula, alojamiento y comidas incluidos. NO hay edicion 2027 anunciada. Tres semanas presenciales en Burdeos con registros, optogenetica y modelos animales: es formacion de laboratorio humedo que no cierra ninguno de sus huecos reales, que son metodologicos y computacionales.</t>
         </is>
       </c>
     </row>
@@ -29084,8 +33730,432 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Advanced Mendelian Randomization</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Universidad de Bristol / Bristol Medical School (MRC IEU)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Curso corto avanzado</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Online en directo</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>No consta ninguna beca ni exencion de cuota; el coste corre por cuenta del asistente</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Cierra de lleno el hueco de aleatorizacion mendeliana avanzada que ella no domina sola (metodos robustos a pleiotropia, MR multivariante, MR intrafamiliar, multiancestral, sesgo de colisionador), pero exige haber hecho antes el curso introductorio de MR (T-0003, marzo-2027), asi que su edicion realista es la siguiente (previsiblemente nov-2027) y no la de nov-2026; la financiacion NO lo cubre, son 730 EUR a su cargo.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>No reservar todavia: hacer primero el MR introductorio (T-0003) en marzo-2027 y buscar la edicion de finales de 2027 cuando Bristol publique el programa 2027-28</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/advanced-mr/</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Pagina oficial del curso leida el 2026-09-07. Cuota original 630 GBP (~730 EUR). Duracion 2,5 dias, formato online en directo, acceso a materiales y grabaciones 5 meses. Las reservas del programa 2026-27 abren el 2026-10-07 a mediodia. Requisitos: MR introductorio o equivalente, experiencia previa en analisis MR y soltura con R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Machine Learning with Omics Data</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Universidad de Bristol / Bristol Medical School</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Curso corto</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Online en directo</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2027-06-22</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2027-06-24</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Desconocida; no consta beca en el catalogo</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Toca su hueco de bioinformatica de datos omicos y ademas cae en junio de 2027, ya fuera de la residencia, pero no es genetica estadistica nuclear y no he podido leer cuota ni programa detallado.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Abrir la ficha del curso cuando se publiquen cuota y programa, y decidir junto con el resto de la oferta de Bristol de 2027</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fechas tomadas del catalogo oficial de cursos cortos de Bristol Medical School el 2026-09-07; no abri la ficha individual, asi que cuota y plazo estan sin verificar. Por el patron del resto del catalogo, el plazo suele ser dos semanas antes del inicio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T-0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Molecular Epidemiology</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Universidad de Bristol / Bristol Medical School (MRC IEU)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Curso corto</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Online en directo</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2027-03-22</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2027-03-24</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Desconocida; no consta beca en el catalogo</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Datos omicos y multiomicos con enfoque causal, util para su hueco de bioinformatica omica, pero cae en plena residencia y solapa parcialmente con el curso de epidemiologia genetica que ya tiene fichado.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Solo si sobra presupuesto y tiempo: va justo despues del MR introductorio (15-19 mar 2027), semana siguiente</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fechas del catalogo oficial de Bristol leido el 2026-09-07; cuota no verificada porque no abri la ficha individual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T-0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>From Genetic Variants to Risk Prediction (UniTartu Summer School)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Universidad de Tartu, Estonia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Escuela de verano</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Tartu, Estonia (presencial)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>La pagina menciona becas pero sin detallar importes ni criterios</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Escuela de verano en la UE (sin visado), barata y practica, que cubre control de calidad, PCA/UMAP, GWAS, puntuaciones poligenicas y flujos de trabajo reproducibles en R/Python y Unix, es decir refuerza su parte de programacion y buenas practicas; pero gran parte del contenido GWAS/PRS ya lo maneja sola y no llega a los metodos avanzados que de verdad le faltan.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Revisar en marzo-2027 si se convoca la edicion 2027: por el patron anual caeria a finales de julio, ya sin residencia, con plazo hacia el 20 de abril</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>https://ut.ee/en/content/genetic-variants-risk-prediction</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Pagina oficial leida el 2026-09-07: la edicion documentada es la de 2026 (27 jul - 7 ago 2026, plazo 2026-04-20, 750 EUR mas 25 EUR de tasa de solicitud, 3 ECTS, 10 dias lectivos). La edicion 2027 NO esta anunciada todavia; las fechas se dejan vacias a proposito para no inventar. Requisitos: nivel basico de R o Python y preferiblemente Unix/Bash. Descubierta via el agregador summerschoolsineurope.eu.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W7"/>
+  <autoFilter ref="A1:W11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30519,7 +35589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -31210,8 +36280,112 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SUB-0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ISPG - membresia y lista de correo (incluye el programa de Early Career Investigators)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://ispg.net/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Avisos de la sociedad de genetica psiquiatrica: congreso anual, programa y becas de investigadores noveles, seminarios y anuncios de puestos que circulan por la lista antes de llegar a los portales generalistas.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>La linea 2 de ella (GWAS/PRS psiquiatrico) tiene a la ISPG como sociedad de referencia, y cuatro de los ocho grupos de esta pasada salen de su junta directiva. Entrar en la lista convierte un rastreo manual anual en un flujo continuo, y el programa de investigadores noveles esta pensado exactamente para alguien que termina la tesis. Ademas ser socia da un motivo natural para escribir a Middeldorp o a Huckins.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>La URL es la pagina principal de la sociedad porque no he verificado la ruta exacta de alta ni si la membresia de estudiante es gratuita o de pago: hay que abrirla a mano y confirmarlo antes de dar datos. No inventar el enlace de registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SUB-0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>World Sleep Society - avisos de congreso y noticias</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://worldsleepsociety.org/news/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Anuncios de apertura y cierre del envio de resumenes, simposios, cuotas y becas de World Sleep 2027 (Montreal, 10-15 sep 2027)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Es el unico congreso grande de su linea de sueno que cae ya fuera de la residencia y cuyo plazo de resumenes todavia no esta publicado: sin aviso por correo es facil que se le pase entre guardias</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>No verifique el formulario exacto de alta; comprobar el pie de pagina de worldsleepsociety.org antes de dar la suscripcion por hecha.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J13"/>
+  <autoFilter ref="A1:J15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -36328,7 +36328,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>La URL es la pagina principal de la sociedad porque no he verificado la ruta exacta de alta ni si la membresia de estudiante es gratuita o de pago: hay que abrirla a mano y confirmarlo antes de dar datos. No inventar el enlace de registro.</t>
+          <t>DUPLICADA de SUB-0005 (misma sociedad, otra URL: la deduplicacion por URL no la detecto). Canonica: SUB-0005 https://ispg.net/membership/. Se conserva la fila porque el fichero es de solo apendice; darse de alta UNA sola vez. Anadida por ecosystem el 2026-09-07.</t>
         </is>
       </c>
     </row>
